--- a/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.33994744585594e-05</v>
+        <v>1.339947445855927e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.347624260177693e-05</v>
+        <v>1.347624260177692e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.33937629086824e-05</v>
+        <v>1.339376290868229e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.339806014587002e-05</v>
+        <v>1.339806014586995e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.339390051506764e-05</v>
+        <v>1.339390051506753e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.341293100685667e-05</v>
+        <v>1.341293100685658e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.339769198844378e-05</v>
+        <v>1.339769198844369e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.339678957862235e-05</v>
+        <v>1.339678957862237e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.340605272930051e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.340131014157397e-05</v>
+        <v>1.340131014157389e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.339564327848828e-05</v>
+        <v>1.339564327848829e-05</v>
       </c>
       <c r="M2" t="n">
         <v>1.340497240585475e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.339819394463015e-05</v>
+        <v>1.339819394463007e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.490092529175467e-05</v>
+        <v>1.49009252917546e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.340218919900306e-05</v>
+        <v>1.340218919900301e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.339670311663611e-05</v>
+        <v>1.339670311663603e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.339358384833354e-05</v>
+        <v>1.339358384833342e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34041541806025e-05</v>
+        <v>1.340415418060243e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.339623385316376e-05</v>
+        <v>1.339623385316371e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.391049529833896e-05</v>
+        <v>1.391049529833901e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.340513106116172e-05</v>
+        <v>1.340513106116168e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.397633416144378e-05</v>
+        <v>1.397633416144387e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.340041458203628e-05</v>
+        <v>1.340041458203633e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.340672301733837e-05</v>
+        <v>1.340672301733825e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.373800500168557e-05</v>
+        <v>1.373800500168552e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.340124256540715e-05</v>
+        <v>1.340124256540722e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.34056209950906e-05</v>
+        <v>1.340562099509059e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.342382107962472e-05</v>
+        <v>1.342382107962483e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.350076545987309e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.338247685994899e-05</v>
+        <v>1.3382476859949e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.337079960298207e-05</v>
+        <v>1.337079960298212e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.338537132366482e-05</v>
+        <v>1.338537132366486e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.351719344128078e-05</v>
+        <v>1.351719344128077e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.341345386073124e-05</v>
+        <v>1.341345386073141e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.340455977095891e-05</v>
+        <v>1.340455977095895e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.346886009000294e-05</v>
+        <v>1.3468860090003e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.343623222853127e-05</v>
+        <v>1.343623222853114e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.339403022223051e-05</v>
+        <v>1.339403022223046e-05</v>
       </c>
       <c r="M3" t="n">
         <v>1.348326783634442e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.341372397830279e-05</v>
+        <v>1.341372397830272e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59283484612147e-05</v>
+        <v>1.592834846121469e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.343957680445507e-05</v>
+        <v>1.343957680445504e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.340355378038003e-05</v>
+        <v>1.340355378038005e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.338205916818807e-05</v>
+        <v>1.338205916818813e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.345607839509493e-05</v>
+        <v>1.34560783950949e-05</v>
       </c>
       <c r="T3" t="n">
         <v>1.34003062476069e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.431007611617347e-05</v>
+        <v>1.431007611617345e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.346593140455405e-05</v>
+        <v>1.346593140455419e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.445364388799591e-05</v>
+        <v>1.44536438879959e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.343065433061453e-05</v>
+        <v>1.34306543306145e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.347554210612814e-05</v>
+        <v>1.347554210612817e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.400595422210826e-05</v>
+        <v>1.400595422210828e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.343452396382171e-05</v>
+        <v>1.34345239638217e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.349474387747034e-05</v>
+        <v>1.349474387747033e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.189394505064474e-05</v>
+        <v>1.189394505064471e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.181184615389185e-05</v>
+        <v>1.181184615389182e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.182943046734123e-05</v>
+        <v>1.182943046734119e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.187796973820232e-05</v>
+        <v>1.187796973820228e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.183098479476467e-05</v>
+        <v>1.183098479476465e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.204594295398035e-05</v>
+        <v>1.204594295398033e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.187381123071241e-05</v>
+        <v>1.187381123071237e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.18636180966508e-05</v>
+        <v>1.186361809665077e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.19567816312256e-05</v>
+        <v>1.195678163122557e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.191467993475044e-05</v>
+        <v>1.191467993475041e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.185067010931285e-05</v>
+        <v>1.185067010931282e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.19887005016313e-05</v>
+        <v>1.198870050163128e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.187948105674851e-05</v>
+        <v>1.187948105674847e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.194257016892042e-05</v>
+        <v>1.194257016892039e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.192460929279911e-05</v>
+        <v>1.192460929279907e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.186264146874074e-05</v>
+        <v>1.186264146874069e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.182740789832903e-05</v>
+        <v>1.182740789832899e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.19468046638999e-05</v>
+        <v>1.194680466389987e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.185734092194917e-05</v>
+        <v>1.185734092194914e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.190755743604421e-05</v>
+        <v>1.19075574360442e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.190986804714171e-05</v>
+        <v>1.19098680471417e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.205734038736901e-05</v>
+        <v>1.205734038736898e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.190456417779562e-05</v>
+        <v>1.190456417779559e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.189986517120437e-05</v>
+        <v>1.189986517120434e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.194698417661485e-05</v>
+        <v>1.194698417661483e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.191391663086112e-05</v>
+        <v>1.191391663086111e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.200573043879141e-05</v>
+        <v>1.200573043879137e-05</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.448260456499711e-05</v>
+        <v>4.448260456499701e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.30588805675232e-05</v>
+        <v>4.305888056752315e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.283833812004271e-05</v>
+        <v>4.283833812004164e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.864697484381264e-05</v>
+        <v>1.864697484381256e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.400624959198935e-05</v>
+        <v>4.400624959198824e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.595797202012193e-05</v>
+        <v>4.595797202012332e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.547646543410504e-05</v>
+        <v>4.547646543410492e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.381293335149836e-05</v>
+        <v>4.381293335149785e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.483200426511673e-05</v>
+        <v>4.483200426511687e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.448993306229785e-05</v>
+        <v>4.448993306229775e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.215644906638232e-05</v>
+        <v>4.215644906638234e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.785660446980685e-05</v>
+        <v>4.785660446980675e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.572549024355342e-05</v>
+        <v>4.572549024355334e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.694173712983853e-05</v>
+        <v>4.694173712983835e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.294885991326371e-05</v>
+        <v>4.29488599132636e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.356211936068305e-05</v>
+        <v>4.356211936068255e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.330890967561974e-05</v>
+        <v>4.330890967561968e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.486828021377844e-05</v>
+        <v>4.486828021377801e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.351577795769505e-05</v>
+        <v>4.351577795769485e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.582952230819961e-05</v>
+        <v>4.582952230819948e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.675481690281396e-05</v>
+        <v>4.675481690281392e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.673102530119863e-05</v>
+        <v>4.673102530119865e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.476987861196626e-05</v>
+        <v>4.476987861196611e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.612409736332373e-05</v>
+        <v>4.612409736332307e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.410324463315556e-05</v>
+        <v>4.410324463315552e-05</v>
       </c>
       <c r="AA5" t="n">
         <v>4.374590670820211e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.913550039930719e-05</v>
+        <v>4.913550039930715e-05</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.329158751211733e-05</v>
+        <v>1.661636387214863e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.653426497539573e-05</v>
+        <v>1.653426497539577e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.322707292881381e-05</v>
+        <v>1.322707292881377e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.660038855970619e-05</v>
+        <v>1.327561219967486e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.322862725623727e-05</v>
+        <v>1.655340361626858e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.344358541545295e-05</v>
+        <v>1.676836177548423e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.659623005221629e-05</v>
+        <v>1.65962300522163e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.658603691815468e-05</v>
+        <v>1.326126055812336e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.335442409269819e-05</v>
+        <v>1.667920045272951e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.331232239622303e-05</v>
+        <v>1.3312322396223e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.657308893081672e-05</v>
+        <v>1.324831257078541e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.33863429631039e-05</v>
+        <v>1.338634296310387e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.327932385245706e-05</v>
+        <v>1.327932385245704e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.667529360795988e-05</v>
+        <v>1.66752936079599e-05</v>
       </c>
       <c r="P6" t="n">
         <v>1.665732264717497e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.326028393021335e-05</v>
+        <v>1.326028393021329e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65498267198329e-05</v>
+        <v>1.322505035980158e-05</v>
       </c>
       <c r="S6" t="n">
         <v>1.666922348540379e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.325498338342176e-05</v>
+        <v>1.325498338342172e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33811555828673e-05</v>
+        <v>1.338115558286725e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.663228686864558e-05</v>
+        <v>1.66322868686456e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.354541828768526e-05</v>
+        <v>1.679005786929153e-05</v>
       </c>
       <c r="X6" t="n">
         <v>1.66269829992995e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.345053687115984e-05</v>
+        <v>1.345053687115983e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.334462663808745e-05</v>
+        <v>1.334462663808742e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6636335452365e-05</v>
+        <v>1.33115590923337e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.340602261227749e-05</v>
+        <v>1.340602261227748e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1026,16 +1026,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.101509691962419e-05</v>
+        <v>2.101509691962416e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.093299802287129e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.095058233632066e-05</v>
+        <v>2.095058233632065e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.099912160718176e-05</v>
+        <v>2.099912160718175e-05</v>
       </c>
       <c r="F7" t="n">
         <v>2.095213666374411e-05</v>
@@ -1044,16 +1044,16 @@
         <v>2.116709482295978e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.099496309969184e-05</v>
+        <v>2.099496309969183e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.098476996563027e-05</v>
+        <v>2.098476996563025e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.107793350020503e-05</v>
+        <v>2.107793350020501e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.103583180372988e-05</v>
+        <v>2.103583180372987e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.097182197829227e-05</v>
@@ -1062,49 +1062,49 @@
         <v>2.110985237061074e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.100063292572793e-05</v>
+        <v>2.100063292572794e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.106369238351338e-05</v>
+        <v>2.106369238351335e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.104573150739205e-05</v>
+        <v>2.104573150739204e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.098379333772013e-05</v>
+        <v>2.098379333772015e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.094855976730845e-05</v>
+        <v>2.094855976730844e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.106795653287938e-05</v>
+        <v>2.106795653287932e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.097849279092861e-05</v>
+        <v>2.097849279092859e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.110465419899834e-05</v>
+        <v>2.110465419899832e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.103101991612117e-05</v>
+        <v>2.103101991612115e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.117849225634844e-05</v>
+        <v>2.117849225634845e-05</v>
       </c>
       <c r="X7" t="n">
         <v>2.102571604677505e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.109697272553429e-05</v>
+        <v>2.109697272553426e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.106813604559427e-05</v>
+        <v>2.106813604559428e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.103506849984058e-05</v>
+        <v>2.103506849984056e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.112688230777084e-05</v>
+        <v>2.112688230777083e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,82 +1114,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.706947451496285e-05</v>
+        <v>5.706947451496289e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.590046956018331e-05</v>
+        <v>8.590046956018341e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.591805387363267e-05</v>
+        <v>8.59180538736328e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.596659314449379e-05</v>
+        <v>7.057122350227044e-05</v>
       </c>
       <c r="F8" t="n">
         <v>6.151083638142076e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.613456636027178e-05</v>
+        <v>9.212988474080012e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.596243463700374e-05</v>
+        <v>8.596243463700397e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.59522415029423e-05</v>
+        <v>8.595224150294239e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.604540503751715e-05</v>
+        <v>8.604540503751719e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.60033033410419e-05</v>
+        <v>8.600330334104205e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.593929351560432e-05</v>
+        <v>8.593929351560449e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.607732390792278e-05</v>
+        <v>8.607732390792282e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.355561960414024e-05</v>
+        <v>6.355561960414029e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.977785416264202e-05</v>
+        <v>6.977785416264203e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.825013791150786e-05</v>
+        <v>6.825013791150797e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.135608806294085e-05</v>
+        <v>5.135608806294082e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.591603130462044e-05</v>
+        <v>8.591603130462062e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.603542807019135e-05</v>
+        <v>8.603542807019146e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.59459643282405e-05</v>
+        <v>8.594596432824077e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.828053769013019e-05</v>
+        <v>7.196005589487463e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>8.59984914534331e-05</v>
+        <v>7.809612304914374e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.615164605035806e-05</v>
+        <v>8.615164605035819e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.404795328619067e-05</v>
+        <v>5.404795328619075e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001148121004739574</v>
+        <v>0.0001148121004739576</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.60356075829062e-05</v>
+        <v>5.658543807654549e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.600254003715266e-05</v>
+        <v>8.600254003715267e-05</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001162964981459123</v>
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.094635114642815e-05</v>
+        <v>4.094635114642813e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.898984741763304e-05</v>
+        <v>4.898984741763297e-05</v>
       </c>
       <c r="D9" t="n">
         <v>4.900743173108238e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.905597100194351e-05</v>
+        <v>4.718061693660118e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.900898605850585e-05</v>
+        <v>3.027727124679015e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.922394421772153e-05</v>
+        <v>4.92239444201693e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.905181249445363e-05</v>
+        <v>4.905181249445351e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.904161936039199e-05</v>
+        <v>4.904161936039191e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.913478289496679e-05</v>
+        <v>4.913478289496669e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.909268119849164e-05</v>
+        <v>4.909268119849157e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.902867137305405e-05</v>
+        <v>4.902867137305397e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.916670176537251e-05</v>
+        <v>4.916670176537243e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.905748232048969e-05</v>
+        <v>4.905748232048963e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>5.18133833013002e-05</v>
+        <v>5.181338330130008e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.238106276170917e-05</v>
+        <v>5.238106276170913e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.904064293492981e-05</v>
+        <v>4.904064293492972e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.900540916207016e-05</v>
+        <v>4.900540916207015e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.912480592764108e-05</v>
+        <v>4.912480592764104e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.903534218569032e-05</v>
+        <v>4.903534218569026e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.916151438513587e-05</v>
+        <v>4.91615143851358e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.908786931088289e-05</v>
+        <v>5.846463221622387e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.923534165111018e-05</v>
+        <v>4.923534165111017e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.90825654415368e-05</v>
+        <v>4.908256544153675e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.915382212029602e-05</v>
+        <v>4.915382212029595e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.912498544035602e-05</v>
+        <v>4.422597419058109e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.909191789460232e-05</v>
+        <v>4.909191789460224e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.91837317025326e-05</v>
+        <v>4.918373170253255e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.353116828177321e-05</v>
+        <v>1.353116828177315e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.359729047948759e-05</v>
+        <v>1.359729047948756e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.355127321852961e-05</v>
+        <v>1.355127321852957e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.351678678319474e-05</v>
+        <v>1.351678678319468e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.351472442304948e-05</v>
+        <v>1.351472442304941e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356233525533307e-05</v>
+        <v>1.356233525533299e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.353441831877023e-05</v>
+        <v>1.35344183187702e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.354523337072644e-05</v>
+        <v>1.354523337072639e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.354166107053346e-05</v>
+        <v>1.354166107053344e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.352377650305809e-05</v>
+        <v>1.352377650305804e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35258840938275e-05</v>
+        <v>1.352588409382744e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.355543991408042e-05</v>
+        <v>1.355543991408041e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.352066889317536e-05</v>
+        <v>1.35206688931753e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.509301433158134e-05</v>
+        <v>1.509301433158133e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.351171712649002e-05</v>
+        <v>1.351171712648997e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.352600570308903e-05</v>
+        <v>1.352600570308896e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.353481474506934e-05</v>
+        <v>1.353481474506928e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.352444153568283e-05</v>
+        <v>1.352444153568279e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.352929969911406e-05</v>
+        <v>1.352929969911398e-05</v>
       </c>
       <c r="U2" t="n">
         <v>1.40665415512873e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.353555189634614e-05</v>
+        <v>1.353555189634607e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.418472381431203e-05</v>
+        <v>1.418472381431189e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.351589877028505e-05</v>
+        <v>1.351589877028503e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.354967706918512e-05</v>
+        <v>1.354967706918511e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.389320085178124e-05</v>
+        <v>1.389320085178121e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.354086793504732e-05</v>
+        <v>1.354086793504725e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.355183692349029e-05</v>
+        <v>1.355183692349025e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.370958157818008e-05</v>
+        <v>1.370958157818006e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.369838144431726e-05</v>
+        <v>1.369838144431725e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386060830407572e-05</v>
+        <v>1.386060830407571e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.357244015760191e-05</v>
+        <v>1.357244015760188e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.359767471600911e-05</v>
+        <v>1.359767471600906e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.393710002738171e-05</v>
+        <v>1.393710002738164e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.373878809701446e-05</v>
+        <v>1.373878809701443e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.381448035766918e-05</v>
+        <v>1.381448035766915e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.378882305641326e-05</v>
+        <v>1.378882305641317e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.367303713218169e-05</v>
+        <v>1.367303713218168e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.368059121608584e-05</v>
+        <v>1.368059121608586e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.391011729919711e-05</v>
+        <v>1.39101172991971e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.36328202870414e-05</v>
+        <v>1.363282028704138e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.620775674701404e-05</v>
+        <v>1.620775674701394e-05</v>
       </c>
       <c r="P3" t="n">
         <v>1.357270764313505e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.367684182639185e-05</v>
+        <v>1.367684182639186e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.373835964634883e-05</v>
+        <v>1.373835964634882e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.366470119005871e-05</v>
+        <v>1.366470119005874e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.369770839774592e-05</v>
+        <v>1.369770839774589e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.456191474148518e-05</v>
+        <v>1.456191474148514e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.374666241027459e-05</v>
+        <v>1.374666241027457e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.50147364200222e-05</v>
+        <v>1.501473642002217e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.360586988127335e-05</v>
+        <v>1.360586988127318e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.383944882025446e-05</v>
+        <v>1.383944882025442e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.428785569107629e-05</v>
+        <v>1.428785569107634e-05</v>
       </c>
       <c r="AA3" t="n">
         <v>1.377628549382793e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.388590111876087e-05</v>
+        <v>1.388590111876086e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.239493185774651e-05</v>
+        <v>1.239493185774653e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.214989663232277e-05</v>
+        <v>1.214989663232276e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.262202636713791e-05</v>
+        <v>1.262202636713792e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.223248621548661e-05</v>
+        <v>1.223248621548665e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.22091909089133e-05</v>
+        <v>1.220919090891333e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.274697716162097e-05</v>
+        <v>1.274697716162101e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.243164252071895e-05</v>
+        <v>1.243164252071897e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.255380350773383e-05</v>
+        <v>1.255380350773385e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.250191568135393e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.231143831677303e-05</v>
+        <v>1.231143831677304e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.233524452405316e-05</v>
+        <v>1.233524452405318e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.270108837787574e-05</v>
+        <v>1.270108837787577e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.375258567442666e-05</v>
+        <v>4.37525856744258e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.222250089162089e-05</v>
+        <v>1.222250089162091e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.217522211084941e-05</v>
+        <v>1.217522211084942e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.233661815660519e-05</v>
+        <v>1.233661815660521e-05</v>
       </c>
       <c r="R4" t="n">
         <v>1.24361203381323e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.231895016619955e-05</v>
+        <v>1.231895016619956e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.23738253570207e-05</v>
+        <v>1.237382535702072e-05</v>
       </c>
       <c r="U4" t="n">
         <v>1.224925804966098e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.239601979313819e-05</v>
+        <v>1.239601979313823e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.286424782303719e-05</v>
+        <v>1.286424782303723e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.22224557011657e-05</v>
+        <v>1.222245570116569e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.254326758499675e-05</v>
+        <v>1.254326758499669e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.234457933306786e-05</v>
+        <v>1.234457933306789e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.250449390353848e-05</v>
+        <v>1.250449390353849e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.266964345242851e-05</v>
+        <v>1.266964345242853e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1710,58 +1710,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.679674686632102e-05</v>
+        <v>4.6796746866321e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.703607826535425e-05</v>
+        <v>4.70360782653543e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.471903856801737e-05</v>
+        <v>5.471903856801741e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.604490304222962e-05</v>
+        <v>2.604490304222967e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.633789367342868e-05</v>
+        <v>4.633789367342873e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.56549002248861e-05</v>
+        <v>5.565490022488656e-05</v>
       </c>
       <c r="H5" t="n">
         <v>5.056100257465081e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.194671761814046e-05</v>
+        <v>5.194671761814043e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.113775678464506e-05</v>
+        <v>5.113775678464475e-05</v>
       </c>
       <c r="K5" t="n">
         <v>5.372099052552372e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.026162984064666e-05</v>
+        <v>5.026162984064664e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.735403283743768e-05</v>
+        <v>5.735403283743764e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.375258567442666e-05</v>
+        <v>4.37525856744258e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.572380293477105e-05</v>
+        <v>4.572380293477108e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.392131923145698e-05</v>
+        <v>4.392131923145693e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.789311508194897e-05</v>
+        <v>4.789311508194892e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.895194598568544e-05</v>
+        <v>4.895194598568546e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.707427247581069e-05</v>
+        <v>4.707427247581074e-05</v>
       </c>
       <c r="T5" t="n">
         <v>4.718159962061563e-05</v>
@@ -1770,25 +1770,25 @@
         <v>5.041750793347465e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.062705908560492e-05</v>
+        <v>5.06270590856049e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.426215140842534e-05</v>
+        <v>5.426215140842508e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.647600505502443e-05</v>
+        <v>4.64760050550267e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.933830556081781e-05</v>
+        <v>4.933830556081689e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.856468312555869e-05</v>
+        <v>4.856468312555867e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.74270550392111e-05</v>
+        <v>4.7427055039211e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.49693053292946e-05</v>
+        <v>5.496930532929481e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.661417700464509e-05</v>
+        <v>1.364569166943517e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.636914177922136e-05</v>
+        <v>1.340065644401142e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.684127151403649e-05</v>
+        <v>1.684127151403654e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.645173136238521e-05</v>
+        <v>1.348324602717528e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.642843605581188e-05</v>
+        <v>1.345995072060196e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.399773697330964e-05</v>
+        <v>1.696622230851958e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.368240233240759e-05</v>
+        <v>1.665088766761756e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.380456331942246e-05</v>
+        <v>1.677304865463248e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.375267549304257e-05</v>
+        <v>1.672116082825255e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.653068346367161e-05</v>
+        <v>1.356219812846169e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.358600433574181e-05</v>
+        <v>1.655448967095178e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.395184818956442e-05</v>
+        <v>1.692033352477439e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.375258567442666e-05</v>
+        <v>4.37525856744258e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.645036317506128e-05</v>
+        <v>1.645036317506135e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.333983004818449e-05</v>
+        <v>1.64031896837902e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.655586330350379e-05</v>
+        <v>1.655586330350377e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.368688014982096e-05</v>
+        <v>1.665536548503091e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.356970997788819e-05</v>
+        <v>1.653819531309813e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.659307050391926e-05</v>
+        <v>1.362458516870935e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.356074740238028e-05</v>
+        <v>1.652923273759026e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.364677960482684e-05</v>
+        <v>1.661526494003683e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.419854192428175e-05</v>
+        <v>1.419854192428173e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.347321551285434e-05</v>
+        <v>1.347321551285432e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.392439846665961e-05</v>
+        <v>1.39243984666596e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.656382447996647e-05</v>
+        <v>1.359533914475651e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.375525371522711e-05</v>
+        <v>1.375525371522715e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.39243787325774e-05</v>
+        <v>1.392437873257742e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.036710413937436e-05</v>
+        <v>2.036710413937438e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.012206891395064e-05</v>
+        <v>2.012206891395059e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.059419864876577e-05</v>
+        <v>2.059419864876572e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.020465849711446e-05</v>
+        <v>2.020465849711442e-05</v>
       </c>
       <c r="F7" t="n">
         <v>2.018136319054118e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.071914944324886e-05</v>
+        <v>2.071914944324883e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.040381480234682e-05</v>
+        <v>2.040381480234681e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.05259757893617e-05</v>
+        <v>2.052597578936167e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.047408796298178e-05</v>
+        <v>2.047408796298176e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.02836105984009e-05</v>
+        <v>2.028361059840088e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.030741680568101e-05</v>
+        <v>2.030741680568098e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.067326065950361e-05</v>
+        <v>2.067326065950357e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.375258567442666e-05</v>
+        <v>4.37525856744258e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.019464054748732e-05</v>
+        <v>2.019464054748728e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.014736176671583e-05</v>
+        <v>2.014736176671584e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.030879043823305e-05</v>
+        <v>2.030879043823299e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.040829261976016e-05</v>
+        <v>2.040829261976011e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.029112244782741e-05</v>
+        <v>2.029112244782737e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.034599763864855e-05</v>
+        <v>2.034599763864851e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.028465056648488e-05</v>
+        <v>2.028465056648483e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.036819207476604e-05</v>
+        <v>2.036819207476603e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.083642010466506e-05</v>
+        <v>2.083642010466503e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.019462798279354e-05</v>
+        <v>2.019462798279351e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.057616940765526e-05</v>
+        <v>2.057616940765531e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.031675161469573e-05</v>
+        <v>2.031675161469569e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.047666618516634e-05</v>
+        <v>2.04766661851663e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.064181573405635e-05</v>
+        <v>2.064181573405638e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.187049150253457e-05</v>
+        <v>5.187049150253466e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.689921391929666e-05</v>
+        <v>7.689921391929677e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.737134365411165e-05</v>
+        <v>7.73713436541119e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.69818035024604e-05</v>
+        <v>6.352427308630078e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.562210661424929e-05</v>
+        <v>5.562210661424927e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.74962944485948e-05</v>
+        <v>8.2736972739248e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.718095980769273e-05</v>
+        <v>7.718095980769284e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.730312079470765e-05</v>
+        <v>7.730312079470773e-05</v>
       </c>
       <c r="J8" t="n">
         <v>7.725123296832783e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.706075560374686e-05</v>
+        <v>7.706075560374695e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.708456181102695e-05</v>
+        <v>7.708456181102692e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.745040566484954e-05</v>
+        <v>7.745040566484965e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.375258567442666e-05</v>
+        <v>4.37525856744258e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.276431198727117e-05</v>
+        <v>6.276431198727113e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.139731309894584e-05</v>
+        <v>6.139731309894596e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.684530757814296e-05</v>
+        <v>4.684530757814313e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.718543762510614e-05</v>
+        <v>7.718543762510624e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.706826745317342e-05</v>
+        <v>7.706826745317343e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.712314264399441e-05</v>
+        <v>7.712314264399463e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.150898657593204e-05</v>
+        <v>6.472547661129348e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.714533708011186e-05</v>
+        <v>7.023979490844459e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.761853213211477e-05</v>
+        <v>7.761853213211486e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.904753523311454e-05</v>
+        <v>4.904753523311471e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001024857816803124</v>
+        <v>0.0001024857816803126</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.709389662004164e-05</v>
+        <v>5.135066595371097e-05</v>
       </c>
       <c r="AA8" t="n">
         <v>7.72538111905123e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001038195139581171</v>
+        <v>0.0001038195139581173</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.376378654683399e-05</v>
+        <v>3.3763786546834e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.951174284328674e-05</v>
+        <v>3.951174284328669e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.998387257810188e-05</v>
+        <v>3.998387257810194e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.959433242645052e-05</v>
+        <v>3.821117459727664e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.957103711987729e-05</v>
+        <v>2.575555573242268e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.010882337258495e-05</v>
+        <v>4.010882359243312e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.97934887316829e-05</v>
+        <v>3.979348873168282e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.991564971869777e-05</v>
+        <v>3.99156497186977e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.986376189231791e-05</v>
+        <v>3.986376189231789e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.967328452773699e-05</v>
+        <v>3.967328452773697e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.969709073501713e-05</v>
+        <v>3.969709073501718e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.00629345888397e-05</v>
+        <v>4.006293458883977e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.375258567442666e-05</v>
+        <v>4.37525856744258e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.157041693848584e-05</v>
+        <v>4.157041693848589e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.195507422399081e-05</v>
+        <v>4.195507422399072e-05</v>
       </c>
       <c r="Q9" t="n">
         <v>3.969846458741734e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.979796654909623e-05</v>
+        <v>3.979796654909625e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.96807963771635e-05</v>
+        <v>3.968079637716351e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.973567156798464e-05</v>
+        <v>3.973567156798465e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.967183380165559e-05</v>
+        <v>3.967183380165549e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>3.975786600410215e-05</v>
+        <v>4.667364966213815e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.022609403400113e-05</v>
+        <v>4.022609403400114e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.958430191212965e-05</v>
+        <v>3.958430191212963e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.996584333699133e-05</v>
+        <v>3.996584333699132e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.97064255440318e-05</v>
+        <v>3.609318466123829e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.986634011450244e-05</v>
+        <v>3.986634011450243e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.003148966339246e-05</v>
+        <v>4.003148966339247e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.341481054732611e-05</v>
+        <v>1.341481054732619e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.34904326607059e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.342119240932172e-05</v>
+        <v>1.342119240932184e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.341053284358728e-05</v>
+        <v>1.341053284358733e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.340861000017922e-05</v>
+        <v>1.340861000017926e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.342811892711431e-05</v>
+        <v>1.342811892711443e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341069998521399e-05</v>
+        <v>1.341069998521411e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.340933645790403e-05</v>
+        <v>1.34093364579041e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.342064808790723e-05</v>
+        <v>1.342064808790721e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.341712279813096e-05</v>
+        <v>1.341712279813097e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341144735044604e-05</v>
+        <v>1.341144735044617e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.341757373440295e-05</v>
+        <v>1.341757373440298e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.341568229278759e-05</v>
+        <v>1.341568229278769e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.492639922203488e-05</v>
+        <v>1.492639922203482e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.34135662012122e-05</v>
+        <v>1.341356620121225e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.341499413927052e-05</v>
+        <v>1.341499413927055e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34155898345995e-05</v>
+        <v>1.341558983459959e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.341937438163914e-05</v>
+        <v>1.341937438163925e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.341642298608588e-05</v>
+        <v>1.341642298608599e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.392643203496482e-05</v>
+        <v>1.392643203496477e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.341607908230351e-05</v>
+        <v>1.341607908230363e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.399538157874862e-05</v>
+        <v>1.399538157874851e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341812895245977e-05</v>
+        <v>1.341812895245986e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.342036581864959e-05</v>
+        <v>1.342036581864974e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.375554625272784e-05</v>
+        <v>1.375554625272813e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.341738189595691e-05</v>
+        <v>1.341738189595707e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.34202046097596e-05</v>
+        <v>1.342020460975959e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.346483402123181e-05</v>
+        <v>1.346483402123217e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.353566205142622e-05</v>
+        <v>1.353566205142624e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.350966545221142e-05</v>
+        <v>1.350966545221178e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.339131858546406e-05</v>
+        <v>1.339131858546448e-05</v>
       </c>
       <c r="F3" t="n">
         <v>1.342343272006301e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.355790945422635e-05</v>
+        <v>1.355790945422663e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34380903646778e-05</v>
+        <v>1.343809036467814e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.342521786983703e-05</v>
+        <v>1.342521786983735e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.350548697983929e-05</v>
+        <v>1.350548697983944e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.349003149055331e-05</v>
+        <v>1.349003149055378e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.343787728215644e-05</v>
+        <v>1.343787728215673e-05</v>
       </c>
       <c r="M3" t="n">
         <v>1.350545981886013e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.346967699906093e-05</v>
+        <v>1.346967699906128e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.595020346137163e-05</v>
+        <v>1.595020346137157e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.345215091551519e-05</v>
+        <v>1.345215091551555e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.346569837602085e-05</v>
+        <v>1.346569837602079e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.347054188943106e-05</v>
+        <v>1.347054188943135e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.349656303293013e-05</v>
+        <v>1.349656303293012e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.347650665867586e-05</v>
+        <v>1.347650665867617e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.434164629708834e-05</v>
+        <v>1.43416462970881e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.348016736986455e-05</v>
+        <v>1.348016736986486e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.449990590105908e-05</v>
+        <v>1.449990590105919e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.348872788421612e-05</v>
+        <v>1.348872788421611e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.350549854769851e-05</v>
+        <v>1.350549854769869e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.404756760779116e-05</v>
+        <v>1.404756760779123e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.348202089188977e-05</v>
+        <v>1.348202089188967e-05</v>
       </c>
       <c r="AB3" t="n">
         <v>1.3530175804112e-05</v>
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.195823818147425e-05</v>
+        <v>1.195823818147426e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.186034884553489e-05</v>
+        <v>1.186034884553492e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.20303242485165e-05</v>
+        <v>1.203032424851653e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.190991954990338e-05</v>
+        <v>1.19099195499034e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1888200149057e-05</v>
+        <v>1.188820014905702e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.210856245333949e-05</v>
+        <v>1.210856245333946e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.191180749146639e-05</v>
+        <v>1.191180749146642e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.189640582324632e-05</v>
+        <v>1.189640582324634e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.201268677064002e-05</v>
+        <v>1.201268677064007e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.198435611800316e-05</v>
+        <v>1.198435611800319e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.192024932556758e-05</v>
+        <v>1.192024932556763e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.202284216028728e-05</v>
+        <v>1.20228421602873e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.196808494748465e-05</v>
+        <v>1.196808494748467e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.193174310715918e-05</v>
+        <v>1.193174310715919e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.194418271968976e-05</v>
+        <v>1.194418271968978e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.196031193694224e-05</v>
+        <v>1.196031193694225e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19670405897171e-05</v>
+        <v>1.196704058971713e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.200978878950789e-05</v>
+        <v>1.200978878950793e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.197645141902436e-05</v>
+        <v>1.197645141902438e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.195652736564863e-05</v>
+        <v>1.195652736564866e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.192444205678082e-05</v>
+        <v>1.192444205678084e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21208682047302e-05</v>
+        <v>1.212086820473022e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.199572109400087e-05</v>
+        <v>1.199572109400088e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.195068667899417e-05</v>
+        <v>1.19506866789942e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.20047428471375e-05</v>
+        <v>1.200474284713752e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.198728274713872e-05</v>
+        <v>1.198728274713875e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.206192341576899e-05</v>
+        <v>1.2061923415769e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2570,82 +2570,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.368097477675666e-05</v>
+        <v>4.368097477675613e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.394888100474087e-05</v>
+        <v>4.394888100474086e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.464563485565875e-05</v>
+        <v>4.464563485565878e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.886102660537238e-05</v>
+        <v>1.886102660537239e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.394302260565133e-05</v>
+        <v>4.394302260565136e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.546263321557097e-05</v>
+        <v>4.546263321557275e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.424552097738444e-05</v>
+        <v>4.424552097738458e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.220747104797729e-05</v>
+        <v>4.22074710479774e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.435459385999618e-05</v>
+        <v>4.435459385999701e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.901045398021718e-05</v>
+        <v>4.90104539802172e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.132012543493614e-05</v>
+        <v>4.132012543493663e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.643857861597906e-05</v>
+        <v>4.643857861597924e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.435805016448551e-05</v>
+        <v>4.435805016448479e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.489553971163591e-05</v>
+        <v>4.489553971163594e-05</v>
       </c>
       <c r="P5" t="n">
         <v>4.130064368367236e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.347216901111642e-05</v>
+        <v>4.347216901111646e-05</v>
       </c>
       <c r="R5" t="n">
         <v>4.392863928901322e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.418668482793478e-05</v>
+        <v>4.418668482793484e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.411688137850108e-05</v>
+        <v>4.411688137850105e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.441679343027993e-05</v>
+        <v>4.441679343027929e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.739627320257959e-05</v>
+        <v>4.739627320257893e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.549982820960945e-05</v>
+        <v>4.549982820960952e-05</v>
       </c>
       <c r="X5" t="n">
         <v>4.450662362133723e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.543263875052993e-05</v>
+        <v>4.543263875053052e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.328054299045705e-05</v>
+        <v>4.328054299045712e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.358224445606158e-05</v>
+        <v>4.358224445606182e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>4.765107600111723e-05</v>
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.639334896811432e-05</v>
+        <v>1.32703792829238e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.629545963217496e-05</v>
+        <v>1.629545963217505e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.334246534996605e-05</v>
+        <v>1.646543503515662e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.322206065135292e-05</v>
+        <v>1.322206065135295e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.632331093569708e-05</v>
+        <v>1.320034125050659e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.654367323997954e-05</v>
+        <v>1.3420703554789e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.322394859291593e-05</v>
+        <v>1.634691827810647e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.320854692469587e-05</v>
+        <v>1.320854692469591e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.644779755728009e-05</v>
+        <v>1.644779755728007e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.32964972194527e-05</v>
+        <v>1.641946690464327e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.323239042701715e-05</v>
+        <v>1.323239042701717e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.333498326173681e-05</v>
+        <v>1.333498326173684e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.328233302779188e-05</v>
+        <v>1.328233302779192e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.63746093778042e-05</v>
+        <v>1.637460937780428e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63871093927826e-05</v>
+        <v>1.638710939278269e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.327245303839179e-05</v>
+        <v>1.639542272358234e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.327918169116665e-05</v>
+        <v>1.640215137635719e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.332192989095744e-05</v>
+        <v>1.644489957614804e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.641156220566444e-05</v>
+        <v>1.328859252047393e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.646193899991923e-05</v>
+        <v>1.333896931472872e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.635955284342087e-05</v>
+        <v>1.635955284342092e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.656353601326327e-05</v>
+        <v>1.656353601326333e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.33078621954504e-05</v>
+        <v>1.643083188064092e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.340536594223679e-05</v>
+        <v>1.340536594223682e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.331688394858705e-05</v>
+        <v>1.643985363377762e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.642239353377881e-05</v>
+        <v>1.32994238485883e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.337669381445198e-05</v>
+        <v>1.337669381445201e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2746,67 +2746,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.049313077482617e-05</v>
+        <v>2.049313077482619e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.039524143888682e-05</v>
+        <v>2.039524143888683e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.056521684186844e-05</v>
+        <v>2.056521684186847e-05</v>
       </c>
       <c r="E7" t="n">
         <v>2.044481214325531e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.042309274240893e-05</v>
+        <v>2.042309274240895e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.06434550466914e-05</v>
+        <v>2.064345504669142e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.044670008481833e-05</v>
+        <v>2.044670008481835e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.043129841659824e-05</v>
+        <v>2.043129841659829e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.054757936399195e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.051924871135509e-05</v>
+        <v>2.051924871135512e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.045514191891953e-05</v>
+        <v>2.045514191891958e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.05577347536392e-05</v>
+        <v>2.055773475363921e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.050297754083656e-05</v>
+        <v>2.050297754083659e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.046660407398191e-05</v>
+        <v>2.046660407398193e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.047904368651248e-05</v>
+        <v>2.04790436865125e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.049520453029415e-05</v>
+        <v>2.049520453029417e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.050193318306903e-05</v>
+        <v>2.050193318306906e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.054468138285981e-05</v>
+        <v>2.054468138285985e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.051134401237629e-05</v>
+        <v>2.051134401237632e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.056177674593264e-05</v>
+        <v>2.056177674593265e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.045933465013273e-05</v>
+        <v>2.045933465013278e-05</v>
       </c>
       <c r="W7" t="n">
         <v>2.065576079808212e-05</v>
@@ -2818,13 +2818,13 @@
         <v>2.055588011997662e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.053963544048943e-05</v>
+        <v>2.053963544048945e-05</v>
       </c>
       <c r="AA7" t="n">
         <v>2.052217534049065e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.059681600912092e-05</v>
+        <v>2.059681600912095e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2834,22 +2834,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.424195033738801e-05</v>
+        <v>5.424195033738806e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.120660897172704e-05</v>
+        <v>8.120660897172711e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.137658437470867e-05</v>
+        <v>8.137658437470873e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.125617967609554e-05</v>
+        <v>6.684617117617388e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.838794099266026e-05</v>
+        <v>5.838794099266028e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.145482257953165e-05</v>
+        <v>8.706641819762305e-05</v>
       </c>
       <c r="H8" t="n">
         <v>8.12580676176586e-05</v>
@@ -2858,58 +2858,58 @@
         <v>8.12426659494385e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.135894689683223e-05</v>
+        <v>8.13589468968322e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.133061624419532e-05</v>
+        <v>8.13306162441954e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.126650945175978e-05</v>
+        <v>8.126650945175982e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.13691022864794e-05</v>
+        <v>8.136910228647864e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.033634293234466e-05</v>
+        <v>6.033634293234464e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.606493823197933e-05</v>
+        <v>6.606493823197934e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.466425245081693e-05</v>
+        <v>6.466425245081699e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.892561574290954e-05</v>
+        <v>4.892561574290958e-05</v>
       </c>
       <c r="R8" t="n">
         <v>8.131330071590929e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.135604891570002e-05</v>
+        <v>8.135604891570009e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.132271154521656e-05</v>
+        <v>8.132271154521652e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.472026913301152e-05</v>
+        <v>6.816428773927752e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>8.127070218297301e-05</v>
+        <v>7.387417462087157e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.14724469019664e-05</v>
+        <v>8.147244690196642e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.144136119855913e-05</v>
+        <v>5.144136119855917e-05</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0001082750392086164</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.135100297332969e-05</v>
+        <v>5.378575428018173e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.133354287333094e-05</v>
+        <v>8.133354287333087e-05</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001096772778349091</v>
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.728322323707301e-05</v>
+        <v>3.728322323707308e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.427438189508973e-05</v>
+        <v>4.427438189508982e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.444435729807133e-05</v>
+        <v>4.444435729807148e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.43239525994582e-05</v>
+        <v>4.268782939598376e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.430223319861182e-05</v>
+        <v>2.796004251995849e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.452259550289431e-05</v>
+        <v>4.452259570808147e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.432584054102123e-05</v>
+        <v>4.432584054102139e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.431043887280116e-05</v>
+        <v>4.43104388728013e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.442671982019486e-05</v>
+        <v>4.442671982019496e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.439838916755797e-05</v>
+        <v>4.439838916755812e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.433428237512241e-05</v>
+        <v>4.433428237512259e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.443687520984209e-05</v>
+        <v>4.443687520984225e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.438211799703948e-05</v>
+        <v>4.438211799703956e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.669507765277841e-05</v>
+        <v>4.669507765277856e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.721844998885391e-05</v>
+        <v>4.721844998885412e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.437434519168408e-05</v>
+        <v>4.437434519168415e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.438107363927195e-05</v>
+        <v>4.4381073639272e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.442382183906273e-05</v>
+        <v>4.442382183906289e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.439048446857921e-05</v>
+        <v>4.439048446857926e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.444086126283401e-05</v>
+        <v>4.444086126283414e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.43384751063357e-05</v>
+        <v>5.251908464685242e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.453490125428503e-05</v>
+        <v>4.453490125428517e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.440975414355566e-05</v>
+        <v>4.44097541435558e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.443502057617952e-05</v>
+        <v>4.443502057617964e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.441877589669233e-05</v>
+        <v>4.014471042055731e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.440131579669358e-05</v>
+        <v>4.440131579669371e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.447595646532383e-05</v>
+        <v>4.447595646532399e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3169,82 +3169,82 @@
         <v>1.344155360842263e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.351829135598582e-05</v>
+        <v>1.351829135598581e-05</v>
       </c>
       <c r="D2" t="n">
         <v>1.345054047197759e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.343923015611597e-05</v>
+        <v>1.343923015611596e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.343145108945764e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.345147741599469e-05</v>
+        <v>1.345147741599464e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.343592321742568e-05</v>
+        <v>1.343592321742566e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.344664686743555e-05</v>
+        <v>1.344664686743553e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.344544704195426e-05</v>
+        <v>1.344544704195422e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.345099738369847e-05</v>
+        <v>1.345099738369844e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.343797285317984e-05</v>
+        <v>1.343797285317981e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344452410918489e-05</v>
+        <v>1.344452410918487e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.343923308878774e-05</v>
+        <v>1.343923308878771e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.497266912255107e-05</v>
+        <v>1.497266912255104e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343435844262658e-05</v>
+        <v>1.34343584426266e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.343807965245002e-05</v>
+        <v>1.343807965244998e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.343747514821065e-05</v>
+        <v>1.34374751482107e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344509849105965e-05</v>
+        <v>1.344509849105964e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344288027620247e-05</v>
+        <v>1.344288027620246e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39580453792372e-05</v>
+        <v>1.395804537923721e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344043155201506e-05</v>
+        <v>1.344043155201503e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.403866351817541e-05</v>
+        <v>1.403866351817539e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344105008368907e-05</v>
+        <v>1.344105008368904e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.343748817533494e-05</v>
+        <v>1.343748817533497e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.379188604722379e-05</v>
+        <v>1.379188604722375e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.34443004956714e-05</v>
+        <v>1.344430049567139e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.344400522698262e-05</v>
+        <v>1.344400522698259e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3257,67 +3257,67 @@
         <v>1.352388919185729e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.36053163506795e-05</v>
+        <v>1.360531635067951e-05</v>
       </c>
       <c r="D3" t="n">
         <v>1.3590895166846e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.346590472093227e-05</v>
+        <v>1.346590472093226e-05</v>
       </c>
       <c r="F3" t="n">
         <v>1.345790797878325e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.359694279652318e-05</v>
+        <v>1.359694279652315e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34874924737128e-05</v>
+        <v>1.348749247371283e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.356277732732875e-05</v>
+        <v>1.356277732732876e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.355438882368747e-05</v>
+        <v>1.355438882368751e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.360758541920864e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.349812600466752e-05</v>
+        <v>1.349812600466751e-05</v>
       </c>
       <c r="M3" t="n">
         <v>1.356812345008146e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.350786997035595e-05</v>
+        <v>1.350786997035597e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.600824940223896e-05</v>
+        <v>1.6008249402239e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34722591249849e-05</v>
+        <v>1.347225912498491e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.35023626980588e-05</v>
+        <v>1.350236269805881e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.349702301374959e-05</v>
+        <v>1.349702301374953e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35509985993768e-05</v>
+        <v>1.355099859937679e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.353534741177948e-05</v>
+        <v>1.353534741177946e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.437446623309325e-05</v>
+        <v>1.437446623309324e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352565099978372e-05</v>
+        <v>1.352565099978371e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.460043002014485e-05</v>
+        <v>1.460043002014482e-05</v>
       </c>
       <c r="X3" t="n">
         <v>1.3523014036105e-05</v>
@@ -3326,13 +3326,13 @@
         <v>1.34974749490631e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.413014206388145e-05</v>
+        <v>1.413014206388148e-05</v>
       </c>
       <c r="AA3" t="n">
         <v>1.354397005692258e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.357050640349355e-05</v>
+        <v>1.357050640349357e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3342,67 +3342,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.206648458953494e-05</v>
+        <v>1.206648458953497e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.197352704006902e-05</v>
+        <v>1.197352704006904e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.216799534754974e-05</v>
+        <v>1.216799534754976e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.204024012689047e-05</v>
+        <v>1.204024012689048e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.195237199043718e-05</v>
+        <v>1.195237199043716e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.217857856123804e-05</v>
+        <v>1.217857856123803e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.200288673311639e-05</v>
+        <v>1.200288673311638e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.212401529310058e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.209896737874387e-05</v>
+        <v>1.209896737874385e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.217315637562672e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.202603831183863e-05</v>
+        <v>1.202603831183864e-05</v>
       </c>
       <c r="M4" t="n">
         <v>1.213380967387146e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.204027325276678e-05</v>
+        <v>1.204027325276676e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19652070608929e-05</v>
+        <v>1.196520706089292e-05</v>
       </c>
       <c r="P4" t="n">
         <v>1.198521188192892e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.202724465872521e-05</v>
+        <v>1.202724465872522e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.202041650525683e-05</v>
+        <v>1.202041650525685e-05</v>
       </c>
       <c r="S4" t="n">
         <v>1.210652566964656e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.208146991240563e-05</v>
+        <v>1.208146991240567e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19920819419015e-05</v>
+        <v>1.199208194190152e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.200565572632342e-05</v>
+        <v>1.200565572632343e-05</v>
       </c>
       <c r="W4" t="n">
         <v>1.225416703333736e-05</v>
@@ -3414,13 +3414,13 @@
         <v>1.195555905391571e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.211377539463257e-05</v>
+        <v>1.211377539463258e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.209751194464032e-05</v>
+        <v>1.209751194464034e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.213763711276862e-05</v>
+        <v>1.213763711276863e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.18231565923564e-05</v>
+        <v>4.182315659235648e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.54565691798588e-05</v>
+        <v>4.545656917985884e-05</v>
       </c>
       <c r="D5" t="n">
         <v>4.510391980827241e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.990350611713231e-05</v>
+        <v>1.990350611713236e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.297692385904536e-05</v>
+        <v>4.297692385904539e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.495975555279221e-05</v>
+        <v>4.495975555279074e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.266118404005876e-05</v>
+        <v>4.266118404005869e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.415556934104608e-05</v>
+        <v>4.415556934104612e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.399491361448117e-05</v>
+        <v>4.399491361448053e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.215457018996663e-05</v>
+        <v>5.215457018996668e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.100044277535247e-05</v>
+        <v>4.10004427753524e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.544163355586921e-05</v>
+        <v>4.544163355586912e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.298796471268016e-05</v>
+        <v>4.29879647126803e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.32271141783927e-05</v>
+        <v>4.322711417839266e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.024174670546113e-05</v>
+        <v>4.024174670546122e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.282233079361929e-05</v>
+        <v>4.282233079361942e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.217022402585085e-05</v>
+        <v>4.217022402585089e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.346902667159224e-05</v>
+        <v>4.346902667159234e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.311932178783731e-05</v>
+        <v>4.311932178783754e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.300477800051743e-05</v>
+        <v>4.300477800051765e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.661388370712775e-05</v>
+        <v>4.661388370712306e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.500869883837214e-05</v>
+        <v>4.500869883837167e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.313136993613803e-05</v>
+        <v>4.313136993613815e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.235884854065065e-05</v>
+        <v>4.235884854065093e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.524822126410915e-05</v>
+        <v>4.52482212641092e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.261870196237076e-05</v>
+        <v>4.261870196237087e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.593547015740499e-05</v>
+        <v>4.593547015740507e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.622726768668488e-05</v>
+        <v>1.329640641438828e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.320344886492233e-05</v>
+        <v>1.320344886492239e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.63287784446996e-05</v>
+        <v>1.632877844469967e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.327016195174374e-05</v>
+        <v>1.327016195174383e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.31822938152905e-05</v>
+        <v>1.611315508758711e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.633936165838793e-05</v>
+        <v>1.340850038609135e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.323280855796968e-05</v>
+        <v>1.323280855796975e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.628479839025042e-05</v>
+        <v>1.335393711795393e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.625975047589372e-05</v>
+        <v>1.625975047589377e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.340307820047997e-05</v>
+        <v>1.633393947277662e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.618682140898845e-05</v>
+        <v>1.325596013669195e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.629459277102141e-05</v>
+        <v>1.629459277102138e-05</v>
       </c>
       <c r="N6" t="n">
         <v>1.327184002654098e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.613088050482937e-05</v>
+        <v>1.319677383466713e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.615092905444057e-05</v>
+        <v>1.615092905444062e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.618802775587503e-05</v>
+        <v>1.618802775587512e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.618119960240669e-05</v>
+        <v>1.618119960240674e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.333644749449986e-05</v>
+        <v>1.333644749449991e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.331139173725904e-05</v>
+        <v>1.331139173725901e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.621786963775395e-05</v>
+        <v>1.328700836545748e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.616643882347329e-05</v>
+        <v>1.616643882347334e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.641975209296892e-05</v>
+        <v>1.356380741743697e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.329071887088977e-05</v>
+        <v>1.329071887088983e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.331788117679584e-05</v>
+        <v>1.331788117679591e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.627455849178241e-05</v>
+        <v>1.334369721948592e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.332743376949365e-05</v>
+        <v>1.625829504179026e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.336971593946776e-05</v>
+        <v>1.336971593946781e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3606,34 +3606,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.001887470321767e-05</v>
+        <v>2.001887470321778e-05</v>
       </c>
       <c r="C7" t="n">
         <v>1.992591715375185e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.012038546123254e-05</v>
+        <v>2.012038546123256e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.999263024057327e-05</v>
+        <v>1.999263024057325e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.990476210411991e-05</v>
+        <v>1.990476210411998e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.013096867492086e-05</v>
+        <v>2.013096867492082e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.995527684679914e-05</v>
+        <v>1.995527684679918e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.007640540678339e-05</v>
+        <v>2.007640540678335e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.00513574924267e-05</v>
+        <v>2.005135749242664e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.012554648930949e-05</v>
+        <v>2.012554648930956e-05</v>
       </c>
       <c r="L7" t="n">
         <v>1.997842842552142e-05</v>
@@ -3642,49 +3642,49 @@
         <v>2.008619978755426e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.999266336644957e-05</v>
+        <v>1.999266336644959e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.991756520318491e-05</v>
+        <v>1.991756520318495e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.993757002422092e-05</v>
+        <v>1.993757002422096e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.997963477240796e-05</v>
+        <v>1.997963477240801e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.997280661893962e-05</v>
+        <v>1.997280661893964e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.005891578332933e-05</v>
+        <v>2.005891578332938e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.003386002608848e-05</v>
+        <v>2.003386002608849e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.001023601532494e-05</v>
+        <v>2.0010236015325e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.995804584000624e-05</v>
+        <v>1.995804584000622e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.020655714702013e-05</v>
+        <v>2.020655714702019e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.001318715971925e-05</v>
+        <v>2.001318715971927e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.99729537663011e-05</v>
+        <v>1.997295376630113e-05</v>
       </c>
       <c r="Z7" t="n">
         <v>2.006616550831536e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.004990205832314e-05</v>
+        <v>2.004990205832317e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.009002722645141e-05</v>
+        <v>2.00900272264514e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.14930483965631e-05</v>
+        <v>5.149304839656307e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.663566227693304e-05</v>
+        <v>7.663566227693306e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.683013058441387e-05</v>
+        <v>7.683013058441375e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.670237536375459e-05</v>
+        <v>6.326517797924361e-05</v>
       </c>
       <c r="F8" t="n">
         <v>5.531034289242754e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6840713798102e-05</v>
+        <v>8.207347392886532e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.666502196998044e-05</v>
+        <v>7.666502196998049e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.678615052996464e-05</v>
+        <v>7.678615052996463e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.676110261560788e-05</v>
+        <v>7.676110261560791e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.683529161249074e-05</v>
+        <v>7.683529161249082e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.668817354870257e-05</v>
+        <v>7.66881735487026e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.679594491073555e-05</v>
+        <v>7.679594491073512e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.71406188135594e-05</v>
+        <v>5.714061881355941e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.24413022792442e-05</v>
+        <v>6.244130227924426e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.114358096263101e-05</v>
+        <v>6.114358096263108e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.649444270478325e-05</v>
+        <v>4.649444270478323e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.668255174212087e-05</v>
+        <v>7.66825517421209e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.676866090651056e-05</v>
+        <v>7.676866090651057e-05</v>
       </c>
       <c r="T8" t="n">
         <v>7.674360514926975e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.119114093132991e-05</v>
+        <v>6.440268944390603e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.666779096318746e-05</v>
+        <v>6.97712051991191e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.692126178765424e-05</v>
+        <v>7.69212617876544e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.88408853602859e-05</v>
+        <v>4.884088536028595e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001017749022795787</v>
+        <v>0.0001017749022795788</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.677591063149664e-05</v>
+        <v>5.10715755060158e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.675964718150437e-05</v>
+        <v>7.675964718150439e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001031604368764938</v>
+        <v>0.0001031604368764937</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.434366595209846e-05</v>
+        <v>3.434366595209853e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.049183164369302e-05</v>
+        <v>4.049183164369303e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.068629995117369e-05</v>
+        <v>4.068629995117372e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.055854473051434e-05</v>
+        <v>3.911811911004421e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.047067659406117e-05</v>
+        <v>2.608318387676134e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.069688316486222e-05</v>
+        <v>4.06968833813048e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.052119133674051e-05</v>
+        <v>4.052119133674041e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.064231989672458e-05</v>
+        <v>4.064231989672454e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.061727198236781e-05</v>
+        <v>4.061727198236784e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.069146097925077e-05</v>
+        <v>4.06914609792507e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.054434291546272e-05</v>
+        <v>4.054434291546266e-05</v>
       </c>
       <c r="M9" t="n">
         <v>4.065211427749545e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.05585778563908e-05</v>
+        <v>4.055857785639077e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.25518120227206e-05</v>
+        <v>4.255181202272064e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.302163663853642e-05</v>
+        <v>4.302163663853644e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.054554947879199e-05</v>
+        <v>4.054554947879198e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.053872110888082e-05</v>
+        <v>4.053872110888084e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.06248302732706e-05</v>
+        <v>4.062483027327055e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.059977451602965e-05</v>
+        <v>4.059977451602964e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.057539114422787e-05</v>
+        <v>4.057539114422808e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.052396032994747e-05</v>
+        <v>4.772608279743968e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.077247163696129e-05</v>
+        <v>4.077247163696136e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.057910164966054e-05</v>
+        <v>4.057910164966044e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.05388682562424e-05</v>
+        <v>4.053886825624225e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.063207999825642e-05</v>
+        <v>3.686923775217614e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.061581654826426e-05</v>
+        <v>4.06158165482643e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.065594171639257e-05</v>
+        <v>4.065594171639262e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.345856762189207e-05</v>
+        <v>1.345856762189204e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.353448711631573e-05</v>
+        <v>1.35344871163157e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347875696255069e-05</v>
+        <v>1.347875696255078e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.345683319434093e-05</v>
+        <v>1.345683319434104e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.344920961598092e-05</v>
+        <v>1.344920961598106e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.347116977750494e-05</v>
+        <v>1.347116977750508e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3457022444695e-05</v>
+        <v>1.345702244469501e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.346830823779105e-05</v>
+        <v>1.346830823779118e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.346412456375503e-05</v>
+        <v>1.346412456375501e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.346465218532333e-05</v>
+        <v>1.346465218532323e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.345353730572775e-05</v>
+        <v>1.34535373057279e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.346313119074851e-05</v>
+        <v>1.346313119074848e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.345443010508952e-05</v>
+        <v>1.345443010508963e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.500818315217246e-05</v>
+        <v>1.500818315217221e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.345281394700195e-05</v>
+        <v>1.345281394700206e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.345312037209681e-05</v>
+        <v>1.345312037209693e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.345469865190751e-05</v>
+        <v>1.345469865190761e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.345990724841716e-05</v>
+        <v>1.345990724841728e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.346317029712488e-05</v>
+        <v>1.3463170297125e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.398302950309255e-05</v>
+        <v>1.398302950309273e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.346084402060497e-05</v>
+        <v>1.346084402060512e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.407303767081767e-05</v>
+        <v>1.407303767081769e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.345697876107961e-05</v>
+        <v>1.345697876107965e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.345734270816109e-05</v>
+        <v>1.345734270816117e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.38166278601543e-05</v>
+        <v>1.381662786015446e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.346821724255988e-05</v>
+        <v>1.346821724256003e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.346439409350263e-05</v>
+        <v>1.34643940935026e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.354472016453572e-05</v>
+        <v>1.354472016453583e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.361752714353709e-05</v>
+        <v>1.361752714353705e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.369406612400806e-05</v>
+        <v>1.36940661240082e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.349522274363887e-05</v>
+        <v>1.34952227436388e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.348153358180074e-05</v>
+        <v>1.348153358180077e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.363795940973667e-05</v>
+        <v>1.363795940973666e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.353404718924814e-05</v>
+        <v>1.353404718924801e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.361621562718497e-05</v>
+        <v>1.361621562718496e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.358706110331583e-05</v>
+        <v>1.358706110331587e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.360092509946781e-05</v>
+        <v>1.360092509946771e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.351077136749906e-05</v>
+        <v>1.351077136749908e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.36029700901047e-05</v>
+        <v>1.360297009010466e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.35123447399703e-05</v>
+        <v>1.351234473997013e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.607916993018555e-05</v>
+        <v>1.607916993018554e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.350417673099777e-05</v>
+        <v>1.35041767309978e-05</v>
       </c>
       <c r="Q3" t="n">
         <v>1.350782923917255e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.351623613981319e-05</v>
+        <v>1.351623613981322e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.355408523306737e-05</v>
+        <v>1.355408523306736e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.357631796516524e-05</v>
+        <v>1.357631796516523e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.441204523033468e-05</v>
+        <v>1.441204523033462e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.356837783214063e-05</v>
+        <v>1.356837783214051e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.469275709883097e-05</v>
+        <v>1.469275709883079e-05</v>
       </c>
       <c r="X3" t="n">
         <v>1.353571927451506e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.353266753910376e-05</v>
+        <v>1.353266753910373e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.416975808107868e-05</v>
+        <v>1.416975808107864e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.36101499593379e-05</v>
+        <v>1.361014995933788e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.361343644671352e-05</v>
+        <v>1.361343644671351e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.211784134886224e-05</v>
+        <v>1.211784134886221e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.201459437190588e-05</v>
+        <v>1.201459437190587e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.234588923915831e-05</v>
+        <v>1.23458892391583e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.209825019179756e-05</v>
+        <v>1.209825019179754e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.201213836720231e-05</v>
+        <v>1.201213836720226e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.226018849378955e-05</v>
+        <v>1.226018849378951e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.210038786160527e-05</v>
+        <v>1.210038786160524e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.222786608634777e-05</v>
+        <v>1.222786608634775e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.216912230515467e-05</v>
+        <v>1.216912230515465e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.218656929185514e-05</v>
+        <v>1.218656929185511e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.206102161372853e-05</v>
+        <v>1.206102161372851e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.220343979212462e-05</v>
+        <v>1.220343979212459e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.207110619322727e-05</v>
+        <v>1.207110619322721e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.206459715466087e-05</v>
+        <v>1.206459715466085e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.205285094415872e-05</v>
+        <v>1.205285094415868e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.205631215656769e-05</v>
+        <v>1.205631215656764e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.207413955307385e-05</v>
+        <v>1.207413955307382e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.21329730467236e-05</v>
+        <v>1.213297304672357e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.216983068295372e-05</v>
+        <v>1.216983068295367e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.204953870731382e-05</v>
+        <v>1.204953870731377e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.20954590111707e-05</v>
+        <v>1.209545901117067e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.240063859892142e-05</v>
+        <v>1.240063859892139e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.209989443507428e-05</v>
+        <v>1.209989443507423e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.204047118341361e-05</v>
+        <v>1.204047118341357e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.217537365277015e-05</v>
+        <v>1.217537365277014e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.222683825335194e-05</v>
+        <v>1.222683825335191e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.222706106660031e-05</v>
+        <v>1.222706106660029e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.373742777788601e-05</v>
+        <v>4.373742777788609e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.60017638352703e-05</v>
+        <v>4.600176383527023e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.049339107410494e-05</v>
+        <v>5.049339107410486e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.415508652921966e-05</v>
+        <v>2.415508652921959e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.373452688569048e-05</v>
+        <v>4.373452688569036e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.796367545412815e-05</v>
+        <v>4.796367545412795e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.361272008677955e-05</v>
+        <v>4.361272008678016e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.670751314337117e-05</v>
+        <v>4.67075131433706e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.62253399389104e-05</v>
+        <v>4.622533993891029e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.157544108293607e-05</v>
+        <v>5.157544108293561e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.374447662007766e-05</v>
+        <v>4.374447662007754e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.89717158972288e-05</v>
+        <v>4.897171589722871e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.565592670734394e-05</v>
+        <v>4.565592670734366e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.403277712404166e-05</v>
+        <v>4.403277712404152e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.285787269682275e-05</v>
+        <v>4.285787269682265e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.367856738787642e-05</v>
+        <v>4.367856738787636e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.251311930360174e-05</v>
+        <v>4.251311930360168e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.390352999575894e-05</v>
+        <v>4.39035299957588e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.400827173063632e-05</v>
+        <v>4.400827173063642e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.569789342280174e-05</v>
+        <v>4.569789342279863e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.798461824478453e-05</v>
+        <v>4.798461824478452e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.68647197673801e-05</v>
+        <v>4.686471976737994e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.463207689044752e-05</v>
+        <v>4.463207689044763e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.17772082318119e-05</v>
+        <v>4.177720823181176e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.789007437161987e-05</v>
+        <v>4.789007437161981e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.388250999423982e-05</v>
+        <v>4.388250999423976e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.750810415313976e-05</v>
+        <v>4.750810415313966e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.335358427601193e-05</v>
+        <v>1.629343687853167e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.32503372990556e-05</v>
+        <v>1.325033729905557e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.358163216630803e-05</v>
+        <v>1.3581632166308e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.333399311894725e-05</v>
+        <v>1.627384572146699e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3247881294352e-05</v>
+        <v>1.324788129435199e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.349593142093926e-05</v>
+        <v>1.643578402345898e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.627598339127473e-05</v>
+        <v>1.333613078875495e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.346360901349747e-05</v>
+        <v>1.346360901349745e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.340486523230439e-05</v>
+        <v>1.634471783482412e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.636216482152457e-05</v>
+        <v>1.636216482152456e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.329676454087825e-05</v>
+        <v>1.623661714339797e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.343918271927434e-05</v>
+        <v>1.34391827192743e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.330861779068839e-05</v>
+        <v>1.330861779068836e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.330210875212202e-05</v>
+        <v>1.624400860347632e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.623230572693254e-05</v>
+        <v>1.320259522311905e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.623190768623714e-05</v>
+        <v>1.623190768623711e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.624973508274332e-05</v>
+        <v>1.62497350827433e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.630856857639306e-05</v>
+        <v>1.630856857639304e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.340557361010336e-05</v>
+        <v>1.634542621262315e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.628866843835359e-05</v>
+        <v>1.334881583583381e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.627105454084014e-05</v>
+        <v>1.333120193832036e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.658000085209655e-05</v>
+        <v>1.658000085209657e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.333563736222395e-05</v>
+        <v>1.333563736222394e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.340762560947028e-05</v>
+        <v>1.340762560947025e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.635096918243962e-05</v>
+        <v>1.63509691824396e-05</v>
       </c>
       <c r="AA6" t="n">
         <v>1.64024337830214e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.346513636672524e-05</v>
+        <v>1.346513636672522e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.007283006629319e-05</v>
+        <v>2.007283006629318e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.996958308933687e-05</v>
+        <v>1.996958308933685e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.030087795658931e-05</v>
+        <v>2.030087795658928e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.005323890922854e-05</v>
+        <v>2.005323890922851e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.996712708463328e-05</v>
+        <v>1.996712708463323e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.021517721122053e-05</v>
+        <v>2.021517721122049e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.005537657903625e-05</v>
+        <v>2.005537657903621e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.018285480377874e-05</v>
+        <v>2.018285480377872e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.012411102258568e-05</v>
+        <v>2.012411102258565e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.014155800928612e-05</v>
+        <v>2.014155800928608e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.001601033115951e-05</v>
+        <v>2.001601033115949e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.015842850955562e-05</v>
+        <v>2.015842850955557e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.002609491065824e-05</v>
+        <v>2.002609491065819e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.001955267671101e-05</v>
+        <v>2.001955267671097e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.000780646620884e-05</v>
+        <v>2.000780646620881e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.001130087399864e-05</v>
+        <v>2.001130087399861e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.002912827050483e-05</v>
+        <v>2.00291282705048e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.008796176415459e-05</v>
+        <v>2.008796176415454e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.012481940038469e-05</v>
+        <v>2.012481940038466e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.007014279324695e-05</v>
+        <v>2.00701427932469e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.005044772860167e-05</v>
+        <v>2.005044772860164e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.035562731635242e-05</v>
+        <v>2.035562731635236e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.005488315250525e-05</v>
+        <v>2.005488315250521e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.005899410221492e-05</v>
+        <v>2.005899410221487e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.013036237020113e-05</v>
+        <v>2.013036237020111e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.018182697078293e-05</v>
+        <v>2.018182697078288e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.018204978403129e-05</v>
+        <v>2.018204978403125e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.155638092227232e-05</v>
+        <v>5.155638092227224e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.669700571822677e-05</v>
+        <v>7.669700571822662e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.702830058547918e-05</v>
+        <v>7.702830058547901e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.678066153811843e-05</v>
+        <v>6.333904446576414e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.538337813201346e-05</v>
+        <v>5.538337813201333e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.694259984011048e-05</v>
+        <v>8.217708110108221e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.678279920792622e-05</v>
+        <v>7.678279920792597e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.691027743266867e-05</v>
+        <v>7.691027743266853e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.685153365147559e-05</v>
+        <v>7.685153365147536e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.686898063817603e-05</v>
+        <v>7.686898063817588e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.67434329600494e-05</v>
+        <v>7.674343296004921e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.688585113844551e-05</v>
+        <v>7.688585113844531e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.718529370897132e-05</v>
+        <v>5.718529370897115e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.255630248948507e-05</v>
+        <v>6.255630248948489e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.122639672222048e-05</v>
+        <v>6.122639672222029e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.653385476214467e-05</v>
+        <v>4.653385476214459e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.675655089939477e-05</v>
+        <v>7.675655089939452e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.681538439304454e-05</v>
+        <v>7.681538439304432e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.685224202927455e-05</v>
+        <v>7.685224202927445e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.126325856662055e-05</v>
+        <v>6.447592595060182e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.677787035749163e-05</v>
+        <v>6.988014687786264e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.708801109394112e-05</v>
+        <v>7.708801109394094e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.889108805177441e-05</v>
+        <v>4.889108805177423e-05</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0001018886269804813</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.685778499909113e-05</v>
+        <v>5.114499534739788e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.690924959967282e-05</v>
+        <v>7.690924959967261e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001032788073421859</v>
+        <v>0.0001032788073421857</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.33423795754351e-05</v>
+        <v>3.334237957543503e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.918944281481742e-05</v>
+        <v>3.918944281481733e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.952073768206982e-05</v>
+        <v>3.952073768206975e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.927309863470907e-05</v>
+        <v>3.789979148671545e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.91869868101138e-05</v>
+        <v>2.546989746386249e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.943503693670104e-05</v>
+        <v>3.943503716949268e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.927523630451678e-05</v>
+        <v>3.927523630451668e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.940271452925931e-05</v>
+        <v>3.940271452925921e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.93439707480662e-05</v>
+        <v>3.934397074806612e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.936141773476662e-05</v>
+        <v>3.936141773476656e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.923587005664007e-05</v>
+        <v>3.923587005663996e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.937828823503612e-05</v>
+        <v>3.937828823503607e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.924595463613875e-05</v>
+        <v>3.924595463613868e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.121137092193746e-05</v>
+        <v>4.121137092193741e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.162848458631666e-05</v>
+        <v>4.162848458631657e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.923116083227085e-05</v>
+        <v>3.923116083227081e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.92489879959854e-05</v>
+        <v>3.924898799598528e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.93078214896351e-05</v>
+        <v>3.930782148963505e-05</v>
       </c>
       <c r="T9" t="n">
         <v>3.934467912586513e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.928792135159564e-05</v>
+        <v>3.928792135159555e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>3.92703074540822e-05</v>
+        <v>4.613683787637975e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.957548704183293e-05</v>
+        <v>3.957548704183286e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.927474287798577e-05</v>
+        <v>3.927474287798571e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.927885382769545e-05</v>
+        <v>3.927885382769537e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.935022209568168e-05</v>
+        <v>3.576271424989731e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.940168669626344e-05</v>
+        <v>3.940168669626341e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.940190950951182e-05</v>
+        <v>3.940190950951174e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4886,82 +4886,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.345430853666593e-05</v>
+        <v>1.345430853666623e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.351680326145909e-05</v>
+        <v>1.351680326145907e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3473086937224e-05</v>
+        <v>1.347308693722402e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.343573064770402e-05</v>
+        <v>1.343573064770414e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343709861898342e-05</v>
+        <v>1.34370986189834e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.346141541006906e-05</v>
+        <v>1.346141541006911e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.345401115451937e-05</v>
+        <v>1.345401115451946e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.343823912350151e-05</v>
+        <v>1.343823912350158e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.345101596915692e-05</v>
+        <v>1.345101596915689e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.344781409070123e-05</v>
+        <v>1.344781409070124e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.345051230786954e-05</v>
+        <v>1.345051230786958e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344388662933501e-05</v>
+        <v>1.344388662933499e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.344387214723017e-05</v>
+        <v>1.344387214723021e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.496214079090988e-05</v>
+        <v>1.496214079090994e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343926070911802e-05</v>
+        <v>1.343926070911796e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.344723475675938e-05</v>
+        <v>1.344723475675952e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.344871712950524e-05</v>
+        <v>1.344871712950518e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344741850122875e-05</v>
+        <v>1.344741850122864e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344483232704042e-05</v>
+        <v>1.344483232704047e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.395428692463033e-05</v>
+        <v>1.395428692463048e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344569435586228e-05</v>
+        <v>1.34456943558623e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.403221102885745e-05</v>
+        <v>1.403221102885771e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344560801846512e-05</v>
+        <v>1.344560801846536e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.344642097609305e-05</v>
+        <v>1.344642097609304e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.379292607128478e-05</v>
+        <v>1.379292607128465e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.344446356889113e-05</v>
+        <v>1.344446356889115e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.3447573837048e-05</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.358157364023292e-05</v>
+        <v>1.358157364023291e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.355677553416964e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.371688895211423e-05</v>
+        <v>1.371688895211414e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.340534585720689e-05</v>
+        <v>1.340534585720684e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.346276326799582e-05</v>
+        <v>1.346276326799576e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.364233644532259e-05</v>
+        <v>1.364233644532274e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.358259020968546e-05</v>
+        <v>1.358259020968529e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.346762217197809e-05</v>
+        <v>1.346762217197796e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.356347225477422e-05</v>
+        <v>1.356347225477451e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.35476312623951e-05</v>
+        <v>1.354763126239543e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.356710692947174e-05</v>
+        <v>1.356710692947172e-05</v>
       </c>
       <c r="M3" t="n">
         <v>1.354212891675131e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.35073911199039e-05</v>
+        <v>1.350739111990386e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59889824050205e-05</v>
+        <v>1.598898240502055e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.347096425213024e-05</v>
+        <v>1.347096425213026e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.353376217742047e-05</v>
+        <v>1.353376217742033e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35413702315868e-05</v>
+        <v>1.354137023158689e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.354254598459219e-05</v>
+        <v>1.354254598459221e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.352106504475787e-05</v>
+        <v>1.352106504475784e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43529765081322e-05</v>
+        <v>1.435297650813218e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352615424351192e-05</v>
+        <v>1.352615424351229e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.456530992514495e-05</v>
+        <v>1.456530992514543e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.352003051380981e-05</v>
+        <v>1.352003051380987e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.352593699565204e-05</v>
+        <v>1.352593699565214e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.411520746041687e-05</v>
+        <v>1.411520746041703e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.350962231154568e-05</v>
+        <v>1.350962231154565e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.356345340805897e-05</v>
+        <v>1.356345340805894e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5065,13 +5065,13 @@
         <v>1.218165241780322e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.193096488027357e-05</v>
+        <v>1.193096488027356e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.239376309059673e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.197180661572606e-05</v>
+        <v>1.197180661572605e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.198725848062485e-05</v>
@@ -5080,7 +5080,7 @@
         <v>1.226192782221388e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.217829334965578e-05</v>
+        <v>1.217829334965577e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.200014100381635e-05</v>
@@ -5089,16 +5089,16 @@
         <v>1.213293906951843e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.210829466303842e-05</v>
+        <v>1.210829466303841e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.213877226719518e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.209865607672439e-05</v>
+        <v>1.209865607672438e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.206376859814891e-05</v>
+        <v>1.20637685981489e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.200471860319722e-05</v>
@@ -5113,31 +5113,31 @@
         <v>1.211849490174696e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.210382629796489e-05</v>
+        <v>1.210382629796487e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.207461427081021e-05</v>
+        <v>1.20746142708102e-05</v>
       </c>
       <c r="U4" t="n">
         <v>1.199570080521491e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.203600372790278e-05</v>
+        <v>1.203600372790273e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22489693730369e-05</v>
+        <v>1.224896937303689e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.208337606228715e-05</v>
+        <v>1.208337606228716e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.202179232664856e-05</v>
+        <v>1.202179232664857e-05</v>
       </c>
       <c r="Z4" t="n">
         <v>1.21241070727168e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.207044897787656e-05</v>
+        <v>1.207044897787657e-05</v>
       </c>
       <c r="AB4" t="n">
         <v>1.214956214629988e-05</v>
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.725844172143004e-05</v>
+        <v>4.725844172142998e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.474175035936941e-05</v>
+        <v>4.474175035936931e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.198807653164834e-05</v>
+        <v>5.198807653164831e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.90221799765031e-05</v>
+        <v>1.902217997650311e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.581729494346609e-05</v>
+        <v>4.581729494346718e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.436043671437572e-05</v>
+        <v>5.436043671437599e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.894069106545297e-05</v>
+        <v>4.89406910654529e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.42361778406202e-05</v>
+        <v>4.423617784062014e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.954573131366921e-05</v>
+        <v>4.954573131366914e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.277258612878501e-05</v>
+        <v>5.277258612878491e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.34702932921033e-05</v>
+        <v>5.347029329210338e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.462694399694098e-05</v>
+        <v>5.462694399694086e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.622544223439826e-05</v>
+        <v>4.622544223439821e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.635721605588929e-05</v>
+        <v>4.63572160558892e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.22581009991018e-05</v>
+        <v>4.22581009991017e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.723507522896155e-05</v>
+        <v>4.723507522896151e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.58989452910065e-05</v>
+        <v>4.589894529100641e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>5.143011789994556e-05</v>
+        <v>5.143011789994546e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.919637251500345e-05</v>
+        <v>4.919637251500335e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.622814090748967e-05</v>
+        <v>4.62281409074896e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.87408615736617e-05</v>
+        <v>4.874086157366056e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.6921545667456e-05</v>
+        <v>4.69215456674559e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.570774153437204e-05</v>
+        <v>4.570774153437195e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.593940928768234e-05</v>
+        <v>4.593940928768233e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.763538899565879e-05</v>
+        <v>4.763538899565868e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.421742039852667e-05</v>
+        <v>4.421742039852665e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.001626691671282e-05</v>
+        <v>5.001626691671269e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349854197463753e-05</v>
+        <v>1.349854197463751e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.638074858366656e-05</v>
+        <v>1.638074858366655e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.684354679398969e-05</v>
+        <v>1.371065264743102e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.642159031911904e-05</v>
+        <v>1.328869617256035e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.643704218401782e-05</v>
+        <v>1.643704218401789e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.357881737904818e-05</v>
+        <v>1.671171152560688e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.349518290649008e-05</v>
+        <v>1.349518290649007e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.644992470720931e-05</v>
+        <v>1.331703056065065e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.344982862635272e-05</v>
+        <v>1.344982862635271e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.655807836643141e-05</v>
+        <v>1.342518421987271e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.658855597058819e-05</v>
+        <v>1.345566182402947e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.341554563355868e-05</v>
+        <v>1.654843978011736e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.338318969959035e-05</v>
+        <v>1.338318969959034e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64624621145634e-05</v>
+        <v>1.646246211456352e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.646949298193966e-05</v>
+        <v>1.323744025043359e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.655153452305231e-05</v>
+        <v>1.655153452305232e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.656827860513994e-05</v>
+        <v>1.343538445858125e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.655361000135784e-05</v>
+        <v>1.342071585479916e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.339150382764453e-05</v>
+        <v>1.652439797420319e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.651625097463329e-05</v>
+        <v>1.338335682807459e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.335289328473709e-05</v>
+        <v>1.648578743129575e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.365167989069267e-05</v>
+        <v>1.365167989069269e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.340026561912147e-05</v>
+        <v>1.340026561912145e-05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.34823876816398e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.344099662955111e-05</v>
+        <v>1.65738907761098e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.338733853471087e-05</v>
+        <v>1.652023268126956e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.346923311219695e-05</v>
+        <v>1.346923311219694e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5332,25 +5332,25 @@
         <v>2.047123110861368e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.093402931893686e-05</v>
+        <v>2.093402931893687e-05</v>
       </c>
       <c r="E7" t="n">
         <v>2.051207284406618e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.052752470896498e-05</v>
+        <v>2.052752470896496e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.080219405055401e-05</v>
+        <v>2.080219405055402e-05</v>
       </c>
       <c r="H7" t="n">
         <v>2.071855957799593e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.054040723215649e-05</v>
+        <v>2.054040723215648e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.067320529785856e-05</v>
+        <v>2.067320529785855e-05</v>
       </c>
       <c r="K7" t="n">
         <v>2.064856089137855e-05</v>
@@ -5365,46 +5365,46 @@
         <v>2.060403482648902e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.054495199409755e-05</v>
+        <v>2.054495199409752e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.055191367420543e-05</v>
+        <v>2.055191367420547e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.064201704799942e-05</v>
+        <v>2.064201704799946e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.065876113008711e-05</v>
+        <v>2.065876113008709e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0644092526305e-05</v>
+        <v>2.064409252630499e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.061488049915033e-05</v>
+        <v>2.061488049915035e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.060818243499926e-05</v>
+        <v>2.060818243499927e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.05762699562429e-05</v>
+        <v>2.057626995624287e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.078923560137703e-05</v>
+        <v>2.078923560137705e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.06236422906273e-05</v>
+        <v>2.062364229062731e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.063282502101405e-05</v>
+        <v>2.063282502101407e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.066437330105695e-05</v>
+        <v>2.066437330105691e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.061071520621666e-05</v>
+        <v>2.061071520621669e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.068982837464e-05</v>
+        <v>2.068982837464003e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.447586944733634e-05</v>
+        <v>5.447586944733628e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.129626720453197e-05</v>
+        <v>8.12962672045319e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.175906541485517e-05</v>
+        <v>8.17590654148552e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.133710893998446e-05</v>
+        <v>6.692255456663333e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.849883421321728e-05</v>
+        <v>5.849883421321735e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.162723014647235e-05</v>
+        <v>8.724059603440309e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.154359567391425e-05</v>
+        <v>8.154359567391411e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.136544332807472e-05</v>
+        <v>8.136544332807474e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.149824139377689e-05</v>
+        <v>8.149824139377681e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.147359698729685e-05</v>
+        <v>8.147359698729674e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.150407459145352e-05</v>
+        <v>8.150407459145351e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.146395840098283e-05</v>
+        <v>8.14639584009821e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.044445092636325e-05</v>
+        <v>6.044445092636323e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.615215671530217e-05</v>
+        <v>6.615215671530204e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.474554720814581e-05</v>
+        <v>6.474554720814574e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.907588172014087e-05</v>
+        <v>4.907588172014082e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.148379722600542e-05</v>
+        <v>8.148379722600534e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.146912862222337e-05</v>
+        <v>8.146912862222324e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.143991659506863e-05</v>
+        <v>8.143991659506858e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.47747115155982e-05</v>
+        <v>6.821988251740306e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>8.140130605216122e-05</v>
+        <v>7.400363684420566e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.161959194615689e-05</v>
+        <v>8.161959194615692e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.153862572410201e-05</v>
+        <v>5.153862572410185e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001083759895205587</v>
+        <v>0.0001083759895205586</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.148940939697523e-05</v>
+        <v>5.391546479419681e-05</v>
       </c>
       <c r="AA8" t="n">
         <v>8.143575130213495e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001097928767127597</v>
+        <v>0.0001097928767127596</v>
       </c>
     </row>
     <row r="9">
@@ -5502,70 +5502,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.754894986985111e-05</v>
+        <v>3.754894986985117e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.43998226938397e-05</v>
+        <v>4.439982269383969e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.486262090416282e-05</v>
+        <v>4.486262090416287e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.444066442929218e-05</v>
+        <v>4.280165347256435e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.445611629419099e-05</v>
+        <v>2.808508110826923e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.473078563577994e-05</v>
+        <v>4.473078590615528e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.464715116322191e-05</v>
+        <v>4.464715116322196e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.446899881738247e-05</v>
+        <v>4.446899881738248e-05</v>
       </c>
       <c r="J9" t="n">
         <v>4.460179688308457e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.457715247660453e-05</v>
+        <v>4.457715247660451e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.460763008076127e-05</v>
+        <v>4.460763008076132e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.456751389029049e-05</v>
+        <v>4.456751389029048e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.453262641171503e-05</v>
+        <v>4.453262641171505e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.682702458184581e-05</v>
+        <v>4.682702458184587e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.734582080068789e-05</v>
+        <v>4.734582080068795e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.45706089036007e-05</v>
+        <v>4.457060890360069e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.458735271531309e-05</v>
+        <v>4.45873527153131e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.457268411153103e-05</v>
+        <v>4.457268411153101e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.454347208437631e-05</v>
+        <v>4.454347208437635e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.453532508480639e-05</v>
+        <v>4.453532508480642e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.450486154146886e-05</v>
+        <v>5.269991017952239e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.471782718660305e-05</v>
+        <v>4.471782718660298e-05</v>
       </c>
       <c r="X9" t="n">
         <v>4.45522338758533e-05</v>
@@ -5574,13 +5574,13 @@
         <v>4.456141660624007e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.459296488628293e-05</v>
+        <v>4.031135559103648e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.453930679144272e-05</v>
+        <v>4.453930679144267e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.461841995986601e-05</v>
+        <v>4.461841995986603e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.351276099408997e-05</v>
+        <v>1.351276099408994e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.357456407859201e-05</v>
+        <v>1.3574564078592e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.353462751460471e-05</v>
+        <v>1.353462751460458e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.350021629763847e-05</v>
+        <v>1.350021629763833e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.349513960213273e-05</v>
+        <v>1.349513960213262e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.352583987163883e-05</v>
+        <v>1.352583987163872e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.351233887136147e-05</v>
+        <v>1.351233887136128e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.352116789460458e-05</v>
+        <v>1.35211678946045e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35146851958082e-05</v>
+        <v>1.35146851958083e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.353443522092233e-05</v>
+        <v>1.353443522092226e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.352902418218038e-05</v>
+        <v>1.35290241821801e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.352553081440388e-05</v>
+        <v>1.352553081440389e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.350004665414554e-05</v>
+        <v>1.350004665414544e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.505299849991357e-05</v>
+        <v>1.505299849991349e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.349267117348919e-05</v>
+        <v>1.349267117348904e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.350802131835029e-05</v>
+        <v>1.350802131835017e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.351351557812611e-05</v>
+        <v>1.351351557812595e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.350533645538932e-05</v>
+        <v>1.350533645538921e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.350505722396201e-05</v>
+        <v>1.350505722396186e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.403514326702351e-05</v>
+        <v>1.40351432670236e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.350661782227077e-05</v>
+        <v>1.350661782227062e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.411801398635531e-05</v>
+        <v>1.411801398635515e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.349505423019037e-05</v>
+        <v>1.349505423019024e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.351430674355914e-05</v>
+        <v>1.351430674355908e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.387032130600084e-05</v>
+        <v>1.387032130600071e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.352107572915944e-05</v>
+        <v>1.352107572915933e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.351525998482911e-05</v>
+        <v>1.35152599848291e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.369524377446498e-05</v>
+        <v>1.369524377446481e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.366583892301748e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386246857581966e-05</v>
+        <v>1.386246857581951e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.356478137166444e-05</v>
+        <v>1.356478137166407e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.357758716082219e-05</v>
+        <v>1.357758716082211e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.380305051726205e-05</v>
+        <v>1.380305051726197e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3699686741092e-05</v>
+        <v>1.369968674109199e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.376259065939644e-05</v>
+        <v>1.376259065939623e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.371949380485511e-05</v>
+        <v>1.371949380485502e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.386627354835528e-05</v>
+        <v>1.386627354835522e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.383490043881057e-05</v>
+        <v>1.383490043881033e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.382932133605335e-05</v>
+        <v>1.382932133605331e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.360816594988311e-05</v>
+        <v>1.360816594988304e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.612015595887775e-05</v>
+        <v>1.612015595887765e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.355253105058187e-05</v>
+        <v>1.355253105058182e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.367167626285616e-05</v>
+        <v>1.367167626285606e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37072238778806e-05</v>
+        <v>1.370722387788048e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.365255140326172e-05</v>
+        <v>1.365255140326162e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.365271199482967e-05</v>
+        <v>1.365271199482954e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45269902756802e-05</v>
+        <v>1.452699027568013e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.366196586252192e-05</v>
+        <v>1.366196586252157e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.474865109040177e-05</v>
+        <v>1.474865109040163e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.357674026872551e-05</v>
+        <v>1.357674026872542e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37072725508822e-05</v>
+        <v>1.370727255088208e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.427465229404325e-05</v>
+        <v>1.427465229404318e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.375502003558727e-05</v>
+        <v>1.375502003558723e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.374808629947958e-05</v>
+        <v>1.374808629947957e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5925,43 +5925,43 @@
         <v>1.239131066759556e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.212005233801626e-05</v>
+        <v>1.212005233801625e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.263830307590612e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.224961255033059e-05</v>
+        <v>1.224961255033057e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.219226893919808e-05</v>
+        <v>1.219226893919811e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.253904260609127e-05</v>
+        <v>1.253904260609126e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.23865425971914e-05</v>
+        <v>1.238654259719138e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.248627047627407e-05</v>
+        <v>1.248627047627406e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.240150683969126e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.263613103030509e-05</v>
+        <v>1.263613103030505e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.257501085851303e-05</v>
+        <v>1.257501085851304e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.256875350350001e-05</v>
+        <v>1.256875350349999e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.224769634903824e-05</v>
+        <v>1.224769634903825e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.213582545791475e-05</v>
+        <v>1.213582545791477e-05</v>
       </c>
       <c r="P4" t="n">
         <v>1.216438690213608e-05</v>
@@ -5970,37 +5970,37 @@
         <v>1.233777384975782e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.239983404140975e-05</v>
+        <v>1.239983404140974e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.230744708751539e-05</v>
+        <v>1.230744708751537e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.230429304009129e-05</v>
+        <v>1.23042930400913e-05</v>
       </c>
       <c r="U4" t="n">
         <v>1.222359679073386e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.227347769149789e-05</v>
+        <v>1.227347769149797e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.248913209631666e-05</v>
+        <v>1.248913209631663e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.219130462383606e-05</v>
+        <v>1.219130462383608e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.234105561447352e-05</v>
+        <v>1.234105561447351e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.235874215548855e-05</v>
+        <v>1.235874215548852e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.24852294251725e-05</v>
+        <v>1.248522942517247e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.246330268270739e-05</v>
+        <v>1.246330268270741e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.611536385633673e-05</v>
+        <v>4.611536385633677e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.674265026588306e-05</v>
+        <v>4.674265026588307e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.626843965582347e-05</v>
+        <v>5.626843965582342e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.239811825900944e-05</v>
+        <v>2.239811825900947e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.679682027879524e-05</v>
+        <v>4.679682027879529e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.622288570189376e-05</v>
+        <v>5.622288570189371e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.989474877775664e-05</v>
+        <v>4.989474877775659e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.160197927883605e-05</v>
+        <v>5.160197927883647e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.193836073017689e-05</v>
+        <v>5.193836073017684e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.89130706332379e-05</v>
+        <v>5.891307063323789e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>6.158698273811578e-05</v>
+        <v>6.158698273811584e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.215726423871071e-05</v>
+        <v>6.215726423871074e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.365901368684113e-05</v>
+        <v>5.365901368684117e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.499677755395171e-05</v>
+        <v>4.499677755395168e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.244870451476835e-05</v>
+        <v>4.244870451476836e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.048535347960449e-05</v>
+        <v>5.048535347960445e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.968359800537415e-05</v>
+        <v>4.968359800537417e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.996822213465764e-05</v>
+        <v>4.996822213465761e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>5.1028424176506e-05</v>
+        <v>5.102842417650595e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.370262913299318e-05</v>
+        <v>5.370262913299315e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.031531663117771e-05</v>
+        <v>5.031531663117918e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.137625470914827e-05</v>
+        <v>5.137625470914836e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.66566406563045e-05</v>
+        <v>4.665664065630461e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.694067887571151e-05</v>
+        <v>4.694067887571206e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.813499859735689e-05</v>
+        <v>4.813499859735693e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.800116517514149e-05</v>
+        <v>4.800116517514144e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.320771791768173e-05</v>
+        <v>5.320771791768172e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6098,70 +6098,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.363176448982885e-05</v>
+        <v>1.363176448982887e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.631601437402818e-05</v>
+        <v>1.336050616024957e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.387875689813945e-05</v>
+        <v>1.387875689813944e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.644557458634251e-05</v>
+        <v>1.644557458634248e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.638823097521002e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.673500464210319e-05</v>
+        <v>1.377949642832458e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.658250463320331e-05</v>
+        <v>1.362699641942469e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.372672429850738e-05</v>
+        <v>1.372672429850739e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.659746887570319e-05</v>
+        <v>1.364196066192457e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.387658485253835e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.677097289452495e-05</v>
+        <v>1.677097289452494e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.38092073257333e-05</v>
+        <v>1.676471553951191e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.349030146576407e-05</v>
+        <v>1.349030146576408e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.337843057464058e-05</v>
+        <v>1.33784305746406e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.636814245435142e-05</v>
+        <v>1.331845103770265e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.653373588576977e-05</v>
+        <v>1.357822767199115e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65957960774217e-05</v>
+        <v>1.659579607742167e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.650340912352732e-05</v>
+        <v>1.354790090974869e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.650025507610322e-05</v>
+        <v>1.65002550761032e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.353176561742361e-05</v>
+        <v>1.35317656174236e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.351393151373131e-05</v>
+        <v>1.646943972750989e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.381046757571519e-05</v>
+        <v>1.381046757571525e-05</v>
       </c>
       <c r="X6" t="n">
         <v>1.34317584460694e-05</v>
@@ -6170,13 +6170,13 @@
         <v>1.371790888669884e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.655470419150047e-05</v>
+        <v>1.655470419150045e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.372568324740579e-05</v>
+        <v>1.668119146118439e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.370656051495171e-05</v>
+        <v>1.370656051495169e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6186,16 +6186,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.036006296249543e-05</v>
+        <v>2.036006296249538e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.008880463291609e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.060705537080597e-05</v>
+        <v>2.060705537080594e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.021836484523043e-05</v>
+        <v>2.021836484523039e-05</v>
       </c>
       <c r="F7" t="n">
         <v>2.016102123409794e-05</v>
@@ -6204,64 +6204,64 @@
         <v>2.050779490099109e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.035529489209122e-05</v>
+        <v>2.03552948920912e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.045502277117393e-05</v>
+        <v>2.045502277117392e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.037025913459108e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.06048833252049e-05</v>
+        <v>2.060488332520489e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.054376315341287e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.053750579839983e-05</v>
+        <v>2.053750579839981e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02164486439381e-05</v>
+        <v>2.021644864393808e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.01045448748723e-05</v>
+        <v>2.010454487487226e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.013310631909358e-05</v>
+        <v>2.013310631909355e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.030652614465766e-05</v>
+        <v>2.030652614465764e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.036858633630958e-05</v>
+        <v>2.036858633630957e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.027619938241522e-05</v>
+        <v>2.02761993824152e-05</v>
       </c>
       <c r="T7" t="n">
         <v>2.027304533499113e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.026246563650611e-05</v>
+        <v>2.026246563650607e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.024222998639784e-05</v>
+        <v>2.024222998639778e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.045788439121651e-05</v>
+        <v>2.045788439121647e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.016005691873592e-05</v>
+        <v>2.01600569187359e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.03775229138298e-05</v>
+        <v>2.037752291382979e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.032749445038837e-05</v>
+        <v>2.032749445038834e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.045398172007233e-05</v>
+        <v>2.04539817200723e-05</v>
       </c>
       <c r="AB7" t="n">
         <v>2.043205497760727e-05</v>
@@ -6274,82 +6274,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.184926123297413e-05</v>
+        <v>5.184926123297416e-05</v>
       </c>
       <c r="C8" t="n">
         <v>7.683995572596561e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.735820646385544e-05</v>
+        <v>7.735820646385549e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.696951593827988e-05</v>
+        <v>6.351827124035019e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.558573651219605e-05</v>
+        <v>5.558573651219603e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.725894599404055e-05</v>
+        <v>8.249717647844342e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.710644598514076e-05</v>
+        <v>7.710644598514075e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.720617386422341e-05</v>
+        <v>7.72061738642234e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.712141022764058e-05</v>
+        <v>7.712141022764059e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.735603441825439e-05</v>
+        <v>7.735603441825442e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.729491424646236e-05</v>
+        <v>7.729491424646232e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.728865689144931e-05</v>
+        <v>7.72886568914493e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.738536006802443e-05</v>
+        <v>5.738536006802438e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.265485867004617e-05</v>
+        <v>6.26548586700462e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.136431641912411e-05</v>
+        <v>6.136431641912398e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.683117410838114e-05</v>
+        <v>4.683117410838117e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.711973742935904e-05</v>
+        <v>7.711973742935912e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.702735047546468e-05</v>
+        <v>7.702735047546467e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.702419642804061e-05</v>
+        <v>7.702419642804062e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.146809626426354e-05</v>
+        <v>6.468307979977423e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.699338107944719e-05</v>
+        <v>7.009098935723703e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.721400018637173e-05</v>
+        <v>7.721400018637183e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.900001305768692e-05</v>
+        <v>4.900001305768693e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001022492861567637</v>
+        <v>0.0001022492861567638</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.707864554343785e-05</v>
+        <v>5.134743897731262e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.720513281312183e-05</v>
+        <v>7.720513281312176e-05</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001035714281681611</v>
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.475501810218044e-05</v>
+        <v>3.475501810218042e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.07516146371612e-05</v>
+        <v>4.075161463716116e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.126986537505106e-05</v>
+        <v>4.126986537505102e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.088117484947553e-05</v>
+        <v>3.943457970137688e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.082383123834306e-05</v>
+        <v>2.637471479572581e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.117060490523621e-05</v>
+        <v>4.117060515033077e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.101810489633631e-05</v>
+        <v>4.101810489633629e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.111783277541904e-05</v>
+        <v>4.111783277541897e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.103306913883617e-05</v>
+        <v>4.103306913883615e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.126769332944998e-05</v>
+        <v>4.126769332944992e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.120657315765798e-05</v>
+        <v>4.120657315765794e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.120031580264492e-05</v>
+        <v>4.120031580264485e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.087925864818317e-05</v>
+        <v>4.087925864818315e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.28445469784362e-05</v>
+        <v>4.284454697843612e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.332485486195355e-05</v>
+        <v>4.332485486195346e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.096933639399746e-05</v>
+        <v>4.096933639399735e-05</v>
       </c>
       <c r="R9" t="n">
         <v>4.103139634055466e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.093900938666033e-05</v>
+        <v>4.093900938666025e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.093585533923621e-05</v>
+        <v>4.093585533923617e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.092287409433525e-05</v>
+        <v>4.092287409433517e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.090503999064293e-05</v>
+        <v>4.81380101600236e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.112069439546157e-05</v>
+        <v>4.112069439546153e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.0822866922981e-05</v>
+        <v>4.082286692298091e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.104033291807491e-05</v>
+        <v>4.104033291807482e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.099030445463348e-05</v>
+        <v>3.721134542802883e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.111679172431736e-05</v>
+        <v>4.111679172431735e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.109486498185238e-05</v>
+        <v>4.109486498185227e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.357393314974473e-05</v>
+        <v>1.357393314974478e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.363422398449052e-05</v>
+        <v>1.363422398449054e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.358559339309932e-05</v>
+        <v>1.358559339309936e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.35645653523822e-05</v>
+        <v>1.356456535238226e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.355074859698157e-05</v>
+        <v>1.355074859698161e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.362626029307605e-05</v>
+        <v>1.36262602930761e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.357251406950209e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.358087183481084e-05</v>
+        <v>1.358087183481089e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.358624971494197e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.359603543028918e-05</v>
+        <v>1.359603543028923e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.357967421237187e-05</v>
+        <v>1.35796742123719e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.35932666984997e-05</v>
+        <v>1.359326669849969e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.355789563110001e-05</v>
+        <v>1.355789563110006e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.514485236598453e-05</v>
+        <v>1.514485236598455e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.354943930010236e-05</v>
+        <v>1.354943930010243e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.356608634223104e-05</v>
+        <v>1.356608634223108e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35732449564065e-05</v>
+        <v>1.357324495640651e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.355685716380988e-05</v>
+        <v>1.355685716380997e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.356570844126088e-05</v>
+        <v>1.356570844126089e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.410573078852262e-05</v>
+        <v>1.410573078852263e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.356867954197615e-05</v>
+        <v>1.356867954197616e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.425168573086546e-05</v>
+        <v>1.425168573086539e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.355111183684487e-05</v>
+        <v>1.355111183684484e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.358966122598645e-05</v>
+        <v>1.358966122598647e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.393369658880536e-05</v>
+        <v>1.393369658880539e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.358758323884073e-05</v>
+        <v>1.358758323884072e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.357592142669046e-05</v>
+        <v>1.357592142669048e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.380967772399955e-05</v>
+        <v>1.38096777239995e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.375527288529814e-05</v>
+        <v>1.375527288529815e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.390077130194979e-05</v>
+        <v>1.390077130194973e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.370805605265789e-05</v>
+        <v>1.370805605265786e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.364978924484498e-05</v>
+        <v>1.364978924484497e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.418816621526175e-05</v>
+        <v>1.418816621526179e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.380787641856204e-05</v>
+        <v>1.380787641856199e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.386444924874861e-05</v>
+        <v>1.38644492487486e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.390334359081581e-05</v>
+        <v>1.390334359081576e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.397797688173564e-05</v>
+        <v>1.397797688173563e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38660905928813e-05</v>
+        <v>1.386609059288132e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.397951799475699e-05</v>
+        <v>1.3979517994757e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.369669025660381e-05</v>
+        <v>1.369669025660379e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.62818914244859e-05</v>
+        <v>1.628189142448592e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.363782708569294e-05</v>
+        <v>1.363782708569293e-05</v>
       </c>
       <c r="Q3" t="n">
         <v>1.375923413884614e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.380933385784562e-05</v>
+        <v>1.380933385784559e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.369244510718006e-05</v>
+        <v>1.369244510718009e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.375773519873237e-05</v>
+        <v>1.375773519873236e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.462022809620445e-05</v>
+        <v>1.462022809620442e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.377843262782687e-05</v>
+        <v>1.377843262782698e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.526570402565834e-05</v>
+        <v>1.526570402565833e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.365517216574363e-05</v>
+        <v>1.365517216574366e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.392078922018612e-05</v>
+        <v>1.392078922018613e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.436476795633188e-05</v>
+        <v>1.436476795633191e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.390647541479377e-05</v>
+        <v>1.390647541479375e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.385646130747712e-05</v>
+        <v>1.385646130747714e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.257270867509856e-05</v>
+        <v>1.257270867509863e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.225987629016134e-05</v>
+        <v>1.225987629016139e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.270441648776559e-05</v>
+        <v>1.270441648776564e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.246689509448931e-05</v>
+        <v>1.246689509448935e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.231082848621758e-05</v>
+        <v>1.231082848621762e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.316376783070119e-05</v>
+        <v>1.316376783070133e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.255667951094862e-05</v>
+        <v>1.255667951094865e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.265108431487329e-05</v>
+        <v>1.265108431487335e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.27001530462391e-05</v>
+        <v>1.270015304623917e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.282236410139968e-05</v>
+        <v>1.282236410139972e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.263755661849146e-05</v>
+        <v>1.263755661849151e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.282450011526269e-05</v>
+        <v>1.282450011526275e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.23915575243837e-05</v>
+        <v>1.239155752438377e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.231419891411398e-05</v>
+        <v>1.231419891411404e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.229603937566084e-05</v>
+        <v>1.229603937566087e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.248407537452192e-05</v>
+        <v>1.248407537452194e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.256493521475867e-05</v>
+        <v>1.256493521475869e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.237982755862331e-05</v>
+        <v>1.237982755862336e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.247980680922035e-05</v>
+        <v>1.24798068092204e-05</v>
       </c>
       <c r="U4" t="n">
         <v>1.233349820698223e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.246399599488122e-05</v>
+        <v>1.246399599488129e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.326115162219415e-05</v>
+        <v>1.326115162219418e-05</v>
       </c>
       <c r="X4" t="n">
         <v>1.231493144757124e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.267514880046263e-05</v>
+        <v>1.267514880046268e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.248114708982131e-05</v>
+        <v>1.248114708982134e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.272689271078866e-05</v>
+        <v>1.272689271078869e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.264014784157255e-05</v>
+        <v>1.264014784157259e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.844161429873776e-05</v>
+        <v>4.844161429873779e-05</v>
       </c>
       <c r="C5" t="n">
         <v>4.710567977333763e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.485150241719826e-05</v>
+        <v>5.485150241719822e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.855496048526349e-05</v>
+        <v>2.855496048526344e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.670195470152896e-05</v>
+        <v>4.67019547015289e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>6.15006177003832e-05</v>
+        <v>6.150061770038329e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.247323475238964e-05</v>
+        <v>5.247323475238958e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.254838419459176e-05</v>
+        <v>5.254838419459124e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.38764993879169e-05</v>
+        <v>5.387649938791709e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.832656700334211e-05</v>
+        <v>5.832656700334205e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.758923039286664e-05</v>
+        <v>5.758923039286654e-05</v>
       </c>
       <c r="M5" t="n">
         <v>5.999639384547919e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.195057358908893e-05</v>
+        <v>5.195057358908892e-05</v>
       </c>
       <c r="O5" t="n">
         <v>4.629776099156378e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.508385816691618e-05</v>
+        <v>4.508385816691617e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.975504331959273e-05</v>
+        <v>4.975504331959272e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>5.067127658662867e-05</v>
+        <v>5.067127658662873e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.74345207418956e-05</v>
+        <v>4.743452074189562e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>5.030046171612591e-05</v>
+        <v>5.030046171612604e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.196773000274612e-05</v>
+        <v>5.196773000274607e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.058167324520843e-05</v>
+        <v>5.058167324520853e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>6.211293502448002e-05</v>
+        <v>6.211293502447988e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.822060751949034e-05</v>
+        <v>4.822060751948883e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.099268077705634e-05</v>
+        <v>5.099268077705628e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.978000962683647e-05</v>
+        <v>4.97800096268365e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.084540932374394e-05</v>
+        <v>5.084540932374396e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.386012369410272e-05</v>
+        <v>5.386012369410276e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6958,55 +6958,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.681710652349109e-05</v>
+        <v>1.681710652349111e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.650427413855388e-05</v>
+        <v>1.650427413855386e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.694881433615814e-05</v>
+        <v>1.69488143361581e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.671129294288184e-05</v>
+        <v>1.671129294288182e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.356306293934632e-05</v>
+        <v>1.655522633461007e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.441600228382995e-05</v>
+        <v>1.740816567909384e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.380891396407736e-05</v>
+        <v>1.380891396407737e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.689548216326586e-05</v>
+        <v>1.390331876800207e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.694455089463166e-05</v>
+        <v>1.395238749936786e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.407459855452841e-05</v>
+        <v>1.706676194979217e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.688195446688401e-05</v>
+        <v>1.688195446688399e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.706889796365524e-05</v>
+        <v>1.706889796365523e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.364574465342471e-05</v>
+        <v>1.364574465342472e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.356838604315498e-05</v>
+        <v>1.657156788218267e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.655342207246923e-05</v>
+        <v>1.655342207246924e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.672847322291444e-05</v>
+        <v>1.67284732229144e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.680933306315119e-05</v>
+        <v>1.381716966788743e-05</v>
       </c>
       <c r="S6" t="n">
         <v>1.363206201175207e-05</v>
@@ -7015,28 +7015,28 @@
         <v>1.672420465761286e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.665311178643344e-05</v>
+        <v>1.665311178643346e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.371623044801e-05</v>
+        <v>1.371623044800998e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.751844721293686e-05</v>
+        <v>1.751844721293688e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.655932929596384e-05</v>
+        <v>1.356716590069998e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.407164874293869e-05</v>
+        <v>1.407164874293878e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.672554493821384e-05</v>
+        <v>1.373338154295005e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.697129055918115e-05</v>
+        <v>1.397912716391741e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.389497071308406e-05</v>
+        <v>1.389497071308407e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7049,82 +7049,82 @@
         <v>2.055900302558474e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.024617064064755e-05</v>
+        <v>2.02461706406475e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.069071083825179e-05</v>
+        <v>2.069071083825175e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.04531894449755e-05</v>
+        <v>2.045318944497549e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.029712283670375e-05</v>
+        <v>2.029712283670372e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.11500621811874e-05</v>
+        <v>2.115006218118756e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.05429738614348e-05</v>
+        <v>2.054297386143478e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.063737866535948e-05</v>
+        <v>2.063737866535947e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.06864473967253e-05</v>
+        <v>2.068644739672522e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.080865845188589e-05</v>
+        <v>2.080865845188582e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.06238509689777e-05</v>
+        <v>2.062385096897762e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.08107944657489e-05</v>
+        <v>2.081079446574888e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.037785187486995e-05</v>
+        <v>2.037785187486987e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.030046044782571e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.028230090937253e-05</v>
+        <v>2.028230090937251e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04703697250081e-05</v>
+        <v>2.047036972500808e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.055122956524483e-05</v>
+        <v>2.055122956524479e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.03661219091095e-05</v>
+        <v>2.036612190910949e-05</v>
       </c>
       <c r="T7" t="n">
         <v>2.04661011597065e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.039776686201752e-05</v>
+        <v>2.03977668620175e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.045029034536742e-05</v>
+        <v>2.04502903453674e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.124744597268033e-05</v>
+        <v>2.124744597268026e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.030122579805726e-05</v>
+        <v>2.030122579805737e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.073665888200751e-05</v>
+        <v>2.073665888200757e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.046744144030749e-05</v>
+        <v>2.046744144030746e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.071318706127486e-05</v>
+        <v>2.071318706127484e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.062644219205873e-05</v>
+        <v>2.062644219205871e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.207617828774301e-05</v>
+        <v>5.2076178287743e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.706415407930637e-05</v>
+        <v>7.706415407930634e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.750869427691052e-05</v>
+        <v>7.75086942769106e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.727117288363431e-05</v>
+        <v>6.379923885590851e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.575586831650185e-05</v>
+        <v>5.575586831650175e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.796804561984618e-05</v>
+        <v>8.32143330150015e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.736095730009369e-05</v>
+        <v>7.736095730009353e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.745536210401836e-05</v>
+        <v>7.745536210401818e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.750443083538432e-05</v>
+        <v>7.750443083538407e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.762664189054466e-05</v>
+        <v>7.762664189054464e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.744183440763648e-05</v>
+        <v>7.74418344076364e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.762877790440777e-05</v>
+        <v>7.762877790440808e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.758347624489253e-05</v>
+        <v>5.758347624489243e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.289576420028941e-05</v>
+        <v>6.289576420028942e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.155647205621908e-05</v>
+        <v>6.155647205621893e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.701535871654603e-05</v>
+        <v>4.701535871654599e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.736921300390366e-05</v>
+        <v>7.736921300390364e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.718410534776838e-05</v>
+        <v>7.718410534776821e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.728408459836534e-05</v>
+        <v>7.728408459836527e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.164622300737912e-05</v>
+        <v>6.48661682039409e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.726827378402623e-05</v>
+        <v>7.035556743330205e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.80704017495732e-05</v>
+        <v>7.807040174957301e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.916508413518037e-05</v>
+        <v>4.916508413518051e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001027143607147815</v>
+        <v>0.0001027143607147813</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.728542487896635e-05</v>
+        <v>5.151464120076547e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.753117049993362e-05</v>
+        <v>7.753117049993364e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.000103873235394381</v>
+        <v>0.0001038732353943809</v>
       </c>
     </row>
     <row r="9">
@@ -7222,37 +7222,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.396660891753885e-05</v>
+        <v>3.396660891753891e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.965774965418801e-05</v>
+        <v>3.965774965418802e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.010228985179228e-05</v>
+        <v>4.010228985179221e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.986476845851593e-05</v>
+        <v>3.847907617722475e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.970870185024409e-05</v>
+        <v>2.586790478275451e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.056164119472781e-05</v>
+        <v>4.056164148777201e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.995455287497522e-05</v>
+        <v>3.995455287497523e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.004895767889987e-05</v>
+        <v>4.004895767889995e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.009802641026577e-05</v>
+        <v>4.009802641026572e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.022023746542628e-05</v>
+        <v>4.022023746542625e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.003542998251805e-05</v>
+        <v>4.00354299825181e-05</v>
       </c>
       <c r="M9" t="n">
         <v>4.022237347928929e-05</v>
@@ -7261,46 +7261,46 @@
         <v>3.978943088841038e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.170178149925952e-05</v>
+        <v>4.170178149925948e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.211634951500741e-05</v>
+        <v>4.211634951500743e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.98819490315928e-05</v>
+        <v>3.988194903159286e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.996280857878532e-05</v>
+        <v>3.996280857878527e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.977770092264993e-05</v>
+        <v>3.977770092264989e-05</v>
       </c>
       <c r="T9" t="n">
         <v>3.987768017324695e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.980658730206754e-05</v>
+        <v>3.980658730206753e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>3.986186935890788e-05</v>
+        <v>4.679032561653527e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.065902498622072e-05</v>
+        <v>4.065902498622073e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.971280481159802e-05</v>
+        <v>3.971280481159785e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.014823789554795e-05</v>
+        <v>4.014823789554806e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.987902045384789e-05</v>
+        <v>3.625915867201663e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.01247660748153e-05</v>
+        <v>4.012476607481532e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.003802120559908e-05</v>
+        <v>4.003802120559918e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7466,82 +7466,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.342320838036893e-05</v>
+        <v>1.342320838036882e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.349476262865163e-05</v>
+        <v>1.349476262865162e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.342989962550484e-05</v>
+        <v>1.342989962550488e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3414624804832e-05</v>
+        <v>1.341462480483204e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.341386055035077e-05</v>
+        <v>1.34138605503508e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.343316671169105e-05</v>
+        <v>1.343316671169107e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341641205847543e-05</v>
+        <v>1.341641205847546e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.341687956220323e-05</v>
+        <v>1.341687956220327e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.342443664284955e-05</v>
+        <v>1.342443664284949e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.342428667842682e-05</v>
+        <v>1.342428667842685e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341687593284873e-05</v>
+        <v>1.341687593284866e-05</v>
       </c>
       <c r="M2" t="n">
         <v>1.342139140521794e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.341794199989825e-05</v>
+        <v>1.341794199989827e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.493279824398526e-05</v>
+        <v>1.493279824398525e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.341811289437708e-05</v>
+        <v>1.341811289437709e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.341958749814628e-05</v>
+        <v>1.341958749814631e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.342465105053549e-05</v>
+        <v>1.342465105053552e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.342061253961587e-05</v>
+        <v>1.342061253961583e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.34251450466589e-05</v>
+        <v>1.342514504665893e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.392724779055346e-05</v>
+        <v>1.392724779055349e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.341992239204677e-05</v>
+        <v>1.341992239204681e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.399812846041632e-05</v>
+        <v>1.399812846041629e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341903642647456e-05</v>
+        <v>1.341903642647454e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.342042617072009e-05</v>
+        <v>1.342042617072012e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.375446135548671e-05</v>
+        <v>1.375446135548663e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.342000958809158e-05</v>
+        <v>1.342000958809161e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.342366031028963e-05</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.34971202761797e-05</v>
+        <v>1.349712027617963e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.353862458529696e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.354369720051742e-05</v>
+        <v>1.354369720051737e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.339233942185649e-05</v>
+        <v>1.339233942185647e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.343378706173796e-05</v>
+        <v>1.343378706173793e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.357184358373096e-05</v>
+        <v>1.357184358373095e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.345095803774271e-05</v>
+        <v>1.34509580377428e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.345274523036976e-05</v>
+        <v>1.345274523036972e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.350799484622976e-05</v>
+        <v>1.350799484622974e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.351786952140239e-05</v>
+        <v>1.351786952140237e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.345361359916241e-05</v>
+        <v>1.345361359916252e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.351567855094373e-05</v>
+        <v>1.351567855094374e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.345765388879252e-05</v>
+        <v>1.345765388879248e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.596398361398656e-05</v>
+        <v>1.596398361398649e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.345652109485046e-05</v>
+        <v>1.345652109485041e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.347228025443584e-05</v>
+        <v>1.347228025443582e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35071617173126e-05</v>
+        <v>1.350716171731257e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.348319563368645e-05</v>
+        <v>1.348319563368644e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.351079715825947e-05</v>
+        <v>1.351079715825943e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.432515451059052e-05</v>
+        <v>1.432515451059044e-05</v>
       </c>
       <c r="V3" t="n">
         <v>1.347994788608828e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.449620594978599e-05</v>
+        <v>1.449620594978598e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.34670402848842e-05</v>
+        <v>1.346704028488417e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.347818115851644e-05</v>
+        <v>1.347818115851642e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.402238567846991e-05</v>
+        <v>1.402238567846988e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.347275808600027e-05</v>
+        <v>1.347275808600025e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.352688814368535e-05</v>
+        <v>1.352688814368534e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7642,25 +7642,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.20268299638018e-05</v>
+        <v>1.202682996380182e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.188250074354579e-05</v>
+        <v>1.188250074354578e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.210241065573835e-05</v>
+        <v>1.210241065573836e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.192987452947391e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.192124192353398e-05</v>
+        <v>1.192124192353399e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.213931389714531e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.195006238155372e-05</v>
+        <v>1.195006238155373e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.195534305122169e-05</v>
@@ -7672,7 +7672,7 @@
         <v>1.20390098364088e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.195530205599164e-05</v>
+        <v>1.195530205599162e-05</v>
       </c>
       <c r="M4" t="n">
         <v>1.203958747979804e-05</v>
@@ -7681,10 +7681,10 @@
         <v>1.196734377373222e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.196835611884422e-05</v>
+        <v>1.196835611884423e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.196927410548574e-05</v>
+        <v>1.196927410548575e-05</v>
       </c>
       <c r="Q4" t="n">
         <v>1.198593043341047e-05</v>
@@ -7693,7 +7693,7 @@
         <v>1.204312558699564e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.199750874835101e-05</v>
+        <v>1.199750874835102e-05</v>
       </c>
       <c r="T4" t="n">
         <v>1.20487055004591e-05</v>
@@ -7702,16 +7702,16 @@
         <v>1.194954103689409e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.194153587234526e-05</v>
+        <v>1.194153587234524e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.213563632524576e-05</v>
+        <v>1.213563632524577e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.197970582537218e-05</v>
+        <v>1.197970582537221e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.192501549041273e-05</v>
+        <v>1.192501549041272e-05</v>
       </c>
       <c r="Z4" t="n">
         <v>1.198338701321281e-05</v>
@@ -7720,7 +7720,7 @@
         <v>1.199069813351363e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.207465321998891e-05</v>
+        <v>1.207465321998893e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.496923441351702e-05</v>
+        <v>4.496923441351712e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.433553758443732e-05</v>
+        <v>4.433553758443731e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.574270031279614e-05</v>
+        <v>4.574270031279584e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.893257142392811e-05</v>
+        <v>1.893257142392815e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.485409006434574e-05</v>
+        <v>4.485409006434569e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.912613709025615e-05</v>
+        <v>4.912613709025591e-05</v>
       </c>
       <c r="H5" t="n">
         <v>4.482103514126929e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.405917657927723e-05</v>
+        <v>4.405917657927725e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.63926527012996e-05</v>
+        <v>4.639265270129947e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.24591959763547e-05</v>
+        <v>5.245919597635469e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.455575265263391e-05</v>
+        <v>4.455575265263377e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.268727183016976e-05</v>
+        <v>5.268727183016971e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.445012142258894e-05</v>
+        <v>4.445012142258897e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.576036913491647e-05</v>
+        <v>4.576036913491648e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.152709059836374e-05</v>
+        <v>4.152709059836344e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.475339433854802e-05</v>
+        <v>4.4753394338548e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.513554960317838e-05</v>
+        <v>4.513554960317836e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.697424565184332e-05</v>
+        <v>4.697424565184328e-05</v>
       </c>
       <c r="T5" t="n">
         <v>4.530210067513568e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.45027068212781e-05</v>
+        <v>4.450270682127814e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.771182227924706e-05</v>
+        <v>4.77118222792471e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.548378062784647e-05</v>
+        <v>4.548378062784644e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.390884044134295e-05</v>
+        <v>4.390884044134309e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.488538205407256e-05</v>
+        <v>4.488538205407259e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.391011308048385e-05</v>
+        <v>4.391011308048378e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.343389280054081e-05</v>
+        <v>4.34338928005408e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.772690711794572e-05</v>
+        <v>4.772690711794576e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7818,82 +7818,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.646206655991505e-05</v>
+        <v>1.646206655991504e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.319473834113738e-05</v>
+        <v>1.319473834113739e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.653764725185161e-05</v>
+        <v>1.653764725185159e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.636511112558715e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.635647851964723e-05</v>
+        <v>1.63564785196472e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.34515514947369e-05</v>
+        <v>1.345155149473691e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.638529897766697e-05</v>
+        <v>1.638529897766694e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.326758064881329e-05</v>
+        <v>1.326758064881331e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.646444321928988e-05</v>
+        <v>1.334144422076822e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.33512474340004e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.326753965358323e-05</v>
+        <v>1.639053865210485e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.647482407591131e-05</v>
+        <v>1.647482407591125e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.328169583086851e-05</v>
+        <v>1.328169583086853e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.328270817598053e-05</v>
+        <v>1.328270817598054e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64128304346547e-05</v>
+        <v>1.641283043465463e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.329816803100206e-05</v>
+        <v>1.64211670295237e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.647836218310889e-05</v>
+        <v>1.647836218310888e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.643274534446426e-05</v>
+        <v>1.643274534446425e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.648394209657237e-05</v>
+        <v>1.336094309805069e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.645516576853464e-05</v>
+        <v>1.645516576853461e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.325377346993686e-05</v>
+        <v>1.637677246845848e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.353289181254518e-05</v>
+        <v>1.353289181254523e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.641494242148544e-05</v>
+        <v>1.32919434229638e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.337989183757975e-05</v>
+        <v>1.337989183757976e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.329562461080442e-05</v>
+        <v>1.329562461080441e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.642593472962689e-05</v>
+        <v>1.642593472962684e-05</v>
       </c>
       <c r="AB6" t="n">
         <v>1.338947700492473e-05</v>
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.056058546392906e-05</v>
+        <v>2.05605854639291e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.041625624367304e-05</v>
+        <v>2.041625624367307e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.063616615586562e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.046363002960117e-05</v>
+        <v>2.046363002960119e-05</v>
       </c>
       <c r="F7" t="n">
         <v>2.045499742366125e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.067306939727259e-05</v>
+        <v>2.06730693972726e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.048381788168099e-05</v>
+        <v>2.048381788168101e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.048909855134896e-05</v>
+        <v>2.048909855134897e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.056296212330389e-05</v>
+        <v>2.056296212330392e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.057276533653608e-05</v>
+        <v>2.057276533653607e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.048905755611891e-05</v>
+        <v>2.048905755611889e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.05733429799253e-05</v>
+        <v>2.057334297992532e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.050109927385949e-05</v>
+        <v>2.05010992738595e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.050207973811851e-05</v>
+        <v>2.050207973811852e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.050299772476004e-05</v>
+        <v>2.050299772476001e-05</v>
       </c>
       <c r="Q7" t="n">
         <v>2.051968593353775e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.057688108712291e-05</v>
+        <v>2.057688108712292e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.053126424847827e-05</v>
+        <v>2.053126424847829e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.058246100058636e-05</v>
+        <v>2.05824610005864e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.055406038908468e-05</v>
+        <v>2.055406038908469e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.047529137247254e-05</v>
+        <v>2.047529137247252e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.066939182537302e-05</v>
+        <v>2.066939182537305e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.051346132549944e-05</v>
+        <v>2.051346132549946e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.052915912606731e-05</v>
+        <v>2.052915912606729e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.051714251334008e-05</v>
+        <v>2.05171425133401e-05</v>
       </c>
       <c r="AA7" t="n">
         <v>2.05244536336409e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.060840872011617e-05</v>
+        <v>2.060840872011619e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.430927535132975e-05</v>
+        <v>5.43092753513297e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.122670670175228e-05</v>
+        <v>8.122670670175239e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.144661661394482e-05</v>
+        <v>8.144661661394489e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.127408048768047e-05</v>
+        <v>6.686449125481987e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.841959333109602e-05</v>
+        <v>5.841959333109605e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.148351985535176e-05</v>
+        <v>8.709495220100701e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.129426833976028e-05</v>
+        <v>8.129426833976021e-05</v>
       </c>
       <c r="I8" t="n">
         <v>8.129954900942821e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.137341258138309e-05</v>
+        <v>8.137341258138318e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.138321579461529e-05</v>
+        <v>8.138321579461538e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.129950801419815e-05</v>
+        <v>8.129950801419814e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.138379343800456e-05</v>
+        <v>8.138379343800387e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.033415795702491e-05</v>
+        <v>6.033415795702489e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.609993970810428e-05</v>
+        <v>6.609993970810422e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.468777341670768e-05</v>
+        <v>6.468777341670777e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.895012221298554e-05</v>
+        <v>4.895012221298552e-05</v>
       </c>
       <c r="R8" t="n">
         <v>8.138733154520213e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.134171470655748e-05</v>
+        <v>8.134171470655751e-05</v>
       </c>
       <c r="T8" t="n">
         <v>8.139291145866558e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.471203333287549e-05</v>
+        <v>6.815596686626939e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>8.128574183055174e-05</v>
+        <v>7.388970303168516e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.148516069974733e-05</v>
+        <v>8.148516069974734e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.142416173679882e-05</v>
+        <v>5.14241617367988e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001082470425306913</v>
+        <v>0.0001082470425306914</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.132759297141932e-05</v>
+        <v>5.376314630422325e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.13349040917201e-05</v>
+        <v>8.133490409172015e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001096871309664177</v>
+        <v>0.0001096871309664178</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.735218858745582e-05</v>
+        <v>3.735218858745584e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.429701828023748e-05</v>
+        <v>4.429701828023751e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.451692819243011e-05</v>
+        <v>4.451692819243007e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.434439206616563e-05</v>
+        <v>4.270824326748979e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.43357594602257e-05</v>
+        <v>2.799331307523077e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.455383143383706e-05</v>
+        <v>4.455383164483568e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.436457991824545e-05</v>
+        <v>4.436457991824543e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.436986058791341e-05</v>
+        <v>4.436986058791339e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.444372415986834e-05</v>
+        <v>4.444372415986837e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.445352737310055e-05</v>
+        <v>4.445352737310053e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.436981959268338e-05</v>
+        <v>4.436981959268331e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.445410501648977e-05</v>
+        <v>4.445410501648973e-05</v>
       </c>
       <c r="N9" t="n">
         <v>4.438186131042392e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.67322119177764e-05</v>
+        <v>4.673221191777641e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.72440706227114e-05</v>
+        <v>4.724407062271135e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.440044818110079e-05</v>
+        <v>4.440044818110078e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.445764312368736e-05</v>
+        <v>4.445764312368732e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.441202628504273e-05</v>
+        <v>4.441202628504269e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.446322303715082e-05</v>
+        <v>4.446322303715085e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.443444670911313e-05</v>
+        <v>4.443444670911311e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.435605340903698e-05</v>
+        <v>5.253679096472948e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.455015386193748e-05</v>
+        <v>4.455015386193746e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.439422336206392e-05</v>
+        <v>4.439422336206387e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.440992116263174e-05</v>
+        <v>4.440992116263176e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.439790454990454e-05</v>
+        <v>4.012377220173424e-05</v>
       </c>
       <c r="AA9" t="n">
         <v>4.440521567020534e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.448917075668061e-05</v>
+        <v>4.448917075668062e-05</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.347394938345388e-05</v>
+        <v>1.347394938345385e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.353872986630176e-05</v>
+        <v>1.353872986630173e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.349180649494576e-05</v>
+        <v>1.349180649494574e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.346140681157863e-05</v>
+        <v>1.34614068115786e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.345846283873706e-05</v>
+        <v>1.345846283873704e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.346678785782035e-05</v>
+        <v>1.346678785782031e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.346087196125163e-05</v>
+        <v>1.346087196125158e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.348659503012132e-05</v>
+        <v>1.348659503012135e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.346880813186146e-05</v>
+        <v>1.346880813186141e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.347323569708834e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.347123424618442e-05</v>
+        <v>1.347123424618441e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.347983042260719e-05</v>
+        <v>1.347983042260722e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.346266388894357e-05</v>
+        <v>1.346266388894354e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.500623243836601e-05</v>
+        <v>1.500623243836596e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.345657932914167e-05</v>
+        <v>1.345657932914165e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.346568819602113e-05</v>
+        <v>1.346568819602116e-05</v>
       </c>
       <c r="R2" t="n">
         <v>1.347481003414942e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.346786721904749e-05</v>
+        <v>1.346786721904748e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.347408466657999e-05</v>
+        <v>1.347408466657994e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.398822205635476e-05</v>
+        <v>1.398822205635472e-05</v>
       </c>
       <c r="V2" t="n">
         <v>1.346838523368889e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.406334886799225e-05</v>
+        <v>1.406334886799217e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.346041368637432e-05</v>
+        <v>1.34604136863743e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.345716686575539e-05</v>
+        <v>1.345716686575536e-05</v>
       </c>
       <c r="Z2" t="n">
         <v>1.381951468757125e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.347667891932637e-05</v>
+        <v>1.347667891932634e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.346781770002816e-05</v>
+        <v>1.346781770002806e-05</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363789118459951e-05</v>
+        <v>1.363789118459948e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.363548135405755e-05</v>
+        <v>1.363548135405754e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.377117597848576e-05</v>
+        <v>1.377117597848574e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.350659421763844e-05</v>
+        <v>1.350659421763841e-05</v>
       </c>
       <c r="F3" t="n">
         <v>1.353448204379181e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.359751726668093e-05</v>
+        <v>1.359751726668078e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.354796458959301e-05</v>
+        <v>1.354796458959297e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.373116051319297e-05</v>
+        <v>1.373116051319299e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.360840995991811e-05</v>
+        <v>1.360840995991804e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.36505689995566e-05</v>
+        <v>1.365056899955662e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36293799190717e-05</v>
+        <v>1.362937991907174e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.371507211417805e-05</v>
+        <v>1.371507211417799e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.355722878464873e-05</v>
+        <v>1.355722878464871e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.607866981556e-05</v>
+        <v>1.607866981555991e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3514509172024e-05</v>
+        <v>1.351450917202397e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.358684091304003e-05</v>
+        <v>1.358684091304004e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.364683345814593e-05</v>
+        <v>1.364683345814595e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.360088791240241e-05</v>
+        <v>1.36008879124024e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.364257314038023e-05</v>
+        <v>1.364257314038015e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.445722038462425e-05</v>
+        <v>1.445722038462423e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.360752479511268e-05</v>
+        <v>1.360752479511265e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.463533751016969e-05</v>
+        <v>1.463533751016971e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.354590574565682e-05</v>
+        <v>1.354590574565679e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35204402645471e-05</v>
+        <v>1.352044026454708e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.418187754985473e-05</v>
+        <v>1.418187754985468e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.365726054066611e-05</v>
+        <v>1.365726054066609e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.362506478271695e-05</v>
+        <v>1.362506478271683e-05</v>
       </c>
     </row>
     <row r="4">
@@ -8505,82 +8505,82 @@
         <v>1.22739642636378e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.204873913560232e-05</v>
+        <v>1.204873913560221e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.247566855261575e-05</v>
+        <v>1.247566855261566e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.213229014443876e-05</v>
+        <v>1.213229014443865e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.209903661689881e-05</v>
+        <v>1.209903661689873e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.219307153714257e-05</v>
+        <v>1.21930715371422e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2126248763952e-05</v>
+        <v>1.212624876395191e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.241680266003153e-05</v>
+        <v>1.241680266003151e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.220444284784739e-05</v>
+        <v>1.220444284784734e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.226590284782732e-05</v>
+        <v>1.226590284782723e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.224329553915432e-05</v>
+        <v>1.22432955391542e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.237310583867002e-05</v>
+        <v>1.237310583866992e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.214648941155981e-05</v>
+        <v>1.214648941155978e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.207913092427375e-05</v>
+        <v>1.207913092427362e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.207776150956156e-05</v>
+        <v>1.207776150956161e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.218065035125095e-05</v>
+        <v>1.218065035125087e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.228368570916289e-05</v>
+        <v>1.228368570916288e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22052634187338e-05</v>
+        <v>1.220526341873382e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.227549234878057e-05</v>
+        <v>1.227549234878054e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.213257013124686e-05</v>
+        <v>1.213257013124685e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.216328047766564e-05</v>
+        <v>1.216328047766561e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.232652870386433e-05</v>
+        <v>1.232652870386434e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.212107233839586e-05</v>
+        <v>1.212107233839582e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.202116634060672e-05</v>
+        <v>1.202116634060665e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.220920266229717e-05</v>
+        <v>1.220920266229709e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.230479562696612e-05</v>
+        <v>1.230479562696608e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.224840420640572e-05</v>
+        <v>1.224840420640573e-05</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.514368990831223e-05</v>
+        <v>4.51436899083121e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.648993412955995e-05</v>
+        <v>4.64899341295598e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.173640275891766e-05</v>
+        <v>5.173640275891763e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.098651906531986e-05</v>
+        <v>2.098651906531972e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.573909957805764e-05</v>
+        <v>4.573909957805763e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.927779343149378e-05</v>
+        <v>4.927779343148993e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.429700990163457e-05</v>
+        <v>4.429700990163442e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.923336032176158e-05</v>
+        <v>4.923336032176144e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.78426390895757e-05</v>
+        <v>4.784263908957457e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.421070412061294e-05</v>
+        <v>5.421070412061285e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.023270918036008e-05</v>
+        <v>5.023270918035995e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.593204918560966e-05</v>
+        <v>5.593204918560954e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.807342985629342e-05</v>
+        <v>4.807342985629332e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.485801915439952e-05</v>
+        <v>4.485801915439938e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.197871901073952e-05</v>
+        <v>4.197871901073949e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.759255836459169e-05</v>
+        <v>4.759255836459156e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.676653787266301e-05</v>
+        <v>4.676653787266255e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.724805834166814e-05</v>
+        <v>4.724805834166806e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.709666409941892e-05</v>
+        <v>4.709666409941847e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.81227422412674e-05</v>
+        <v>4.812274224126733e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.882718241552749e-05</v>
+        <v>4.882718241552742e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.555685033373395e-05</v>
+        <v>4.555685033373388e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.483348587338059e-05</v>
+        <v>4.483348587338047e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.299667471814276e-05</v>
+        <v>4.29966747181418e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.660142337534999e-05</v>
+        <v>4.660142337534981e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.563122303847536e-05</v>
+        <v>4.563122303847509e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.841898694395556e-05</v>
+        <v>4.841898694395551e-05</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.64457606280055e-05</v>
+        <v>1.351187794746342e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.622053549996996e-05</v>
+        <v>1.622053549996982e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.371358223644145e-05</v>
+        <v>1.371358223644125e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.33702038282644e-05</v>
+        <v>1.630408650880622e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.333695030072431e-05</v>
+        <v>1.627083298126632e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.636486790151009e-05</v>
+        <v>1.343098522096782e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.336416244777757e-05</v>
+        <v>1.629804512831952e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.365471634385718e-05</v>
+        <v>1.658859902439911e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.637623921221508e-05</v>
+        <v>1.344235653167292e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.350381653165278e-05</v>
+        <v>1.643769921219482e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.641509190352197e-05</v>
+        <v>1.348120922297982e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.36110195224957e-05</v>
+        <v>1.65449022030375e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.338640124736735e-05</v>
+        <v>1.338640124736732e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.625559335933044e-05</v>
+        <v>1.331904276008116e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.322980403731006e-05</v>
+        <v>1.322980403730988e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.341856403507665e-05</v>
+        <v>1.635244671561849e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.645548207353066e-05</v>
+        <v>1.645548207353048e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.344317710255955e-05</v>
+        <v>1.344317710255941e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.351340603260635e-05</v>
+        <v>1.351340603260614e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.636759816090156e-05</v>
+        <v>1.343371548035944e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.633507684203329e-05</v>
+        <v>1.633507684203321e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.364447864296107e-05</v>
+        <v>1.364447864296109e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.62928687027636e-05</v>
+        <v>1.335898602222143e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33906924928731e-05</v>
+        <v>1.3390692492873e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.344711634612287e-05</v>
+        <v>1.344711634612271e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.647659199133376e-05</v>
+        <v>1.647659199133369e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.348858064186002e-05</v>
+        <v>1.34885806418601e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.023094878278706e-05</v>
+        <v>2.023094878278699e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.000572365475151e-05</v>
+        <v>2.000572365475144e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.043265307176495e-05</v>
+        <v>2.043265307176487e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.008927466358794e-05</v>
+        <v>2.008927466358787e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.005602113604814e-05</v>
+        <v>2.005602113604794e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.015005605629177e-05</v>
+        <v>2.015005605629131e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.008323328310117e-05</v>
+        <v>2.008323328310115e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.037378717918074e-05</v>
+        <v>2.037378717918073e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.016142736699667e-05</v>
+        <v>2.016142736699653e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.02228873669765e-05</v>
+        <v>2.022288736697646e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.020028005830354e-05</v>
+        <v>2.020028005830343e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.03300903578192e-05</v>
+        <v>2.033009035781914e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.010347393070908e-05</v>
+        <v>2.010347393070899e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.003608287586408e-05</v>
+        <v>2.003608287586403e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.003471346115206e-05</v>
+        <v>2.003471346115201e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.013763487040026e-05</v>
+        <v>2.01376348704001e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.024067022831216e-05</v>
+        <v>2.02406702283121e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.016224793788303e-05</v>
+        <v>2.016224793788306e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.023247686792977e-05</v>
+        <v>2.023247686792978e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.015422987931069e-05</v>
+        <v>2.015422987931067e-05</v>
       </c>
       <c r="V7" t="n">
         <v>2.012026499681482e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.028351322301367e-05</v>
+        <v>2.028351322301353e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.007805685754524e-05</v>
+        <v>2.007805685754503e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.004138252504296e-05</v>
+        <v>2.004138252504283e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.01661871814464e-05</v>
+        <v>2.016618718144631e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.026178014611524e-05</v>
+        <v>2.026178014611528e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.020538872555504e-05</v>
+        <v>2.020538872555494e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.170814232023925e-05</v>
+        <v>5.170814232023923e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.672374981061902e-05</v>
+        <v>7.672374981061876e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.715067922763252e-05</v>
+        <v>7.715067922763221e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.680730081945554e-05</v>
+        <v>6.336730200722323e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.546544140015329e-05</v>
+        <v>5.546544140015312e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.686808221215909e-05</v>
+        <v>8.210193328464735e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.680125943896864e-05</v>
+        <v>7.680125943896856e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.709181333504832e-05</v>
+        <v>7.70918133350481e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.687945352286417e-05</v>
+        <v>7.687945352286384e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.694091352284398e-05</v>
+        <v>7.694091352284384e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.691830621417102e-05</v>
+        <v>7.691830621417074e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.704811651368677e-05</v>
+        <v>7.704811651368614e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.725563210917645e-05</v>
+        <v>5.725563210917631e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.256514403206089e-05</v>
+        <v>6.256514403206082e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.124577375615393e-05</v>
+        <v>6.124577375615361e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.665442870324814e-05</v>
+        <v>4.665442870324802e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.695869638417974e-05</v>
+        <v>7.695869638417948e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.688027409375064e-05</v>
+        <v>7.68802740937503e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.695050302379743e-05</v>
+        <v>7.695050302379712e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.133999248559373e-05</v>
+        <v>6.45522429242843e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.68382911526823e-05</v>
+        <v>6.994085277546543e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.700649993029978e-05</v>
+        <v>7.700649993029958e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.890822315696657e-05</v>
+        <v>4.890822315696644e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001018577510281603</v>
+        <v>0.0001018577510281604</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.688421333731396e-05</v>
+        <v>5.117451929397532e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.697980630198283e-05</v>
+        <v>7.697980630198267e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001032895751596803</v>
+        <v>0.00010328957515968</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.457050194495376e-05</v>
+        <v>3.457050194495364e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.05919373527294e-05</v>
+        <v>4.059193735272913e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.10188667697428e-05</v>
+        <v>4.10188667697426e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.067548836156577e-05</v>
+        <v>3.923378474461947e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.064223483402574e-05</v>
+        <v>2.624197716045625e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.073626975426948e-05</v>
+        <v>4.073626995584766e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.066944698107899e-05</v>
+        <v>4.066944698107885e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.096000087715866e-05</v>
+        <v>4.096000087715837e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.074764106497444e-05</v>
+        <v>4.074764106497429e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.080910106495422e-05</v>
+        <v>4.080910106495411e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.078649375628136e-05</v>
+        <v>4.078649375628112e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.091630405579707e-05</v>
+        <v>4.091630405579684e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.068968762868686e-05</v>
+        <v>4.068968762868665e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.269246453204411e-05</v>
+        <v>4.269246453204405e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.314131400341649e-05</v>
+        <v>4.314131400341637e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.07238487699566e-05</v>
+        <v>4.072384876995643e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.082688392629013e-05</v>
+        <v>4.082688392628982e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.074846163586096e-05</v>
+        <v>4.074846163586076e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.081869056590757e-05</v>
+        <v>4.081869056590746e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.073900001366093e-05</v>
+        <v>4.073900001366074e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.070647869479261e-05</v>
+        <v>4.791499103661173e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.086972692099137e-05</v>
+        <v>4.086972692099124e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.066427055552287e-05</v>
+        <v>4.06642705555227e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.062759622302065e-05</v>
+        <v>4.062759622302056e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.075240087942414e-05</v>
+        <v>3.698622013110208e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.084799384409326e-05</v>
+        <v>4.084799384409299e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.07916024235329e-05</v>
+        <v>4.079160242353262e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.339947445855927e-05</v>
+        <v>1.339247146463488e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.347624260177692e-05</v>
+        <v>1.346629612651376e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.339376290868229e-05</v>
+        <v>1.338582815276488e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.339806014586995e-05</v>
+        <v>1.338875556989311e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.339390051506753e-05</v>
+        <v>1.338504651533894e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.341293100685658e-05</v>
+        <v>1.340329471018692e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.339769198844369e-05</v>
+        <v>1.338881494472772e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.339678957862237e-05</v>
+        <v>1.338792459422489e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.340605272930051e-05</v>
+        <v>1.339693742835759e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.340131014157389e-05</v>
+        <v>1.339275637780558e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.339564327848829e-05</v>
+        <v>1.338950447469479e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.340497240585475e-05</v>
+        <v>1.339529725097015e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.339819394463007e-05</v>
+        <v>1.338970309543942e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.49009252917546e-05</v>
+        <v>1.488069660071456e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.340218919900301e-05</v>
+        <v>1.339285542876507e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.339670311663603e-05</v>
+        <v>1.338799460497308e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.339358384833342e-05</v>
+        <v>1.338487208650801e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.340415418060243e-05</v>
+        <v>1.339373781704932e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.339623385316371e-05</v>
+        <v>1.338749309009191e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.391049529833901e-05</v>
+        <v>1.389336015294617e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.340513106116168e-05</v>
+        <v>1.339661020542037e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.397633416144387e-05</v>
+        <v>1.395824088291372e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.340041458203633e-05</v>
+        <v>1.339172613075451e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.340672301733825e-05</v>
+        <v>1.339825956982869e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.373800500168552e-05</v>
+        <v>1.37284278367086e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.340124256540722e-05</v>
+        <v>1.339257163770348e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.340562099509059e-05</v>
+        <v>1.33982442063629e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.342382107962483e-05</v>
+        <v>1.342731752308024e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.350076545987309e-05</v>
+        <v>1.349066022625944e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3382476859949e-05</v>
+        <v>1.337938465845134e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.337079960298212e-05</v>
+        <v>1.335791683007493e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.338537132366486e-05</v>
+        <v>1.337569621742637e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.351719344128077e-05</v>
+        <v>1.35019605728499e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.341345386073141e-05</v>
+        <v>1.34036115474492e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.340455977095895e-05</v>
+        <v>1.339480715917314e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3468860090003e-05</v>
+        <v>1.345733298978935e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.343623222853114e-05</v>
+        <v>1.342870852622612e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.339403022223046e-05</v>
+        <v>1.34037376026027e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.348326783634442e-05</v>
+        <v>1.346773470337447e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.341372397830272e-05</v>
+        <v>1.340664927074842e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.592834846121469e-05</v>
+        <v>1.590260584102356e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.343957680445504e-05</v>
+        <v>1.34265006609645e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.340355378038005e-05</v>
+        <v>1.339492327628631e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.338205916818813e-05</v>
+        <v>1.337340366123891e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.34560783950949e-05</v>
+        <v>1.343529019002103e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34003062476069e-05</v>
+        <v>1.339144389931369e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.431007611617345e-05</v>
+        <v>1.42889110265661e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.346593140455419e-05</v>
+        <v>1.345863773519898e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44536438879959e-05</v>
+        <v>1.442913119577872e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.34306543306145e-05</v>
+        <v>1.342216700458733e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.347554210612817e-05</v>
+        <v>1.346866198226708e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.400595422210828e-05</v>
+        <v>1.39922899404135e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.34345239638217e-05</v>
+        <v>1.342616262618322e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.349474387747033e-05</v>
+        <v>1.349549844215407e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.189394505064471e-05</v>
+        <v>1.162121861049681e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.181184615389182e-05</v>
+        <v>1.152103331403813e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.182943046734119e-05</v>
+        <v>1.154617934685017e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.187796973820228e-05</v>
+        <v>1.157924586999173e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.183098479476465e-05</v>
+        <v>1.153735039255391e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.204594295398033e-05</v>
+        <v>1.174347214794563e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.187381123071237e-05</v>
+        <v>1.157991653606277e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.186361809665077e-05</v>
+        <v>1.156985961755149e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.195678163122557e-05</v>
+        <v>1.166019751268631e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.191467993475041e-05</v>
+        <v>1.162443683582592e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.185067010931282e-05</v>
+        <v>1.158770509424005e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.198870050163128e-05</v>
+        <v>1.168583346696136e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.187948105674847e-05</v>
+        <v>4.336637662839929e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.194257016892039e-05</v>
+        <v>1.165451826365157e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.192460929279907e-05</v>
+        <v>1.162555566197918e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.186264146874069e-05</v>
+        <v>1.15706504211584e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.182740789832899e-05</v>
+        <v>1.153538013866673e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.194680466389987e-05</v>
+        <v>1.163552264356882e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.185734092194914e-05</v>
+        <v>1.156498557986813e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19075574360442e-05</v>
+        <v>1.161552370206846e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19098680471417e-05</v>
+        <v>1.162000962860252e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.205734038736898e-05</v>
+        <v>1.176454276599692e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.190456417779559e-05</v>
+        <v>1.161279972144692e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.189986517120434e-05</v>
+        <v>1.160776668047006e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.194698417661483e-05</v>
+        <v>1.164755170453931e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.191391663086111e-05</v>
+        <v>1.162235011138807e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.200573043879137e-05</v>
+        <v>1.172847104525062e-05</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.448260456499701e-05</v>
+        <v>4.453710201292045e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.305888056752315e-05</v>
+        <v>4.277693576808562e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.283833812004164e-05</v>
+        <v>4.271737639525012e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.864697484381256e-05</v>
+        <v>1.820604650088142e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.400624959198824e-05</v>
+        <v>4.366298693236301e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.595797202012332e-05</v>
+        <v>4.545193698689379e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.547646543410492e-05</v>
+        <v>4.512633195797068e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.381293335149785e-05</v>
+        <v>4.346770255627737e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.483200426511687e-05</v>
+        <v>4.443698865028663e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.448993306229775e-05</v>
+        <v>4.422007828678785e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.215644906638234e-05</v>
+        <v>4.243317802511644e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.785660446980675e-05</v>
+        <v>4.731517445871703e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.572549024355334e-05</v>
+        <v>4.336637662839929e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.694173712983835e-05</v>
+        <v>4.670910951550492e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.29488599132636e-05</v>
+        <v>4.251020034927094e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.356211936068255e-05</v>
+        <v>4.325566297427137e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.330890967561968e-05</v>
+        <v>4.300064042251035e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.486828021377801e-05</v>
+        <v>4.419196200484582e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.351577795769485e-05</v>
+        <v>4.32009962951304e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.582952230819948e-05</v>
+        <v>4.557984069451741e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.675481690281392e-05</v>
+        <v>4.648958790440015e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.673102530119865e-05</v>
+        <v>4.640883270315522e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.476987861196611e-05</v>
+        <v>4.446798892669562e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.612409736332307e-05</v>
+        <v>4.587418429683656e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.410324463315552e-05</v>
+        <v>4.365555216518541e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.374590670820211e-05</v>
+        <v>4.344855088076053e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.913550039930715e-05</v>
+        <v>4.915503477661031e-05</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.661636387214863e-05</v>
+        <v>1.302253999556927e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.653426497539577e-05</v>
+        <v>1.623971253512984e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.322707292881377e-05</v>
+        <v>1.62648585679419e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.327561219967486e-05</v>
+        <v>1.629792509108343e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.655340361626858e-05</v>
+        <v>1.293867177762638e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.676836177548423e-05</v>
+        <v>1.646215136903734e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.65962300522163e-05</v>
+        <v>1.629859575715449e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.326126055812336e-05</v>
+        <v>1.297118100262397e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.667920045272951e-05</v>
+        <v>1.30615188977588e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3312322396223e-05</v>
+        <v>1.634311605691763e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.324831257078541e-05</v>
+        <v>1.630638431533178e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.338634296310387e-05</v>
+        <v>1.640451268805307e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.327932385245704e-05</v>
+        <v>4.336637662839929e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.66752936079599e-05</v>
+        <v>1.30580893964524e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.665732264717497e-05</v>
+        <v>1.635892346348345e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.326028393021329e-05</v>
+        <v>1.628932964225013e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.322505035980158e-05</v>
+        <v>1.625405935975845e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.666922348540379e-05</v>
+        <v>1.303684402864129e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.325498338342172e-05</v>
+        <v>1.29663069649406e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.338115558286725e-05</v>
+        <v>1.309567632799108e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66322868686456e-05</v>
+        <v>1.633868884969423e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.679005786929153e-05</v>
+        <v>1.649791474523053e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.66269829992995e-05</v>
+        <v>1.633147894253864e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.345053687115983e-05</v>
+        <v>1.316499299859264e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.334462663808742e-05</v>
+        <v>1.304887308961178e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.33115590923337e-05</v>
+        <v>1.634102933247979e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.340602261227748e-05</v>
+        <v>1.31325502570647e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.101509691962416e-05</v>
+        <v>2.072178017721052e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.093299802287129e-05</v>
+        <v>2.062159488075184e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.095058233632065e-05</v>
+        <v>2.064674091356392e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.099912160718175e-05</v>
+        <v>2.067980743670545e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.095213666374411e-05</v>
+        <v>2.063791195926762e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.116709482295978e-05</v>
+        <v>2.084403371465935e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.099496309969183e-05</v>
+        <v>2.068047810277648e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.098476996563025e-05</v>
+        <v>2.067042118426521e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.107793350020501e-05</v>
+        <v>2.076075907940005e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.103583180372987e-05</v>
+        <v>2.072499840253964e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.097182197829227e-05</v>
+        <v>2.068826666095378e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.110985237061074e-05</v>
+        <v>2.078639503367505e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.100063292572794e-05</v>
+        <v>4.336637662839929e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.106369238351335e-05</v>
+        <v>2.07550518155332e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.104573150739204e-05</v>
+        <v>2.072608921386078e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.098379333772015e-05</v>
+        <v>2.067121198787213e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.094855976730844e-05</v>
+        <v>2.063594170538047e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.106795653287932e-05</v>
+        <v>2.073608421028254e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.097849279092859e-05</v>
+        <v>2.066554714658186e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.110465419899832e-05</v>
+        <v>2.079477466937346e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.103101991612115e-05</v>
+        <v>2.072057119531623e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.117849225634845e-05</v>
+        <v>2.086510433271063e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.102571604677505e-05</v>
+        <v>2.071336128816065e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.109697272553426e-05</v>
+        <v>2.078715948803394e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.106813604559428e-05</v>
+        <v>2.074811327125303e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.103506849984056e-05</v>
+        <v>2.072291167810178e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.112688230777083e-05</v>
+        <v>2.082903261196434e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.706947451496289e-05</v>
+        <v>5.678341767653877e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.590046956018341e-05</v>
+        <v>8.558430745918121e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.59180538736328e-05</v>
+        <v>8.560945349199325e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.057122350227044e-05</v>
+        <v>7.025355006285822e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.151083638142076e-05</v>
+        <v>6.120199918256504e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.212988474080012e-05</v>
+        <v>9.179957248410411e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.596243463700397e-05</v>
+        <v>8.56431906812059e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.595224150294239e-05</v>
+        <v>8.563313376269458e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.604540503751719e-05</v>
+        <v>8.572347165782936e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.600330334104205e-05</v>
+        <v>8.568771098096899e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.593929351560449e-05</v>
+        <v>8.56509792393831e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.607732390792282e-05</v>
+        <v>8.574910761210436e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.355561960414029e-05</v>
+        <v>4.336637662839929e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.977785416264203e-05</v>
+        <v>6.947120933499267e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.825013791150797e-05</v>
+        <v>6.793311894741601e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.135608806294082e-05</v>
+        <v>5.105312859795619e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.591603130462062e-05</v>
+        <v>8.559865428380982e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.603542807019146e-05</v>
+        <v>8.569879678871192e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.594596432824077e-05</v>
+        <v>8.562825972501122e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>7.196005589487463e-05</v>
+        <v>7.165131187151767e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.809612304914374e-05</v>
+        <v>7.778408688710553e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.615164605035819e-05</v>
+        <v>8.583349680577872e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.404795328619075e-05</v>
+        <v>5.374411885977081e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001148121004739576</v>
+        <v>0.000114485402283091</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.658543807654549e-05</v>
+        <v>5.627289846274296e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.600254003715267e-05</v>
+        <v>8.568562425653111e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001162964981459123</v>
+        <v>0.0001159813347839444</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.094635114642813e-05</v>
+        <v>4.065407256597755e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.898984741763297e-05</v>
+        <v>4.867253052087586e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.900743173108238e-05</v>
+        <v>4.869767655368786e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.718061693660118e-05</v>
+        <v>4.685699349274119e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.027727124679015e-05</v>
+        <v>2.997315884048115e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.92239444201693e-05</v>
+        <v>4.889496956666805e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.905181249445351e-05</v>
+        <v>4.87314137429005e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.904161936039191e-05</v>
+        <v>4.872135682438915e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.913478289496669e-05</v>
+        <v>4.881169471952405e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.909268119849157e-05</v>
+        <v>4.877593404266366e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.902867137305397e-05</v>
+        <v>4.87392023010778e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.916670176537243e-05</v>
+        <v>4.883733067379904e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.905748232048963e-05</v>
+        <v>4.336637662839929e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>5.181338330130008e-05</v>
+        <v>5.149652349563332e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.238106276170913e-05</v>
+        <v>5.205270018200603e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.904064293492972e-05</v>
+        <v>4.872214783988078e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.900540916207015e-05</v>
+        <v>4.868687734550444e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.912480592764104e-05</v>
+        <v>4.878701985040653e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.903534218569026e-05</v>
+        <v>4.871648278670588e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.91615143851358e-05</v>
+        <v>4.884585214975636e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.846463221622387e-05</v>
+        <v>5.814024740130153e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.923534165111017e-05</v>
+        <v>4.891603997283465e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.908256544153675e-05</v>
+        <v>4.876429692828464e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.915382212029595e-05</v>
+        <v>4.883809512815791e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.422597419058109e-05</v>
+        <v>4.390422905287121e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.909191789460224e-05</v>
+        <v>4.877384731822583e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.918373170253255e-05</v>
+        <v>4.887996825208833e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.353116828177315e-05</v>
+        <v>1.353632981591998e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.359729047948756e-05</v>
+        <v>1.360422962953078e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.355127321852957e-05</v>
+        <v>1.355647770816467e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.351678678319468e-05</v>
+        <v>1.352196639073164e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.351472442304941e-05</v>
+        <v>1.351998548186428e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356233525533299e-05</v>
+        <v>1.356736374654751e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.35344183187702e-05</v>
+        <v>1.353966913030211e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.354523337072639e-05</v>
+        <v>1.355085420790247e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.354166107053344e-05</v>
+        <v>1.354686692556298e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.352377650305804e-05</v>
+        <v>1.352958918162356e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.352588409382744e-05</v>
+        <v>1.353115742980324e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.355543991408041e-05</v>
+        <v>1.356065926415284e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35206688931753e-05</v>
+        <v>1.352593033935194e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.509301433158133e-05</v>
+        <v>1.510591907523722e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.351171712648997e-05</v>
+        <v>1.351694776004486e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.352600570308896e-05</v>
+        <v>1.353118166437033e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.353481474506928e-05</v>
+        <v>1.354033709612246e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.352444153568279e-05</v>
+        <v>1.3529361427342e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.352929969911398e-05</v>
+        <v>1.353503897036593e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.40665415512873e-05</v>
+        <v>1.408345145438903e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.353555189634607e-05</v>
+        <v>1.354079540931499e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.418472381431189e-05</v>
+        <v>1.420318025593689e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.351589877028503e-05</v>
+        <v>1.352114306803868e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.354967706918511e-05</v>
+        <v>1.355500067798373e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.389320085178121e-05</v>
+        <v>1.390152006787481e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.354086793504725e-05</v>
+        <v>1.354625508605428e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.355183692349025e-05</v>
+        <v>1.355720201408277e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.370958157818006e-05</v>
+        <v>1.371405897761649e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.369838144431725e-05</v>
+        <v>1.370612541127953e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386060830407571e-05</v>
+        <v>1.386539108012915e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.357244015760188e-05</v>
+        <v>1.357703430174529e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.359767471600906e-05</v>
+        <v>1.360286337092556e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.393710002738164e-05</v>
+        <v>1.394063143173047e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.373878809701443e-05</v>
+        <v>1.374390633552578e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.381448035766915e-05</v>
+        <v>1.382224241193571e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.378882305641317e-05</v>
+        <v>1.379361696035855e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.367303713218168e-05</v>
+        <v>1.36821338999195e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.368059121608586e-05</v>
+        <v>1.368585962500993e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.39101172991971e-05</v>
+        <v>1.391506816408788e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.363282028704138e-05</v>
+        <v>1.363801454324408e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.620775674701394e-05</v>
+        <v>1.622548270402425e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.357270764313505e-05</v>
+        <v>1.35776746861991e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.367684182639186e-05</v>
+        <v>1.368142160355777e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.373835964634882e-05</v>
+        <v>1.374542336965969e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.366470119005874e-05</v>
+        <v>1.36674627045239e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.369770839774589e-05</v>
+        <v>1.370632103263028e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.456191474148514e-05</v>
+        <v>1.458644677673182e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.374666241027457e-05</v>
+        <v>1.37517187366535e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.501473642002217e-05</v>
+        <v>1.504236768038022e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.360586988127318e-05</v>
+        <v>1.361093663540971e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.383944882025442e-05</v>
+        <v>1.38450867254969e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.428785569107634e-05</v>
+        <v>1.429783186522145e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.377628549382793e-05</v>
+        <v>1.378237687564303e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.388590111876086e-05</v>
+        <v>1.389186388670113e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.239493185774653e-05</v>
+        <v>1.205086439088544e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.214989663232276e-05</v>
+        <v>1.18065193084845e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.262202636713792e-05</v>
+        <v>1.227844410227732e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.223248621548665e-05</v>
+        <v>1.188862289588099e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.220919090891333e-05</v>
+        <v>1.186624761896114e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.274697716162101e-05</v>
+        <v>1.240140691363677e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.243164252071897e-05</v>
+        <v>1.208858348299207e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.255380350773385e-05</v>
+        <v>1.221492407987802e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.250191568135393e-05</v>
+        <v>1.215834916522109e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.231143831677304e-05</v>
+        <v>1.197472582566127e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.233524452405318e-05</v>
+        <v>1.199243991028155e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.270108837787577e-05</v>
+        <v>1.235778840194274e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.37525856744258e-05</v>
+        <v>4.342398859320103e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.222250089162091e-05</v>
+        <v>1.187940784858596e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.217522211084942e-05</v>
+        <v>1.183193515358949e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.233661815660521e-05</v>
+        <v>1.199271365086533e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24361203381323e-05</v>
+        <v>1.209612846421222e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.231895016619956e-05</v>
+        <v>1.197215323627974e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.237382535702072e-05</v>
+        <v>1.203628369653395e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.224925804966098e-05</v>
+        <v>1.190264341726859e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.239601979313823e-05</v>
+        <v>1.205288594693267e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.286424782303723e-05</v>
+        <v>1.252266391933631e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.222245570116569e-05</v>
+        <v>1.187932308731729e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.254326758499669e-05</v>
+        <v>1.219710192499902e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.234457933306789e-05</v>
+        <v>1.200111275256676e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.250449390353849e-05</v>
+        <v>1.216297488290244e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.266964345242853e-05</v>
+        <v>1.232792194860407e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6796746866321e-05</v>
+        <v>4.644623077778755e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.70360782653543e-05</v>
+        <v>4.66965657627136e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.471903856801741e-05</v>
+        <v>5.437648280689231e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.604490304222967e-05</v>
+        <v>2.569165146615794e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.633789367342873e-05</v>
+        <v>4.600774917522172e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.565490022488656e-05</v>
+        <v>5.527963894504342e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.056100257465081e-05</v>
+        <v>5.023021992032962e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.194671761814043e-05</v>
+        <v>5.169137369861505e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.113775678464475e-05</v>
+        <v>5.079619083308485e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.372099052552372e-05</v>
+        <v>5.348611024414227e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.026162984064664e-05</v>
+        <v>4.992986030396983e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.735403283743764e-05</v>
+        <v>5.701639476582727e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.37525856744258e-05</v>
+        <v>4.342398859320103e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.572380293477108e-05</v>
+        <v>4.538724653746516e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.392131923145693e-05</v>
+        <v>4.358278240438023e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.789311508194892e-05</v>
+        <v>4.75451757628697e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.895194598568546e-05</v>
+        <v>4.867929460455699e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.707427247581074e-05</v>
+        <v>4.668000517626866e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.718159962061563e-05</v>
+        <v>4.695266846768455e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.041750793347465e-05</v>
+        <v>5.008664387519353e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.06270590856049e-05</v>
+        <v>5.028973600149059e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.426215140842508e-05</v>
+        <v>5.395653550390592e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.64760050550267e-05</v>
+        <v>4.614133244187204e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.933830556081689e-05</v>
+        <v>4.902212275211134e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.856468312555867e-05</v>
+        <v>4.822198772113384e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.7427055039211e-05</v>
+        <v>4.712355245333855e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.496930532929481e-05</v>
+        <v>5.466401440362237e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.364569166943517e-05</v>
+        <v>1.330458930570415e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.340065644401142e-05</v>
+        <v>1.603311691147246e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.684127151403654e-05</v>
+        <v>1.353216901709608e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.348324602717528e-05</v>
+        <v>1.611522049886895e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.345995072060196e-05</v>
+        <v>1.609284522194914e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.696622230851958e-05</v>
+        <v>1.365513182845554e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.665088766761756e-05</v>
+        <v>1.334230839781082e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.677304865463248e-05</v>
+        <v>1.346864899469676e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.672116082825255e-05</v>
+        <v>1.638494676820906e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.356219812846169e-05</v>
+        <v>1.322845074047995e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.655448967095178e-05</v>
+        <v>1.621903751326952e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.692033352477439e-05</v>
+        <v>1.361151331676144e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.37525856744258e-05</v>
+        <v>4.342398859320103e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.645036317506135e-05</v>
+        <v>1.611697359142794e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64031896837902e-05</v>
+        <v>1.299878403117843e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.655586330350377e-05</v>
+        <v>1.324643856568406e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.665536548503091e-05</v>
+        <v>1.334985337903097e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.653819531309813e-05</v>
+        <v>1.619875083926772e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.362458516870935e-05</v>
+        <v>1.329000861135273e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.652923273759026e-05</v>
+        <v>1.619389946217397e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.661526494003683e-05</v>
+        <v>1.330661086175144e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.419854192428173e-05</v>
+        <v>1.386013844014575e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.347321551285432e-05</v>
+        <v>1.610592069030527e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39243984666596e-05</v>
+        <v>1.358523300209229e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.359533914475651e-05</v>
+        <v>1.325483766738552e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.375525371522715e-05</v>
+        <v>1.638957248589043e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.392437873257742e-05</v>
+        <v>1.35853770895789e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.036710413937438e-05</v>
+        <v>2.002434922369343e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.012206891395059e-05</v>
+        <v>1.978000414129248e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.059419864876572e-05</v>
+        <v>2.025192893508529e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.020465849711442e-05</v>
+        <v>1.986210772868897e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.018136319054118e-05</v>
+        <v>1.983973245176914e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.071914944324883e-05</v>
+        <v>2.037489174644476e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.040381480234681e-05</v>
+        <v>2.006206831580004e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.052597578936167e-05</v>
+        <v>2.0188408912686e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.047408796298176e-05</v>
+        <v>2.013183399802905e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.028361059840088e-05</v>
+        <v>1.994821065846926e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.030741680568098e-05</v>
+        <v>1.996592474308952e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.067326065950357e-05</v>
+        <v>2.033127323475071e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.37525856744258e-05</v>
+        <v>4.342398859320103e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.019464054748728e-05</v>
+        <v>1.985286066033034e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.014736176671584e-05</v>
+        <v>1.980538796533385e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.030879043823299e-05</v>
+        <v>1.996619848367329e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.040829261976011e-05</v>
+        <v>2.00696132970202e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.029112244782737e-05</v>
+        <v>1.994563806908774e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.034599763864851e-05</v>
+        <v>2.000976852934195e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.028465056648483e-05</v>
+        <v>1.994213044316984e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.036819207476603e-05</v>
+        <v>2.002637077974067e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.083642010466503e-05</v>
+        <v>2.049614875214428e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.019462798279351e-05</v>
+        <v>1.985280792012529e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.057616940765531e-05</v>
+        <v>2.023524519972438e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.031675161469569e-05</v>
+        <v>1.997459758537473e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04766661851663e-05</v>
+        <v>2.013645971571042e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.064181573405638e-05</v>
+        <v>2.030140678141206e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.187049150253466e-05</v>
+        <v>5.153234321668131e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.689921391929677e-05</v>
+        <v>7.656958696831124e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.73713436541119e-05</v>
+        <v>7.704151176210407e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.352427308630078e-05</v>
+        <v>6.31899902609174e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.562210661424927e-05</v>
+        <v>5.528630251345841e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.2736972739248e-05</v>
+        <v>8.240677671275272e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.718095980769284e-05</v>
+        <v>7.68516511428187e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.730312079470773e-05</v>
+        <v>7.697799173970467e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.725123296832783e-05</v>
+        <v>7.692141682504784e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.706075560374695e-05</v>
+        <v>7.673779348548793e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.708456181102692e-05</v>
+        <v>7.675550757010826e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.745040566484965e-05</v>
+        <v>7.712085606176911e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.37525856744258e-05</v>
+        <v>4.342398859320103e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.276431198727113e-05</v>
+        <v>6.243056705486727e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.139731309894596e-05</v>
+        <v>6.10629653308953e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.684530757814313e-05</v>
+        <v>4.650578324550462e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.718543762510624e-05</v>
+        <v>7.68591961240389e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.706826745317343e-05</v>
+        <v>7.673522089610642e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.712314264399463e-05</v>
+        <v>7.679935135636065e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.472547661129348e-05</v>
+        <v>6.439182963107444e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.023979490844459e-05</v>
+        <v>6.990729015686711e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.761853213211486e-05</v>
+        <v>7.729070014021748e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.904753523311471e-05</v>
+        <v>4.870950053659764e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001024857816803126</v>
+        <v>0.0001021635602998465</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.135066595371097e-05</v>
+        <v>5.101297308581894e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.72538111905123e-05</v>
+        <v>7.692604254272903e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001038195139581173</v>
+        <v>0.0001034997231617619</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3763786546834e-05</v>
+        <v>3.337579328487214e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.951174284328669e-05</v>
+        <v>3.911406339047588e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.998387257810194e-05</v>
+        <v>3.958598818426863e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.821117459727664e-05</v>
+        <v>3.781540396944461e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.575555573242268e-05</v>
+        <v>2.538223058619677e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.010882359243312e-05</v>
+        <v>3.970895122225335e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.979348873168282e-05</v>
+        <v>3.93961275649834e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.99156497186977e-05</v>
+        <v>3.95224681618693e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.986376189231789e-05</v>
+        <v>3.946589324721243e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.967328452773697e-05</v>
+        <v>3.928226990765261e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.969709073501718e-05</v>
+        <v>3.929998399227289e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.006293458883977e-05</v>
+        <v>3.966533248393408e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.37525856744258e-05</v>
+        <v>4.342398859320103e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.157041693848589e-05</v>
+        <v>4.116958307204277e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.195507422399072e-05</v>
+        <v>4.155329858480715e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.969846458741734e-05</v>
+        <v>3.930025795948191e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.979796654909625e-05</v>
+        <v>3.940367254620356e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.968079637716351e-05</v>
+        <v>3.927969731827109e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.973567156798465e-05</v>
+        <v>3.93438277785253e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.967183380165549e-05</v>
+        <v>3.927484594117734e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.667364966213815e-05</v>
+        <v>4.62642396263428e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.022609403400114e-05</v>
+        <v>3.983020800132765e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.958430191212963e-05</v>
+        <v>3.918686716930864e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.996584333699132e-05</v>
+        <v>3.95693044489077e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.609318466123829e-05</v>
+        <v>3.570167196108073e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.986634011450243e-05</v>
+        <v>3.947051896489378e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.003148966339247e-05</v>
+        <v>3.963546603059539e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.341481054732619e-05</v>
+        <v>1.340936403023107e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.34904326607059e-05</v>
+        <v>1.348262044315811e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.342119240932184e-05</v>
+        <v>1.341579283206172e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.341053284358733e-05</v>
+        <v>1.340318116955502e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.340861000017926e-05</v>
+        <v>1.340092208492976e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.342811892711443e-05</v>
+        <v>1.342019768564215e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341069998521411e-05</v>
+        <v>1.340395136211968e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.34093364579041e-05</v>
+        <v>1.340325556663909e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.342064808790721e-05</v>
+        <v>1.341335491260772e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.341712279813097e-05</v>
+        <v>1.341070790402082e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341144735044617e-05</v>
+        <v>1.340709835249202e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.341757373440298e-05</v>
+        <v>1.340967498114829e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.341568229278769e-05</v>
+        <v>1.340954051986059e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.492639922203482e-05</v>
+        <v>1.490981444530199e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.341356620121225e-05</v>
+        <v>1.340576168139249e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.341499413927055e-05</v>
+        <v>1.340816114059997e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.341558983459959e-05</v>
+        <v>1.341038792529181e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.341937438163925e-05</v>
+        <v>1.341060584398961e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.341642298608599e-05</v>
+        <v>1.341007932039398e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.392643203496477e-05</v>
+        <v>1.391389491907314e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.341607908230363e-05</v>
+        <v>1.340936073452049e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.399538157874851e-05</v>
+        <v>1.398233173969559e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341812895245986e-05</v>
+        <v>1.341128345035362e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.342036581864974e-05</v>
+        <v>1.341371069420504e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.375554625272813e-05</v>
+        <v>1.374878821169527e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.341738189595707e-05</v>
+        <v>1.341103720685333e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.342020460975959e-05</v>
+        <v>1.341517600346998e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.346483402123217e-05</v>
+        <v>1.34677136437302e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.353566205142624e-05</v>
+        <v>1.352762794985046e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.350966545221178e-05</v>
+        <v>1.351294891170603e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.339131858546448e-05</v>
+        <v>1.338064208975101e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.342343272006301e-05</v>
+        <v>1.341033439583547e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.355790945422663e-05</v>
+        <v>1.354319239688395e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.343809036467814e-05</v>
+        <v>1.343171616604613e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.342521786983735e-05</v>
+        <v>1.342362721934682e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.350548697983944e-05</v>
+        <v>1.349523619937713e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.349003149055378e-05</v>
+        <v>1.348603647379182e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.343787728215673e-05</v>
+        <v>1.344862667211322e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.350545981886013e-05</v>
+        <v>1.349089177521446e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.346967699906128e-05</v>
+        <v>1.346763995672986e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.595020346137157e-05</v>
+        <v>1.592896767805462e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.345215091551555e-05</v>
+        <v>1.3438266031775e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.346569837602079e-05</v>
+        <v>1.345872154744225e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.347054188943135e-05</v>
+        <v>1.34752564510615e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.349656303293012e-05</v>
+        <v>1.347581496213852e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.347650665867617e-05</v>
+        <v>1.347303140217613e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43416462970881e-05</v>
+        <v>1.432702475889982e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.348016736986486e-05</v>
+        <v>1.347400814629163e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.449990590105919e-05</v>
+        <v>1.44828142235043e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.348872788421611e-05</v>
+        <v>1.348166128577242e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.350549854769869e-05</v>
+        <v>1.349979203394401e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.404756760779123e-05</v>
+        <v>1.403780207690862e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.348202089188967e-05</v>
+        <v>1.347853066756696e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.3530175804112e-05</v>
+        <v>1.353594190908283e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.195823818147426e-05</v>
+        <v>1.167772502315472e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.186034884553492e-05</v>
+        <v>1.156533397075751e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.203032424851653e-05</v>
+        <v>1.175034129722671e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.19099195499034e-05</v>
+        <v>1.160788676756216e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.188820014905702e-05</v>
+        <v>1.15823693674896e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.210856245333946e-05</v>
+        <v>1.180009614475051e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.191180749146642e-05</v>
+        <v>1.161658644688599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.189640582324634e-05</v>
+        <v>1.160872711685102e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.201268677064007e-05</v>
+        <v>1.171131547598142e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.198435611800319e-05</v>
+        <v>1.169290469582235e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.192024932556763e-05</v>
+        <v>1.165213315082861e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.20228421602873e-05</v>
+        <v>1.171470757523179e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.196808494748467e-05</v>
+        <v>4.293813936921933e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.193174310715919e-05</v>
+        <v>1.163937194295056e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.194418271968978e-05</v>
+        <v>1.163703483586042e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.196031193694225e-05</v>
+        <v>1.166413783141451e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.196704058971713e-05</v>
+        <v>1.168929038888062e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.200978878950793e-05</v>
+        <v>1.169175188081973e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.197645141902438e-05</v>
+        <v>1.168580455459434e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.195652736564866e-05</v>
+        <v>1.166090444603885e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.192444205678084e-05</v>
+        <v>1.162956965664536e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.212086820473022e-05</v>
+        <v>1.182499522745522e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.199572109400088e-05</v>
+        <v>1.169940575641543e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19506866789942e-05</v>
+        <v>1.165342348480201e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.200474284713752e-05</v>
+        <v>1.170254324260243e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.198728274713875e-05</v>
+        <v>1.169662432280222e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.2061923415769e-05</v>
+        <v>1.178575682668178e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.368097477675613e-05</v>
+        <v>4.364196493280554e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.394888100474086e-05</v>
+        <v>4.365788446439394e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.464563485565878e-05</v>
+        <v>4.465492732421391e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.886102660537239e-05</v>
+        <v>1.843797351509388e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.394302260565136e-05</v>
+        <v>4.343588959938994e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.546263321557275e-05</v>
+        <v>4.493154443932531e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.424552097738458e-05</v>
+        <v>4.395031392996172e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.22074710479774e-05</v>
+        <v>4.206483604763881e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.435459385999701e-05</v>
+        <v>4.394859953940255e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.90104539802172e-05</v>
+        <v>4.878504404722218e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.132012543493663e-05</v>
+        <v>4.153593772474235e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.643857861597924e-05</v>
+        <v>4.588389300908374e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.435805016448479e-05</v>
+        <v>4.293813936921933e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.489553971163594e-05</v>
+        <v>4.464896777981309e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.130064368367236e-05</v>
+        <v>4.079399711797668e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.347216901111646e-05</v>
+        <v>4.315869839894481e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.392863928901322e-05</v>
+        <v>4.399145836104349e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.418668482793484e-05</v>
+        <v>4.348363549695603e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.411688137850105e-05</v>
+        <v>4.391302379863582e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.441679343027929e-05</v>
+        <v>4.417164105589418e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.739627320257893e-05</v>
+        <v>4.710692631314327e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.549982820960952e-05</v>
+        <v>4.519256400988708e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.450662362133723e-05</v>
+        <v>4.419018661067321e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.543263875053052e-05</v>
+        <v>4.5157612069226e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.328054299045712e-05</v>
+        <v>4.286106109041111e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.358224445606182e-05</v>
+        <v>4.337390612860885e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.765107600111723e-05</v>
+        <v>4.775375533503333e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.32703792829238e-05</v>
+        <v>1.299323172281241e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.629545963217505e-05</v>
+        <v>1.599812817219437e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.646543503515662e-05</v>
+        <v>1.306584799688455e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.322206065135295e-05</v>
+        <v>1.604068096899902e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.320034125050659e-05</v>
+        <v>1.289787606714747e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3420703554789e-05</v>
+        <v>1.623289034618735e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.634691827810647e-05</v>
+        <v>1.604938064832285e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.320854692469591e-05</v>
+        <v>1.604152131828787e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.644779755728007e-05</v>
+        <v>1.614410967741826e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.641946690464327e-05</v>
+        <v>1.300841139548022e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.323239042701717e-05</v>
+        <v>1.608492735226562e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.333498326173684e-05</v>
+        <v>1.614750177666865e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.328233302779192e-05</v>
+        <v>4.293813936921933e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.637460937780428e-05</v>
+        <v>1.295703376553004e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.638710939278269e-05</v>
+        <v>1.60821687490523e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.639542272358234e-05</v>
+        <v>1.297964453107237e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.640215137635719e-05</v>
+        <v>1.612208459031749e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.644489957614804e-05</v>
+        <v>1.300725858047762e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.328859252047393e-05</v>
+        <v>1.300131125425218e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.333896931472872e-05</v>
+        <v>1.304981025319941e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.635955284342092e-05</v>
+        <v>1.294507635630322e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.656353601326333e-05</v>
+        <v>1.322551033673545e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.643083188064092e-05</v>
+        <v>1.613219995785228e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.340536594223682e-05</v>
+        <v>1.311458573184648e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.643985363377762e-05</v>
+        <v>1.301804994226041e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.32994238485883e-05</v>
+        <v>1.612941852423905e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.337669381445201e-05</v>
+        <v>1.310398084185577e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.049313077482619e-05</v>
+        <v>2.019504771264028e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.039524143888683e-05</v>
+        <v>2.008265666024313e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.056521684186847e-05</v>
+        <v>2.026766398671231e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.044481214325531e-05</v>
+        <v>2.012520945704779e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.042309274240895e-05</v>
+        <v>2.009969205697522e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.064345504669142e-05</v>
+        <v>2.031741883423612e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.044670008481835e-05</v>
+        <v>2.013390913637161e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.043129841659829e-05</v>
+        <v>2.012604980633664e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.054757936399195e-05</v>
+        <v>2.022863816546705e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.051924871135512e-05</v>
+        <v>2.021022738530796e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.045514191891958e-05</v>
+        <v>2.016945584031455e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.055773475363921e-05</v>
+        <v>2.023203026471741e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.050297754083659e-05</v>
+        <v>4.293813936921933e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.046660407398193e-05</v>
+        <v>2.015666461509543e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04790436865125e-05</v>
+        <v>2.015432750800527e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.049520453029417e-05</v>
+        <v>2.018146052090014e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.050193318306906e-05</v>
+        <v>2.020661307836624e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.054468138285985e-05</v>
+        <v>2.020907457030539e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.051134401237632e-05</v>
+        <v>2.020312724407996e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.056177674593265e-05</v>
+        <v>2.025141003063986e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.045933465013278e-05</v>
+        <v>2.014689234613098e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.065576079808212e-05</v>
+        <v>2.034231791694084e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.053061368735281e-05</v>
+        <v>2.021672844590109e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.055588011997662e-05</v>
+        <v>2.024414528179032e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.053963544048945e-05</v>
+        <v>2.021986593208808e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.052217534049065e-05</v>
+        <v>2.02139470122878e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.059681600912095e-05</v>
+        <v>2.03030795161674e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.424195033738806e-05</v>
+        <v>5.395093710375516e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.120660897172711e-05</v>
+        <v>8.089214102868054e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.137658437470873e-05</v>
+        <v>8.107714835514979e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.684617117617388e-05</v>
+        <v>6.652945253022042e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.838794099266028e-05</v>
+        <v>5.807021536411058e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.706641819762305e-05</v>
+        <v>8.673664235935027e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.12580676176586e-05</v>
+        <v>8.094339350480905e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.12426659494385e-05</v>
+        <v>8.093553417477411e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.13589468968322e-05</v>
+        <v>8.103812253390447e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.13306162441954e-05</v>
+        <v>8.101971175374545e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.126650945175982e-05</v>
+        <v>8.097894020875178e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.136910228647864e-05</v>
+        <v>8.104151463315389e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.033634293234464e-05</v>
+        <v>4.293813936921933e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.606493823197934e-05</v>
+        <v>6.575814687606399e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.466425245081699e-05</v>
+        <v>6.434315187382556e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.892561574290958e-05</v>
+        <v>4.862070102953311e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.131330071590929e-05</v>
+        <v>8.101609744680372e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.135604891570009e-05</v>
+        <v>8.101855893874288e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.132271154521652e-05</v>
+        <v>8.101261161251743e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.816428773927752e-05</v>
+        <v>6.78564676896653e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.387417462087157e-05</v>
+        <v>7.356206213640309e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.147244690196642e-05</v>
+        <v>8.115711909688e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.144136119855917e-05</v>
+        <v>5.113548469351672e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001082750392086164</v>
+        <v>0.0001079521565083654</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.378575428018173e-05</v>
+        <v>5.347322090677644e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.133354287333087e-05</v>
+        <v>8.10234313807253e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001096772778349091</v>
+        <v>0.0001093723060277514</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.728322323707308e-05</v>
+        <v>3.698593892397389e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.427438189508982e-05</v>
+        <v>4.395696473485043e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.444435729807148e-05</v>
+        <v>4.41419720613196e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.268782939598376e-05</v>
+        <v>4.236469397769966e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.796004251995849e-05</v>
+        <v>2.764479073326187e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.452259570808147e-05</v>
+        <v>4.419172712381527e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.432584054102139e-05</v>
+        <v>4.400821721097892e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.43104388728013e-05</v>
+        <v>4.400035788094393e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.442671982019496e-05</v>
+        <v>4.410294624007434e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.439838916755812e-05</v>
+        <v>4.408453545991522e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.433428237512259e-05</v>
+        <v>4.404376391492173e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.443687520984225e-05</v>
+        <v>4.410633833932472e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.438211799703956e-05</v>
+        <v>4.293813936921933e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.669507765277856e-05</v>
+        <v>4.637843806680051e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.721844998885412e-05</v>
+        <v>4.688662782849796e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.437434519168415e-05</v>
+        <v>4.405576881047927e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.4381073639272e-05</v>
+        <v>4.408092115297353e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.442382183906289e-05</v>
+        <v>4.408338264491264e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.439048446857926e-05</v>
+        <v>4.407743531868722e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.444086126283414e-05</v>
+        <v>4.412593431763447e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.251908464685242e-05</v>
+        <v>5.219531177986899e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.453490125428517e-05</v>
+        <v>4.421662599154813e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.44097541435558e-05</v>
+        <v>4.409103652050839e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.443502057617964e-05</v>
+        <v>4.411845335639762e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.014471042055731e-05</v>
+        <v>3.982350360550765e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.440131579669371e-05</v>
+        <v>4.40882550868951e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.447595646532399e-05</v>
+        <v>4.417738759077469e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.344155360842263e-05</v>
+        <v>1.344549561464646e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.351829135598581e-05</v>
+        <v>1.352249402739239e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.345054047197759e-05</v>
+        <v>1.345498381017016e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.343923015611596e-05</v>
+        <v>1.344161402297617e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343145108945764e-05</v>
+        <v>1.343440127032411e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.345147741599464e-05</v>
+        <v>1.345308109440236e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.343592321742566e-05</v>
+        <v>1.343900223300975e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.344664686743553e-05</v>
+        <v>1.345067329792468e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.344544704195422e-05</v>
+        <v>1.344782070460527e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.345099738369844e-05</v>
+        <v>1.345440343725685e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.343797285317981e-05</v>
+        <v>1.344233973966822e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344452410918487e-05</v>
+        <v>1.34461976783164e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.343923308878771e-05</v>
+        <v>1.344241050738783e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.497266912255104e-05</v>
+        <v>1.497872954988998e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.34343584426266e-05</v>
+        <v>1.343602809896707e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.343807965244998e-05</v>
+        <v>1.34409198672943e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34374751482107e-05</v>
+        <v>1.344221646643321e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344509849105964e-05</v>
+        <v>1.344606350094564e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344288027620246e-05</v>
+        <v>1.344626094961088e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.395804537923721e-05</v>
+        <v>1.39693597649695e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344043155201503e-05</v>
+        <v>1.344341663147083e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.403866351817539e-05</v>
+        <v>1.405186008317631e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344105008368904e-05</v>
+        <v>1.344375441390423e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.343748817533497e-05</v>
+        <v>1.344069231897628e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.379188604722375e-05</v>
+        <v>1.380058476910582e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.344430049567139e-05</v>
+        <v>1.34481373095097e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.344400522698259e-05</v>
+        <v>1.34490349183358e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.352388919185729e-05</v>
+        <v>1.353318610754688e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.360531635067951e-05</v>
+        <v>1.360945308660796e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3590895166846e-05</v>
+        <v>1.360382200546394e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.346590472093226e-05</v>
+        <v>1.346410566296643e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.345790797878325e-05</v>
+        <v>1.346015228808179e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.359694279652315e-05</v>
+        <v>1.358961287470409e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.348749247371283e-05</v>
+        <v>1.349066172237374e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.356277732732876e-05</v>
+        <v>1.357272924406222e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.355438882368751e-05</v>
+        <v>1.355253235955207e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.360758541920864e-05</v>
+        <v>1.361307126011856e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.349812600466751e-05</v>
+        <v>1.351047537157513e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.356812345008146e-05</v>
+        <v>1.356131224148794e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.350786997035597e-05</v>
+        <v>1.351173751422843e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6008249402239e-05</v>
+        <v>1.60166222127817e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.347225912498491e-05</v>
+        <v>1.346539792195378e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.350236269805881e-05</v>
+        <v>1.350382131078375e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.349702301374953e-05</v>
+        <v>1.351210817197909e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.355099859937679e-05</v>
+        <v>1.353912051825565e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.353534741177946e-05</v>
+        <v>1.354067320777435e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.437446623309324e-05</v>
+        <v>1.439207388597848e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352565099978371e-05</v>
+        <v>1.352814111061851e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.460043002014482e-05</v>
+        <v>1.462255890631855e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.3523014036105e-05</v>
+        <v>1.352350027273149e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.34974749490631e-05</v>
+        <v>1.350153066066e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.413014206388148e-05</v>
+        <v>1.4138542141867e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.354397005692258e-05</v>
+        <v>1.355254337762699e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.357050640349357e-05</v>
+        <v>1.358746441580916e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.206648458953497e-05</v>
+        <v>1.178371716005569e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.197352704006904e-05</v>
+        <v>1.167920581038823e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.216799534754976e-05</v>
+        <v>1.189089069328046e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.204024012689048e-05</v>
+        <v>1.173987279651945e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.195237199043716e-05</v>
+        <v>1.16584014372844e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.217857856123803e-05</v>
+        <v>1.186939864339172e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.200288673311638e-05</v>
+        <v>1.17103714273657e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.212401529310058e-05</v>
+        <v>1.18422014745354e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.209896737874385e-05</v>
+        <v>1.179848975196506e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.217315637562672e-05</v>
+        <v>1.188433511424055e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.202603831183864e-05</v>
+        <v>1.174807010040218e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.213380967387146e-05</v>
+        <v>1.182557980753126e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.204027325276676e-05</v>
+        <v>4.139652223361452e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.196520706089292e-05</v>
+        <v>1.167330385448432e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.198521188192892e-05</v>
+        <v>1.167677721518427e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.202724465872522e-05</v>
+        <v>1.173203198876536e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.202041650525685e-05</v>
+        <v>1.174667767250421e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.210652566964656e-05</v>
+        <v>1.179013169704539e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.208146991240567e-05</v>
+        <v>1.179236197055027e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.199208194190152e-05</v>
+        <v>1.169962760749066e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.200565572632343e-05</v>
+        <v>1.171211531794953e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.225416703333736e-05</v>
+        <v>1.196631335683422e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.206079704603647e-05</v>
+        <v>1.176404949668042e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.195555905391571e-05</v>
+        <v>1.166275661061634e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.211377539463258e-05</v>
+        <v>1.181289011879864e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.209751194464034e-05</v>
+        <v>1.181355631877535e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.213763711276863e-05</v>
+        <v>1.186676250441775e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.182315659235648e-05</v>
+        <v>4.171748838205333e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.545656917985884e-05</v>
+        <v>4.516025374015736e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.510391980827241e-05</v>
+        <v>4.512529866881377e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.990350611713236e-05</v>
+        <v>1.949927426549226e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.297692385904539e-05</v>
+        <v>4.268663590993305e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.495975555279074e-05</v>
+        <v>4.441902980172272e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.266118404005869e-05</v>
+        <v>4.239945345694845e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.415556934104612e-05</v>
+        <v>4.40939538222304e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.399491361448053e-05</v>
+        <v>4.3596640089301e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.215457018996668e-05</v>
+        <v>5.194910901467413e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.10004427753524e-05</v>
+        <v>4.09900520294019e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.544163355586912e-05</v>
+        <v>4.488280366493079e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.29879647126803e-05</v>
+        <v>4.139652223361452e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.322711417839266e-05</v>
+        <v>4.29683794935635e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.024174670546122e-05</v>
+        <v>3.971307791683216e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.282233079361942e-05</v>
+        <v>4.250962642470959e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.217022402585089e-05</v>
+        <v>4.226751992288936e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.346902667159234e-05</v>
+        <v>4.280591650013488e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.311932178783754e-05</v>
+        <v>4.291972187575564e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.300477800051765e-05</v>
+        <v>4.276864783496456e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.661388370712306e-05</v>
+        <v>4.632890836899251e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.500869883837167e-05</v>
+        <v>4.482659246380526e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.313136993613815e-05</v>
+        <v>4.279019166088577e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.235884854065093e-05</v>
+        <v>4.211870481442562e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.52482212641092e-05</v>
+        <v>4.484876127158363e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.261870196237087e-05</v>
+        <v>4.250609782940151e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.593547015740507e-05</v>
+        <v>4.609808538495135e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.329640641438828e-05</v>
+        <v>1.594640893017641e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.320344886492239e-05</v>
+        <v>1.29100953680972e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.632877844469967e-05</v>
+        <v>1.605358246340117e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.327016195174383e-05</v>
+        <v>1.590256456664016e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.611315508758711e-05</v>
+        <v>1.288929099499336e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.340850038609135e-05</v>
+        <v>1.310028820110065e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.323280855796975e-05</v>
+        <v>1.294126098507469e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.335393711795393e-05</v>
+        <v>1.307309103224438e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.625975047589377e-05</v>
+        <v>1.596118152208582e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.633393947277662e-05</v>
+        <v>1.604702688436135e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.325596013669195e-05</v>
+        <v>1.59107618705229e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.629459277102138e-05</v>
+        <v>1.305646936524025e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.327184002654098e-05</v>
+        <v>4.139652223361452e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.319677383466713e-05</v>
+        <v>1.584583466049602e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.615092905444062e-05</v>
+        <v>1.584939427173142e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.618802775587512e-05</v>
+        <v>1.589472375888607e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.618119960240674e-05</v>
+        <v>1.297756723021318e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.333644749449991e-05</v>
+        <v>1.59528234671661e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.331139173725901e-05</v>
+        <v>1.302325152825923e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.328700836545748e-05</v>
+        <v>1.299722228041896e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.616643882347334e-05</v>
+        <v>1.587480708807024e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.356380741743697e-05</v>
+        <v>1.613873785551042e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.329071887088983e-05</v>
+        <v>1.299493905438938e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.331788117679591e-05</v>
+        <v>1.302788047382669e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.334369721948592e-05</v>
+        <v>1.597558188891939e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.625829504179026e-05</v>
+        <v>1.597624808889605e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.336971593946781e-05</v>
+        <v>1.309982550301552e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.001887470321778e-05</v>
+        <v>1.973239257841826e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.992591715375185e-05</v>
+        <v>1.962788122875083e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.012038546123256e-05</v>
+        <v>1.983956611164301e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.999263024057325e-05</v>
+        <v>1.968854821488202e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.990476210411998e-05</v>
+        <v>1.960707685564696e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.013096867492082e-05</v>
+        <v>1.981807406175434e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.995527684679918e-05</v>
+        <v>1.965904684572823e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.007640540678335e-05</v>
+        <v>1.979087689289799e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.005135749242664e-05</v>
+        <v>1.974716517032761e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.012554648930956e-05</v>
+        <v>1.983301053260316e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.997842842552142e-05</v>
+        <v>1.969674551876473e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.008619978755426e-05</v>
+        <v>1.977425522589387e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.999266336644959e-05</v>
+        <v>4.139652223361452e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.991756520318495e-05</v>
+        <v>1.962194863131458e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.993757002422096e-05</v>
+        <v>1.962542199201456e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.997963477240801e-05</v>
+        <v>1.968070740712792e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.997280661893964e-05</v>
+        <v>1.969535309086675e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.005891578332938e-05</v>
+        <v>1.973880711540799e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.003386002608849e-05</v>
+        <v>1.974103738891283e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0010236015325e-05</v>
+        <v>1.971539325666936e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.995804584000622e-05</v>
+        <v>1.96607907363121e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.020655714702019e-05</v>
+        <v>1.991498877519675e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.001318715971927e-05</v>
+        <v>1.971272491504298e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.997295376630113e-05</v>
+        <v>1.967813714419825e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.006616550831536e-05</v>
+        <v>1.976156553716125e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.004990205832317e-05</v>
+        <v>1.976223173713789e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.00900272264514e-05</v>
+        <v>1.981543792278033e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.149304839656307e-05</v>
+        <v>5.121309969772811e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.663566227693306e-05</v>
+        <v>7.634831390149109e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.683013058441375e-05</v>
+        <v>7.655999878438342e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.326517797924361e-05</v>
+        <v>6.296957155484698e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.531034289242754e-05</v>
+        <v>5.501983823381927e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.207347392886532e-05</v>
+        <v>8.177212824984254e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.666502196998049e-05</v>
+        <v>7.63794795184686e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.678615052996463e-05</v>
+        <v>7.651130956563833e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.676110261560791e-05</v>
+        <v>7.646759784306794e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.683529161249082e-05</v>
+        <v>7.65534432053435e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.66881735487026e-05</v>
+        <v>7.641717819150507e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.679594491073512e-05</v>
+        <v>7.649468789863353e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.714061881355941e-05</v>
+        <v>4.139652223361452e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.244130227924426e-05</v>
+        <v>6.215403670892204e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.114358096263108e-05</v>
+        <v>6.083956701605984e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.649444270478323e-05</v>
+        <v>4.620123238538314e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.66825517421209e-05</v>
+        <v>7.64157857636072e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.676866090651057e-05</v>
+        <v>7.645923978814832e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.674360514926975e-05</v>
+        <v>7.64614700616533e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.440268944390603e-05</v>
+        <v>6.411658984630026e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.97712051991191e-05</v>
+        <v>6.94831812278705e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.69212617876544e-05</v>
+        <v>7.664038178174229e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.884088536028595e-05</v>
+        <v>4.854652089513925e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001017749022795788</v>
+        <v>0.0001014944056357764</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.10715755060158e-05</v>
+        <v>5.077343179585287e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.675964718150439e-05</v>
+        <v>7.648266440987836e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001031604368764937</v>
+        <v>0.0001029008744517881</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.434366595209853e-05</v>
+        <v>3.405382736816177e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.049183164369303e-05</v>
+        <v>4.01895122464439e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.068629995117372e-05</v>
+        <v>4.04011971293362e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.911811911004421e-05</v>
+        <v>3.880996757236762e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.608318387676134e-05</v>
+        <v>2.578335215828492e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.06968833813048e-05</v>
+        <v>4.037970530813412e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.052119133674041e-05</v>
+        <v>4.022067786342143e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.064231989672454e-05</v>
+        <v>4.035250791059114e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.061727198236784e-05</v>
+        <v>4.030879618802079e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.06914609792507e-05</v>
+        <v>4.039464155029631e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.054434291546266e-05</v>
+        <v>4.025837653645794e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.065211427749545e-05</v>
+        <v>4.033588624358704e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.055857785639077e-05</v>
+        <v>4.139652223361452e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.255181202272064e-05</v>
+        <v>4.2251603454114e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.302163663853644e-05</v>
+        <v>4.270482979736957e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.054554947879198e-05</v>
+        <v>4.024233865350766e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.053872110888084e-05</v>
+        <v>4.02569841085599e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.062483027327055e-05</v>
+        <v>4.030043813310114e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.059977451602964e-05</v>
+        <v>4.030266840660594e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.057539114422808e-05</v>
+        <v>4.027663915876573e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.772608279743968e-05</v>
+        <v>4.742347449394627e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.077247163696136e-05</v>
+        <v>4.047661979288995e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.057910164966044e-05</v>
+        <v>4.02743559327361e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.053886825624225e-05</v>
+        <v>4.02397681618914e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.686923775217614e-05</v>
+        <v>3.656091322010844e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.06158165482643e-05</v>
+        <v>4.032386275483098e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.065594171639262e-05</v>
+        <v>4.037706894047352e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.345856762189204e-05</v>
+        <v>1.346646534323776e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.35344871163157e-05</v>
+        <v>1.354427162869862e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347875696255078e-05</v>
+        <v>1.348703839268194e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.345683319434104e-05</v>
+        <v>1.346346766670699e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.344920961598106e-05</v>
+        <v>1.345610667764808e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.347116977750508e-05</v>
+        <v>1.347703022435332e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.345702244469501e-05</v>
+        <v>1.346418562379768e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.346830823779118e-05</v>
+        <v>1.347616680352303e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.346412456375501e-05</v>
+        <v>1.347070470683227e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.346465218532323e-05</v>
+        <v>1.347229082348234e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34535373057279e-05</v>
+        <v>1.346159624192126e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.346313119074848e-05</v>
+        <v>1.346913236361163e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.345443010508963e-05</v>
+        <v>1.346170647934245e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.500818315217221e-05</v>
+        <v>1.50231502545743e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.345281394700206e-05</v>
+        <v>1.345855546216597e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.345312037209693e-05</v>
+        <v>1.345996766172563e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.345469865190761e-05</v>
+        <v>1.346338316605256e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.345990724841728e-05</v>
+        <v>1.346511262395807e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3463170297125e-05</v>
+        <v>1.347095383797871e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.398302950309273e-05</v>
+        <v>1.400463400857542e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.346084402060512e-05</v>
+        <v>1.346785820759749e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.407303767081769e-05</v>
+        <v>1.409756556424011e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.345697876107965e-05</v>
+        <v>1.346372978005451e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.345734270816117e-05</v>
+        <v>1.346494271087122e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.381662786015446e-05</v>
+        <v>1.383063190864566e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.346821724256003e-05</v>
+        <v>1.347610487970079e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.34643940935026e-05</v>
+        <v>1.347347130865084e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.354472016453583e-05</v>
+        <v>1.355672184666945e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.361752714353705e-05</v>
+        <v>1.362823930582176e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.36940661240082e-05</v>
+        <v>1.370883947186615e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.34952227436388e-05</v>
+        <v>1.349824953299813e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.348153358180077e-05</v>
+        <v>1.348642420356484e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.363795940973666e-05</v>
+        <v>1.363550017387519e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.353404718924801e-05</v>
+        <v>1.354084377704812e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.361621562718496e-05</v>
+        <v>1.362798403664767e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.358706110331587e-05</v>
+        <v>1.358971191241832e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.360092509946771e-05</v>
+        <v>1.361109534019466e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.351077136749908e-05</v>
+        <v>1.352393648567795e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.360297009010466e-05</v>
+        <v>1.36015465404088e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.351234473997013e-05</v>
+        <v>1.351994580809025e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.607916993018554e-05</v>
+        <v>1.609894962954048e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.35041767309978e-05</v>
+        <v>1.350087316717113e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.350782923917255e-05</v>
+        <v>1.351236743514314e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.351623613981322e-05</v>
+        <v>1.353393796103206e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.355408523306736e-05</v>
+        <v>1.354695570982389e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.357631796516523e-05</v>
+        <v>1.358755314116458e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.441204523033462e-05</v>
+        <v>1.444351349188369e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.356837783214051e-05</v>
+        <v>1.357410651767097e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.469275709883079e-05</v>
+        <v>1.473182473013366e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.353571927451506e-05</v>
+        <v>1.353956914656753e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.353266753910373e-05</v>
+        <v>1.354257926145482e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.416975808107864e-05</v>
+        <v>1.418380037824929e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.361014995933788e-05</v>
+        <v>1.362211474646996e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.361343644671351e-05</v>
+        <v>1.36337592285444e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.211784134886221e-05</v>
+        <v>1.182266975413061e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.201459437190587e-05</v>
+        <v>1.171030120890343e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.23458892391583e-05</v>
+        <v>1.205505181167286e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.209825019179754e-05</v>
+        <v>1.178880961871613e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.201213836720226e-05</v>
+        <v>1.170566386107348e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.226018849378951e-05</v>
+        <v>1.19420049464161e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.210038786160524e-05</v>
+        <v>1.179691927433215e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.222786608634775e-05</v>
+        <v>1.19322522109448e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.216912230515465e-05</v>
+        <v>1.185907337343515e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.218656929185511e-05</v>
+        <v>1.188847123334639e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.206102161372851e-05</v>
+        <v>1.176767101486341e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.220343979212459e-05</v>
+        <v>1.188700228704156e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.207110619322721e-05</v>
+        <v>4.117839694573052e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.206459715466085e-05</v>
+        <v>1.176136228835629e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.205285094415868e-05</v>
+        <v>1.173332400869964e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.205631215656764e-05</v>
+        <v>1.174927545236979e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.207413955307382e-05</v>
+        <v>1.178785514495219e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.213297304672357e-05</v>
+        <v>1.180739016758496e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.216983068295367e-05</v>
+        <v>1.187336936703917e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.204953870731377e-05</v>
+        <v>1.174713640939999e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.209545901117067e-05</v>
+        <v>1.179034737241867e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.240063859892139e-05</v>
+        <v>1.210460560569516e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.209989443507423e-05</v>
+        <v>1.179177030955449e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.204047118341357e-05</v>
+        <v>1.174125858319928e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.217537365277014e-05</v>
+        <v>1.186350512333201e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.222683825335191e-05</v>
+        <v>1.193155275288636e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.222706106660029e-05</v>
+        <v>1.194484285747499e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.373742777788609e-05</v>
+        <v>4.358625612140884e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.600176383527023e-05</v>
+        <v>4.570608664502582e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.049339107410486e-05</v>
+        <v>5.043603836092125e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.415508652921959e-05</v>
+        <v>2.37727803437957e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.373452688569036e-05</v>
+        <v>4.339935286563199e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.796367545412795e-05</v>
+        <v>4.744654887722895e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.361272008678016e-05</v>
+        <v>4.333416862409289e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.67075131433706e-05</v>
+        <v>4.657245214053695e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.622533993891029e-05</v>
+        <v>4.583828503393575e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.157544108293561e-05</v>
+        <v>5.138165582454352e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.374447662007754e-05</v>
+        <v>4.363216506267406e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.897171589722871e-05</v>
+        <v>4.84576424881657e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.565592670734366e-05</v>
+        <v>4.117839694573052e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.403277712404152e-05</v>
+        <v>4.375202973435695e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.285787269682265e-05</v>
+        <v>4.231931467288332e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.367856738787636e-05</v>
+        <v>4.333490085396972e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.251311930360168e-05</v>
+        <v>4.256305675169712e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.39035299957588e-05</v>
+        <v>4.32581195510837e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.400827173063642e-05</v>
+        <v>4.385937427031993e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.569789342279863e-05</v>
+        <v>4.544340397386276e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.798461824478452e-05</v>
+        <v>4.76739894113375e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.686471976737994e-05</v>
+        <v>4.671551753422174e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.463207689044763e-05</v>
+        <v>4.426853726901703e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.177720823181176e-05</v>
+        <v>4.158463071843226e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.789007437161981e-05</v>
+        <v>4.748035513070728e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.388250999423976e-05</v>
+        <v>4.374750122028851e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.750810415313966e-05</v>
+        <v>4.763981162399743e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.629343687853167e-05</v>
+        <v>1.30584086140675e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.325033729905557e-05</v>
+        <v>1.294604006884029e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3581632166308e-05</v>
+        <v>1.623479430166701e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.627384572146699e-05</v>
+        <v>1.59685521087103e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.324788129435199e-05</v>
+        <v>1.294140272101035e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.643578402345898e-05</v>
+        <v>1.317774380635303e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.333613078875495e-05</v>
+        <v>1.597666176432629e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.346360901349745e-05</v>
+        <v>1.316799107088164e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.634471783482412e-05</v>
+        <v>1.60388158634293e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.636216482152456e-05</v>
+        <v>1.606821372334056e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.623661714339797e-05</v>
+        <v>1.30034098748003e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.34391827192743e-05</v>
+        <v>1.312274114697844e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.330861779068836e-05</v>
+        <v>4.117839694573052e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.624400860347632e-05</v>
+        <v>1.299880134210095e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.320259522311905e-05</v>
+        <v>1.592288389099652e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.623190768623711e-05</v>
+        <v>1.592901794236394e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62497350827433e-05</v>
+        <v>1.596759763494636e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.630856857639304e-05</v>
+        <v>1.304312902752187e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.634542621262315e-05</v>
+        <v>1.605311185703334e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.334881583583381e-05</v>
+        <v>1.599109123729978e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.333120193832036e-05</v>
+        <v>1.302608623235557e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.658000085209657e-05</v>
+        <v>1.342112514960753e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.333563736222394e-05</v>
+        <v>1.302750916949136e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.340762560947025e-05</v>
+        <v>1.310924713052338e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.63509691824396e-05</v>
+        <v>1.309924398326888e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64024337830214e-05</v>
+        <v>1.611129524288055e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.346513636672522e-05</v>
+        <v>1.31828569519869e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.007283006629318e-05</v>
+        <v>1.977818459583239e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.996958308933685e-05</v>
+        <v>1.966581605060521e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.030087795658928e-05</v>
+        <v>2.001056665337464e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.005323890922851e-05</v>
+        <v>1.974432446041789e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.996712708463323e-05</v>
+        <v>1.966117870277526e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.021517721122049e-05</v>
+        <v>1.989751978811788e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.005537657903621e-05</v>
+        <v>1.975243411603394e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.018285480377872e-05</v>
+        <v>1.988776705264655e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.012411102258565e-05</v>
+        <v>1.981458821513695e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.014155800928608e-05</v>
+        <v>1.984398607504818e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.001601033115949e-05</v>
+        <v>1.972318585656518e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.015842850955557e-05</v>
+        <v>1.984251712874333e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.002609491065819e-05</v>
+        <v>4.117839694573052e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.001955267671097e-05</v>
+        <v>1.971684556719827e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.000780646620881e-05</v>
+        <v>1.968880728754161e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.001130087399861e-05</v>
+        <v>1.970479029407158e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.00291282705048e-05</v>
+        <v>1.974336998665398e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.008796176415454e-05</v>
+        <v>1.976290500928672e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.012481940038466e-05</v>
+        <v>1.982888420874094e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.00701427932469e-05</v>
+        <v>1.976804613701486e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.005044772860164e-05</v>
+        <v>1.974586221412044e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.035562731635236e-05</v>
+        <v>2.006012044739694e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.005488315250521e-05</v>
+        <v>1.974728515125626e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.005899410221487e-05</v>
+        <v>1.976098576280671e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.013036237020111e-05</v>
+        <v>1.981901996503379e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.018182697078288e-05</v>
+        <v>1.988706759458813e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.018204978403125e-05</v>
+        <v>1.990035769917677e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.155638092227224e-05</v>
+        <v>5.126956091201835e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.669700571822662e-05</v>
+        <v>7.641117276392205e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.702830058547901e-05</v>
+        <v>7.675592336669152e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.333904446576414e-05</v>
+        <v>6.304268155718401e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.538337813201333e-05</v>
+        <v>5.508683001586619e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.217708110108221e-05</v>
+        <v>8.187945385148445e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.678279920792597e-05</v>
+        <v>7.649779082935075e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.691027743266853e-05</v>
+        <v>7.663312376596342e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.685153365147536e-05</v>
+        <v>7.655994492845384e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.686898063817588e-05</v>
+        <v>7.658934278836503e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.674343296004921e-05</v>
+        <v>7.646854256988212e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.688585113844531e-05</v>
+        <v>7.658787384205979e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.718529370897115e-05</v>
+        <v>4.117839694573052e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.255630248948489e-05</v>
+        <v>6.226584532338312e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.122639672222029e-05</v>
+        <v>6.09191196448235e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.653385476214459e-05</v>
+        <v>4.6233183067068e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.675655089939452e-05</v>
+        <v>7.648872669997085e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.681538439304432e-05</v>
+        <v>7.650826172260358e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.685224202927445e-05</v>
+        <v>7.657424092205781e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.447592595060182e-05</v>
+        <v>6.418703044038951e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.988014687786264e-05</v>
+        <v>6.958996309552842e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.708801109394094e-05</v>
+        <v>7.681044029597475e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.889108805177423e-05</v>
+        <v>4.859025541082715e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001018886269804813</v>
+        <v>0.0001016174099850623</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.114499534739788e-05</v>
+        <v>5.084129062956022e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.690924959967261e-05</v>
+        <v>7.663242430790505e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001032788073421857</v>
+        <v>0.0001030256086449559</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.334237957543503e-05</v>
+        <v>3.304191872510958e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.918944281481733e-05</v>
+        <v>3.888048775286318e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.952073768206975e-05</v>
+        <v>3.922523835563263e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.789979148671545e-05</v>
+        <v>3.758554423442672e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.546989746386249e-05</v>
+        <v>2.515731481166708e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.943503716949268e-05</v>
+        <v>3.911219173759584e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.927523630451668e-05</v>
+        <v>3.896710581829184e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.940271452925921e-05</v>
+        <v>3.910243875490451e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.934397074806612e-05</v>
+        <v>3.902925991739489e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.936141773476656e-05</v>
+        <v>3.905865777730617e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.923587005663996e-05</v>
+        <v>3.893785755882316e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.937828823503607e-05</v>
+        <v>3.905718883100134e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.924595463613868e-05</v>
+        <v>4.117839694573052e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.121137092193741e-05</v>
+        <v>4.090368208106083e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.162848458631657e-05</v>
+        <v>4.130454889313274e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.923116083227081e-05</v>
+        <v>3.891946224354968e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.924898799598528e-05</v>
+        <v>3.895804168891187e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.930782148963505e-05</v>
+        <v>3.897757671154468e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.934467912586513e-05</v>
+        <v>3.904355591099886e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.928792135159555e-05</v>
+        <v>3.898153529126537e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.613683787637975e-05</v>
+        <v>4.582778832418769e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.957548704183286e-05</v>
+        <v>3.92747921496549e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.927474287798571e-05</v>
+        <v>3.896195685351424e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.927885382769537e-05</v>
+        <v>3.897565746506463e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.576271424989731e-05</v>
+        <v>3.544580558696838e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.940168669626341e-05</v>
+        <v>3.910173929684612e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.940190950951174e-05</v>
+        <v>3.911502940143472e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.345430853666623e-05</v>
+        <v>1.34536987171587e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.351680326145907e-05</v>
+        <v>1.351849681435856e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347308693722402e-05</v>
+        <v>1.347250452342797e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.343573064770414e-05</v>
+        <v>1.343502122143537e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.34370986189834e-05</v>
+        <v>1.343592770667736e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.346141541006911e-05</v>
+        <v>1.346024080263274e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.345401115451946e-05</v>
+        <v>1.345343462831851e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.343823912350158e-05</v>
+        <v>1.343808270658372e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.345101596915689e-05</v>
+        <v>1.345018792875419e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.344781409070124e-05</v>
+        <v>1.344724803683534e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.345051230786958e-05</v>
+        <v>1.345041867541864e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344388662933499e-05</v>
+        <v>1.344290425386707e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.344387214723021e-05</v>
+        <v>1.344324982859843e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.496214079090994e-05</v>
+        <v>1.495975204377937e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343926070911796e-05</v>
+        <v>1.343841496155345e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.344723475675952e-05</v>
+        <v>1.344656245419342e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.344871712950518e-05</v>
+        <v>1.344867948096995e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344741850122864e-05</v>
+        <v>1.344603506167148e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344483232704047e-05</v>
+        <v>1.344441662817757e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.395428692463048e-05</v>
+        <v>1.395498874058909e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34456943558623e-05</v>
+        <v>1.344508282105596e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.403221102885771e-05</v>
+        <v>1.403299162101448e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344560801846536e-05</v>
+        <v>1.344493328019817e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.344642097609304e-05</v>
+        <v>1.344575674028578e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.379292607128465e-05</v>
+        <v>1.379697950221665e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.344446356889115e-05</v>
+        <v>1.344441058990458e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.3447573837048e-05</v>
+        <v>1.344725206838595e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.358157364023291e-05</v>
+        <v>1.358099864774307e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.355677553416964e-05</v>
+        <v>1.355960124932224e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.371688895211414e-05</v>
+        <v>1.371651487994393e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.340534585720684e-05</v>
+        <v>1.340406192226052e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.346276326799576e-05</v>
+        <v>1.345818196014144e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.364233644532274e-05</v>
+        <v>1.363776374444977e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.358259020968529e-05</v>
+        <v>1.358226132212398e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.346762217197796e-05</v>
+        <v>1.347029820635837e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.356347225477451e-05</v>
+        <v>1.356135379950281e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.354763126239543e-05</v>
+        <v>1.354737214735992e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.356710692947172e-05</v>
+        <v>1.357019364394801e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.354212891675131e-05</v>
+        <v>1.353896284728466e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.350739111990386e-05</v>
+        <v>1.350672989733251e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.598898240502055e-05</v>
+        <v>1.59850262632102e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.347096425213026e-05</v>
+        <v>1.346871171916478e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.353376217742033e-05</v>
+        <v>1.353274481295613e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.354137023158689e-05</v>
+        <v>1.354490339994602e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.354254598459221e-05</v>
+        <v>1.353650222140012e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.352106504475784e-05</v>
+        <v>1.352188036407819e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.435297650813218e-05</v>
+        <v>1.43583655206433e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352615424351229e-05</v>
+        <v>1.352556727020363e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.456530992514543e-05</v>
+        <v>1.456741697141588e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.352003051380987e-05</v>
+        <v>1.351899584340583e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.352593699565214e-05</v>
+        <v>1.35249769739857e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.411520746041703e-05</v>
+        <v>1.412217282765588e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.350962231154565e-05</v>
+        <v>1.35130248087499e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.356345340805894e-05</v>
+        <v>1.356493044229018e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.218165241780322e-05</v>
+        <v>1.185443157680595e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.193096488027356e-05</v>
+        <v>1.160291186853164e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.239376309059673e-05</v>
+        <v>1.206685180971575e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.197180661572605e-05</v>
+        <v>1.164346067053854e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.198725848062485e-05</v>
+        <v>1.165369983835058e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.226192782221388e-05</v>
+        <v>1.192832744174331e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.217829334965577e-05</v>
+        <v>1.185144857186916e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.200014100381635e-05</v>
+        <v>1.167804155364191e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.213293906951843e-05</v>
+        <v>1.180325230819489e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.210829466303841e-05</v>
+        <v>1.1781568175094e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.213877226719518e-05</v>
+        <v>1.181738199645828e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.209865607672438e-05</v>
+        <v>1.17673293219705e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.20637685981489e-05</v>
+        <v>4.489367678312357e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.200471860319722e-05</v>
+        <v>1.167657549049556e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.201168028330514e-05</v>
+        <v>1.168179452636986e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.210175081965933e-05</v>
+        <v>1.177382420377006e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.211849490174696e-05</v>
+        <v>1.179773699509141e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.210382629796487e-05</v>
+        <v>1.176786706262223e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.20746142708102e-05</v>
+        <v>1.17495861117923e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.199570080521491e-05</v>
+        <v>1.167797865239112e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.203600372790273e-05</v>
+        <v>1.170875985880199e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.224896937303689e-05</v>
+        <v>1.192253936939657e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.208337606228716e-05</v>
+        <v>1.175542193403661e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.202179232664857e-05</v>
+        <v>1.169560735526014e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.21241070727168e-05</v>
+        <v>1.17965600595523e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.207044897787657e-05</v>
+        <v>1.17495179067212e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.214956214629988e-05</v>
+        <v>1.18255634935874e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.725844172142998e-05</v>
+        <v>4.695538435177079e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.474175035936931e-05</v>
+        <v>4.442541761241058e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.198807653164831e-05</v>
+        <v>5.169383346767035e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.902217997650311e-05</v>
+        <v>1.869893705834226e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.581729494346718e-05</v>
+        <v>4.539341970612978e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.436043671437599e-05</v>
+        <v>5.395522611752534e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.89406910654529e-05</v>
+        <v>4.864946540707762e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.423617784062014e-05</v>
+        <v>4.403833644653548e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.954573131366914e-05</v>
+        <v>4.920384765189012e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.277258612878491e-05</v>
+        <v>5.248083353420992e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.347029329210338e-05</v>
+        <v>5.326505212749366e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.462694399694086e-05</v>
+        <v>5.425309542861056e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.622544223439821e-05</v>
+        <v>4.489367678312357e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.63572160558892e-05</v>
+        <v>4.603853183287432e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.22581009991017e-05</v>
+        <v>4.190815375647915e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.723507522896151e-05</v>
+        <v>4.692066011730673e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.589894529100641e-05</v>
+        <v>4.573174094624433e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>5.143011789994546e-05</v>
+        <v>5.099108616487394e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.919637251500335e-05</v>
+        <v>4.893747878710668e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.62281409074896e-05</v>
+        <v>4.6066478004875e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.874086157366056e-05</v>
+        <v>4.843757956271169e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.69215456674559e-05</v>
+        <v>4.663499233388156e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.570774153437195e-05</v>
+        <v>4.539284947838136e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.593940928768233e-05</v>
+        <v>4.562658907223986e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.763538899565868e-05</v>
+        <v>4.732685272815245e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.421742039852665e-05</v>
+        <v>4.403511976993195e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.001626691671269e-05</v>
+        <v>4.97815291931481e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349854197463751e-05</v>
+        <v>1.317786650636367e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.638074858366655e-05</v>
+        <v>1.292634679808937e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.371065264743102e-05</v>
+        <v>1.65223724573515e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.328869617256035e-05</v>
+        <v>1.609898131817425e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.643704218401789e-05</v>
+        <v>1.297713476790829e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.671171152560688e-05</v>
+        <v>1.3251762371301e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.349518290649007e-05</v>
+        <v>1.630696921950487e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.331703056065065e-05</v>
+        <v>1.613356220127761e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.344982862635271e-05</v>
+        <v>1.31266872377526e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.342518421987271e-05</v>
+        <v>1.623708882272972e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.345566182402947e-05</v>
+        <v>1.3140816926016e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.654843978011736e-05</v>
+        <v>1.622284996960616e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.338318969959034e-05</v>
+        <v>4.489367678312357e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.646246211456352e-05</v>
+        <v>1.614346239447391e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.323744025043359e-05</v>
+        <v>1.614879145720301e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.655153452305232e-05</v>
+        <v>1.622934485140572e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.343538445858125e-05</v>
+        <v>1.625325764272714e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.342071585479916e-05</v>
+        <v>1.309130199217992e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.652439797420319e-05</v>
+        <v>1.307302104135001e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.338335682807459e-05</v>
+        <v>1.307052952122528e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.648578743129575e-05</v>
+        <v>1.616428050643766e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.365167989069269e-05</v>
+        <v>1.638920789474357e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.340026561912145e-05</v>
+        <v>1.307885686359432e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34823876816398e-05</v>
+        <v>1.316116605889381e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65738907761098e-05</v>
+        <v>1.311999498911002e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.652023268126956e-05</v>
+        <v>1.620503855435687e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.346923311219694e-05</v>
+        <v>1.31516080000888e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.072191864614335e-05</v>
+        <v>2.037940112599153e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.047123110861368e-05</v>
+        <v>2.012788141771722e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.093402931893687e-05</v>
+        <v>2.059182135890135e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.051207284406618e-05</v>
+        <v>2.016843021972412e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.052752470896496e-05</v>
+        <v>2.017866938753617e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.080219405055402e-05</v>
+        <v>2.045329699092886e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.071855957799593e-05</v>
+        <v>2.037641812105475e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.054040723215648e-05</v>
+        <v>2.020301110282749e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.067320529785855e-05</v>
+        <v>2.032822185738046e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.064856089137855e-05</v>
+        <v>2.030653772427956e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.067903849553531e-05</v>
+        <v>2.034235154564386e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.063892230506451e-05</v>
+        <v>2.029229887115607e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.060403482648902e-05</v>
+        <v>4.489367678312357e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.054495199409752e-05</v>
+        <v>2.020151352283034e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.055191367420547e-05</v>
+        <v>2.020673255870466e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.064201704799946e-05</v>
+        <v>2.029879375295558e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.065876113008709e-05</v>
+        <v>2.032270654427701e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.064409252630499e-05</v>
+        <v>2.029283661180783e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.061488049915035e-05</v>
+        <v>2.027455566097789e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.060818243499927e-05</v>
+        <v>2.027320116442099e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.057626995624287e-05</v>
+        <v>2.02337294079876e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.078923560137705e-05</v>
+        <v>2.044750891858213e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.062364229062731e-05</v>
+        <v>2.028039148322217e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.063282502101407e-05</v>
+        <v>2.028969284372214e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.066437330105691e-05</v>
+        <v>2.032152960873787e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.061071520621669e-05</v>
+        <v>2.027448745590676e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.068982837464003e-05</v>
+        <v>2.035053304277296e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.447586944733628e-05</v>
+        <v>5.414293887413317e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.12962672045319e-05</v>
+        <v>8.095823663478393e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.17590654148552e-05</v>
+        <v>8.142217657596797e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.692255456663333e-05</v>
+        <v>6.658650355479973e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.849883421321735e-05</v>
+        <v>5.815890096134926e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.724059603440309e-05</v>
+        <v>8.689613313443877e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.154359567391411e-05</v>
+        <v>8.120677333812137e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.136544332807474e-05</v>
+        <v>8.103336631989423e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.149824139377681e-05</v>
+        <v>8.115857707444713e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.147359698729674e-05</v>
+        <v>8.113689294134632e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.150407459145351e-05</v>
+        <v>8.117270676271052e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.14639584009821e-05</v>
+        <v>8.112265408822176e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.044445092636323e-05</v>
+        <v>4.489367678312357e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.615215671530204e-05</v>
+        <v>6.581643517974179e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.474554720814574e-05</v>
+        <v>6.440830588147466e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.907588172014082e-05</v>
+        <v>4.874308409724382e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.148379722600534e-05</v>
+        <v>8.115306176134371e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.146912862222324e-05</v>
+        <v>8.112319182887446e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.143991659506858e-05</v>
+        <v>8.110491087804451e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.821988251740306e-05</v>
+        <v>6.789237260114255e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.400363684420566e-05</v>
+        <v>7.36673141348655e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.161959194615692e-05</v>
+        <v>8.128318354569104e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.153862572410185e-05</v>
+        <v>5.120540943408614e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001083759895205586</v>
+        <v>0.0001080335177920786</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.391546479419681e-05</v>
+        <v>5.358228732588904e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.143575130213495e-05</v>
+        <v>8.110484267297343e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001097928767127596</v>
+        <v>0.0001094544424010554</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.754894986985117e-05</v>
+        <v>3.721126398642126e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.439982269383969e-05</v>
+        <v>4.405813193827457e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.486262090416287e-05</v>
+        <v>4.452207187945871e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.280165347256435e-05</v>
+        <v>4.246040203766005e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.808508110826923e-05</v>
+        <v>2.774519865194972e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.473078590615528e-05</v>
+        <v>4.43835477916985e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.464715116322196e-05</v>
+        <v>4.430666864161208e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.446899881738248e-05</v>
+        <v>4.413326162338484e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.460179688308457e-05</v>
+        <v>4.425847237793781e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.457715247660451e-05</v>
+        <v>4.423678824483688e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.460763008076132e-05</v>
+        <v>4.427260206620121e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.456751389029048e-05</v>
+        <v>4.42225493917134e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.453262641171505e-05</v>
+        <v>4.489367678312357e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.682702458184587e-05</v>
+        <v>4.648419230933132e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.734582080068795e-05</v>
+        <v>4.700101721686202e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.457060890360069e-05</v>
+        <v>4.422904455372518e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.45873527153131e-05</v>
+        <v>4.425295706483434e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.457268411153101e-05</v>
+        <v>4.422308713236512e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.454347208437635e-05</v>
+        <v>4.420480618153521e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.453532508480642e-05</v>
+        <v>4.420231466141052e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.269991017952239e-05</v>
+        <v>5.235536735472787e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.471782718660298e-05</v>
+        <v>4.437775943913944e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.45522338758533e-05</v>
+        <v>4.421064200377949e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.456141660624007e-05</v>
+        <v>4.421994336427951e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.031135559103648e-05</v>
+        <v>3.997208369476596e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.453930679144267e-05</v>
+        <v>4.420473797646408e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.461841995986603e-05</v>
+        <v>4.428078356333026e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.351276099408994e-05</v>
+        <v>1.35212199505113e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3574564078592e-05</v>
+        <v>1.358725930835996e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.353462751460458e-05</v>
+        <v>1.354296653877448e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.350021629763833e-05</v>
+        <v>1.350869081668343e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.349513960213262e-05</v>
+        <v>1.350357741257587e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.352583987163872e-05</v>
+        <v>1.353411392557181e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.351233887136128e-05</v>
+        <v>1.352093872982523e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.35211678946045e-05</v>
+        <v>1.353017894316742e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35146851958083e-05</v>
+        <v>1.352315542735606e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.353443522092226e-05</v>
+        <v>1.354310253008317e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35290241821801e-05</v>
+        <v>1.353764838385754e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.352553081440389e-05</v>
+        <v>1.353407008467976e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.350004665414544e-05</v>
+        <v>1.350850841927277e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.505299849991349e-05</v>
+        <v>1.506979605397166e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.349267117348904e-05</v>
+        <v>1.350113996104933e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.350802131835017e-05</v>
+        <v>1.351643658182052e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.351351557812595e-05</v>
+        <v>1.352220123850123e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.350533645538921e-05</v>
+        <v>1.351364748047672e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.350505722396186e-05</v>
+        <v>1.351383719726319e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.40351432670236e-05</v>
+        <v>1.405585626844407e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.350661782227062e-05</v>
+        <v>1.351523895697728e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.411801398635515e-05</v>
+        <v>1.414090821681645e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.349505423019024e-05</v>
+        <v>1.350350364852782e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.351430674355908e-05</v>
+        <v>1.352280787480032e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.387032130600071e-05</v>
+        <v>1.388952571821216e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.352107572915933e-05</v>
+        <v>1.352962214728451e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35152599848291e-05</v>
+        <v>1.35236809721541e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.369524377446481e-05</v>
+        <v>1.370234264974037e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.366583892301748e-05</v>
+        <v>1.367980571721002e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386246857581951e-05</v>
+        <v>1.386871875554433e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.356478137166407e-05</v>
+        <v>1.357199192397275e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.357758716082211e-05</v>
+        <v>1.358454051877205e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.380305051726197e-05</v>
+        <v>1.380884561825755e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.369968674109199e-05</v>
+        <v>1.37078029260491e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.376259065939623e-05</v>
+        <v>1.377364049812851e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.371949380485502e-05</v>
+        <v>1.372667827193978e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.386627354835522e-05</v>
+        <v>1.387485898238896e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.383490043881033e-05</v>
+        <v>1.384317082747553e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.382932133605331e-05</v>
+        <v>1.383706079210508e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.360816594988304e-05</v>
+        <v>1.361528747650626e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.612015595887765e-05</v>
+        <v>1.61410303472376e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.355253105058182e-05</v>
+        <v>1.355969963392583e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.367167626285606e-05</v>
+        <v>1.367846767267778e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.370722387788048e-05</v>
+        <v>1.371595132193709e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.365255140326162e-05</v>
+        <v>1.365860479704613e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.365271199482954e-05</v>
+        <v>1.366210447132188e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.452699027568013e-05</v>
+        <v>1.45545798512793e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.366196586252157e-05</v>
+        <v>1.36702153165781e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.474865109040163e-05</v>
+        <v>1.478048206593175e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.357674026872542e-05</v>
+        <v>1.358377524411817e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.370727255088208e-05</v>
+        <v>1.371467536087792e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.427465229404318e-05</v>
+        <v>1.430013939705122e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.375502003558723e-05</v>
+        <v>1.376274575430764e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.374808629947957e-05</v>
+        <v>1.375496891105973e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.239131066759556e-05</v>
+        <v>1.203879728097558e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.212005233801625e-05</v>
+        <v>1.176727083848372e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.263830307590612e-05</v>
+        <v>1.228443499933299e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.224961255033057e-05</v>
+        <v>1.189727495070347e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.219226893919811e-05</v>
+        <v>1.183951669902637e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.253904260609126e-05</v>
+        <v>1.218444066080553e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.238654259719138e-05</v>
+        <v>1.203562076395835e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.248627047627406e-05</v>
+        <v>1.213999322436666e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.240150683969126e-05</v>
+        <v>1.204912005603023e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.263613103030505e-05</v>
+        <v>1.228597108372379e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.257501085851304e-05</v>
+        <v>1.22243639930741e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.256875350349999e-05</v>
+        <v>1.22172620355181e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.224769634903825e-05</v>
+        <v>4.51434178881662e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.213582545791477e-05</v>
+        <v>1.178333486153332e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.216438690213608e-05</v>
+        <v>1.181198456275108e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.233777384975782e-05</v>
+        <v>1.198476693115476e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.239983404140974e-05</v>
+        <v>1.204988138023647e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.230744708751537e-05</v>
+        <v>1.195326274842664e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.23042930400913e-05</v>
+        <v>1.195540568680397e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.222359679073386e-05</v>
+        <v>1.18756471954947e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.227347769149797e-05</v>
+        <v>1.192279632598906e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.248913209631663e-05</v>
+        <v>1.213848058268066e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.219130462383608e-05</v>
+        <v>1.183868350017066e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.234105561447351e-05</v>
+        <v>1.19930411252143e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.235874215548852e-05</v>
+        <v>1.200757991595783e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.248522942517247e-05</v>
+        <v>1.213370395873049e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.246330268270741e-05</v>
+        <v>1.21104490839985e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.611536385633677e-05</v>
+        <v>4.578224161689731e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.674265026588307e-05</v>
+        <v>4.640776041028914e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.626843965582342e-05</v>
+        <v>5.591512338005113e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.239811825900947e-05</v>
+        <v>2.206841904954581e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.679682027879529e-05</v>
+        <v>4.64622732679842e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.622288570189371e-05</v>
+        <v>5.586105533556678e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.989474877775659e-05</v>
+        <v>4.959583112807885e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.160197927883647e-05</v>
+        <v>5.138467470393014e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.193836073017684e-05</v>
+        <v>5.161014392506056e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.891307063323789e-05</v>
+        <v>5.862133182264848e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>6.158698273811584e-05</v>
+        <v>6.128280481818874e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.215726423871074e-05</v>
+        <v>6.184482715387985e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.365901368684117e-05</v>
+        <v>4.51434178881662e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.499677755395168e-05</v>
+        <v>4.466409031622833e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.244870451476836e-05</v>
+        <v>4.211730936601608e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.048535347960445e-05</v>
+        <v>5.014576867337112e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.968359800537417e-05</v>
+        <v>4.940124476139383e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.996822213465761e-05</v>
+        <v>4.961089018006313e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>5.102842417650595e-05</v>
+        <v>5.076072352939727e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.370262913299315e-05</v>
+        <v>5.337958028375688e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.031531663117918e-05</v>
+        <v>5.001102079096687e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.137625470914836e-05</v>
+        <v>5.107590698724714e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.665664065630461e-05</v>
+        <v>4.63237759261691e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.694067887571206e-05</v>
+        <v>4.661750115285702e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.813499859735693e-05</v>
+        <v>4.782298261029234e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.800116517514144e-05</v>
+        <v>4.768687622496435e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.320771791768172e-05</v>
+        <v>5.287197255201616e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.363176448982887e-05</v>
+        <v>1.624687311349246e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.336050616024957e-05</v>
+        <v>1.301538421931004e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.387875689813944e-05</v>
+        <v>1.35325483801593e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.644557458634248e-05</v>
+        <v>1.314538833152977e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.638823097521002e-05</v>
+        <v>1.604759253154321e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.377949642832458e-05</v>
+        <v>1.639251649332237e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.362699641942469e-05</v>
+        <v>1.624369659647519e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.372672429850739e-05</v>
+        <v>1.634806905688352e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.364196066192457e-05</v>
+        <v>1.625719588854709e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.387658485253835e-05</v>
+        <v>1.649404691624064e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.677097289452494e-05</v>
+        <v>1.347247737390042e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.676471553951191e-05</v>
+        <v>1.642533786803495e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.349030146576408e-05</v>
+        <v>4.51434178881662e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33784305746406e-05</v>
+        <v>1.600161795437108e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.331845103770265e-05</v>
+        <v>1.297304060909203e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.357822767199115e-05</v>
+        <v>1.619284276367161e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.659579607742167e-05</v>
+        <v>1.329799476106278e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.354790090974869e-05</v>
+        <v>1.616133858094349e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65002550761032e-05</v>
+        <v>1.32035190676303e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35317656174236e-05</v>
+        <v>1.318745306740801e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.646943972750989e-05</v>
+        <v>1.317090970681537e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.381046757571525e-05</v>
+        <v>1.346769185221521e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.34317584460694e-05</v>
+        <v>1.604675933268751e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.371790888669884e-05</v>
+        <v>1.337364766720493e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.655470419150045e-05</v>
+        <v>1.325569329678415e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.668119146118439e-05</v>
+        <v>1.634177979124734e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.370656051495169e-05</v>
+        <v>1.336101040764785e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.036006296249538e-05</v>
+        <v>2.0004858949821e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.008880463291609e-05</v>
+        <v>1.973333250732911e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.060705537080594e-05</v>
+        <v>2.025049666817836e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.021836484523039e-05</v>
+        <v>1.986333661954887e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.016102123409794e-05</v>
+        <v>1.980557836787175e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.050779490099109e-05</v>
+        <v>2.01505023296509e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.03552948920912e-05</v>
+        <v>2.000168243280374e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.045502277117392e-05</v>
+        <v>2.010605489321204e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.037025913459108e-05</v>
+        <v>2.001518172487563e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.060488332520489e-05</v>
+        <v>2.025203275256917e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.054376315341287e-05</v>
+        <v>2.019042566191949e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.053750579839981e-05</v>
+        <v>2.018332370436349e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.021644864393808e-05</v>
+        <v>4.51434178881662e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.010454487487226e-05</v>
+        <v>1.974936477425401e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.013310631909355e-05</v>
+        <v>1.977801447547177e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.030652614465764e-05</v>
+        <v>1.995082860000015e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.036858633630957e-05</v>
+        <v>2.001594304908184e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.02761993824152e-05</v>
+        <v>1.991932441727202e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.027304533499113e-05</v>
+        <v>1.992146735564936e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.026246563650607e-05</v>
+        <v>1.99068652806213e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.024222998639778e-05</v>
+        <v>1.988885799483445e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.045788439121647e-05</v>
+        <v>2.010454225152604e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.01600569187359e-05</v>
+        <v>1.980474516901605e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.037752291382979e-05</v>
+        <v>2.002279528514668e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.032749445038834e-05</v>
+        <v>1.997364158480324e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04539817200723e-05</v>
+        <v>2.00997656275759e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.043205497760727e-05</v>
+        <v>2.007651075284389e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.184926123297416e-05</v>
+        <v>5.150109494472759e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.683995572596561e-05</v>
+        <v>7.649671405566552e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.735820646385549e-05</v>
+        <v>7.701387821651481e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.351827124035019e-05</v>
+        <v>6.317270849396941e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.558573651219603e-05</v>
+        <v>5.523814033716629e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.249717647844342e-05</v>
+        <v>8.215319110895322e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.710644598514075e-05</v>
+        <v>7.676506398114017e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.72061738642234e-05</v>
+        <v>7.686943644154845e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.712141022764059e-05</v>
+        <v>7.677856327321196e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.735603441825442e-05</v>
+        <v>7.701541430090555e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.729491424646232e-05</v>
+        <v>7.695380721025595e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.72886568914493e-05</v>
+        <v>7.694670525269968e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.738536006802438e-05</v>
+        <v>4.51434178881662e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.26548586700462e-05</v>
+        <v>6.230898883725432e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.136431641912398e-05</v>
+        <v>6.101826369445538e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.683117410838117e-05</v>
+        <v>4.648149379804776e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.711973742935912e-05</v>
+        <v>7.677932459741827e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.702735047546467e-05</v>
+        <v>7.668270596560842e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.702419642804062e-05</v>
+        <v>7.668484890398584e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.468307979977423e-05</v>
+        <v>6.433738551490287e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.009098935723703e-05</v>
+        <v>6.974762615495241e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.721400018637183e-05</v>
+        <v>7.687288952238966e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.900001305768693e-05</v>
+        <v>4.86511944663314e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001022492861567638</v>
+        <v>0.0001019107074517904</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.134743897731262e-05</v>
+        <v>5.100052737852356e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.720513281312176e-05</v>
+        <v>7.686314717591222e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001035714281681611</v>
+        <v>0.0001032335386401805</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.475501810218042e-05</v>
+        <v>3.440230656864642e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.075161463716116e-05</v>
+        <v>4.03996381258554e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.126986537505102e-05</v>
+        <v>4.091680228670463e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.943457970137688e-05</v>
+        <v>3.908281557722196e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.637471479572581e-05</v>
+        <v>2.602045503205565e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.117060515033077e-05</v>
+        <v>4.081680820203948e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.101810489633629e-05</v>
+        <v>4.066798805132994e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.111783277541897e-05</v>
+        <v>4.077236051173831e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.103306913883615e-05</v>
+        <v>4.06814873434019e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.126769332944992e-05</v>
+        <v>4.091833837109544e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.120657315765794e-05</v>
+        <v>4.085673128044577e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.120031580264485e-05</v>
+        <v>4.084962932288977e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.087925864818315e-05</v>
+        <v>4.51434178881662e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.284454697843612e-05</v>
+        <v>4.24931938196269e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.332485486195346e-05</v>
+        <v>4.297366226026264e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.096933639399735e-05</v>
+        <v>4.06171344723887e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.103139634055466e-05</v>
+        <v>4.068224866760811e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.093900938666025e-05</v>
+        <v>4.05856300357983e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.093585533923617e-05</v>
+        <v>4.058777297417562e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.092287409433517e-05</v>
+        <v>4.057170697395332e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.81380101600236e-05</v>
+        <v>4.778929139244527e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.112069439546153e-05</v>
+        <v>4.077084787005229e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.082286692298091e-05</v>
+        <v>4.04710507875423e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.104033291807482e-05</v>
+        <v>4.068910090367294e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.721134542802883e-05</v>
+        <v>3.686038337891879e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.111679172431735e-05</v>
+        <v>4.076607124610213e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.109486498185227e-05</v>
+        <v>4.074281637137017e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.357393314974478e-05</v>
+        <v>1.358191623446899e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.363422398449054e-05</v>
+        <v>1.364615534097097e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.358559339309936e-05</v>
+        <v>1.359350600692677e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.356456535238226e-05</v>
+        <v>1.357255822292613e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.355074859698161e-05</v>
+        <v>1.355852964040293e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.36262602930761e-05</v>
+        <v>1.363420810496852e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.357251406950209e-05</v>
+        <v>1.358049621165296e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.358087183481089e-05</v>
+        <v>1.358896187974664e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.358624971494197e-05</v>
+        <v>1.359425353385227e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.359603543028923e-05</v>
+        <v>1.360416419635227e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35796742123719e-05</v>
+        <v>1.35877170686876e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.359326669849969e-05</v>
+        <v>1.360136814695856e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.355789563110006e-05</v>
+        <v>1.35657856526933e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.514485236598455e-05</v>
+        <v>1.515994446452488e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.354943930010243e-05</v>
+        <v>1.355734898644996e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.356608634223108e-05</v>
+        <v>1.357400876572287e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.357324495640651e-05</v>
+        <v>1.358142665294142e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.355685716380997e-05</v>
+        <v>1.356480281357134e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.356570844126089e-05</v>
+        <v>1.357377931202621e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.410573078852263e-05</v>
+        <v>1.413575094027547e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.356867954197616e-05</v>
+        <v>1.357672640954988e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.425168573086539e-05</v>
+        <v>1.428587802262302e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.355111183684484e-05</v>
+        <v>1.355897771581821e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.358966122598647e-05</v>
+        <v>1.359765350673753e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.393369658880539e-05</v>
+        <v>1.395169812056492e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.358758323884072e-05</v>
+        <v>1.359561443794518e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.357592142669048e-05</v>
+        <v>1.358388768107922e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.38096777239995e-05</v>
+        <v>1.3816825253684e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.375527288529815e-05</v>
+        <v>1.376841596978118e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.390077130194973e-05</v>
+        <v>1.390742586420818e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.370805605265786e-05</v>
+        <v>1.371527714836899e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.364978924484497e-05</v>
+        <v>1.365550096884655e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.418816621526179e-05</v>
+        <v>1.419507040701752e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.380787641856199e-05</v>
+        <v>1.381502946289811e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.38644492487486e-05</v>
+        <v>1.387237025761199e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.390334359081576e-05</v>
+        <v>1.391064593816874e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.397797688173563e-05</v>
+        <v>1.398617313686463e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.386609059288132e-05</v>
+        <v>1.38736737728566e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3979517994757e-05</v>
+        <v>1.398756930012791e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.369669025660379e-05</v>
+        <v>1.370317745856315e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.628189142448592e-05</v>
+        <v>1.630041946235475e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.363782708569293e-05</v>
+        <v>1.364445574689723e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.375923413884614e-05</v>
+        <v>1.376595545644926e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.380933385784559e-05</v>
+        <v>1.381791245952455e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.369244510718009e-05</v>
+        <v>1.369932952071509e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.375773519873236e-05</v>
+        <v>1.376551891250635e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.462022809620442e-05</v>
+        <v>1.466358131098216e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.377843262782698e-05</v>
+        <v>1.378603665514673e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.526570402565833e-05</v>
+        <v>1.531832610893233e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.365517216574366e-05</v>
+        <v>1.366149339081185e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.392078922018613e-05</v>
+        <v>1.392800467620802e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.436476795633191e-05</v>
+        <v>1.438868049902275e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.390647541479375e-05</v>
+        <v>1.391396883335355e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.385646130747714e-05</v>
+        <v>1.386354041808529e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.257270867509863e-05</v>
+        <v>1.219917502505978e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.225987629016139e-05</v>
+        <v>1.188524582475869e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.270441648776564e-05</v>
+        <v>1.233008683653027e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.246689509448935e-05</v>
+        <v>1.209347197978525e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.231082848621762e-05</v>
+        <v>1.193501268671946e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.316376783070133e-05</v>
+        <v>1.278983575780075e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.255667951094865e-05</v>
+        <v>1.218313521411003e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.265108431487335e-05</v>
+        <v>1.227875882962837e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.270015304623917e-05</v>
+        <v>1.232685612725644e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.282236410139972e-05</v>
+        <v>1.245047598909958e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.263755661849151e-05</v>
+        <v>1.226469811607474e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.282450011526275e-05</v>
+        <v>1.245238674874548e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.239155752438377e-05</v>
+        <v>4.56482460140957e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.231419891411404e-05</v>
+        <v>1.193992703026586e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.229603937566087e-05</v>
+        <v>1.192167665719273e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.248407537452194e-05</v>
+        <v>1.210985652795707e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.256493521475869e-05</v>
+        <v>1.219364497648806e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.237982755862336e-05</v>
+        <v>1.200587106345892e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.24798068092204e-05</v>
+        <v>1.210726474289982e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.233349820698223e-05</v>
+        <v>1.196888795932624e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.246399599488129e-05</v>
+        <v>1.209120442654697e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.326115162219418e-05</v>
+        <v>1.289217279136561e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.231493144757124e-05</v>
+        <v>1.194007390466e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.267514880046268e-05</v>
+        <v>1.231101449162504e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.248114708982134e-05</v>
+        <v>1.210807994002773e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.272689271078869e-05</v>
+        <v>1.235390253480855e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.264014784157259e-05</v>
+        <v>1.226649905928443e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.844161429873779e-05</v>
+        <v>4.810539218254801e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.710567977333763e-05</v>
+        <v>4.67553141209811e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.485150241719822e-05</v>
+        <v>5.450637715240986e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.855496048526344e-05</v>
+        <v>2.822262331212652e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.67019547015289e-05</v>
+        <v>4.63285680941534e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>6.150061770038329e-05</v>
+        <v>6.11617050308425e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.247323475238958e-05</v>
+        <v>5.214316835601581e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.254838419459124e-05</v>
+        <v>5.223876392243324e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.387649938791709e-05</v>
+        <v>5.354796502430911e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.832656700334205e-05</v>
+        <v>5.802410801917189e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.758923039286654e-05</v>
+        <v>5.726964317716245e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.999639384547919e-05</v>
+        <v>5.969241397908524e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.195057358908892e-05</v>
+        <v>4.564824601409569e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.629776099156378e-05</v>
+        <v>4.595073635915338e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.508385816691617e-05</v>
+        <v>4.473555305184219e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.975504331959272e-05</v>
+        <v>4.941019010649173e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>5.067127658662873e-05</v>
+        <v>5.03817650111342e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.743452074189562e-05</v>
+        <v>4.709292340973161e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>5.030046171612604e-05</v>
+        <v>4.998677864458749e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.196773000274607e-05</v>
+        <v>5.163059128723773e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.058167324520853e-05</v>
+        <v>5.025887660711913e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>6.211293502447988e-05</v>
+        <v>6.185681548669891e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.822060751948883e-05</v>
+        <v>4.786625537573735e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.099268077705628e-05</v>
+        <v>5.065948455477219e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.97800096268365e-05</v>
+        <v>4.945263234914688e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.084540932374396e-05</v>
+        <v>5.052009197047775e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.386012369410276e-05</v>
+        <v>5.352754756524756e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.681710652349111e-05</v>
+        <v>1.645679066029204e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.650427413855386e-05</v>
+        <v>1.614286145999096e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.69488143361581e-05</v>
+        <v>1.658770247176255e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.671129294288182e-05</v>
+        <v>1.335607084316898e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.655522633461007e-05</v>
+        <v>1.619262832195173e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.740816567909384e-05</v>
+        <v>1.704745139303302e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.380891396407737e-05</v>
+        <v>1.64407508493423e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.390331876800207e-05</v>
+        <v>1.653637446486064e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.395238749936786e-05</v>
+        <v>1.358945499064018e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.706676194979217e-05</v>
+        <v>1.371307485248334e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.688195446688399e-05</v>
+        <v>1.652231375130702e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.706889796365523e-05</v>
+        <v>1.671000238397775e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.364574465342472e-05</v>
+        <v>4.564824601409569e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.657156788218267e-05</v>
+        <v>1.320435749222119e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.655342207246924e-05</v>
+        <v>1.619089456406503e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67284732229144e-05</v>
+        <v>1.636747216318932e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.381716966788743e-05</v>
+        <v>1.645126061172033e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.363206201175207e-05</v>
+        <v>1.626348669869118e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.672420465761286e-05</v>
+        <v>1.336986360628358e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.665311178643346e-05</v>
+        <v>1.629242385776929e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.371623044800998e-05</v>
+        <v>1.335380328993073e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.751844721293688e-05</v>
+        <v>1.716122406182341e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.356716590069998e-05</v>
+        <v>1.320267276804358e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.407164874293878e-05</v>
+        <v>1.370851325683093e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.373338154295005e-05</v>
+        <v>1.337067880341149e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.397912716391741e-05</v>
+        <v>1.661151817004081e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.389497071308407e-05</v>
+        <v>1.353126716101529e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.055900302558474e-05</v>
+        <v>2.018478565814634e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.02461706406475e-05</v>
+        <v>1.987085645784524e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.069071083825175e-05</v>
+        <v>2.031569746961682e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.045318944497549e-05</v>
+        <v>2.007908261287177e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.029712283670372e-05</v>
+        <v>1.992062331980599e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.115006218118756e-05</v>
+        <v>2.077544639088728e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.054297386143478e-05</v>
+        <v>2.016874584719657e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.063737866535947e-05</v>
+        <v>2.026436946271491e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.068644739672522e-05</v>
+        <v>2.031246676034296e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.080865845188582e-05</v>
+        <v>2.043608662218611e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.062385096897762e-05</v>
+        <v>2.025030874916128e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.081079446574888e-05</v>
+        <v>2.043799738183199e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.037785187486987e-05</v>
+        <v>4.564824601409569e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.030046044782571e-05</v>
+        <v>1.992550524716402e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.028230090937251e-05</v>
+        <v>1.990725487409091e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.047036972500808e-05</v>
+        <v>2.00954671610436e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.055122956524479e-05</v>
+        <v>2.017925560957459e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.036612190910949e-05</v>
+        <v>1.999148169654544e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04661011597065e-05</v>
+        <v>2.009287537598637e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.03977668620175e-05</v>
+        <v>2.002209928445266e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.04502903453674e-05</v>
+        <v>2.007681505963355e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.124744597268026e-05</v>
+        <v>2.087778342445214e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.030122579805737e-05</v>
+        <v>1.992568453774656e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.073665888200757e-05</v>
+        <v>2.036254538792233e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.046744144030746e-05</v>
+        <v>2.009369057311426e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.071318706127484e-05</v>
+        <v>2.033951316789509e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.062644219205871e-05</v>
+        <v>2.025210969237096e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.2076178287743e-05</v>
+        <v>5.170369396583843e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.706415407930634e-05</v>
+        <v>7.669103273803321e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.75086942769106e-05</v>
+        <v>7.713587374980482e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.379923885590851e-05</v>
+        <v>6.342708003754784e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.575586831650175e-05</v>
+        <v>5.538117347597077e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.32143330150015e-05</v>
+        <v>8.284200540791858e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.736095730009353e-05</v>
+        <v>7.698892212738453e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.745536210401818e-05</v>
+        <v>7.70845457429029e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.750443083538407e-05</v>
+        <v>7.7132643040531e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.762664189054464e-05</v>
+        <v>7.725626290237409e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.74418344076364e-05</v>
+        <v>7.707048502934928e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.762877790440808e-05</v>
+        <v>7.725817366202036e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.758347624489243e-05</v>
+        <v>4.564824601409569e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.289576420028942e-05</v>
+        <v>6.252274296867638e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.155647205621893e-05</v>
+        <v>6.118333598082759e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.701535871654599e-05</v>
+        <v>4.664209883773311e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.736921300390364e-05</v>
+        <v>7.699943188976267e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.718410534776821e-05</v>
+        <v>7.681165797673346e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.728408459836527e-05</v>
+        <v>7.691305165617439e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.48661682039409e-05</v>
+        <v>6.44927113461355e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.035556743330205e-05</v>
+        <v>6.998323740609147e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.807040174957301e-05</v>
+        <v>7.770293213314882e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.916508413518051e-05</v>
+        <v>4.879122770118344e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001027143607147813</v>
+        <v>0.0001023414673374164</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.151464120076547e-05</v>
+        <v>5.114261483816818e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.753117049993364e-05</v>
+        <v>7.715968944808309e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001038732353943809</v>
+        <v>0.0001035015760315023</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.396660891753891e-05</v>
+        <v>3.359755213408979e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.965774965418802e-05</v>
+        <v>3.928874408651531e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.010228985179221e-05</v>
+        <v>3.973358509828693e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.847907617722475e-05</v>
+        <v>3.811101299923349e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.586790478275451e-05</v>
+        <v>2.549506735607204e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.056164148777201e-05</v>
+        <v>4.019333431245508e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.995455287497523e-05</v>
+        <v>3.95866334758667e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.004895767889995e-05</v>
+        <v>3.968225709138501e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.009802641026572e-05</v>
+        <v>3.973035438901309e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.022023746542625e-05</v>
+        <v>3.985397425085622e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.00354299825181e-05</v>
+        <v>3.966819637783146e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.022237347928929e-05</v>
+        <v>3.985588501050213e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.978943088841038e-05</v>
+        <v>4.564824601409569e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.170178149925948e-05</v>
+        <v>4.133351496896284e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.211634951500743e-05</v>
+        <v>4.174807489273631e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.988194903159286e-05</v>
+        <v>3.951335508261138e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.996280857878527e-05</v>
+        <v>3.95971432382447e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.977770092264989e-05</v>
+        <v>3.940936932521555e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.987768017324695e-05</v>
+        <v>3.951076300465645e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.980658730206753e-05</v>
+        <v>3.943830648429364e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.679032561653527e-05</v>
+        <v>4.642448374454042e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.065902498622073e-05</v>
+        <v>4.029567105312231e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.971280481159785e-05</v>
+        <v>3.934357216641662e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.014823789554806e-05</v>
+        <v>3.978043301659241e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.625915867201663e-05</v>
+        <v>3.589102425920416e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.012476607481532e-05</v>
+        <v>3.975740079656521e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.003802120559918e-05</v>
+        <v>3.966999732104107e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.342320838036882e-05</v>
+        <v>1.341914514629238e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.349476262865162e-05</v>
+        <v>1.34891352076083e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.342989962550488e-05</v>
+        <v>1.342570539214742e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.341462480483204e-05</v>
+        <v>1.340950293939889e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.34138605503508e-05</v>
+        <v>1.340853728870288e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.343316671169107e-05</v>
+        <v>1.342738972883602e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341641205847546e-05</v>
+        <v>1.341166995429875e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.341687956220327e-05</v>
+        <v>1.341273331176118e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.342443664284949e-05</v>
+        <v>1.341925819007392e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.342428667842685e-05</v>
+        <v>1.341990715633537e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341687593284866e-05</v>
+        <v>1.341421273846514e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.342139140521794e-05</v>
+        <v>1.341562562891051e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.341794199989827e-05</v>
+        <v>1.341326317819973e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.493279824398525e-05</v>
+        <v>1.491947964576756e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.341811289437709e-05</v>
+        <v>1.341271220259807e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.341958749814631e-05</v>
+        <v>1.341480144357781e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.342465105053552e-05</v>
+        <v>1.342098081091204e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.342061253961583e-05</v>
+        <v>1.341471028676451e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.342514504665893e-05</v>
+        <v>1.342073367208771e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.392724779055349e-05</v>
+        <v>1.391995006274421e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.341992239204681e-05</v>
+        <v>1.341524767729105e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.399812846041629e-05</v>
+        <v>1.399053299088142e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341903642647454e-05</v>
+        <v>1.341422160842677e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.342042617072012e-05</v>
+        <v>1.341583276567208e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.375446135548663e-05</v>
+        <v>1.375139649640048e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.342000958809161e-05</v>
+        <v>1.341574272442905e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.342366031028963e-05</v>
+        <v>1.342042841642729e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.349712027617963e-05</v>
+        <v>1.349720584684245e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.353862458529696e-05</v>
+        <v>1.353253140063086e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.354369720051737e-05</v>
+        <v>1.354288094826289e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.339233942185647e-05</v>
+        <v>1.338489198533898e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.343378706173793e-05</v>
+        <v>1.342489182802959e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.357184358373095e-05</v>
+        <v>1.35597606903882e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34509580377428e-05</v>
+        <v>1.344621963877101e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.345274523036972e-05</v>
+        <v>1.345227246762234e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.350799484622974e-05</v>
+        <v>1.350016001932672e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.351786952140237e-05</v>
+        <v>1.351571247246893e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.345361359916252e-05</v>
+        <v>1.346368113814726e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.351567855094374e-05</v>
+        <v>1.350369952887032e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.345765388879248e-05</v>
+        <v>1.345336809899691e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.596398361398649e-05</v>
+        <v>1.594536971946246e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.345652109485041e-05</v>
+        <v>1.34470988677258e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.347228025443582e-05</v>
+        <v>1.346722895987636e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.350716171731257e-05</v>
+        <v>1.351010761422862e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.348319563368644e-05</v>
+        <v>1.347023090102278e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.351079715825943e-05</v>
+        <v>1.350842618698644e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.432515451059044e-05</v>
+        <v>1.431844100620736e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.347994788608828e-05</v>
+        <v>1.347568907512826e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.449620594978598e-05</v>
+        <v>1.448719117634384e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.346704028488417e-05</v>
+        <v>1.346178233581862e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.347818115851642e-05</v>
+        <v>1.347450440761933e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.402238567846988e-05</v>
+        <v>1.40183081418311e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.347275808600025e-05</v>
+        <v>1.347141246021198e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.352688814368534e-05</v>
+        <v>1.353282042307578e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.202682996380182e-05</v>
+        <v>1.172530773558669e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.188250074354578e-05</v>
+        <v>1.157353576025647e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.210241065573836e-05</v>
+        <v>1.179940873038135e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.192987452947391e-05</v>
+        <v>1.161639457309032e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.192124192353399e-05</v>
+        <v>1.160548710425769e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.213931389714531e-05</v>
+        <v>1.181843408811238e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.195006238155373e-05</v>
+        <v>1.164087200326036e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.195534305122169e-05</v>
+        <v>1.165288311496707e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.202920662317662e-05</v>
+        <v>1.171508926263739e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.20390098364088e-05</v>
+        <v>1.173391498956414e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.195530205599162e-05</v>
+        <v>1.166959392015826e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.203958747979804e-05</v>
+        <v>1.171893403447837e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.196734377373222e-05</v>
+        <v>4.250235099084591e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.196835611884423e-05</v>
+        <v>1.16597464261762e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.196927410548575e-05</v>
+        <v>1.165264467725914e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.198593043341047e-05</v>
+        <v>1.167624361522344e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.204312558699564e-05</v>
+        <v>1.174604241191306e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.199750874835102e-05</v>
+        <v>1.167521395708327e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.20487055004591e-05</v>
+        <v>1.174325086520289e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.194954103689409e-05</v>
+        <v>1.164309375945562e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.194153587234524e-05</v>
+        <v>1.163312070350078e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.213563632524577e-05</v>
+        <v>1.182733733559261e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.197970582537221e-05</v>
+        <v>1.166969411045525e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.192501549041272e-05</v>
+        <v>1.161561965639073e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.198338701321281e-05</v>
+        <v>1.166982999910132e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.199069813351363e-05</v>
+        <v>1.1686875815449e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.207465321998893e-05</v>
+        <v>1.178221818599338e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.496923441351712e-05</v>
+        <v>4.479182992065145e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.433553758443731e-05</v>
+        <v>4.402975327693761e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.574270031279584e-05</v>
+        <v>4.555574065905874e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.893257142392815e-05</v>
+        <v>1.854158343259787e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.485409006434569e-05</v>
+        <v>4.441429276033688e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.912613709025591e-05</v>
+        <v>4.861756227821386e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.482103514126929e-05</v>
+        <v>4.451041024403849e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.405917657927725e-05</v>
+        <v>4.388303933572189e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.639265270129947e-05</v>
+        <v>4.599874426066209e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.245919597635469e-05</v>
+        <v>5.222244051282965e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.455575265263377e-05</v>
+        <v>4.467169523047344e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.268727183016971e-05</v>
+        <v>5.216611275383129e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.445012142258897e-05</v>
+        <v>4.250235099084591e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.576036913491648e-05</v>
+        <v>4.546046274628264e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.152709059836344e-05</v>
+        <v>4.10850100588386e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4753394338548e-05</v>
+        <v>4.4433816907683e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.513554960317836e-05</v>
+        <v>4.507294767332755e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.697424565184328e-05</v>
+        <v>4.644571205255058e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.530210067513568e-05</v>
+        <v>4.506600058876184e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.450270682127814e-05</v>
+        <v>4.427725662713061e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.77118222792471e-05</v>
+        <v>4.741484003462218e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.548378062784644e-05</v>
+        <v>4.519038107775642e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.390884044134309e-05</v>
+        <v>4.358235901066299e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.488538205407259e-05</v>
+        <v>4.460672389335438e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.391011308048378e-05</v>
+        <v>4.352426537243835e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.34338928005408e-05</v>
+        <v>4.322529943532125e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.772690711794576e-05</v>
+        <v>4.776476555683693e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.646206655991504e-05</v>
+        <v>1.304168154221235e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.319473834113739e-05</v>
+        <v>1.288990956688211e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.653764725185159e-05</v>
+        <v>1.311578253700702e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.636511112558715e-05</v>
+        <v>1.60514072626856e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.63564785196472e-05</v>
+        <v>1.292186091088334e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.345155149473691e-05</v>
+        <v>1.625344677770768e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.638529897766694e-05</v>
+        <v>1.295724580988601e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.326758064881331e-05</v>
+        <v>1.296925692159274e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.334144422076822e-05</v>
+        <v>1.303146306926303e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.33512474340004e-05</v>
+        <v>1.616892767915943e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.639053865210485e-05</v>
+        <v>1.610460660975354e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.647482407591125e-05</v>
+        <v>1.303530784110403e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.328169583086853e-05</v>
+        <v>4.250235099084591e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.328270817598054e-05</v>
+        <v>1.610743762035578e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.641283043465463e-05</v>
+        <v>1.610044461291755e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.64211670295237e-05</v>
+        <v>1.29926174218491e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.647836218310888e-05</v>
+        <v>1.618105510150836e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.643274534446425e-05</v>
+        <v>1.299158776370893e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.336094309805069e-05</v>
+        <v>1.305962467182854e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.645516576853461e-05</v>
+        <v>1.615037966537018e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.637677246845848e-05</v>
+        <v>1.294949451012643e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.353289181254523e-05</v>
+        <v>1.322873249831279e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.32919434229638e-05</v>
+        <v>1.610470680005054e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.337989183757976e-05</v>
+        <v>1.307654817481437e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.329562461080441e-05</v>
+        <v>1.61048426886966e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.642593472962684e-05</v>
+        <v>1.612188850504423e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.338947700492473e-05</v>
+        <v>1.310119579490841e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.05605854639291e-05</v>
+        <v>2.02422025444564e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.041625624367307e-05</v>
+        <v>2.009043056912621e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.063616615586562e-05</v>
+        <v>2.031630353925108e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.046363002960119e-05</v>
+        <v>2.013328938196001e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.045499742366125e-05</v>
+        <v>2.012238191312743e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.06730693972726e-05</v>
+        <v>2.03353288969821e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.048381788168101e-05</v>
+        <v>2.015776681213005e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.048909855134897e-05</v>
+        <v>2.016977792383677e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.056296212330392e-05</v>
+        <v>2.023198407150709e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.057276533653607e-05</v>
+        <v>2.025080979843385e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.048905755611889e-05</v>
+        <v>2.018648872902795e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.057334297992532e-05</v>
+        <v>2.023582884334807e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.05010992738595e-05</v>
+        <v>4.250235099084591e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.050207973811852e-05</v>
+        <v>2.017661085456939e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.050299772476001e-05</v>
+        <v>2.016950910565237e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.051968593353775e-05</v>
+        <v>2.019313842409318e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.057688108712292e-05</v>
+        <v>2.02629372207828e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.053126424847829e-05</v>
+        <v>2.0192108765953e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.05824610005864e-05</v>
+        <v>2.026014567407261e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.055406038908469e-05</v>
+        <v>2.0232410133885e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.047529137247252e-05</v>
+        <v>2.015001551237051e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.066939182537305e-05</v>
+        <v>2.03442321444623e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.051346132549946e-05</v>
+        <v>2.018658891932501e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.052915912606729e-05</v>
+        <v>2.020478768157974e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.05171425133401e-05</v>
+        <v>2.018672480797104e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05244536336409e-05</v>
+        <v>2.02037706243187e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.060840872011619e-05</v>
+        <v>2.029911299486309e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.43092753513297e-05</v>
+        <v>5.39987524938877e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.122670670175239e-05</v>
+        <v>8.090138620749481e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.144661661394489e-05</v>
+        <v>8.11272591776197e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.686449125481987e-05</v>
+        <v>6.653857204504778e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.841959333109605e-05</v>
+        <v>5.809369207797187e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.709495220100701e-05</v>
+        <v>8.675619179836124e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.129426833976021e-05</v>
+        <v>8.096872245049872e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.129954900942821e-05</v>
+        <v>8.098073356220542e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.137341258138318e-05</v>
+        <v>8.104293970987566e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.138321579461538e-05</v>
+        <v>8.106176543680246e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.129950801419814e-05</v>
+        <v>8.099744436739651e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.138379343800387e-05</v>
+        <v>8.104678448171574e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.033415795702489e-05</v>
+        <v>4.250235099084591e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.609993970810422e-05</v>
+        <v>6.577910901144205e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.468777341670777e-05</v>
+        <v>6.435930703444173e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.895012221298552e-05</v>
+        <v>4.863288016771167e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.138733154520213e-05</v>
+        <v>8.107389285915141e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.134171470655751e-05</v>
+        <v>8.100306440432166e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.139291145866558e-05</v>
+        <v>8.107110131244122e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.815596686626939e-05</v>
+        <v>6.783846161141807e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.388970303168516e-05</v>
+        <v>7.356674692150846e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.148516069974734e-05</v>
+        <v>8.116050475364309e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.14241617367988e-05</v>
+        <v>5.110592070524584e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001082470425306914</v>
+        <v>0.000107915560051936</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.376314630422325e-05</v>
+        <v>5.344072528159302e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.133490409172015e-05</v>
+        <v>8.101472626268733e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001096871309664178</v>
+        <v>0.0001093706576324334</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.735218858745584e-05</v>
+        <v>3.703568653410515e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.429701828023751e-05</v>
+        <v>4.396821864645658e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.451692819243007e-05</v>
+        <v>4.419409161658149e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.270824326748979e-05</v>
+        <v>4.237604914214048e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.799331307523077e-05</v>
+        <v>2.766891528995819e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.455383164483568e-05</v>
+        <v>4.421311719523849e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.436457991824543e-05</v>
+        <v>4.403555488946045e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.436986058791339e-05</v>
+        <v>4.404756600116718e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.444372415986837e-05</v>
+        <v>4.41097721488375e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.445352737310053e-05</v>
+        <v>4.412859787576429e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.436981959268331e-05</v>
+        <v>4.406427680635836e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.445410501648973e-05</v>
+        <v>4.411361692067845e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.438186131042392e-05</v>
+        <v>4.250235099084591e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.673221191777641e-05</v>
+        <v>4.640215870506786e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.724407062271135e-05</v>
+        <v>4.690564777076199e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.440044818110078e-05</v>
+        <v>4.407092672234956e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.445764312368732e-05</v>
+        <v>4.41407252981132e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.441202628504269e-05</v>
+        <v>4.40698968432834e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.446322303715085e-05</v>
+        <v>4.413793375140299e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.443444670911311e-05</v>
+        <v>4.411004986197501e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.253679096472948e-05</v>
+        <v>5.220293880259593e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.455015386193746e-05</v>
+        <v>4.422202022179272e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.439422336206387e-05</v>
+        <v>4.40643769966554e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.440992116263176e-05</v>
+        <v>4.408257575891013e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.012377220173424e-05</v>
+        <v>3.979330756905494e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.440521567020534e-05</v>
+        <v>4.408155870164909e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.448917075668062e-05</v>
+        <v>4.41769010721935e-05</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.347394938345385e-05</v>
+        <v>1.348097236986997e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.353872986630173e-05</v>
+        <v>1.354909004044861e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.349180649494574e-05</v>
+        <v>1.349890551495116e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.34614068115786e-05</v>
+        <v>1.346843468040358e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.345846283873704e-05</v>
+        <v>1.346551636847449e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.346678785782031e-05</v>
+        <v>1.347270636889538e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.346087196125158e-05</v>
+        <v>1.346795042837879e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.348659503012135e-05</v>
+        <v>1.349408738021811e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.346880813186141e-05</v>
+        <v>1.347559588027317e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.347323569708834e-05</v>
+        <v>1.348110084396592e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.347123424618441e-05</v>
+        <v>1.347878184386652e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.347983042260722e-05</v>
+        <v>1.348682608194424e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.346266388894354e-05</v>
+        <v>1.346987708652457e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.500623243836596e-05</v>
+        <v>1.502111055462826e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.345657932914165e-05</v>
+        <v>1.346326155030893e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.346568819602116e-05</v>
+        <v>1.347271954527409e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.347481003414942e-05</v>
+        <v>1.348230794945451e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.346786721904748e-05</v>
+        <v>1.347498359583552e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.347408466657994e-05</v>
+        <v>1.348185763750539e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.398822205635472e-05</v>
+        <v>1.400717223442483e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.346838523368889e-05</v>
+        <v>1.347551299690292e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.406334886799217e-05</v>
+        <v>1.408445725642757e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.34604136863743e-05</v>
+        <v>1.34674424323169e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.345716686575536e-05</v>
+        <v>1.346445057771593e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.381951468757125e-05</v>
+        <v>1.38355060254906e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.347667891932634e-05</v>
+        <v>1.348421201164429e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.346781770002806e-05</v>
+        <v>1.347573051014894e-05</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363789118459948e-05</v>
+        <v>1.364369841749726e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.363548135405754e-05</v>
+        <v>1.36470419642426e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.377117597848574e-05</v>
+        <v>1.377752878185684e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.350659421763841e-05</v>
+        <v>1.351243698276881e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.353448204379181e-05</v>
+        <v>1.354050994131798e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.359751726668078e-05</v>
+        <v>1.359549878381959e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.354796458959297e-05</v>
+        <v>1.355417441936919e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.373116051319299e-05</v>
+        <v>1.374033145020291e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.360840995991804e-05</v>
+        <v>1.361255509360222e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.365056899955662e-05</v>
+        <v>1.366235770041227e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.362937991907174e-05</v>
+        <v>1.363891089182762e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.371507211417799e-05</v>
+        <v>1.372073285641706e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.355722878464871e-05</v>
+        <v>1.356439780548691e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.607866981555991e-05</v>
+        <v>1.609764834075788e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.351450917202397e-05</v>
+        <v>1.351789532940152e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.358684091304004e-05</v>
+        <v>1.359270792652441e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.364683345814595e-05</v>
+        <v>1.365604823480617e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36008879124024e-05</v>
+        <v>1.360735629077407e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.364257314038015e-05</v>
+        <v>1.365374720833661e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.445722038462423e-05</v>
+        <v>1.44830640517622e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.360752479511265e-05</v>
+        <v>1.361407332152769e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.463533751016971e-05</v>
+        <v>1.46659212866365e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.354590574565679e-05</v>
+        <v>1.355175603619055e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.352044026454708e-05</v>
+        <v>1.352810928985133e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.418187754985468e-05</v>
+        <v>1.420237675642605e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.365726054066609e-05</v>
+        <v>1.366671131232899e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.362506478271683e-05</v>
+        <v>1.363718623297016e-05</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.22739642636378e-05</v>
+        <v>1.195589560336369e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.204873913560221e-05</v>
+        <v>1.173117857867358e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.247566855261566e-05</v>
+        <v>1.215845872671003e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.213229014443865e-05</v>
+        <v>1.181427663321867e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.209903661689873e-05</v>
+        <v>1.178131295748974e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.21930715371422e-05</v>
+        <v>1.18625273198076e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.212624876395191e-05</v>
+        <v>1.180880678383189e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.241680266003151e-05</v>
+        <v>1.2104035678449e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.220444284784734e-05</v>
+        <v>1.18837219871729e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.226590284782723e-05</v>
+        <v>1.195734677737869e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.22432955391542e-05</v>
+        <v>1.193115260446325e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.237310583866992e-05</v>
+        <v>1.205481474724622e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.214648941155978e-05</v>
+        <v>4.255614880189212e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.207913092427362e-05</v>
+        <v>1.176149003634982e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.207776150956161e-05</v>
+        <v>1.175584374904244e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.218065035125087e-05</v>
+        <v>1.186267615306646e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.228368570916288e-05</v>
+        <v>1.197098158916821e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.220526341873382e-05</v>
+        <v>1.188824964567243e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.227549234878054e-05</v>
+        <v>1.196589510854926e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.213257013124685e-05</v>
+        <v>1.1814133731885e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.216328047766561e-05</v>
+        <v>1.184643254972666e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.232652870386434e-05</v>
+        <v>1.20115968090123e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.212107233839582e-05</v>
+        <v>1.180306873462345e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.202116634060665e-05</v>
+        <v>1.170495168204125e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.220920266229709e-05</v>
+        <v>1.189090369939017e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.230479562696608e-05</v>
+        <v>1.199248884751356e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.224840420640573e-05</v>
+        <v>1.194026631380245e-05</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.51436899083121e-05</v>
+        <v>4.483132235302142e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.64899341295598e-05</v>
+        <v>4.618707400723505e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.173640275891763e-05</v>
+        <v>5.144073570874736e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.098651906531972e-05</v>
+        <v>2.067548253709671e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.573909957805763e-05</v>
+        <v>4.543422040174881e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.927779343148993e-05</v>
+        <v>4.877430340695785e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.429700990163442e-05</v>
+        <v>4.399916115599779e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.923336032176144e-05</v>
+        <v>4.902192985072062e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.784263908957457e-05</v>
+        <v>4.749199023948598e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.421070412061285e-05</v>
+        <v>5.405151594341168e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.023270918035995e-05</v>
+        <v>5.001455695402571e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.593204918560954e-05</v>
+        <v>5.561662218787517e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.807342985629332e-05</v>
+        <v>4.255614880189212e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.485801915439938e-05</v>
+        <v>4.45517598434729e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.197871901073949e-05</v>
+        <v>4.160396545276925e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.759255836459156e-05</v>
+        <v>4.728191055278946e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.676653787266255e-05</v>
+        <v>4.655835454761327e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.724805834166806e-05</v>
+        <v>4.695155691132707e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.709666409941847e-05</v>
+        <v>4.694146472933577e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.812274224126733e-05</v>
+        <v>4.782196149026799e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.882718241552742e-05</v>
+        <v>4.853241389451277e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.555685033373388e-05</v>
+        <v>4.53012245699403e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.483348587338047e-05</v>
+        <v>4.452328032107371e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.29966747181418e-05</v>
+        <v>4.273690309312095e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.660142337534981e-05</v>
+        <v>4.628494572841465e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.563122303847509e-05</v>
+        <v>4.542226023435644e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.841898694395551e-05</v>
+        <v>4.829719068247169e-05</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.351187794746342e-05</v>
+        <v>1.613403952558383e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.622053549996982e-05</v>
+        <v>1.590932250089381e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.371358223644125e-05</v>
+        <v>1.633660264893026e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.630408650880622e-05</v>
+        <v>1.305465410696978e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.627083298126632e-05</v>
+        <v>1.302169043124082e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.343098522096782e-05</v>
+        <v>1.310290479355873e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.629804512831952e-05</v>
+        <v>1.304918425758297e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.658859902439911e-05</v>
+        <v>1.628217960066925e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.344235653167292e-05</v>
+        <v>1.606186590939308e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.643769921219482e-05</v>
+        <v>1.319772425112976e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.348120922297982e-05</v>
+        <v>1.610929652668342e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.65449022030375e-05</v>
+        <v>1.32951922209973e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.338640124736732e-05</v>
+        <v>4.255614880189212e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.331904276008116e-05</v>
+        <v>1.594965434771227e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.322980403730988e-05</v>
+        <v>1.291002208363548e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.635244671561849e-05</v>
+        <v>1.310305362681754e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.645548207353048e-05</v>
+        <v>1.614912551138845e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.344317710255941e-05</v>
+        <v>1.312862711942351e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.351340603260614e-05</v>
+        <v>1.320627258230037e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.343371548035944e-05</v>
+        <v>1.605660033264796e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.633507684203321e-05</v>
+        <v>1.308681002347777e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.364447864296109e-05</v>
+        <v>1.333221778058069e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.335898602222143e-05</v>
+        <v>1.598121265684366e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3390692492873e-05</v>
+        <v>1.307817693480897e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.344711634612271e-05</v>
+        <v>1.606904762161035e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.647659199133369e-05</v>
+        <v>1.323286632126465e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34885806418601e-05</v>
+        <v>1.318271962047029e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.023094878278699e-05</v>
+        <v>1.991045058245872e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.000572365475144e-05</v>
+        <v>1.968573355776861e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.043265307176487e-05</v>
+        <v>2.011301370580507e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.008927466358787e-05</v>
+        <v>1.976883161231369e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.005602113604794e-05</v>
+        <v>1.973586793658477e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.015005605629131e-05</v>
+        <v>1.981708229890259e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.008323328310115e-05</v>
+        <v>1.976336176292693e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.037378717918073e-05</v>
+        <v>2.0058590657544e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.016142736699653e-05</v>
+        <v>1.98382769662679e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.022288736697646e-05</v>
+        <v>1.99119017564737e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.020028005830343e-05</v>
+        <v>1.988570758355828e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.033009035781914e-05</v>
+        <v>2.000936972634126e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.010347393070899e-05</v>
+        <v>4.255614880189212e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.003608287586403e-05</v>
+        <v>1.971601391629262e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.003471346115201e-05</v>
+        <v>1.971036762898525e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.01376348704001e-05</v>
+        <v>1.981723113216147e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.02406702283121e-05</v>
+        <v>1.992553656826324e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.016224793788306e-05</v>
+        <v>1.984280462476746e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.023247686792978e-05</v>
+        <v>1.992045008764427e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.015422987931067e-05</v>
+        <v>1.983382778893449e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.012026499681482e-05</v>
+        <v>1.98009875288217e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.028351322301353e-05</v>
+        <v>1.996615178810733e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.007805685754503e-05</v>
+        <v>1.97576237137185e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.004138252504283e-05</v>
+        <v>1.972382933967907e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.016618718144631e-05</v>
+        <v>1.984545867848524e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.026178014611528e-05</v>
+        <v>1.99470438266086e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.020538872555494e-05</v>
+        <v>1.989482129289744e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.170814232023923e-05</v>
+        <v>5.139643017231942e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.672374981061876e-05</v>
+        <v>7.642057401242939e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.715067922763221e-05</v>
+        <v>7.684785416046579e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.336730200722323e-05</v>
+        <v>6.305939845037821e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.546544140015312e-05</v>
+        <v>5.515532496004835e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.210193328464735e-05</v>
+        <v>8.178743853523233e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.680125943896856e-05</v>
+        <v>7.649820221758768e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.70918133350481e-05</v>
+        <v>7.679343111220478e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.687945352286384e-05</v>
+        <v>7.657311742092858e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.694091352284384e-05</v>
+        <v>7.664674221113441e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.691830621417074e-05</v>
+        <v>7.662054803821905e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.704811651368614e-05</v>
+        <v>7.674421018100141e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.725563210917631e-05</v>
+        <v>4.255614880189212e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.256514403206082e-05</v>
+        <v>6.22573748675241e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.124577375615361e-05</v>
+        <v>6.093330850799742e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.665442870324802e-05</v>
+        <v>4.634123328379154e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.695869638417948e-05</v>
+        <v>7.666037702292402e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.68802740937503e-05</v>
+        <v>7.657764507942821e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.695050302379712e-05</v>
+        <v>7.665529054230502e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.45522429242843e-05</v>
+        <v>6.424487664210883e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.994085277546543e-05</v>
+        <v>6.963565802582593e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.700649993029958e-05</v>
+        <v>7.670595437188384e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.890822315696644e-05</v>
+        <v>4.859573413660416e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001018577510281604</v>
+        <v>0.0001015641610297818</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.117451929397532e-05</v>
+        <v>5.086242771463298e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.697980630198267e-05</v>
+        <v>7.668188428126928e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00010328957515968</v>
+        <v>0.0001030042082003951</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.457050194495364e-05</v>
+        <v>3.424743437744773e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.059193735272913e-05</v>
+        <v>4.02697317996341e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.10188667697426e-05</v>
+        <v>4.069701194767052e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.923378474461947e-05</v>
+        <v>3.891104456583958e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.624197716045625e-05</v>
+        <v>2.591879262659144e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.073626995584766e-05</v>
+        <v>4.040108075513537e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.066944698107885e-05</v>
+        <v>4.034736000479239e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.096000087715837e-05</v>
+        <v>4.064258889940963e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.074764106497429e-05</v>
+        <v>4.042227520813332e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.080910106495411e-05</v>
+        <v>4.049589999833924e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.078649375628112e-05</v>
+        <v>4.04697058254237e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.091630405579684e-05</v>
+        <v>4.059336796820682e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.068968762868665e-05</v>
+        <v>4.255614880189212e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.269246453204405e-05</v>
+        <v>4.237029595064369e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.314131400341637e-05</v>
+        <v>4.281489405796184e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.072384876995643e-05</v>
+        <v>4.040122958839387e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.082688392628982e-05</v>
+        <v>4.050953481012881e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.074846163586076e-05</v>
+        <v>4.042680286663295e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.081869056590746e-05</v>
+        <v>4.050444832950978e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.073900001366074e-05</v>
+        <v>4.041700963138832e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.791499103661173e-05</v>
+        <v>4.759390654191547e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.086972692099124e-05</v>
+        <v>4.05501500299728e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.06642705555227e-05</v>
+        <v>4.034162195558396e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.062759622302056e-05</v>
+        <v>4.030782758154469e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.698622013110208e-05</v>
+        <v>3.66630628002054e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.084799384409299e-05</v>
+        <v>4.053104206847419e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.079160242353262e-05</v>
+        <v>4.047881953476289e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -798,7 +798,7 @@
         <v>1.168583346696136e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.336637662839929e-05</v>
+        <v>1.158994860692113e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.165451826365157e-05</v>
@@ -974,7 +974,7 @@
         <v>1.640451268805307e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.336637662839929e-05</v>
+        <v>1.299351948511479e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.30580893964524e-05</v>
@@ -1062,7 +1062,7 @@
         <v>2.078639503367505e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.336637662839929e-05</v>
+        <v>2.069051017363485e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.07550518155332e-05</v>
@@ -1150,7 +1150,7 @@
         <v>8.574910761210436e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.336637662839929e-05</v>
+        <v>6.325005452260047e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.947120933499267e-05</v>
@@ -1238,7 +1238,7 @@
         <v>4.883733067379904e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.336637662839929e-05</v>
+        <v>4.874144581375885e-05</v>
       </c>
       <c r="O9" t="n">
         <v>5.149652349563332e-05</v>
@@ -1658,7 +1658,7 @@
         <v>1.235778840194274e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.342398859320103e-05</v>
+        <v>1.193339751905373e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.187940784858596e-05</v>
@@ -1834,7 +1834,7 @@
         <v>1.361151331676144e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.342398859320103e-05</v>
+        <v>1.318993934215458e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.611697359142794e-05</v>
@@ -1922,7 +1922,7 @@
         <v>2.033127323475071e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.342398859320103e-05</v>
+        <v>1.990688235186171e-05</v>
       </c>
       <c r="O7" t="n">
         <v>1.985286066033034e-05</v>
@@ -2010,7 +2010,7 @@
         <v>7.712085606176911e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.342398859320103e-05</v>
+        <v>5.709900431597729e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.243056705486727e-05</v>
@@ -2098,7 +2098,7 @@
         <v>3.966533248393408e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.342398859320103e-05</v>
+        <v>3.924094160104508e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.116958307204277e-05</v>
@@ -2518,7 +2518,7 @@
         <v>1.171470757523179e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.293813936921933e-05</v>
+        <v>1.167971855470917e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.163937194295056e-05</v>
@@ -2694,7 +2694,7 @@
         <v>1.614750177666865e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.293813936921933e-05</v>
+        <v>1.299759266560053e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.295703376553004e-05</v>
@@ -2782,7 +2782,7 @@
         <v>2.023203026471741e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.293813936921933e-05</v>
+        <v>2.019704124419479e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.015666461509543e-05</v>
@@ -2870,7 +2870,7 @@
         <v>8.104151463315389e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.293813936921933e-05</v>
+        <v>6.003546353863856e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.575814687606399e-05</v>
@@ -2958,7 +2958,7 @@
         <v>4.410633833932472e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.293813936921933e-05</v>
+        <v>4.407134931880209e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.637843806680051e-05</v>
@@ -3169,52 +3169,52 @@
         <v>1.344549561464646e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.352249402739239e-05</v>
+        <v>1.352249402739238e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.345498381017016e-05</v>
+        <v>1.345498381017009e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.344161402297617e-05</v>
+        <v>1.344161402297619e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343440127032411e-05</v>
+        <v>1.343440127032414e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.345308109440236e-05</v>
+        <v>1.345308109440238e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.343900223300975e-05</v>
+        <v>1.343900223300974e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.345067329792468e-05</v>
+        <v>1.345067329792471e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.344782070460527e-05</v>
+        <v>1.34478207046053e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.345440343725685e-05</v>
+        <v>1.345440343725682e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.344233973966822e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.34461976783164e-05</v>
+        <v>1.344619767831637e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.344241050738783e-05</v>
+        <v>1.344241050738781e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.497872954988998e-05</v>
+        <v>1.497872954988995e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343602809896707e-05</v>
+        <v>1.343602809896705e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.34409198672943e-05</v>
+        <v>1.344091986729431e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.344221646643321e-05</v>
+        <v>1.344221646643322e-05</v>
       </c>
       <c r="S2" t="n">
         <v>1.344606350094564e-05</v>
@@ -3223,16 +3223,16 @@
         <v>1.344626094961088e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39693597649695e-05</v>
+        <v>1.396935976496956e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344341663147083e-05</v>
+        <v>1.344341663147084e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.405186008317631e-05</v>
+        <v>1.405186008317625e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344375441390423e-05</v>
+        <v>1.344375441390426e-05</v>
       </c>
       <c r="Y2" t="n">
         <v>1.344069231897628e-05</v>
@@ -3241,10 +3241,10 @@
         <v>1.380058476910582e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.34481373095097e-05</v>
+        <v>1.344813730950968e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.34490349183358e-05</v>
+        <v>1.344903491833579e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.353318610754688e-05</v>
+        <v>1.353318610754685e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.360945308660796e-05</v>
+        <v>1.360945308660795e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.360382200546394e-05</v>
+        <v>1.360382200546389e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.346410566296643e-05</v>
+        <v>1.346410566296639e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.346015228808179e-05</v>
+        <v>1.346015228808176e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.358961287470409e-05</v>
+        <v>1.358961287470406e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.349066172237374e-05</v>
+        <v>1.34906617223737e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.357272924406222e-05</v>
+        <v>1.35727292440622e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.355253235955207e-05</v>
+        <v>1.355253235955203e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.361307126011856e-05</v>
+        <v>1.361307126011849e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.351047537157513e-05</v>
+        <v>1.35104753715751e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.356131224148794e-05</v>
+        <v>1.356131224148793e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.351173751422843e-05</v>
+        <v>1.351173751422838e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.60166222127817e-05</v>
+        <v>1.601662221278165e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.346539792195378e-05</v>
+        <v>1.346539792195374e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.350382131078375e-05</v>
+        <v>1.350382131078373e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.351210817197909e-05</v>
+        <v>1.351210817197905e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.353912051825565e-05</v>
+        <v>1.353912051825561e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.354067320777435e-05</v>
+        <v>1.35406732077743e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.439207388597848e-05</v>
+        <v>1.439207388597852e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352814111061851e-05</v>
+        <v>1.352814111061846e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.462255890631855e-05</v>
+        <v>1.462255890631848e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.352350027273149e-05</v>
+        <v>1.352350027273147e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.350153066066e-05</v>
+        <v>1.350153066066002e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4138542141867e-05</v>
+        <v>1.413854214186701e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.355254337762699e-05</v>
+        <v>1.355254337762697e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.358746441580916e-05</v>
+        <v>1.358746441580915e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3348,79 +3348,79 @@
         <v>1.167920581038823e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.189089069328046e-05</v>
+        <v>1.189089069328045e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.173987279651945e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.16584014372844e-05</v>
+        <v>1.165840143728438e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.186939864339172e-05</v>
+        <v>1.186939864339174e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17103714273657e-05</v>
+        <v>1.171037142736571e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.18422014745354e-05</v>
+        <v>1.184220147453538e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.179848975196506e-05</v>
+        <v>1.179848975196504e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.188433511424055e-05</v>
+        <v>1.188433511424056e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.174807010040218e-05</v>
+        <v>1.174807010040216e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.182557980753126e-05</v>
+        <v>1.182557980753127e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.139652223361452e-05</v>
+        <v>1.174886945434966e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.167330385448432e-05</v>
+        <v>1.167330385448429e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.167677721518427e-05</v>
+        <v>1.167677721518428e-05</v>
       </c>
       <c r="Q4" t="n">
         <v>1.173203198876536e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.174667767250421e-05</v>
+        <v>1.174667767250418e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.179013169704539e-05</v>
+        <v>1.17901316970454e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.179236197055027e-05</v>
+        <v>1.179236197055025e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.169962760749066e-05</v>
+        <v>1.169962760749074e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.171211531794953e-05</v>
+        <v>1.17121153179495e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.196631335683422e-05</v>
+        <v>1.196631335683421e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.176404949668042e-05</v>
+        <v>1.176404949668041e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.166275661061634e-05</v>
+        <v>1.166275661061633e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.181289011879864e-05</v>
+        <v>1.181289011879865e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.181355631877535e-05</v>
+        <v>1.181355631877534e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.186676250441775e-05</v>
+        <v>1.186676250441774e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.171748838205333e-05</v>
+        <v>4.171748838205328e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.516025374015736e-05</v>
+        <v>4.516025374015735e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.512529866881377e-05</v>
+        <v>4.512529866881366e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.949927426549226e-05</v>
+        <v>1.949927426549221e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.268663590993305e-05</v>
+        <v>4.268663590993303e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.441902980172272e-05</v>
+        <v>4.441902980172203e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.239945345694845e-05</v>
+        <v>4.239945345694898e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.40939538222304e-05</v>
+        <v>4.40939538222305e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3596640089301e-05</v>
+        <v>4.359664008930103e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.194910901467413e-05</v>
+        <v>5.1949109014674e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.09900520294019e-05</v>
+        <v>4.099005202940175e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.488280366493079e-05</v>
+        <v>4.488280366493053e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.139652223361452e-05</v>
+        <v>4.139652223361499e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.29683794935635e-05</v>
+        <v>4.29683794935634e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.971307791683216e-05</v>
+        <v>3.971307791683176e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.250962642470959e-05</v>
+        <v>4.250962642470944e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.226751992288936e-05</v>
+        <v>4.22675199228893e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.280591650013488e-05</v>
+        <v>4.280591650013485e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.291972187575564e-05</v>
+        <v>4.291972187575529e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.276864783496456e-05</v>
+        <v>4.276864783496925e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.632890836899251e-05</v>
+        <v>4.632890836899291e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.482659246380526e-05</v>
+        <v>4.482659246380436e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.279019166088577e-05</v>
+        <v>4.279019166088566e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.211870481442562e-05</v>
+        <v>4.211870481442559e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.484876127158363e-05</v>
+        <v>4.484876127158351e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.250609782940151e-05</v>
+        <v>4.250609782940127e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>4.609808538495135e-05</v>
@@ -3518,73 +3518,73 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.594640893017641e-05</v>
+        <v>1.594640893017642e-05</v>
       </c>
       <c r="C6" t="n">
         <v>1.29100953680972e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.605358246340117e-05</v>
+        <v>1.605358246340119e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.590256456664016e-05</v>
+        <v>1.590256456664019e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.288929099499336e-05</v>
+        <v>1.288929099499337e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.310028820110065e-05</v>
+        <v>1.310028820110069e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.294126098507469e-05</v>
+        <v>1.294126098507467e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.307309103224438e-05</v>
+        <v>1.30730910322444e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.596118152208582e-05</v>
+        <v>1.596118152208577e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.604702688436135e-05</v>
+        <v>1.604702688436129e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.59107618705229e-05</v>
+        <v>1.591076187052288e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.305646936524025e-05</v>
+        <v>1.305646936524021e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.139652223361452e-05</v>
+        <v>1.298164414071475e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.584583466049602e-05</v>
+        <v>1.584583466049598e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.584939427173142e-05</v>
+        <v>1.584939427173138e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.589472375888607e-05</v>
+        <v>1.589472375888609e-05</v>
       </c>
       <c r="R6" t="n">
         <v>1.297756723021318e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.59528234671661e-05</v>
+        <v>1.595282346716612e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.302325152825923e-05</v>
+        <v>1.302325152825919e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.299722228041896e-05</v>
+        <v>1.299722228041911e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.587480708807024e-05</v>
+        <v>1.587480708807022e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.613873785551042e-05</v>
+        <v>1.613873785551037e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.299493905438938e-05</v>
+        <v>1.299493905438941e-05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.302788047382669e-05</v>
@@ -3593,10 +3593,10 @@
         <v>1.597558188891939e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.597624808889605e-05</v>
+        <v>1.597624808889609e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.309982550301552e-05</v>
+        <v>1.30998255030155e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.973239257841826e-05</v>
+        <v>1.973239257841824e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.962788122875083e-05</v>
+        <v>1.962788122875078e-05</v>
       </c>
       <c r="D7" t="n">
         <v>1.983956611164301e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.968854821488202e-05</v>
+        <v>1.968854821488199e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.960707685564696e-05</v>
+        <v>1.960707685564695e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.981807406175434e-05</v>
+        <v>1.98180740617543e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.965904684572823e-05</v>
+        <v>1.965904684572827e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.979087689289799e-05</v>
+        <v>1.979087689289794e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.974716517032761e-05</v>
+        <v>1.974716517032759e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.983301053260316e-05</v>
+        <v>1.983301053260313e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.969674551876473e-05</v>
+        <v>1.969674551876471e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.977425522589387e-05</v>
+        <v>1.977425522589383e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.139652223361452e-05</v>
+        <v>1.969754487271221e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.962194863131458e-05</v>
+        <v>1.962194863131456e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.962542199201456e-05</v>
+        <v>1.962542199201455e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.968070740712792e-05</v>
+        <v>1.96807074071279e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.969535309086675e-05</v>
+        <v>1.969535309086674e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.973880711540799e-05</v>
+        <v>1.973880711540797e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.974103738891283e-05</v>
+        <v>1.974103738891281e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.971539325666936e-05</v>
+        <v>1.971539325666971e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.96607907363121e-05</v>
+        <v>1.966079073631207e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.991498877519675e-05</v>
+        <v>1.991498877519673e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.971272491504298e-05</v>
+        <v>1.971272491504296e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.967813714419825e-05</v>
+        <v>1.967813714419824e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.976156553716125e-05</v>
+        <v>1.97615655371612e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.976223173713789e-05</v>
+        <v>1.97622317371379e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.981543792278033e-05</v>
+        <v>1.98154379227803e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.121309969772811e-05</v>
+        <v>5.121309969772806e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.634831390149109e-05</v>
+        <v>7.634831390149111e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.655999878438342e-05</v>
+        <v>7.655999878438332e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.296957155484698e-05</v>
+        <v>6.296957155484692e-05</v>
       </c>
       <c r="F8" t="n">
         <v>5.501983823381927e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.177212824984254e-05</v>
+        <v>8.177212824984255e-05</v>
       </c>
       <c r="H8" t="n">
         <v>7.63794795184686e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.651130956563833e-05</v>
+        <v>7.65113095656383e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.646759784306794e-05</v>
+        <v>7.646759784306791e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.65534432053435e-05</v>
+        <v>7.655344320534346e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.641717819150507e-05</v>
+        <v>7.641717819150509e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.649468789863353e-05</v>
+        <v>7.649468789863344e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.139652223361452e-05</v>
+        <v>5.685296772861289e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.215403670892204e-05</v>
+        <v>6.215403670892219e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.083956701605984e-05</v>
+        <v>6.083956701605983e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.620123238538314e-05</v>
+        <v>4.620123238538315e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.64157857636072e-05</v>
+        <v>7.641578576360709e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.645923978814832e-05</v>
+        <v>7.645923978814828e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.64614700616533e-05</v>
+        <v>7.646147006165315e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.411658984630026e-05</v>
+        <v>6.411658984630019e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.94831812278705e-05</v>
+        <v>6.948318122787064e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.664038178174229e-05</v>
+        <v>7.664038178174231e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.854652089513925e-05</v>
+        <v>4.854652089513924e-05</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0001014944056357764</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.077343179585287e-05</v>
+        <v>5.07734317958529e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.648266440987836e-05</v>
+        <v>7.648266440987827e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001029008744517881</v>
+        <v>0.000102900874451788</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.405382736816177e-05</v>
+        <v>3.405382736816171e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.01895122464439e-05</v>
+        <v>4.018951224644395e-05</v>
       </c>
       <c r="D9" t="n">
         <v>4.04011971293362e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.880996757236762e-05</v>
+        <v>3.880996757236759e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.578335215828492e-05</v>
+        <v>2.578335215828491e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.037970530813412e-05</v>
+        <v>4.037970530813405e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.022067786342143e-05</v>
+        <v>4.022067786342145e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.035250791059114e-05</v>
+        <v>4.03525079105911e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.030879618802079e-05</v>
+        <v>4.030879618802074e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.039464155029631e-05</v>
+        <v>4.039464155029625e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.025837653645794e-05</v>
+        <v>4.025837653645786e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.033588624358704e-05</v>
+        <v>4.033588624358697e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.139652223361452e-05</v>
+        <v>4.025917589040545e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2251603454114e-05</v>
+        <v>4.225160345411406e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.270482979736957e-05</v>
+        <v>4.270482979736963e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.024233865350766e-05</v>
+        <v>4.024233865350767e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.02569841085599e-05</v>
+        <v>4.025698410855988e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.030043813310114e-05</v>
+        <v>4.030043813310113e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.030266840660594e-05</v>
+        <v>4.030266840660599e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.027663915876573e-05</v>
+        <v>4.027663915876609e-05</v>
       </c>
       <c r="V9" t="n">
         <v>4.742347449394627e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.047661979288995e-05</v>
+        <v>4.047661979288997e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.02743559327361e-05</v>
+        <v>4.027435593273615e-05</v>
       </c>
       <c r="Y9" t="n">
         <v>4.02397681618914e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.656091322010844e-05</v>
+        <v>3.656091322010846e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.032386275483098e-05</v>
+        <v>4.032386275483106e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.037706894047352e-05</v>
+        <v>4.037706894047344e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4026,82 +4026,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.346646534323776e-05</v>
+        <v>1.346646534323773e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.354427162869862e-05</v>
+        <v>1.354427162869864e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.348703839268194e-05</v>
+        <v>1.348703839268198e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.346346766670699e-05</v>
+        <v>1.346346766670701e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.345610667764808e-05</v>
+        <v>1.34561066776481e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.347703022435332e-05</v>
+        <v>1.347703022435333e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.346418562379768e-05</v>
+        <v>1.346418562379773e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.347616680352303e-05</v>
+        <v>1.347616680352304e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.347070470683227e-05</v>
+        <v>1.347070470683228e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.347229082348234e-05</v>
+        <v>1.347229082348236e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.346159624192126e-05</v>
+        <v>1.346159624192129e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.346913236361163e-05</v>
+        <v>1.34691323636116e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.346170647934245e-05</v>
+        <v>1.346170647934247e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.50231502545743e-05</v>
+        <v>1.502315025457431e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.345855546216597e-05</v>
+        <v>1.345855546216599e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.345996766172563e-05</v>
+        <v>1.345996766172564e-05</v>
       </c>
       <c r="R2" t="n">
         <v>1.346338316605256e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.346511262395807e-05</v>
+        <v>1.346511262395809e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.347095383797871e-05</v>
+        <v>1.347095383797873e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.400463400857542e-05</v>
+        <v>1.400463400857539e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.346785820759749e-05</v>
+        <v>1.346785820759752e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.409756556424011e-05</v>
+        <v>1.409756556424013e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.346372978005451e-05</v>
+        <v>1.346372978005453e-05</v>
       </c>
       <c r="Y2" t="n">
         <v>1.346494271087122e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.383063190864566e-05</v>
+        <v>1.383063190864565e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.347610487970079e-05</v>
+        <v>1.347610487970082e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.347347130865084e-05</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.355672184666945e-05</v>
+        <v>1.355672184666943e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.362823930582176e-05</v>
+        <v>1.362823930582175e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.370883947186615e-05</v>
+        <v>1.370883947186606e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.349824953299813e-05</v>
+        <v>1.349824953299808e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.348642420356484e-05</v>
+        <v>1.348642420356477e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.363550017387519e-05</v>
+        <v>1.363550017387518e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.354084377704812e-05</v>
+        <v>1.35408437770481e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.362798403664767e-05</v>
+        <v>1.362798403664759e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.358971191241832e-05</v>
+        <v>1.35897119124183e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.361109534019466e-05</v>
+        <v>1.361109534019461e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.352393648567795e-05</v>
+        <v>1.352393648567793e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.36015465404088e-05</v>
+        <v>1.360154654040876e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.351994580809025e-05</v>
+        <v>1.351994580809019e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.609894962954048e-05</v>
+        <v>1.609894962954044e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.350087316717113e-05</v>
+        <v>1.350087316717109e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.351236743514314e-05</v>
+        <v>1.351236743514313e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.353393796103206e-05</v>
+        <v>1.353393796103207e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.354695570982389e-05</v>
+        <v>1.35469557098239e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.358755314116458e-05</v>
+        <v>1.35875531411646e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.444351349188369e-05</v>
+        <v>1.444351349188371e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.357410651767097e-05</v>
+        <v>1.357410651767103e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.473182473013366e-05</v>
+        <v>1.47318247301337e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.353956914656753e-05</v>
+        <v>1.353956914656747e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.354257926145482e-05</v>
+        <v>1.354257926145468e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.418380037824929e-05</v>
+        <v>1.418380037824921e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.362211474646996e-05</v>
+        <v>1.36221147464699e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36337592285444e-05</v>
+        <v>1.363375922854437e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,76 +4202,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.182266975413061e-05</v>
+        <v>1.182266975413062e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.171030120890343e-05</v>
+        <v>1.171030120890342e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.205505181167286e-05</v>
+        <v>1.205505181167285e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.178880961871613e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.170566386107348e-05</v>
+        <v>1.170566386107346e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.19420049464161e-05</v>
+        <v>1.1942004946416e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.179691927433215e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.19322522109448e-05</v>
+        <v>1.193225221094478e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.185907337343515e-05</v>
+        <v>1.185907337343509e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.188847123334639e-05</v>
+        <v>1.188847123334637e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.176767101486341e-05</v>
+        <v>1.17676710148634e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.188700228704156e-05</v>
+        <v>1.188700228704154e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.117839694573052e-05</v>
+        <v>1.176891619724744e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.176136228835629e-05</v>
+        <v>1.17613622883563e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.173332400869964e-05</v>
+        <v>1.173332400869962e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.174927545236979e-05</v>
+        <v>1.174927545236978e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.178785514495219e-05</v>
+        <v>1.17878551449522e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.180739016758496e-05</v>
+        <v>1.180739016758495e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.187336936703917e-05</v>
+        <v>1.187336936703916e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.174713640939999e-05</v>
+        <v>1.174713640939997e-05</v>
       </c>
       <c r="V4" t="n">
         <v>1.179034737241867e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.210460560569516e-05</v>
+        <v>1.210460560569517e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.179177030955449e-05</v>
+        <v>1.179177030955444e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.174125858319928e-05</v>
+        <v>1.174125858319931e-05</v>
       </c>
       <c r="Z4" t="n">
         <v>1.186350512333201e-05</v>
@@ -4280,7 +4280,7 @@
         <v>1.193155275288636e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.194484285747499e-05</v>
+        <v>1.194484285747498e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.358625612140884e-05</v>
+        <v>4.358625612140882e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.570608664502582e-05</v>
+        <v>4.570608664502568e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.043603836092125e-05</v>
+        <v>5.043603836092047e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.37727803437957e-05</v>
+        <v>2.377278034379563e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.339935286563199e-05</v>
+        <v>4.339935286563155e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.744654887722895e-05</v>
+        <v>4.744654887722754e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.333416862409289e-05</v>
+        <v>4.333416862409284e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.657245214053695e-05</v>
+        <v>4.65724521405368e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.583828503393575e-05</v>
+        <v>4.583828503393509e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.138165582454352e-05</v>
+        <v>5.138165582454317e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.363216506267406e-05</v>
+        <v>4.363216506267354e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.84576424881657e-05</v>
+        <v>4.845764248816536e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.117839694573052e-05</v>
+        <v>4.117839694573042e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.375202973435695e-05</v>
+        <v>4.375202973435624e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.231931467288332e-05</v>
+        <v>4.231931467288162e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.333490085396972e-05</v>
+        <v>4.333490085396965e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.256305675169712e-05</v>
+        <v>4.256305675169698e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.32581195510837e-05</v>
+        <v>4.325811955108351e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.385937427031993e-05</v>
+        <v>4.385937427031947e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.544340397386276e-05</v>
+        <v>4.544340397386245e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.76739894113375e-05</v>
+        <v>4.767398941133773e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.671551753422174e-05</v>
+        <v>4.671551753422205e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.426853726901703e-05</v>
+        <v>4.426853726901618e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.158463071843226e-05</v>
+        <v>4.158463071843046e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.748035513070728e-05</v>
+        <v>4.748035513070722e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.374750122028851e-05</v>
+        <v>4.374750122028837e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.763981162399743e-05</v>
+        <v>4.763981162399721e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.30584086140675e-05</v>
+        <v>1.305840861406749e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.294604006884029e-05</v>
+        <v>1.29460400688403e-05</v>
       </c>
       <c r="D6" t="n">
         <v>1.623479430166701e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.59685521087103e-05</v>
+        <v>1.596855210871028e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.294140272101035e-05</v>
+        <v>1.294140272101036e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.317774380635303e-05</v>
+        <v>1.317774380635289e-05</v>
       </c>
       <c r="H6" t="n">
         <v>1.597666176432629e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.316799107088164e-05</v>
+        <v>1.316799107088166e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.60388158634293e-05</v>
+        <v>1.603881586342924e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.606821372334056e-05</v>
+        <v>1.606821372334053e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.30034098748003e-05</v>
+        <v>1.300340987480028e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.312274114697844e-05</v>
+        <v>1.312274114697842e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.117839694573052e-05</v>
+        <v>1.300654755768631e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.299880134210095e-05</v>
+        <v>1.299880134210094e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.592288389099652e-05</v>
+        <v>1.59228838909965e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.592901794236394e-05</v>
+        <v>1.592901794236393e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.596759763494636e-05</v>
+        <v>1.596759763494633e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.304312902752187e-05</v>
+        <v>1.304312902752182e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.605311185703334e-05</v>
+        <v>1.605311185703332e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.599109123729978e-05</v>
+        <v>1.599109123729977e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.302608623235557e-05</v>
+        <v>1.302608623235553e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.342112514960753e-05</v>
+        <v>1.342112514960754e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.302750916949136e-05</v>
+        <v>1.30275091694913e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.310924713052338e-05</v>
+        <v>1.310924713052333e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.309924398326888e-05</v>
+        <v>1.309924398326889e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.611129524288055e-05</v>
+        <v>1.611129524288049e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.31828569519869e-05</v>
+        <v>1.318285695198688e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.977818459583239e-05</v>
+        <v>1.977818459583236e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.966581605060521e-05</v>
+        <v>1.966581605060518e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.001056665337464e-05</v>
+        <v>2.001056665337461e-05</v>
       </c>
       <c r="E7" t="n">
         <v>1.974432446041789e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.966117870277526e-05</v>
+        <v>1.966117870277522e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.989751978811788e-05</v>
+        <v>1.989751978811778e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.975243411603394e-05</v>
+        <v>1.975243411603389e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.988776705264655e-05</v>
+        <v>1.988776705264654e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.981458821513695e-05</v>
+        <v>1.981458821513683e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.984398607504818e-05</v>
+        <v>1.984398607504813e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.972318585656518e-05</v>
+        <v>1.972318585656513e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.984251712874333e-05</v>
+        <v>1.98425171287433e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.117839694573052e-05</v>
+        <v>1.972443103894919e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.971684556719827e-05</v>
+        <v>1.971684556719823e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.968880728754161e-05</v>
+        <v>1.968880728754156e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.970479029407158e-05</v>
+        <v>1.970479029407152e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.974336998665398e-05</v>
+        <v>1.974336998665392e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.976290500928672e-05</v>
+        <v>1.976290500928667e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.982888420874094e-05</v>
+        <v>1.982888420874093e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.976804613701486e-05</v>
+        <v>1.976804613701481e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.974586221412044e-05</v>
+        <v>1.974586221412041e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.006012044739694e-05</v>
+        <v>2.006012044739692e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.974728515125626e-05</v>
+        <v>1.974728515125617e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.976098576280671e-05</v>
+        <v>1.976098576280653e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.981901996503379e-05</v>
+        <v>1.981901996503375e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.988706759458813e-05</v>
+        <v>1.98870675945881e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.990035769917677e-05</v>
+        <v>1.990035769917674e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.126956091201835e-05</v>
+        <v>5.126956091201825e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.641117276392205e-05</v>
+        <v>7.641117276392194e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.675592336669152e-05</v>
+        <v>7.675592336669142e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.304268155718401e-05</v>
+        <v>6.304268155718396e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.508683001586619e-05</v>
+        <v>5.508683001586606e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.187945385148445e-05</v>
+        <v>8.187945385148417e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.649779082935075e-05</v>
+        <v>7.64977908293506e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.663312376596342e-05</v>
+        <v>7.663312376596332e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.655994492845384e-05</v>
+        <v>7.655994492845362e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.658934278836503e-05</v>
+        <v>7.658934278836488e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.646854256988212e-05</v>
+        <v>7.646854256988195e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.658787384205979e-05</v>
+        <v>7.658787384205962e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.117839694573052e-05</v>
+        <v>5.689372804676485e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.226584532338312e-05</v>
+        <v>6.226584532338299e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.09191196448235e-05</v>
+        <v>6.091911964482341e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6233183067068e-05</v>
+        <v>4.623318306706794e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.648872669997085e-05</v>
+        <v>7.648872669997066e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.650826172260358e-05</v>
+        <v>7.650826172260345e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.657424092205781e-05</v>
+        <v>7.657424092205766e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.418703044038951e-05</v>
+        <v>6.418703044038935e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.958996309552842e-05</v>
+        <v>6.958996309552828e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.681044029597475e-05</v>
+        <v>7.681044029597457e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.859025541082715e-05</v>
+        <v>4.859025541082694e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001016174099850623</v>
+        <v>0.0001016174099850618</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.084129062956022e-05</v>
+        <v>5.084129062956012e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.663242430790505e-05</v>
+        <v>7.663242430790489e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001030256086449559</v>
+        <v>0.0001030256086449556</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.304191872510958e-05</v>
+        <v>3.304191872510952e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.888048775286318e-05</v>
+        <v>3.888048775286306e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.922523835563263e-05</v>
+        <v>3.922523835563255e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.758554423442672e-05</v>
+        <v>3.758554423442664e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.515731481166708e-05</v>
+        <v>2.515731481166701e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.911219173759584e-05</v>
+        <v>3.91121917375958e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.896710581829184e-05</v>
+        <v>3.896710581829183e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.910243875490451e-05</v>
+        <v>3.910243875490442e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.902925991739489e-05</v>
+        <v>3.902925991739478e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.905865777730617e-05</v>
+        <v>3.905865777730601e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.893785755882316e-05</v>
+        <v>3.893785755882303e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.905718883100134e-05</v>
+        <v>3.905718883100119e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.117839694573052e-05</v>
+        <v>3.893910274120707e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.090368208106083e-05</v>
+        <v>4.09036820810607e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.130454889313274e-05</v>
+        <v>4.130454889313268e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.891946224354968e-05</v>
+        <v>3.891946224354961e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.895804168891187e-05</v>
+        <v>3.895804168891181e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.897757671154468e-05</v>
+        <v>3.897757671154463e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.904355591099886e-05</v>
+        <v>3.904355591099885e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.898153529126537e-05</v>
+        <v>3.89815352912653e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.582778832418769e-05</v>
+        <v>4.582778832418763e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.92747921496549e-05</v>
+        <v>3.927479214965488e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.896195685351424e-05</v>
+        <v>3.896195685351404e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.897565746506463e-05</v>
+        <v>3.897565746506465e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.544580558696838e-05</v>
+        <v>3.544580558696832e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.910173929684612e-05</v>
+        <v>3.910173929684596e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.911502940143472e-05</v>
+        <v>3.911502940143466e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>1.17673293219705e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.489367678312357e-05</v>
+        <v>1.173640657379178e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.167657549049556e-05</v>
@@ -5274,7 +5274,7 @@
         <v>1.622284996960616e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.489367678312357e-05</v>
+        <v>1.306272681214521e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.614346239447391e-05</v>
@@ -5362,7 +5362,7 @@
         <v>2.029229887115607e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.489367678312357e-05</v>
+        <v>2.026137612297734e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.020151352283034e-05</v>
@@ -5450,7 +5450,7 @@
         <v>8.112265408822176e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.489367678312357e-05</v>
+        <v>6.011041962296985e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.581643517974179e-05</v>
@@ -5538,7 +5538,7 @@
         <v>4.42225493917134e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.489367678312357e-05</v>
+        <v>4.419162664353463e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.648419230933132e-05</v>
@@ -5925,7 +5925,7 @@
         <v>1.203879728097558e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176727083848372e-05</v>
+        <v>1.176727083848373e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.228443499933299e-05</v>
@@ -5958,7 +5958,7 @@
         <v>1.22172620355181e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.51434178881662e-05</v>
+        <v>1.189521468804311e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.178333486153332e-05</v>
@@ -6134,7 +6134,7 @@
         <v>1.642533786803495e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.51434178881662e-05</v>
+        <v>1.314568063648163e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.600161795437108e-05</v>
@@ -6167,7 +6167,7 @@
         <v>1.604675933268751e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.337364766720493e-05</v>
+        <v>1.337364766720494e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>1.325569329678415e-05</v>
@@ -6198,7 +6198,7 @@
         <v>1.986333661954887e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.980557836787175e-05</v>
+        <v>1.980557836787174e-05</v>
       </c>
       <c r="G7" t="n">
         <v>2.01505023296509e-05</v>
@@ -6222,7 +6222,7 @@
         <v>2.018332370436349e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.51434178881662e-05</v>
+        <v>1.986127635688852e-05</v>
       </c>
       <c r="O7" t="n">
         <v>1.974936477425401e-05</v>
@@ -6310,7 +6310,7 @@
         <v>7.694670525269968e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.51434178881662e-05</v>
+        <v>5.703839300109647e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.230898883725432e-05</v>
@@ -6328,7 +6328,7 @@
         <v>7.668270596560842e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.668484890398584e-05</v>
+        <v>7.668484890398586e-05</v>
       </c>
       <c r="U8" t="n">
         <v>6.433738551490287e-05</v>
@@ -6349,7 +6349,7 @@
         <v>5.100052737852356e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.686314717591222e-05</v>
+        <v>7.686314717591223e-05</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001032335386401805</v>
@@ -6398,7 +6398,7 @@
         <v>4.084962932288977e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.51434178881662e-05</v>
+        <v>4.052758197541478e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.24931938196269e-05</v>
@@ -6818,7 +6818,7 @@
         <v>1.245238674874548e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.56482460140957e-05</v>
+        <v>1.20169726834691e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.193992703026586e-05</v>
@@ -6906,7 +6906,7 @@
         <v>5.969241397908524e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>4.56482460140957e-05</v>
       </c>
       <c r="O5" t="n">
         <v>4.595073635915338e-05</v>
@@ -6994,7 +6994,7 @@
         <v>1.671000238397775e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>1.328162817154839e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.320435749222119e-05</v>
@@ -7082,7 +7082,7 @@
         <v>2.043799738183199e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>2.000258331655562e-05</v>
       </c>
       <c r="O7" t="n">
         <v>1.992550524716402e-05</v>
@@ -7170,7 +7170,7 @@
         <v>7.725817366202036e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>5.72100441092667e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.252274296867638e-05</v>
@@ -7258,7 +7258,7 @@
         <v>3.985588501050213e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>3.942047094522574e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.133351496896284e-05</v>
@@ -7678,7 +7678,7 @@
         <v>1.171893403447837e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.250235099084591e-05</v>
+        <v>1.16588682001411e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.16597464261762e-05</v>
@@ -7854,7 +7854,7 @@
         <v>1.303530784110403e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.250235099084591e-05</v>
+        <v>1.297755531930272e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.610743762035578e-05</v>
@@ -7942,7 +7942,7 @@
         <v>2.023582884334807e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.250235099084591e-05</v>
+        <v>2.01757630090108e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.017661085456939e-05</v>
@@ -8030,7 +8030,7 @@
         <v>8.104678448171574e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.250235099084591e-05</v>
+        <v>6.001502813625084e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.577910901144205e-05</v>
@@ -8118,7 +8118,7 @@
         <v>4.411361692067845e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.250235099084591e-05</v>
+        <v>4.405355108634118e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.640215870506786e-05</v>
@@ -8538,7 +8538,7 @@
         <v>1.205481474724622e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.255614880189212e-05</v>
+        <v>1.183056927389532e-05</v>
       </c>
       <c r="O4" t="n">
         <v>1.176149003634982e-05</v>
@@ -8714,7 +8714,7 @@
         <v>1.32951922209973e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.255614880189212e-05</v>
+        <v>1.307316744461763e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.594965434771227e-05</v>
@@ -8802,7 +8802,7 @@
         <v>2.000936972634126e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.255614880189212e-05</v>
+        <v>1.978512425299036e-05</v>
       </c>
       <c r="O7" t="n">
         <v>1.971601391629262e-05</v>
@@ -8890,7 +8890,7 @@
         <v>7.674421018100141e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.255614880189212e-05</v>
+        <v>5.694787349618593e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.22573748675241e-05</v>
@@ -8978,7 +8978,7 @@
         <v>4.059336796820682e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.255614880189212e-05</v>
+        <v>4.036912249485586e-05</v>
       </c>
       <c r="O9" t="n">
         <v>4.237029595064369e-05</v>

--- a/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -586,61 +586,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.339247146463488e-05</v>
+        <v>1.339247146463492e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.346629612651376e-05</v>
+        <v>1.346629612651377e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.338582815276488e-05</v>
+        <v>1.338582815276487e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.338875556989311e-05</v>
+        <v>1.338875556989308e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.338504651533894e-05</v>
+        <v>1.3385046515339e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.340329471018692e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.338881494472772e-05</v>
+        <v>1.338881494472773e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.338792459422489e-05</v>
+        <v>1.338792459422485e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.339693742835759e-05</v>
+        <v>1.339693742835764e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.339275637780558e-05</v>
+        <v>1.339275637780559e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.338950447469479e-05</v>
+        <v>1.338950447469477e-05</v>
       </c>
       <c r="M2" t="n">
         <v>1.339529725097015e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.338970309543942e-05</v>
+        <v>1.338970309543945e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.488069660071456e-05</v>
+        <v>1.488069660071457e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.339285542876507e-05</v>
+        <v>1.339285542876509e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.338799460497308e-05</v>
+        <v>1.338799460497302e-05</v>
       </c>
       <c r="R2" t="n">
         <v>1.338487208650801e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.339373781704932e-05</v>
+        <v>1.339373781704935e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.338749309009191e-05</v>
+        <v>1.338749309009192e-05</v>
       </c>
       <c r="U2" t="n">
         <v>1.389336015294617e-05</v>
@@ -649,19 +649,19 @@
         <v>1.339661020542037e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.395824088291372e-05</v>
+        <v>1.395824088291371e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.339172613075451e-05</v>
+        <v>1.33917261307545e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.339825956982869e-05</v>
+        <v>1.339825956982868e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.37284278367086e-05</v>
+        <v>1.372842783670858e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.339257163770348e-05</v>
+        <v>1.339257163770347e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.33982442063629e-05</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.342731752308024e-05</v>
+        <v>1.344139245487867e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.349066022625944e-05</v>
+        <v>1.35025807305651e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.337938465845134e-05</v>
+        <v>1.339187536944099e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.335791683007493e-05</v>
+        <v>1.336485617664937e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.337569621742637e-05</v>
+        <v>1.338801222441441e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.35019605728499e-05</v>
+        <v>1.351874694774842e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34036115474492e-05</v>
+        <v>1.341690067991718e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.339480715917314e-05</v>
+        <v>1.340784058086751e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.345733298978935e-05</v>
+        <v>1.34724126005835e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.342870852622612e-05</v>
+        <v>1.344294920438563e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34037376026027e-05</v>
+        <v>1.34171074651696e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.346773470337447e-05</v>
+        <v>1.34833959689943e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.340664927074842e-05</v>
+        <v>1.34200989688644e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.590260584102356e-05</v>
+        <v>1.59174097810162e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34265006609645e-05</v>
+        <v>1.344065845809451e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.339492327628631e-05</v>
+        <v>1.340794989548743e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.337340366123891e-05</v>
+        <v>1.338567044017491e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.343529019002103e-05</v>
+        <v>1.344970306316156e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.339144389931369e-05</v>
+        <v>1.340436091134698e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42889110265661e-05</v>
+        <v>1.430464835382147e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.345863773519898e-05</v>
+        <v>1.347378196316284e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.442913119577872e-05</v>
+        <v>1.444645634970725e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.342216700458733e-05</v>
+        <v>1.343614893268682e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.346866198226708e-05</v>
+        <v>1.348426108885877e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.39922899404135e-05</v>
+        <v>1.400695582695382e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.342616262618322e-05</v>
+        <v>1.344032094848868e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.349549844215407e-05</v>
+        <v>1.351208804410649e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.162121861049681e-05</v>
+        <v>1.162121861049684e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.152103331403813e-05</v>
+        <v>1.152103331403818e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.154617934685017e-05</v>
+        <v>1.154617934685022e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.157924586999173e-05</v>
+        <v>1.157924586999177e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.153735039255391e-05</v>
+        <v>1.153735039255396e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.174347214794563e-05</v>
+        <v>1.174347214794566e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.157991653606277e-05</v>
+        <v>1.15799165360628e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.156985961755149e-05</v>
+        <v>1.156985961755152e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.166019751268631e-05</v>
+        <v>1.166019751268637e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.162443683582592e-05</v>
+        <v>1.162443683582595e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.158770509424005e-05</v>
+        <v>1.158770509424009e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.168583346696136e-05</v>
+        <v>1.168583346696139e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.158994860692113e-05</v>
+        <v>1.158994860692118e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.165451826365157e-05</v>
+        <v>1.165451826365161e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.162555566197918e-05</v>
+        <v>1.16255556619792e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.15706504211584e-05</v>
+        <v>1.157065042115843e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.153538013866673e-05</v>
+        <v>1.153538013866677e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.163552264356882e-05</v>
+        <v>1.163552264356886e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.156498557986813e-05</v>
+        <v>1.156498557986816e-05</v>
       </c>
       <c r="U4" t="n">
         <v>1.161552370206846e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.162000962860252e-05</v>
+        <v>1.162000962860256e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.176454276599692e-05</v>
+        <v>1.176454276599694e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.161279972144692e-05</v>
+        <v>1.161279972144697e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.160776668047006e-05</v>
+        <v>1.160776668047007e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.164755170453931e-05</v>
+        <v>1.164755170453935e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.162235011138807e-05</v>
+        <v>1.162235011138812e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.172847104525062e-05</v>
+        <v>1.172847104525067e-05</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.453710201292045e-05</v>
+        <v>4.453710201292046e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.277693576808562e-05</v>
+        <v>4.277693576808566e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.271737639525012e-05</v>
+        <v>4.271737639525004e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.820604650088142e-05</v>
+        <v>1.820604650088143e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.366298693236301e-05</v>
+        <v>4.366298693236302e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.545193698689379e-05</v>
+        <v>4.545193698689363e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.512633195797068e-05</v>
+        <v>4.512633195796998e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.346770255627737e-05</v>
+        <v>4.346770255627751e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.443698865028663e-05</v>
+        <v>4.443698865028664e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.422007828678785e-05</v>
+        <v>4.42200782867877e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.243317802511644e-05</v>
+        <v>4.243317802511633e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.731517445871703e-05</v>
+        <v>4.731517445871679e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.336637662839929e-05</v>
+        <v>4.33663766283993e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.670910951550492e-05</v>
+        <v>4.670910951550377e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.251020034927094e-05</v>
+        <v>4.251020034927129e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.325566297427137e-05</v>
+        <v>4.325566297427128e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.300064042251035e-05</v>
+        <v>4.30006404225103e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.419196200484582e-05</v>
+        <v>4.419196200484721e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.32009962951304e-05</v>
+        <v>4.320099629513035e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.557984069451741e-05</v>
+        <v>4.557984069451783e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.648958790440015e-05</v>
+        <v>4.648958790440021e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.640883270315522e-05</v>
+        <v>4.640883270315512e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.446798892669562e-05</v>
+        <v>4.446798892669515e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.587418429683656e-05</v>
+        <v>4.587418429683652e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.365555216518541e-05</v>
+        <v>4.365555216518537e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.344855088076053e-05</v>
+        <v>4.344855088076099e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.915503477661031e-05</v>
+        <v>4.91550347766103e-05</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.302253999556927e-05</v>
+        <v>1.302253999556928e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.623971253512984e-05</v>
+        <v>1.623971253512989e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.62648585679419e-05</v>
+        <v>1.626485856794193e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.629792509108343e-05</v>
+        <v>1.629792509108348e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.293867177762638e-05</v>
+        <v>1.29386717776264e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.646215136903734e-05</v>
+        <v>1.646215136903737e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.629859575715449e-05</v>
+        <v>1.629859575715451e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.297118100262397e-05</v>
+        <v>1.297118100262392e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.30615188977588e-05</v>
+        <v>1.306151889775881e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.634311605691763e-05</v>
+        <v>1.634311605691767e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.630638431533178e-05</v>
+        <v>1.630638431533179e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.640451268805307e-05</v>
+        <v>1.640451268805308e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.299351948511479e-05</v>
+        <v>1.299351948511478e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.30580893964524e-05</v>
+        <v>1.305808939645242e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.635892346348345e-05</v>
+        <v>1.635892346348349e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.628932964225013e-05</v>
+        <v>1.628932964225015e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.625405935975845e-05</v>
+        <v>1.625405935975848e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.303684402864129e-05</v>
+        <v>1.30368440286413e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.29663069649406e-05</v>
+        <v>1.296630696494059e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.309567632799108e-05</v>
+        <v>1.30956763279911e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.633868884969423e-05</v>
+        <v>1.633868884969427e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.649791474523053e-05</v>
+        <v>1.649791474523057e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.633147894253864e-05</v>
+        <v>1.633147894253867e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.316499299859264e-05</v>
+        <v>1.316499299859267e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.304887308961178e-05</v>
+        <v>1.30488730896118e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.634102933247979e-05</v>
+        <v>1.634102933247981e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.31325502570647e-05</v>
+        <v>1.313255025706471e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1026,46 +1026,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.072178017721052e-05</v>
+        <v>2.07217801772105e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.062159488075184e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.064674091356392e-05</v>
+        <v>2.064674091356388e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.067980743670545e-05</v>
+        <v>2.067980743670544e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.063791195926762e-05</v>
+        <v>2.063791195926764e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.084403371465935e-05</v>
+        <v>2.084403371465933e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.068047810277648e-05</v>
+        <v>2.068047810277647e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.067042118426521e-05</v>
+        <v>2.06704211842652e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.076075907940005e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.072499840253964e-05</v>
+        <v>2.072499840253962e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.068826666095378e-05</v>
+        <v>2.068826666095376e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.078639503367505e-05</v>
+        <v>2.078639503367506e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.069051017363485e-05</v>
+        <v>2.069051017363487e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.07550518155332e-05</v>
+        <v>2.075505181553319e-05</v>
       </c>
       <c r="P7" t="n">
         <v>2.072608921386078e-05</v>
@@ -1074,19 +1074,19 @@
         <v>2.067121198787213e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.063594170538047e-05</v>
+        <v>2.063594170538044e-05</v>
       </c>
       <c r="S7" t="n">
         <v>2.073608421028254e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.066554714658186e-05</v>
+        <v>2.066554714658184e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.079477466937346e-05</v>
+        <v>2.07947746693735e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.072057119531623e-05</v>
+        <v>2.072057119531624e-05</v>
       </c>
       <c r="W7" t="n">
         <v>2.086510433271063e-05</v>
@@ -1095,16 +1095,16 @@
         <v>2.071336128816065e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.078715948803394e-05</v>
+        <v>2.078715948803395e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.074811327125303e-05</v>
+        <v>2.074811327125302e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.072291167810178e-05</v>
+        <v>2.072291167810179e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.082903261196434e-05</v>
+        <v>2.082903261196433e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.678341767653877e-05</v>
+        <v>5.678341767653891e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.558430745918121e-05</v>
+        <v>8.558430745918139e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.560945349199325e-05</v>
+        <v>8.560945349199347e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.025355006285822e-05</v>
+        <v>7.02535500628584e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.120199918256504e-05</v>
+        <v>6.120199918256518e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.179957248410411e-05</v>
+        <v>9.179957248410435e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.56431906812059e-05</v>
+        <v>8.564319068120617e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.563313376269458e-05</v>
+        <v>8.563313376269494e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.572347165782936e-05</v>
+        <v>8.572347165782966e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.568771098096899e-05</v>
+        <v>8.568771098096928e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.56509792393831e-05</v>
+        <v>8.565097923938327e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.574910761210436e-05</v>
+        <v>8.574910761210469e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.325005452260047e-05</v>
+        <v>6.325005452260071e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.947120933499267e-05</v>
+        <v>6.947120933499288e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.793311894741601e-05</v>
+        <v>6.793311894741621e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.105312859795619e-05</v>
+        <v>5.105312859795631e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.559865428380982e-05</v>
+        <v>8.559865428381014e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.569879678871192e-05</v>
+        <v>8.569879678871218e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.562825972501122e-05</v>
+        <v>8.56282597250114e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>7.165131187151767e-05</v>
+        <v>7.165131187151796e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.778408688710553e-05</v>
+        <v>7.778408688710588e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.583349680577872e-05</v>
+        <v>8.583349680577895e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.374411885977081e-05</v>
+        <v>5.374411885977089e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.000114485402283091</v>
+        <v>0.0001144854022830914</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.627289846274296e-05</v>
+        <v>5.627289846274315e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.568562425653111e-05</v>
+        <v>8.568562425653144e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001159813347839444</v>
+        <v>0.0001159813347839445</v>
       </c>
     </row>
     <row r="9">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.065407256597755e-05</v>
+        <v>4.065407256597762e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.867253052087586e-05</v>
+        <v>4.867253052087588e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.869767655368786e-05</v>
+        <v>4.869767655368792e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.685699349274119e-05</v>
+        <v>4.685699349274117e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.997315884048115e-05</v>
+        <v>2.99731588404812e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.889496956666805e-05</v>
+        <v>4.889496956666799e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.87314137429005e-05</v>
+        <v>4.873141374290054e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.872135682438915e-05</v>
+        <v>4.872135682438922e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.881169471952405e-05</v>
+        <v>4.881169471952412e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.877593404266366e-05</v>
+        <v>4.877593404266368e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.87392023010778e-05</v>
+        <v>4.873920230107783e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.883733067379904e-05</v>
+        <v>4.883733067379905e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.874144581375885e-05</v>
+        <v>4.874144581375892e-05</v>
       </c>
       <c r="O9" t="n">
         <v>5.149652349563332e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>5.205270018200603e-05</v>
+        <v>5.205270018200619e-05</v>
       </c>
       <c r="Q9" t="n">
         <v>4.872214783988078e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.868687734550444e-05</v>
+        <v>4.868687734550454e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.878701985040653e-05</v>
+        <v>4.87870198504066e-05</v>
       </c>
       <c r="T9" t="n">
         <v>4.871648278670588e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.884585214975636e-05</v>
+        <v>4.884585214975634e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.814024740130153e-05</v>
+        <v>5.814024740130155e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.891603997283465e-05</v>
+        <v>4.891603997283467e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.876429692828464e-05</v>
+        <v>4.876429692828471e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.883809512815791e-05</v>
+        <v>4.883809512815797e-05</v>
       </c>
       <c r="Z9" t="n">
         <v>4.390422905287121e-05</v>
@@ -1280,7 +1280,7 @@
         <v>4.877384731822583e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.887996825208833e-05</v>
+        <v>4.887996825208839e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.353632981591998e-05</v>
+        <v>1.353632981592016e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.360422962953078e-05</v>
+        <v>1.360422962953079e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.355647770816467e-05</v>
+        <v>1.355647770816462e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.352196639073164e-05</v>
+        <v>1.352196639073177e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.351998548186428e-05</v>
+        <v>1.351998548186426e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356736374654751e-05</v>
+        <v>1.356736374654762e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.353966913030211e-05</v>
+        <v>1.353966913030204e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.355085420790247e-05</v>
+        <v>1.355085420790245e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.354686692556298e-05</v>
+        <v>1.354686692556291e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.352958918162356e-05</v>
+        <v>1.352958918162341e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.353115742980324e-05</v>
+        <v>1.353115742980317e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.356065926415284e-05</v>
+        <v>1.356065926415285e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.352593033935194e-05</v>
+        <v>1.352593033935188e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.510591907523722e-05</v>
+        <v>1.510591907523725e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.351694776004486e-05</v>
+        <v>1.351694776004478e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.353118166437033e-05</v>
+        <v>1.353118166437024e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.354033709612246e-05</v>
+        <v>1.35403370961224e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3529361427342e-05</v>
+        <v>1.352936142734215e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.353503897036593e-05</v>
+        <v>1.353503897036613e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.408345145438903e-05</v>
+        <v>1.408345145438917e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.354079540931499e-05</v>
+        <v>1.354079540931493e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.420318025593689e-05</v>
+        <v>1.420318025593699e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.352114306803868e-05</v>
+        <v>1.352114306803892e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.355500067798373e-05</v>
+        <v>1.355500067798369e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.390152006787481e-05</v>
+        <v>1.390152006787501e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.354625508605428e-05</v>
+        <v>1.354625508605426e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.355720201408277e-05</v>
+        <v>1.355720201408283e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.371405897761649e-05</v>
+        <v>1.373555498729557e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.370612541127953e-05</v>
+        <v>1.372233112994478e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386539108012915e-05</v>
+        <v>1.389221573496235e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.357703430174529e-05</v>
+        <v>1.358875703437316e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.360286337092556e-05</v>
+        <v>1.362046878941128e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.394063143173047e-05</v>
+        <v>1.396989880494417e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.374390633552578e-05</v>
+        <v>1.376656294640815e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.382224241193571e-05</v>
+        <v>1.38476718055702e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.379361696035855e-05</v>
+        <v>1.381775963938559e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.36821338999195e-05</v>
+        <v>1.370211360076215e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.368585962500993e-05</v>
+        <v>1.370613989260453e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.391506816408788e-05</v>
+        <v>1.394375536124664e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.363801454324408e-05</v>
+        <v>1.365703523565571e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.622548270402425e-05</v>
+        <v>1.6243172722724e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.35776746861991e-05</v>
+        <v>1.359430745751682e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.368142160355777e-05</v>
+        <v>1.370179067566601e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.374542336965969e-05</v>
+        <v>1.3768207940961e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36674627045239e-05</v>
+        <v>1.368725305694457e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.370632103263028e-05</v>
+        <v>1.372771018614119e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.458644677673182e-05</v>
+        <v>1.460615539321935e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37517187366535e-05</v>
+        <v>1.377437737315962e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.504236768038022e-05</v>
+        <v>1.507449890897601e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.361093663540971e-05</v>
+        <v>1.362877864257493e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38450867254969e-05</v>
+        <v>1.387142636552112e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.429783186522145e-05</v>
+        <v>1.431824057849846e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.378237687564303e-05</v>
+        <v>1.380649620810418e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.389186388670113e-05</v>
+        <v>1.391980407864018e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.205086439088544e-05</v>
+        <v>1.205086439088558e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.18065193084845e-05</v>
+        <v>1.180651930848462e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.227844410227732e-05</v>
+        <v>1.227844410227748e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.188862289588099e-05</v>
+        <v>1.188862289588113e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.186624761896114e-05</v>
+        <v>1.186624761896129e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.240140691363677e-05</v>
+        <v>1.240140691363691e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.208858348299207e-05</v>
+        <v>1.20885834829922e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.221492407987802e-05</v>
+        <v>1.221492407987815e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.215834916522109e-05</v>
+        <v>1.215834916522118e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.197472582566127e-05</v>
+        <v>1.197472582566139e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.199243991028155e-05</v>
+        <v>1.199243991028169e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.235778840194274e-05</v>
+        <v>1.235778840194287e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.193339751905373e-05</v>
+        <v>1.193339751905389e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.187940784858596e-05</v>
+        <v>1.187940784858609e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.183193515358949e-05</v>
+        <v>1.183193515358961e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.199271365086533e-05</v>
+        <v>1.199271365086546e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.209612846421222e-05</v>
+        <v>1.209612846421237e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.197215323627974e-05</v>
+        <v>1.197215323627989e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.203628369653395e-05</v>
+        <v>1.203628369653408e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.190264341726859e-05</v>
+        <v>1.190264341726862e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.205288594693267e-05</v>
+        <v>1.20528859469328e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.252266391933631e-05</v>
+        <v>1.252266391933646e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.187932308731729e-05</v>
+        <v>1.187932308731742e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.219710192499902e-05</v>
+        <v>1.219710192499904e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.200111275256676e-05</v>
+        <v>1.20011127525669e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.216297488290244e-05</v>
+        <v>1.216297488290261e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.232792194860407e-05</v>
+        <v>1.232792194860421e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.644623077778755e-05</v>
+        <v>4.64462307777876e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.66965657627136e-05</v>
+        <v>4.669656576271384e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.437648280689231e-05</v>
+        <v>5.437648280689249e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.569165146615794e-05</v>
+        <v>2.569165146615809e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.600774917522172e-05</v>
+        <v>4.600774917522183e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.527963894504342e-05</v>
+        <v>5.527963894504583e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.023021992032962e-05</v>
+        <v>5.023021992032975e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.169137369861505e-05</v>
+        <v>5.169137369861518e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.079619083308485e-05</v>
+        <v>5.07961908330856e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.348611024414227e-05</v>
+        <v>5.348611024414235e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.992986030396983e-05</v>
+        <v>4.992986030396989e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.701639476582727e-05</v>
+        <v>5.701639476582733e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.342398859320103e-05</v>
+        <v>4.342398859320108e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.538724653746516e-05</v>
+        <v>4.538724653746524e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.358278240438023e-05</v>
+        <v>4.358278240438029e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75451757628697e-05</v>
+        <v>4.754517576286979e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.867929460455699e-05</v>
+        <v>4.867929460455716e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.668000517626866e-05</v>
+        <v>4.668000517626878e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.695266846768455e-05</v>
+        <v>4.695266846768459e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.008664387519353e-05</v>
+        <v>5.008664387519362e-05</v>
       </c>
       <c r="V5" t="n">
         <v>5.028973600149059e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.395653550390592e-05</v>
+        <v>5.39565355039059e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.614133244187204e-05</v>
+        <v>4.614133244187216e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.902212275211134e-05</v>
+        <v>4.902212275211153e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.822198772113384e-05</v>
+        <v>4.822198772113397e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.712355245333855e-05</v>
+        <v>4.712355245333879e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.466401440362237e-05</v>
+        <v>5.466401440362257e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.330458930570415e-05</v>
+        <v>1.330458930570422e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.603311691147246e-05</v>
+        <v>1.603311691147253e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.353216901709608e-05</v>
+        <v>1.35321690170961e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.611522049886895e-05</v>
+        <v>1.611522049886902e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.609284522194914e-05</v>
+        <v>1.609284522194918e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.365513182845554e-05</v>
+        <v>1.365513182845552e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.334230839781082e-05</v>
+        <v>1.334230839781084e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.346864899469676e-05</v>
+        <v>1.346864899469679e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.638494676820906e-05</v>
+        <v>1.638494676820913e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.322845074047995e-05</v>
+        <v>1.322845074048003e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.621903751326952e-05</v>
+        <v>1.621903751326958e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.361151331676144e-05</v>
+        <v>1.36115133167615e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.318993934215458e-05</v>
+        <v>1.318993934215459e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.611697359142794e-05</v>
+        <v>1.611697359142808e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.299878403117843e-05</v>
+        <v>1.299878403117847e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.324643856568406e-05</v>
+        <v>1.324643856568409e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.334985337903097e-05</v>
+        <v>1.334985337903101e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.619875083926772e-05</v>
+        <v>1.619875083926775e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.329000861135273e-05</v>
+        <v>1.329000861135271e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.619389946217397e-05</v>
+        <v>1.6193899462174e-05</v>
       </c>
       <c r="V6" t="n">
         <v>1.330661086175144e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.386013844014575e-05</v>
+        <v>1.386013844014578e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.610592069030527e-05</v>
+        <v>1.610592069030528e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.358523300209229e-05</v>
+        <v>1.358523300209233e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>1.325483766738552e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.638957248589043e-05</v>
+        <v>1.638957248589046e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35853770895789e-05</v>
+        <v>1.358537708957894e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.002434922369343e-05</v>
+        <v>2.002434922369349e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.978000414129248e-05</v>
+        <v>1.978000414129251e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.025192893508529e-05</v>
+        <v>2.025192893508536e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.986210772868897e-05</v>
+        <v>1.986210772868902e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.983973245176914e-05</v>
+        <v>1.983973245176917e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.037489174644476e-05</v>
+        <v>2.037489174644484e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.006206831580004e-05</v>
+        <v>2.00620683158001e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0188408912686e-05</v>
+        <v>2.018840891268603e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.013183399802905e-05</v>
+        <v>2.01318339980291e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.994821065846926e-05</v>
+        <v>1.99482106584693e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.996592474308952e-05</v>
+        <v>1.996592474308957e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.033127323475071e-05</v>
+        <v>2.033127323475076e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.990688235186171e-05</v>
+        <v>1.990688235186178e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.985286066033034e-05</v>
+        <v>1.985286066033035e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.980538796533385e-05</v>
+        <v>1.98053879653339e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.996619848367329e-05</v>
+        <v>1.996619848367336e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.00696132970202e-05</v>
+        <v>2.006961329702026e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.994563806908774e-05</v>
+        <v>1.994563806908778e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.000976852934195e-05</v>
+        <v>2.000976852934199e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.994213044316984e-05</v>
+        <v>1.994213044316989e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.002637077974067e-05</v>
+        <v>2.002637077974069e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.049614875214428e-05</v>
+        <v>2.049614875214433e-05</v>
       </c>
       <c r="X7" t="n">
         <v>1.985280792012529e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.023524519972438e-05</v>
+        <v>2.023524519972445e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.997459758537473e-05</v>
+        <v>1.997459758537477e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.013645971571042e-05</v>
+        <v>2.013645971571049e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.030140678141206e-05</v>
+        <v>2.030140678141209e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.153234321668131e-05</v>
+        <v>5.153234321668154e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.656958696831124e-05</v>
+        <v>7.656958696831154e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.704151176210407e-05</v>
+        <v>7.704151176210438e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.31899902609174e-05</v>
+        <v>6.318999026091776e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.528630251345841e-05</v>
+        <v>5.528630251345867e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.240677671275272e-05</v>
+        <v>8.240677671275315e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.68516511428187e-05</v>
+        <v>7.685165114281911e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.697799173970467e-05</v>
+        <v>7.697799173970515e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.692141682504784e-05</v>
+        <v>7.692141682504824e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.673779348548793e-05</v>
+        <v>7.673779348548841e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.675550757010826e-05</v>
+        <v>7.675550757010866e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.712085606176911e-05</v>
+        <v>7.712085606176952e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.709900431597729e-05</v>
+        <v>5.709900431597752e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.243056705486727e-05</v>
+        <v>6.243056705486752e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.10629653308953e-05</v>
+        <v>6.106296533089564e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.650578324550462e-05</v>
+        <v>4.650578324550481e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.68591961240389e-05</v>
+        <v>7.685919612403938e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.673522089610642e-05</v>
+        <v>7.673522089610688e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.679935135636065e-05</v>
+        <v>7.679935135636083e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.439182963107444e-05</v>
+        <v>6.439182963107476e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.990729015686711e-05</v>
+        <v>6.990729015686751e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.729070014021748e-05</v>
+        <v>7.729070014021787e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.870950053659764e-05</v>
+        <v>4.870950053659786e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001021635602998465</v>
+        <v>0.000102163560299847</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.101297308581894e-05</v>
+        <v>5.101297308581918e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.692604254272903e-05</v>
+        <v>7.692604254272947e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001034997231617619</v>
+        <v>0.0001034997231617625</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.337579328487214e-05</v>
+        <v>3.337579328487224e-05</v>
       </c>
       <c r="C9" t="n">
         <v>3.911406339047588e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.958598818426863e-05</v>
+        <v>3.958598818426868e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.781540396944461e-05</v>
+        <v>3.781540396944466e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.538223058619677e-05</v>
+        <v>2.538223058619682e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.970895122225335e-05</v>
+        <v>3.970895122225339e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.93961275649834e-05</v>
+        <v>3.93961275649835e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95224681618693e-05</v>
+        <v>3.952246816186941e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.946589324721243e-05</v>
+        <v>3.946589324721252e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.928226990765261e-05</v>
+        <v>3.928226990765269e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.929998399227289e-05</v>
+        <v>3.929998399227297e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.966533248393408e-05</v>
+        <v>3.966533248393419e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.924094160104508e-05</v>
+        <v>3.924094160104514e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.116958307204277e-05</v>
+        <v>4.116958307204279e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.155329858480715e-05</v>
+        <v>4.155329858480722e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.930025795948191e-05</v>
+        <v>3.930025795948195e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.940367254620356e-05</v>
+        <v>3.940367254620363e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.927969731827109e-05</v>
+        <v>3.927969731827112e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.93438277785253e-05</v>
+        <v>3.934382777852538e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.927484594117734e-05</v>
+        <v>3.92748459411774e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.62642396263428e-05</v>
+        <v>4.626423962634289e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.983020800132765e-05</v>
+        <v>3.983020800132775e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.918686716930864e-05</v>
+        <v>3.918686716930877e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.95693044489077e-05</v>
+        <v>3.95693044489078e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.570167196108073e-05</v>
+        <v>3.570167196108079e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.947051896489378e-05</v>
+        <v>3.94705189648939e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.963546603059539e-05</v>
+        <v>3.963546603059553e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.340936403023107e-05</v>
+        <v>1.340936403023108e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.348262044315811e-05</v>
+        <v>1.348262044315817e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.341579283206172e-05</v>
+        <v>1.34157928320616e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.340318116955502e-05</v>
+        <v>1.34031811695549e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.340092208492976e-05</v>
+        <v>1.340092208492966e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.342019768564215e-05</v>
+        <v>1.342019768564205e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.340395136211968e-05</v>
+        <v>1.340395136211956e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.340325556663909e-05</v>
+        <v>1.340325556663898e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.341335491260772e-05</v>
+        <v>1.341335491260759e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.341070790402082e-05</v>
+        <v>1.341070790402091e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.340709835249202e-05</v>
+        <v>1.340709835249214e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.340967498114829e-05</v>
+        <v>1.340967498114834e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.340954051986059e-05</v>
+        <v>1.340954051986048e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.490981444530199e-05</v>
+        <v>1.490981444530207e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.340576168139249e-05</v>
+        <v>1.340576168139248e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.340816114059997e-05</v>
+        <v>1.34081611406e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.341038792529181e-05</v>
+        <v>1.341038792529171e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.341060584398961e-05</v>
+        <v>1.341060584398962e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.341007932039398e-05</v>
+        <v>1.341007932039386e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.391389491907314e-05</v>
+        <v>1.39138949190732e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.340936073452049e-05</v>
+        <v>1.340936073452043e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.398233173969559e-05</v>
+        <v>1.398233173969557e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341128345035362e-05</v>
+        <v>1.34112834503535e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.341371069420504e-05</v>
+        <v>1.341371069420492e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.374878821169527e-05</v>
+        <v>1.374878821169538e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.341103720685333e-05</v>
+        <v>1.341103720685322e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.341517600346998e-05</v>
+        <v>1.341517600347019e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.34677136437302e-05</v>
+        <v>1.348288005140632e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.352762794985046e-05</v>
+        <v>1.354038162507146e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.351294891170603e-05</v>
+        <v>1.352986767680814e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.338064208975101e-05</v>
+        <v>1.33880586113917e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.341033439583547e-05</v>
+        <v>1.342350485348904e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.354319239688395e-05</v>
+        <v>1.356107345851156e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.343171616604613e-05</v>
+        <v>1.344567237746667e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.342362721934682e-05</v>
+        <v>1.343737396564008e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.349523619937713e-05</v>
+        <v>1.3511314270314e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.348603647379182e-05</v>
+        <v>1.350165265360981e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.344862667211322e-05</v>
+        <v>1.346327135262879e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.349089177521446e-05</v>
+        <v>1.350704221881951e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.346763995672986e-05</v>
+        <v>1.348293819068174e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.592896767805462e-05</v>
+        <v>1.594327758738571e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3438266031775e-05</v>
+        <v>1.345251843368911e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.345872154744225e-05</v>
+        <v>1.347368314800347e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34752564510615e-05</v>
+        <v>1.349083459623493e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.347581496213852e-05</v>
+        <v>1.34913165346579e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.347303140217613e-05</v>
+        <v>1.348850441752819e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.432702475889982e-05</v>
+        <v>1.434349089872213e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.347400814629163e-05</v>
+        <v>1.348920829051912e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44828142235043e-05</v>
+        <v>1.45013276204147e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.348166128577242e-05</v>
+        <v>1.349742672221961e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.349979203394401e-05</v>
+        <v>1.351612924795639e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.403780207690862e-05</v>
+        <v>1.405352707967573e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.347853066756696e-05</v>
+        <v>1.349418684297863e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.353594190908283e-05</v>
+        <v>1.355365782913946e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.167772502315472e-05</v>
+        <v>1.16777250231546e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.156533397075751e-05</v>
+        <v>1.156533397075755e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.175034129722671e-05</v>
+        <v>1.175034129722673e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.160788676756216e-05</v>
+        <v>1.160788676756217e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.15823693674896e-05</v>
+        <v>1.158236936748964e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.180009614475051e-05</v>
+        <v>1.180009614475052e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.161658644688599e-05</v>
+        <v>1.161658644688601e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.160872711685102e-05</v>
+        <v>1.160872711685103e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.171131547598142e-05</v>
+        <v>1.17113154759815e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.169290469582235e-05</v>
+        <v>1.169290469582239e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.165213315082861e-05</v>
+        <v>1.165213315082917e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.171470757523179e-05</v>
+        <v>1.171470757523181e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.167971855470917e-05</v>
+        <v>1.16797185547092e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.163937194295056e-05</v>
+        <v>1.163937194295059e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.163703483586042e-05</v>
+        <v>1.163703483586047e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.166413783141451e-05</v>
+        <v>1.16641378314146e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.168929038888062e-05</v>
+        <v>1.168929038888066e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.169175188081973e-05</v>
+        <v>1.169175188081977e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.168580455459434e-05</v>
+        <v>1.168580455459438e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.166090444603885e-05</v>
+        <v>1.166090444603888e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.162956965664536e-05</v>
+        <v>1.16295696566454e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.182499522745522e-05</v>
+        <v>1.182499522745525e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.169940575641543e-05</v>
+        <v>1.169940575641565e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.165342348480201e-05</v>
+        <v>1.165342348480204e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.170254324260243e-05</v>
+        <v>1.170254324260253e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.169662432280222e-05</v>
+        <v>1.169662432280224e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.178575682668178e-05</v>
+        <v>1.17857568266818e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.364196493280554e-05</v>
+        <v>4.364196493281334e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.365788446439394e-05</v>
+        <v>4.365788446439408e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.465492732421391e-05</v>
+        <v>4.46549273242141e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.843797351509388e-05</v>
+        <v>1.84379735150957e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.343588959938994e-05</v>
+        <v>4.343588959939006e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.493154443932531e-05</v>
+        <v>4.493154443932381e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.395031392996172e-05</v>
+        <v>4.395031392996184e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.206483604763881e-05</v>
+        <v>4.206483604763949e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.394859953940255e-05</v>
+        <v>4.394859953940417e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.878504404722218e-05</v>
+        <v>4.878504404722205e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.153593772474235e-05</v>
+        <v>4.153593772475643e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.588389300908374e-05</v>
+        <v>4.588389300908382e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.293813936921933e-05</v>
+        <v>4.29381393692196e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.464896777981309e-05</v>
+        <v>4.464896777981325e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.079399711797668e-05</v>
+        <v>4.079399711797699e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.315869839894481e-05</v>
+        <v>4.315869839894464e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.399145836104349e-05</v>
+        <v>4.399145836104352e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.348363549695603e-05</v>
+        <v>4.348363549695441e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.391302379863582e-05</v>
+        <v>4.391302379863561e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.417164105589418e-05</v>
+        <v>4.417164105589425e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.710692631314327e-05</v>
+        <v>4.710692631314336e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.519256400988708e-05</v>
+        <v>4.519256400988747e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.419018661067321e-05</v>
+        <v>4.419018661067571e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.5157612069226e-05</v>
+        <v>4.515761206922609e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.286106109041111e-05</v>
+        <v>4.286106109041325e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.337390612860885e-05</v>
+        <v>4.337390612860968e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.775375533503333e-05</v>
+        <v>4.775375533503336e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.299323172281241e-05</v>
+        <v>1.299323172281261e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.599812817219437e-05</v>
+        <v>1.599812817219444e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.306584799688455e-05</v>
+        <v>1.30658479968846e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.604068096899902e-05</v>
+        <v>1.604068096899905e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.289787606714747e-05</v>
+        <v>1.289787606714752e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.623289034618735e-05</v>
+        <v>1.623289034618741e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.604938064832285e-05</v>
+        <v>1.604938064832291e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.604152131828787e-05</v>
+        <v>1.604152131828795e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.614410967741826e-05</v>
+        <v>1.61441096774184e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.300841139548022e-05</v>
+        <v>1.300841139548027e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.608492735226562e-05</v>
+        <v>1.608492735226558e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.614750177666865e-05</v>
+        <v>1.614750177666872e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.299759266560053e-05</v>
+        <v>1.299759266560058e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.295703376553004e-05</v>
+        <v>1.295703376553007e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.60821687490523e-05</v>
+        <v>1.608216874905236e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.297964453107237e-05</v>
+        <v>1.29796445310725e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.612208459031749e-05</v>
+        <v>1.612208459031753e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.300725858047762e-05</v>
+        <v>1.300725858047763e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.300131125425218e-05</v>
+        <v>1.300131125425226e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.304981025319941e-05</v>
+        <v>1.304981025319945e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.294507635630322e-05</v>
+        <v>1.294507635630326e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.322551033673545e-05</v>
+        <v>1.322551033673551e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.613219995785228e-05</v>
+        <v>1.613219995785237e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.311458573184648e-05</v>
+        <v>1.311458573184652e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.301804994226041e-05</v>
+        <v>1.301804994226048e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.612941852423905e-05</v>
+        <v>1.612941852423915e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.310398084185577e-05</v>
+        <v>1.310398084185582e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.019504771264028e-05</v>
+        <v>2.019504771264021e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.008265666024313e-05</v>
+        <v>2.008265666024321e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.026766398671231e-05</v>
+        <v>2.026766398671237e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.012520945704779e-05</v>
+        <v>2.012520945704789e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.009969205697522e-05</v>
+        <v>2.009969205697529e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.031741883423612e-05</v>
+        <v>2.03174188342362e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.013390913637161e-05</v>
+        <v>2.013390913637168e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.012604980633664e-05</v>
+        <v>2.012604980633668e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.022863816546705e-05</v>
+        <v>2.022863816546715e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.021022738530796e-05</v>
+        <v>2.021022738530801e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.016945584031455e-05</v>
+        <v>2.016945584031437e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.023203026471741e-05</v>
+        <v>2.023203026471745e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.019704124419479e-05</v>
+        <v>2.019704124419485e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.015666461509543e-05</v>
+        <v>2.015666461509548e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.015432750800527e-05</v>
+        <v>2.015432750800534e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.018146052090014e-05</v>
+        <v>2.018146052090026e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.020661307836624e-05</v>
+        <v>2.02066130783663e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.020907457030539e-05</v>
+        <v>2.020907457030546e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.020312724407996e-05</v>
+        <v>2.020312724408003e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.025141003063986e-05</v>
+        <v>2.025141003063993e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.014689234613098e-05</v>
+        <v>2.014689234613105e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.034231791694084e-05</v>
+        <v>2.034231791694089e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.021672844590109e-05</v>
+        <v>2.021672844590121e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.024414528179032e-05</v>
+        <v>2.024414528179037e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.021986593208808e-05</v>
+        <v>2.021986593208818e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.02139470122878e-05</v>
+        <v>2.021394701228791e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.03030795161674e-05</v>
+        <v>2.030307951616747e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.395093710375516e-05</v>
+        <v>5.395093710375539e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.089214102868054e-05</v>
+        <v>8.089214102868081e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.107714835514979e-05</v>
+        <v>8.107714835515003e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.652945253022042e-05</v>
+        <v>6.652945253022064e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.807021536411058e-05</v>
+        <v>5.807021536411079e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.673664235935027e-05</v>
+        <v>8.673664235935056e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.094339350480905e-05</v>
+        <v>8.094339350480926e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.093553417477411e-05</v>
+        <v>8.093553417477432e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.103812253390447e-05</v>
+        <v>8.103812253390482e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.101971175374545e-05</v>
+        <v>8.101971175374578e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.097894020875178e-05</v>
+        <v>8.097894020875224e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.104151463315389e-05</v>
+        <v>8.104151463315425e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.003546353863856e-05</v>
+        <v>6.003546353863874e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.575814687606399e-05</v>
+        <v>6.575814687606417e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.434315187382556e-05</v>
+        <v>6.43431518738258e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.862070102953311e-05</v>
+        <v>4.862070102953328e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.101609744680372e-05</v>
+        <v>8.101609744680397e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.101855893874288e-05</v>
+        <v>8.101855893874321e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.101261161251743e-05</v>
+        <v>8.101261161251773e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.78564676896653e-05</v>
+        <v>6.785646768966562e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.356206213640309e-05</v>
+        <v>7.356206213640332e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.115711909688e-05</v>
+        <v>8.115711909688041e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.113548469351672e-05</v>
+        <v>5.113548469351703e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001079521565083654</v>
+        <v>0.0001079521565083656</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.347322090677644e-05</v>
+        <v>5.347322090677665e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.10234313807253e-05</v>
+        <v>8.102343138072559e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001093723060277514</v>
+        <v>0.0001093723060277517</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.698593892397389e-05</v>
+        <v>3.698593892397404e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.395696473485043e-05</v>
+        <v>4.39569647348505e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.41419720613196e-05</v>
+        <v>4.414197206131968e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.236469397769966e-05</v>
+        <v>4.236469397769973e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.764479073326187e-05</v>
+        <v>2.764479073326195e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.419172712381527e-05</v>
+        <v>4.419172712381533e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.400821721097892e-05</v>
+        <v>4.400821721097898e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.400035788094393e-05</v>
+        <v>4.400035788094399e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.410294624007434e-05</v>
+        <v>4.410294624007448e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.408453545991522e-05</v>
+        <v>4.408453545991531e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.404376391492173e-05</v>
+        <v>4.404376391492176e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.410633833932472e-05</v>
+        <v>4.410633833932481e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.407134931880209e-05</v>
+        <v>4.407134931880222e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.637843806680051e-05</v>
+        <v>4.637843806680061e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.688662782849796e-05</v>
+        <v>4.688662782849812e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.405576881047927e-05</v>
+        <v>4.405576881047941e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.408092115297353e-05</v>
+        <v>4.408092115297361e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.408338264491264e-05</v>
+        <v>4.408338264491284e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.407743531868722e-05</v>
+        <v>4.407743531868733e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.412593431763447e-05</v>
+        <v>4.412593431763451e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.219531177986899e-05</v>
+        <v>5.219531177986909e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.421662599154813e-05</v>
+        <v>4.421662599154824e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.409103652050839e-05</v>
+        <v>4.40910365205085e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.411845335639762e-05</v>
+        <v>4.411845335639766e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.982350360550765e-05</v>
+        <v>3.982350360550775e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.40882550868951e-05</v>
+        <v>4.408825508689522e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.417738759077469e-05</v>
+        <v>4.417738759077476e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.344549561464646e-05</v>
+        <v>1.344549561464635e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.352249402739238e-05</v>
+        <v>1.352249402739241e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.345498381017009e-05</v>
+        <v>1.345498381016996e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.344161402297619e-05</v>
+        <v>1.344161402297614e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343440127032414e-05</v>
+        <v>1.3434401270324e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.345308109440238e-05</v>
+        <v>1.34530810944023e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.343900223300974e-05</v>
+        <v>1.343900223300962e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.345067329792471e-05</v>
+        <v>1.345067329792458e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.34478207046053e-05</v>
+        <v>1.344782070460517e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.345440343725682e-05</v>
+        <v>1.34544034372567e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.344233973966822e-05</v>
+        <v>1.344233973966818e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344619767831637e-05</v>
+        <v>1.344619767831638e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.344241050738781e-05</v>
+        <v>1.344241050738772e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.497872954988995e-05</v>
+        <v>1.497872954988994e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343602809896705e-05</v>
+        <v>1.343602809896691e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.344091986729431e-05</v>
+        <v>1.344091986729418e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.344221646643322e-05</v>
+        <v>1.344221646643308e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344606350094564e-05</v>
+        <v>1.34460635009455e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344626094961088e-05</v>
+        <v>1.344626094961078e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.396935976496956e-05</v>
+        <v>1.39693597649694e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344341663147084e-05</v>
+        <v>1.344341663147073e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.405186008317625e-05</v>
+        <v>1.405186008317621e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344375441390426e-05</v>
+        <v>1.344375441390415e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.344069231897628e-05</v>
+        <v>1.344069231897615e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.380058476910582e-05</v>
+        <v>1.380058476910576e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.344813730950968e-05</v>
+        <v>1.344813730950961e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.344903491833579e-05</v>
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.353318610754685e-05</v>
+        <v>1.355018623063385e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.360945308660795e-05</v>
+        <v>1.362424050630679e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.360382200546389e-05</v>
+        <v>1.362337634834955e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.346410566296639e-05</v>
+        <v>1.347394424306393e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.346015228808176e-05</v>
+        <v>1.347451252292589e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.358961287470406e-05</v>
+        <v>1.36085159562467e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34906617223737e-05</v>
+        <v>1.350621131834182e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.35727292440622e-05</v>
+        <v>1.359120907276311e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.355253235955203e-05</v>
+        <v>1.357006165860891e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.361307126011849e-05</v>
+        <v>1.363246188455214e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35104753715751e-05</v>
+        <v>1.352673986544989e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.356131224148793e-05</v>
+        <v>1.35794376679005e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.351173751422838e-05</v>
+        <v>1.352806284423862e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.601662221278165e-05</v>
+        <v>1.603117077160489e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.346539792195374e-05</v>
+        <v>1.348001733463215e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.350382131078373e-05</v>
+        <v>1.35197831432139e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.351210817197905e-05</v>
+        <v>1.352845437621284e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.353912051825561e-05</v>
+        <v>1.355629172607766e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.35406732077743e-05</v>
+        <v>1.355801864870967e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.439207388597852e-05</v>
+        <v>1.440873633784443e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352814111061846e-05</v>
+        <v>1.354465768243763e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.462255890631848e-05</v>
+        <v>1.464370697911451e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.352350027273147e-05</v>
+        <v>1.354019415145741e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.350153066066002e-05</v>
+        <v>1.351740719088342e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.413854214186701e-05</v>
+        <v>1.415619912939073e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.355254337762697e-05</v>
+        <v>1.35702916278599e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.358746441580915e-05</v>
+        <v>1.360647752472552e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.178371716005569e-05</v>
+        <v>1.178371716005571e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.167920581038823e-05</v>
+        <v>1.167920581038822e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.189089069328045e-05</v>
@@ -3354,73 +3354,73 @@
         <v>1.173987279651945e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.165840143728438e-05</v>
+        <v>1.165840143728437e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.186939864339174e-05</v>
+        <v>1.186939864339189e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.171037142736571e-05</v>
+        <v>1.171037142736569e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.184220147453538e-05</v>
+        <v>1.18422014745354e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.179848975196504e-05</v>
+        <v>1.179848975196487e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.188433511424056e-05</v>
+        <v>1.188433511424051e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.174807010040216e-05</v>
+        <v>1.174807010040215e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.182557980753127e-05</v>
+        <v>1.182557980753124e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.174886945434966e-05</v>
+        <v>1.174886945434965e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.167330385448429e-05</v>
+        <v>1.167330385448427e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.167677721518428e-05</v>
+        <v>1.167677721518424e-05</v>
       </c>
       <c r="Q4" t="n">
         <v>1.173203198876536e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.174667767250418e-05</v>
+        <v>1.17466776725042e-05</v>
       </c>
       <c r="S4" t="n">
         <v>1.17901316970454e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.179236197055025e-05</v>
+        <v>1.179236197055022e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.169962760749074e-05</v>
+        <v>1.169962760749065e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17121153179495e-05</v>
+        <v>1.171211531794951e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.196631335683421e-05</v>
+        <v>1.196631335683419e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.176404949668041e-05</v>
+        <v>1.176404949668043e-05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.166275661061633e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.181289011879865e-05</v>
+        <v>1.181289011879864e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.181355631877534e-05</v>
+        <v>1.181355631877532e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.186676250441774e-05</v>
+        <v>1.18667625044177e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3433,82 +3433,82 @@
         <v>4.171748838205328e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.516025374015735e-05</v>
+        <v>4.516025374015738e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.512529866881366e-05</v>
+        <v>4.512529866881383e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.949927426549221e-05</v>
+        <v>1.949927426549223e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.268663590993303e-05</v>
+        <v>4.268663590993305e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.441902980172203e-05</v>
+        <v>4.441902980172033e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.239945345694898e-05</v>
+        <v>4.239945345694891e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.40939538222305e-05</v>
+        <v>4.409395382223014e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.359664008930103e-05</v>
+        <v>4.359664008930061e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1949109014674e-05</v>
+        <v>5.194910901467373e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.099005202940175e-05</v>
+        <v>4.099005202940188e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.488280366493053e-05</v>
+        <v>4.488280366493071e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.139652223361499e-05</v>
+        <v>4.139652223361506e-05</v>
       </c>
       <c r="O5" t="n">
         <v>4.29683794935634e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.971307791683176e-05</v>
+        <v>3.971307791683203e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.250962642470944e-05</v>
+        <v>4.250962642470954e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.22675199228893e-05</v>
+        <v>4.226751992288931e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.280591650013485e-05</v>
+        <v>4.280591650013483e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.291972187575529e-05</v>
+        <v>4.291972187575584e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.276864783496925e-05</v>
+        <v>4.276864783496463e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.632890836899291e-05</v>
+        <v>4.632890836899241e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.482659246380436e-05</v>
+        <v>4.482659246380524e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.279019166088566e-05</v>
+        <v>4.279019166088573e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.211870481442559e-05</v>
+        <v>4.211870481442565e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.484876127158351e-05</v>
+        <v>4.484876127158359e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.250609782940127e-05</v>
+        <v>4.250609782940011e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.609808538495135e-05</v>
+        <v>4.609808538495134e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.594640893017642e-05</v>
+        <v>1.594640893017634e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.29100953680972e-05</v>
+        <v>1.291009536809721e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.605358246340119e-05</v>
+        <v>1.60535824634011e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.590256456664019e-05</v>
@@ -3533,70 +3533,70 @@
         <v>1.288929099499337e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.310028820110069e-05</v>
+        <v>1.310028820110062e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.294126098507467e-05</v>
+        <v>1.294126098507466e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.30730910322444e-05</v>
+        <v>1.307309103224435e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.596118152208577e-05</v>
+        <v>1.596118152208563e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.604702688436129e-05</v>
+        <v>1.604702688436131e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.591076187052288e-05</v>
+        <v>1.591076187052299e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.305646936524021e-05</v>
+        <v>1.305646936524028e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.298164414071475e-05</v>
+        <v>1.298164414071477e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.584583466049598e-05</v>
+        <v>1.584583466049594e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.584939427173138e-05</v>
+        <v>1.584939427173149e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.589472375888609e-05</v>
+        <v>1.589472375888608e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.297756723021318e-05</v>
+        <v>1.29775672302132e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.595282346716612e-05</v>
+        <v>1.595282346716613e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.302325152825919e-05</v>
+        <v>1.302325152825923e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.299722228041911e-05</v>
+        <v>1.299722228041896e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.587480708807022e-05</v>
+        <v>1.587480708807024e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.613873785551037e-05</v>
+        <v>1.613873785551038e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.299493905438941e-05</v>
+        <v>1.29949390543894e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.302788047382669e-05</v>
+        <v>1.302788047382668e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.597558188891939e-05</v>
+        <v>1.597558188891935e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.597624808889609e-05</v>
+        <v>1.597624808889606e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.30998255030155e-05</v>
+        <v>1.309982550301556e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3609,31 +3609,31 @@
         <v>1.973239257841824e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.962788122875078e-05</v>
+        <v>1.962788122875079e-05</v>
       </c>
       <c r="D7" t="n">
         <v>1.983956611164301e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.968854821488199e-05</v>
+        <v>1.968854821488201e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.960707685564695e-05</v>
+        <v>1.960707685564697e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98180740617543e-05</v>
+        <v>1.981807406175445e-05</v>
       </c>
       <c r="H7" t="n">
         <v>1.965904684572827e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.979087689289794e-05</v>
+        <v>1.979087689289795e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.974716517032759e-05</v>
+        <v>1.974716517032784e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.983301053260313e-05</v>
+        <v>1.983301053260309e-05</v>
       </c>
       <c r="L7" t="n">
         <v>1.969674551876471e-05</v>
@@ -3642,49 +3642,49 @@
         <v>1.977425522589383e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.969754487271221e-05</v>
+        <v>1.969754487271223e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.962194863131456e-05</v>
+        <v>1.962194863131457e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.962542199201455e-05</v>
+        <v>1.962542199201452e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96807074071279e-05</v>
+        <v>1.968070740712792e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.969535309086674e-05</v>
+        <v>1.969535309086678e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.973880711540797e-05</v>
+        <v>1.973880711540795e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.974103738891281e-05</v>
+        <v>1.97410373889128e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.971539325666971e-05</v>
+        <v>1.971539325666939e-05</v>
       </c>
       <c r="V7" t="n">
         <v>1.966079073631207e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.991498877519673e-05</v>
+        <v>1.991498877519679e-05</v>
       </c>
       <c r="X7" t="n">
         <v>1.971272491504296e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.967813714419824e-05</v>
+        <v>1.967813714419823e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.97615655371612e-05</v>
+        <v>1.976156553716126e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.97622317371379e-05</v>
+        <v>1.976223173713788e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.98154379227803e-05</v>
+        <v>1.981543792278034e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3697,73 +3697,73 @@
         <v>5.121309969772806e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.634831390149111e-05</v>
+        <v>7.634831390149117e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.655999878438332e-05</v>
+        <v>7.65599987843834e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.296957155484692e-05</v>
+        <v>6.296957155484695e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.501983823381927e-05</v>
+        <v>5.501983823381936e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.177212824984255e-05</v>
+        <v>8.177212824984233e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.63794795184686e-05</v>
+        <v>7.637947951846859e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.65113095656383e-05</v>
+        <v>7.651130956563838e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.646759784306791e-05</v>
+        <v>7.646759784306796e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.655344320534346e-05</v>
+        <v>7.65534432053435e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.641717819150509e-05</v>
+        <v>7.641717819150514e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.649468789863344e-05</v>
+        <v>7.649468789863357e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.685296772861289e-05</v>
+        <v>5.68529677286129e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.215403670892219e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.083956701605983e-05</v>
+        <v>6.083956701605998e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.620123238538315e-05</v>
+        <v>4.620123238538318e-05</v>
       </c>
       <c r="R8" t="n">
         <v>7.641578576360709e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.645923978814828e-05</v>
+        <v>7.645923978814836e-05</v>
       </c>
       <c r="T8" t="n">
         <v>7.646147006165315e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.411658984630019e-05</v>
+        <v>6.411658984630028e-05</v>
       </c>
       <c r="V8" t="n">
         <v>6.948318122787064e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.664038178174231e-05</v>
+        <v>7.664038178174225e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.854652089513924e-05</v>
+        <v>4.854652089513929e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001014944056357764</v>
+        <v>0.0001014944056357765</v>
       </c>
       <c r="Z8" t="n">
         <v>5.07734317958529e-05</v>
@@ -3772,7 +3772,7 @@
         <v>7.648266440987827e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.000102900874451788</v>
+        <v>0.0001029008744517882</v>
       </c>
     </row>
     <row r="9">
@@ -3782,64 +3782,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.405382736816171e-05</v>
+        <v>3.405382736816185e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.018951224644395e-05</v>
+        <v>4.018951224644392e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.04011971293362e-05</v>
+        <v>4.040119712933626e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.880996757236759e-05</v>
+        <v>3.880996757236769e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.578335215828491e-05</v>
+        <v>2.578335215828497e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.037970530813405e-05</v>
+        <v>4.037970530813377e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.022067786342145e-05</v>
+        <v>4.022067786342132e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.03525079105911e-05</v>
+        <v>4.035250791059112e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.030879618802074e-05</v>
+        <v>4.030879618802083e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.039464155029625e-05</v>
+        <v>4.039464155029624e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.025837653645786e-05</v>
+        <v>4.025837653645793e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.033588624358697e-05</v>
+        <v>4.033588624358702e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.025917589040545e-05</v>
+        <v>4.025917589040529e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.225160345411406e-05</v>
+        <v>4.225160345411421e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.270482979736963e-05</v>
+        <v>4.270482979736969e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.024233865350767e-05</v>
+        <v>4.024233865350774e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.025698410855988e-05</v>
+        <v>4.025698410855999e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.030043813310113e-05</v>
+        <v>4.030043813310115e-05</v>
       </c>
       <c r="T9" t="n">
         <v>4.030266840660599e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.027663915876609e-05</v>
+        <v>4.027663915876569e-05</v>
       </c>
       <c r="V9" t="n">
         <v>4.742347449394627e-05</v>
@@ -3848,19 +3848,19 @@
         <v>4.047661979288997e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.027435593273615e-05</v>
+        <v>4.02743559327361e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.02397681618914e-05</v>
+        <v>4.023976816189139e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.656091322010846e-05</v>
+        <v>3.65609132201085e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.032386275483106e-05</v>
+        <v>4.032386275483109e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.037706894047344e-05</v>
+        <v>4.037706894047348e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.346646534323773e-05</v>
+        <v>1.346646534323771e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.354427162869864e-05</v>
+        <v>1.354427162869858e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.348703839268198e-05</v>
+        <v>1.348703839268188e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.346346766670701e-05</v>
+        <v>1.346346766670694e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.34561066776481e-05</v>
+        <v>1.345610667764803e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.347703022435333e-05</v>
+        <v>1.347703022435325e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.346418562379773e-05</v>
+        <v>1.346418562379763e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.347616680352304e-05</v>
+        <v>1.347616680352297e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.347070470683228e-05</v>
+        <v>1.347070470683221e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.347229082348236e-05</v>
+        <v>1.347229082348229e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.346159624192129e-05</v>
+        <v>1.34615962419212e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.34691323636116e-05</v>
+        <v>1.346913236361156e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.346170647934247e-05</v>
+        <v>1.34617064793424e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.502315025457431e-05</v>
+        <v>1.502315025457422e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.345855546216599e-05</v>
+        <v>1.345855546216591e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.345996766172564e-05</v>
+        <v>1.345996766172557e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.346338316605256e-05</v>
+        <v>1.346338316605252e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.346511262395809e-05</v>
+        <v>1.346511262395802e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.347095383797873e-05</v>
+        <v>1.347095383797866e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.400463400857539e-05</v>
+        <v>1.400463400857534e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.346785820759752e-05</v>
+        <v>1.346785820759745e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.409756556424013e-05</v>
+        <v>1.409756556424004e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.346372978005453e-05</v>
+        <v>1.346372978005446e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.346494271087122e-05</v>
+        <v>1.346494271087115e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.383063190864565e-05</v>
+        <v>1.38306319086456e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.347610487970082e-05</v>
+        <v>1.347610487970074e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.347347130865084e-05</v>
+        <v>1.34734713086508e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.355672184666943e-05</v>
+        <v>1.357410319550366e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.362823930582175e-05</v>
+        <v>1.364323533398557e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.370883947186606e-05</v>
+        <v>1.373159404298709e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.349824953299808e-05</v>
+        <v>1.35086929434078e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.348642420356477e-05</v>
+        <v>1.350135884223622e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.363550017387518e-05</v>
+        <v>1.365552997287369e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.35408437770481e-05</v>
+        <v>1.35578578253636e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.362798403664759e-05</v>
+        <v>1.36480006400208e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.35897119124183e-05</v>
+        <v>1.360813467461192e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.361109534019461e-05</v>
+        <v>1.363008932320407e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.352393648567793e-05</v>
+        <v>1.354015281456081e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.360154654040876e-05</v>
+        <v>1.362056542444265e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.351994580809019e-05</v>
+        <v>1.35362321235087e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.609894962954044e-05</v>
+        <v>1.611496491070472e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.350087316717109e-05</v>
+        <v>1.351626196608398e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.351236743514313e-05</v>
+        <v>1.352822713096798e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.353393796103207e-05</v>
+        <v>1.355072079805227e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35469557098239e-05</v>
+        <v>1.35640272706633e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.35875531411646e-05</v>
+        <v>1.360623016290829e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.444351349188371e-05</v>
+        <v>1.446069349958608e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.357410651767103e-05</v>
+        <v>1.359187423559668e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47318247301337e-05</v>
+        <v>1.475557262440009e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.353956914656747e-05</v>
+        <v>1.355639585899635e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.354257926145468e-05</v>
+        <v>1.35596677098934e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.418380037824921e-05</v>
+        <v>1.420209731998434e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.36221147464699e-05</v>
+        <v>1.364201162515566e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.363375922854437e-05</v>
+        <v>1.365403760526242e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.182266975413062e-05</v>
+        <v>1.18226697541306e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.171030120890342e-05</v>
+        <v>1.17103012089034e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.205505181167285e-05</v>
+        <v>1.205505181167278e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.178880961871613e-05</v>
+        <v>1.178880961871611e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.170566386107346e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1942004946416e-05</v>
+        <v>1.194200494641598e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.179691927433215e-05</v>
+        <v>1.179691927433213e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.193225221094478e-05</v>
+        <v>1.193225221094476e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.185907337343509e-05</v>
+        <v>1.185907337343508e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.188847123334637e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.17676710148634e-05</v>
+        <v>1.176767101486338e-05</v>
       </c>
       <c r="M4" t="n">
         <v>1.188700228704154e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.176891619724744e-05</v>
+        <v>1.17689161972474e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17613622883563e-05</v>
+        <v>1.176136228835624e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.173332400869962e-05</v>
+        <v>1.17333240086996e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.174927545236978e-05</v>
+        <v>1.174927545236976e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17878551449522e-05</v>
+        <v>1.178785514495217e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.180739016758495e-05</v>
+        <v>1.180739016758492e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.187336936703916e-05</v>
+        <v>1.187336936703917e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.174713640939997e-05</v>
+        <v>1.174713640939995e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.179034737241867e-05</v>
+        <v>1.179034737241861e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.210460560569517e-05</v>
+        <v>1.210460560569514e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.179177030955444e-05</v>
+        <v>1.179177030955442e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.174125858319931e-05</v>
+        <v>1.174125858319921e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.186350512333201e-05</v>
+        <v>1.1863505123332e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.193155275288636e-05</v>
+        <v>1.193155275288634e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.194484285747498e-05</v>
+        <v>1.194484285747495e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.358625612140882e-05</v>
+        <v>4.35862561214088e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.570608664502568e-05</v>
+        <v>4.57060866450257e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.043603836092047e-05</v>
+        <v>5.043603836092016e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.377278034379563e-05</v>
+        <v>2.377278034379564e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.339935286563155e-05</v>
+        <v>4.339935286563186e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.744654887722754e-05</v>
+        <v>4.744654887722735e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.333416862409284e-05</v>
+        <v>4.333416862409279e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.65724521405368e-05</v>
+        <v>4.657245214053673e-05</v>
       </c>
       <c r="J5" t="n">
         <v>4.583828503393509e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.138165582454317e-05</v>
+        <v>5.138165582454331e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.363216506267354e-05</v>
+        <v>4.363216506267352e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.845764248816536e-05</v>
+        <v>4.845764248816549e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.117839694573042e-05</v>
+        <v>4.117839694572997e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.375202973435624e-05</v>
+        <v>4.375202973435637e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.231931467288162e-05</v>
+        <v>4.231931467288256e-05</v>
       </c>
       <c r="Q5" t="n">
         <v>4.333490085396965e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.256305675169698e-05</v>
+        <v>4.256305675169699e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.325811955108351e-05</v>
+        <v>4.325811955108324e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.385937427031947e-05</v>
+        <v>4.385937427031974e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.544340397386245e-05</v>
+        <v>4.544340397386261e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.767398941133773e-05</v>
+        <v>4.767398941133729e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.671551753422205e-05</v>
+        <v>4.671551753422183e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.426853726901618e-05</v>
+        <v>4.426853726901627e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.158463071843046e-05</v>
+        <v>4.158463071843162e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.748035513070722e-05</v>
+        <v>4.748035513070717e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.374750122028837e-05</v>
+        <v>4.374750122028835e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.763981162399721e-05</v>
+        <v>4.763981162399736e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4378,70 +4378,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.305840861406749e-05</v>
+        <v>1.305840861406746e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.29460400688403e-05</v>
+        <v>1.294604006884029e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.623479430166701e-05</v>
+        <v>1.623479430166695e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.596855210871028e-05</v>
+        <v>1.596855210871027e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.294140272101036e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.317774380635289e-05</v>
+        <v>1.317774380635287e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.597666176432629e-05</v>
+        <v>1.597666176432626e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.316799107088166e-05</v>
+        <v>1.316799107088164e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.603881586342924e-05</v>
+        <v>1.603881586342923e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.606821372334053e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.300340987480028e-05</v>
+        <v>1.300340987480025e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.312274114697842e-05</v>
+        <v>1.312274114697841e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.300654755768631e-05</v>
+        <v>1.30065475576863e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.299880134210094e-05</v>
+        <v>1.299880134210088e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59228838909965e-05</v>
+        <v>1.592288389099647e-05</v>
       </c>
       <c r="Q6" t="n">
         <v>1.592901794236393e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.596759763494633e-05</v>
+        <v>1.596759763494632e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.304312902752182e-05</v>
+        <v>1.304312902752178e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.605311185703332e-05</v>
+        <v>1.605311185703328e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.599109123729977e-05</v>
+        <v>1.599109123729975e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.302608623235553e-05</v>
+        <v>1.302608623235549e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.342112514960754e-05</v>
+        <v>1.342112514960749e-05</v>
       </c>
       <c r="X6" t="n">
         <v>1.30275091694913e-05</v>
@@ -4450,13 +4450,13 @@
         <v>1.310924713052333e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.309924398326889e-05</v>
+        <v>1.309924398326885e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.611129524288049e-05</v>
+        <v>1.61112952428805e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.318285695198688e-05</v>
+        <v>1.318285695198684e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.977818459583236e-05</v>
+        <v>1.977818459583233e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.966581605060518e-05</v>
+        <v>1.966581605060513e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.001056665337461e-05</v>
+        <v>2.001056665337453e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.974432446041789e-05</v>
+        <v>1.974432446041786e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.966117870277522e-05</v>
+        <v>1.96611787027752e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.989751978811778e-05</v>
+        <v>1.989751978811773e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.975243411603389e-05</v>
+        <v>1.975243411603386e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.988776705264654e-05</v>
+        <v>1.988776705264649e-05</v>
       </c>
       <c r="J7" t="n">
         <v>1.981458821513683e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.984398607504813e-05</v>
+        <v>1.984398607504812e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.972318585656513e-05</v>
+        <v>1.972318585656512e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.98425171287433e-05</v>
+        <v>1.984251712874327e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.972443103894919e-05</v>
+        <v>1.972443103894912e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.971684556719823e-05</v>
+        <v>1.971684556719815e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.968880728754156e-05</v>
+        <v>1.968880728754155e-05</v>
       </c>
       <c r="Q7" t="n">
         <v>1.970479029407152e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.974336998665392e-05</v>
+        <v>1.97433699866539e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.976290500928667e-05</v>
+        <v>1.976290500928665e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.982888420874093e-05</v>
+        <v>1.982888420874086e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.976804613701481e-05</v>
+        <v>1.976804613701478e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.974586221412041e-05</v>
+        <v>1.974586221412035e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.006012044739692e-05</v>
+        <v>2.006012044739685e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.974728515125617e-05</v>
+        <v>1.974728515125619e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.976098576280653e-05</v>
+        <v>1.976098576280661e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.981901996503375e-05</v>
+        <v>1.981901996503372e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98870675945881e-05</v>
+        <v>1.988706759458809e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.990035769917674e-05</v>
+        <v>1.990035769917672e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4554,16 +4554,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.126956091201825e-05</v>
+        <v>5.126956091201824e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.641117276392194e-05</v>
+        <v>7.641117276392197e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.675592336669142e-05</v>
+        <v>7.675592336669134e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.304268155718396e-05</v>
+        <v>6.304268155718392e-05</v>
       </c>
       <c r="F8" t="n">
         <v>5.508683001586606e-05</v>
@@ -4572,64 +4572,64 @@
         <v>8.187945385148417e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.64977908293506e-05</v>
+        <v>7.649779082935072e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.663312376596332e-05</v>
+        <v>7.663312376596335e-05</v>
       </c>
       <c r="J8" t="n">
         <v>7.655994492845362e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.658934278836488e-05</v>
+        <v>7.658934278836491e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.646854256988195e-05</v>
+        <v>7.646854256988194e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.658787384205962e-05</v>
+        <v>7.658787384205967e-05</v>
       </c>
       <c r="N8" t="n">
         <v>5.689372804676485e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.226584532338299e-05</v>
+        <v>6.226584532338302e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.091911964482341e-05</v>
+        <v>6.091911964482342e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.623318306706794e-05</v>
+        <v>4.62331830670679e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.648872669997066e-05</v>
+        <v>7.648872669997071e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.650826172260345e-05</v>
+        <v>7.650826172260348e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.657424092205766e-05</v>
+        <v>7.657424092205778e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.418703044038935e-05</v>
+        <v>6.418703044038939e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.958996309552828e-05</v>
+        <v>6.95899630955283e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.681044029597457e-05</v>
+        <v>7.68104402959746e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.859025541082694e-05</v>
+        <v>4.859025541082705e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001016174099850618</v>
+        <v>0.0001016174099850619</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.084129062956012e-05</v>
+        <v>5.084129062956013e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.663242430790489e-05</v>
+        <v>7.663242430790493e-05</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001030256086449556</v>
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.304191872510952e-05</v>
+        <v>3.304191872510951e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.888048775286306e-05</v>
+        <v>3.888048775286305e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.922523835563255e-05</v>
+        <v>3.922523835563239e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.758554423442664e-05</v>
+        <v>3.758554423442653e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.515731481166701e-05</v>
+        <v>2.515731481166702e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.91121917375958e-05</v>
+        <v>3.91121917375957e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.896710581829183e-05</v>
+        <v>3.896710581829174e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.910243875490442e-05</v>
+        <v>3.910243875490437e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.902925991739478e-05</v>
+        <v>3.902925991739472e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.905865777730601e-05</v>
+        <v>3.905865777730597e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.893785755882303e-05</v>
+        <v>3.893785755882299e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.905718883100119e-05</v>
+        <v>3.905718883100115e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.893910274120707e-05</v>
+        <v>3.893910274120702e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.09036820810607e-05</v>
+        <v>4.090368208106066e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.130454889313268e-05</v>
+        <v>4.130454889313259e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.891946224354961e-05</v>
+        <v>3.891946224354946e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.895804168891181e-05</v>
+        <v>3.89580416889118e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.897757671154463e-05</v>
+        <v>3.897757671154452e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.904355591099885e-05</v>
+        <v>3.904355591099874e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.89815352912653e-05</v>
+        <v>3.898153529126522e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.582778832418763e-05</v>
+        <v>4.58277883241875e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.927479214965488e-05</v>
+        <v>3.927479214965479e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.896195685351404e-05</v>
+        <v>3.896195685351405e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.897565746506465e-05</v>
+        <v>3.897565746506447e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.544580558696832e-05</v>
+        <v>3.544580558696823e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.910173929684596e-05</v>
+        <v>3.910173929684594e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.911502940143466e-05</v>
+        <v>3.91150294014346e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.34536987171587e-05</v>
+        <v>1.345369871715867e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.351849681435856e-05</v>
+        <v>1.351849681435854e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347250452342797e-05</v>
+        <v>1.347250452342796e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.343502122143537e-05</v>
+        <v>1.343502122143536e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343592770667736e-05</v>
+        <v>1.343592770667734e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.346024080263274e-05</v>
+        <v>1.346024080263271e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.345343462831851e-05</v>
+        <v>1.345343462831849e-05</v>
       </c>
       <c r="I2" t="n">
         <v>1.343808270658372e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.345018792875419e-05</v>
+        <v>1.345018792875418e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.344724803683534e-05</v>
+        <v>1.344724803683532e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.345041867541864e-05</v>
+        <v>1.345041867541863e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344290425386707e-05</v>
+        <v>1.344290425386705e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.344324982859843e-05</v>
+        <v>1.344324982859845e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.495975204377937e-05</v>
+        <v>1.495975204377936e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343841496155345e-05</v>
+        <v>1.343841496155344e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.344656245419342e-05</v>
+        <v>1.34465624541934e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.344867948096995e-05</v>
+        <v>1.344867948096994e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344603506167148e-05</v>
+        <v>1.344603506167147e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344441662817757e-05</v>
+        <v>1.344441662817756e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.395498874058909e-05</v>
+        <v>1.395498874058907e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344508282105596e-05</v>
+        <v>1.344508282105594e-05</v>
       </c>
       <c r="W2" t="n">
         <v>1.403299162101448e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344493328019817e-05</v>
+        <v>1.344493328019813e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.344575674028578e-05</v>
+        <v>1.344575674028577e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.379697950221665e-05</v>
+        <v>1.379697950221664e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.344441058990458e-05</v>
+        <v>1.344441058990457e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.344725206838595e-05</v>
+        <v>1.344725206838594e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.358099864774307e-05</v>
+        <v>1.359963913616826e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.355960124932224e-05</v>
+        <v>1.357275353797327e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.371651487994393e-05</v>
+        <v>1.374010341443563e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.340406192226052e-05</v>
+        <v>1.341182952250272e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.345818196014144e-05</v>
+        <v>1.347251533384445e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.363776374444977e-05</v>
+        <v>1.365804715521993e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.358226132212398e-05</v>
+        <v>1.36010838258714e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.347029820635837e-05</v>
+        <v>1.348515927622411e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.356135379950281e-05</v>
+        <v>1.357902431560249e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.354737214735992e-05</v>
+        <v>1.356453371862755e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.357019364394801e-05</v>
+        <v>1.358807845333801e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.353896284728466e-05</v>
+        <v>1.355585285438332e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.350672989733251e-05</v>
+        <v>1.352285366462386e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59850262632102e-05</v>
+        <v>1.599972202629405e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.346871171916478e-05</v>
+        <v>1.348351665300873e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.353274481295613e-05</v>
+        <v>1.35497215899158e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.354490339994602e-05</v>
+        <v>1.356248119098896e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.353650222140012e-05</v>
+        <v>1.355325480187237e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.352188036407819e-05</v>
+        <v>1.353834198897566e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43583655206433e-05</v>
+        <v>1.437467605982788e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352556727020363e-05</v>
+        <v>1.354209015865643e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.456741697141588e-05</v>
+        <v>1.458766509490157e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.351899584340583e-05</v>
+        <v>1.353557407224591e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35249769739857e-05</v>
+        <v>1.354171862057637e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.412217282765588e-05</v>
+        <v>1.413954326486263e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.35130248087499e-05</v>
+        <v>1.35294199734775e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.356493044229018e-05</v>
+        <v>1.358309549898241e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5062,25 +5062,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.185443157680595e-05</v>
+        <v>1.185443157680594e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.160291186853164e-05</v>
+        <v>1.160291186853165e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.206685180971575e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.164346067053854e-05</v>
+        <v>1.164346067053855e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.165369983835058e-05</v>
+        <v>1.165369983835057e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.192832744174331e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.185144857186916e-05</v>
+        <v>1.185144857186917e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.167804155364191e-05</v>
@@ -5089,58 +5089,58 @@
         <v>1.180325230819489e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1781568175094e-05</v>
+        <v>1.178156817509399e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.181738199645828e-05</v>
+        <v>1.181738199645826e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.17673293219705e-05</v>
+        <v>1.176732932197046e-05</v>
       </c>
       <c r="N4" t="n">
         <v>1.173640657379178e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.167657549049556e-05</v>
+        <v>1.167657549049553e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.168179452636986e-05</v>
+        <v>1.168179452636984e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.177382420377006e-05</v>
+        <v>1.177382420377002e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.179773699509141e-05</v>
+        <v>1.179773699509142e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.176786706262223e-05</v>
+        <v>1.176786706262221e-05</v>
       </c>
       <c r="T4" t="n">
         <v>1.17495861117923e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.167797865239112e-05</v>
+        <v>1.167797865239113e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.170875985880199e-05</v>
+        <v>1.170875985880203e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.192253936939657e-05</v>
+        <v>1.192253936939654e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.175542193403661e-05</v>
+        <v>1.175542193403658e-05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.169560735526014e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.17965600595523e-05</v>
+        <v>1.179656005955231e-05</v>
       </c>
       <c r="AA4" t="n">
         <v>1.17495179067212e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.18255634935874e-05</v>
+        <v>1.182556349358737e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.695538435177079e-05</v>
+        <v>4.695538435177095e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.442541761241058e-05</v>
+        <v>4.442541761241062e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.169383346767035e-05</v>
+        <v>5.16938334676703e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.869893705834226e-05</v>
+        <v>1.869893705834221e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.539341970612978e-05</v>
+        <v>4.539341970612975e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.395522611752534e-05</v>
+        <v>5.395522611752537e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.864946540707762e-05</v>
+        <v>4.864946540707715e-05</v>
       </c>
       <c r="I5" t="n">
         <v>4.403833644653548e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.920384765189012e-05</v>
+        <v>4.920384765189001e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.248083353420992e-05</v>
+        <v>5.248083353420994e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.326505212749366e-05</v>
+        <v>5.32650521274937e-05</v>
       </c>
       <c r="M5" t="n">
         <v>5.425309542861056e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.489367678312357e-05</v>
+        <v>4.489367678312363e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.603853183287432e-05</v>
+        <v>4.603853183287427e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.190815375647915e-05</v>
+        <v>4.190815375647919e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.692066011730673e-05</v>
+        <v>4.692066011730672e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.573174094624433e-05</v>
+        <v>4.573174094624524e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>5.099108616487394e-05</v>
+        <v>5.099108616487395e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.893747878710668e-05</v>
+        <v>4.893747878710675e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.6066478004875e-05</v>
+        <v>4.606647800487495e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.843757956271169e-05</v>
+        <v>4.843757956271126e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.663499233388156e-05</v>
+        <v>4.663499233388226e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.539284947838136e-05</v>
+        <v>4.53928494783814e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.562658907223986e-05</v>
+        <v>4.562658907223987e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.732685272815245e-05</v>
+        <v>4.732685272815249e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.403511976993195e-05</v>
+        <v>4.403511976993198e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.97815291931481e-05</v>
+        <v>4.978152919314813e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5238,28 +5238,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.317786650636367e-05</v>
+        <v>1.317786650636365e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.292634679808937e-05</v>
+        <v>1.292634679808935e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.65223724573515e-05</v>
+        <v>1.652237245735149e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.609898131817425e-05</v>
+        <v>1.609898131817426e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.297713476790829e-05</v>
+        <v>1.297713476790828e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3251762371301e-05</v>
+        <v>1.325176237130103e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.630696921950487e-05</v>
+        <v>1.63069692195049e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.613356220127761e-05</v>
+        <v>1.613356220127765e-05</v>
       </c>
       <c r="J6" t="n">
         <v>1.31266872377526e-05</v>
@@ -5268,28 +5268,28 @@
         <v>1.623708882272972e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3140816926016e-05</v>
+        <v>1.314081692601599e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.622284996960616e-05</v>
+        <v>1.622284996960622e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.306272681214521e-05</v>
+        <v>1.306272681214519e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.614346239447391e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.614879145720301e-05</v>
+        <v>1.614879145720302e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.622934485140572e-05</v>
+        <v>1.622934485140577e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.625325764272714e-05</v>
+        <v>1.625325764272716e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.309130199217992e-05</v>
+        <v>1.309130199217995e-05</v>
       </c>
       <c r="T6" t="n">
         <v>1.307302104135001e-05</v>
@@ -5298,25 +5298,25 @@
         <v>1.307052952122528e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.616428050643766e-05</v>
+        <v>1.616428050643775e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.638920789474357e-05</v>
+        <v>1.638920789474361e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.307885686359432e-05</v>
+        <v>1.30788568635943e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.316116605889381e-05</v>
+        <v>1.31611660588938e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.311999498911002e-05</v>
+        <v>1.311999498911e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.620503855435687e-05</v>
+        <v>1.620503855435692e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.31516080000888e-05</v>
+        <v>1.315160800008878e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.037940112599153e-05</v>
+        <v>2.03794011259915e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.012788141771722e-05</v>
+        <v>2.01278814177172e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.059182135890135e-05</v>
+        <v>2.059182135890131e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.016843021972412e-05</v>
+        <v>2.016843021972411e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.017866938753617e-05</v>
+        <v>2.017866938753614e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.045329699092886e-05</v>
+        <v>2.045329699092885e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.037641812105475e-05</v>
+        <v>2.037641812105473e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.020301110282749e-05</v>
+        <v>2.020301110282748e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.032822185738046e-05</v>
+        <v>2.032822185738044e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.030653772427956e-05</v>
+        <v>2.030653772427957e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.034235154564386e-05</v>
+        <v>2.034235154564383e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.029229887115607e-05</v>
+        <v>2.029229887115603e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.026137612297734e-05</v>
+        <v>2.026137612297733e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.020151352283034e-05</v>
+        <v>2.020151352283032e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.020673255870466e-05</v>
+        <v>2.020673255870463e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.029879375295558e-05</v>
+        <v>2.029879375295559e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.032270654427701e-05</v>
+        <v>2.032270654427702e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.029283661180783e-05</v>
+        <v>2.029283661180778e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.027455566097789e-05</v>
+        <v>2.027455566097788e-05</v>
       </c>
       <c r="U7" t="n">
         <v>2.027320116442099e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.02337294079876e-05</v>
+        <v>2.023372940798759e-05</v>
       </c>
       <c r="W7" t="n">
         <v>2.044750891858213e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.028039148322217e-05</v>
+        <v>2.028039148322215e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.028969284372214e-05</v>
+        <v>2.028969284372213e-05</v>
       </c>
       <c r="Z7" t="n">
         <v>2.032152960873787e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.027448745590676e-05</v>
+        <v>2.027448745590677e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.035053304277296e-05</v>
+        <v>2.035053304277295e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.414293887413317e-05</v>
+        <v>5.414293887413326e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.095823663478393e-05</v>
+        <v>8.0958236634784e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.142217657596797e-05</v>
+        <v>8.142217657596817e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.658650355479973e-05</v>
+        <v>6.658650355479986e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.815890096134926e-05</v>
+        <v>5.81589009613493e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.689613313443877e-05</v>
+        <v>8.689613313443893e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.120677333812137e-05</v>
+        <v>8.120677333812149e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.103336631989423e-05</v>
+        <v>8.103336631989421e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.115857707444713e-05</v>
+        <v>8.115857707444719e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.113689294134632e-05</v>
+        <v>8.113689294134633e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.117270676271052e-05</v>
+        <v>8.117270676271063e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.112265408822176e-05</v>
+        <v>8.112265408822183e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.011041962296985e-05</v>
+        <v>6.011041962297001e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.581643517974179e-05</v>
+        <v>6.581643517974181e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.440830588147466e-05</v>
+        <v>6.440830588147467e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.874308409724382e-05</v>
+        <v>4.87430840972439e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.115306176134371e-05</v>
+        <v>8.115306176134372e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.112319182887446e-05</v>
+        <v>8.112319182887454e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.110491087804451e-05</v>
+        <v>8.110491087804465e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.789237260114255e-05</v>
+        <v>6.789237260114268e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.36673141348655e-05</v>
+        <v>7.366731413486565e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.128318354569104e-05</v>
+        <v>8.128318354569121e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.120540943408614e-05</v>
+        <v>5.120540943408619e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001080335177920786</v>
+        <v>0.0001080335177920787</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.358228732588904e-05</v>
+        <v>5.358228732588911e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.110484267297343e-05</v>
+        <v>8.110484267297353e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001094544424010554</v>
+        <v>0.0001094544424010555</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.721126398642126e-05</v>
+        <v>3.721126398642129e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.405813193827457e-05</v>
+        <v>4.405813193827456e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.452207187945871e-05</v>
+        <v>4.452207187945868e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.246040203766005e-05</v>
+        <v>4.246040203766004e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.774519865194972e-05</v>
+        <v>2.774519865194971e-05</v>
       </c>
       <c r="G9" t="n">
         <v>4.43835477916985e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.430666864161208e-05</v>
+        <v>4.430666864161206e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.413326162338484e-05</v>
+        <v>4.41332616233848e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.425847237793781e-05</v>
+        <v>4.425847237793777e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.423678824483688e-05</v>
+        <v>4.423678824483692e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.427260206620121e-05</v>
+        <v>4.427260206620118e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.42225493917134e-05</v>
+        <v>4.422254939171338e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.419162664353463e-05</v>
+        <v>4.419162664353465e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.648419230933132e-05</v>
+        <v>4.648419230933131e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.700101721686202e-05</v>
+        <v>4.7001017216862e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.422904455372518e-05</v>
+        <v>4.422904455372519e-05</v>
       </c>
       <c r="R9" t="n">
         <v>4.425295706483434e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.422308713236512e-05</v>
+        <v>4.422308713236511e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.420480618153521e-05</v>
+        <v>4.420480618153518e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.420231466141052e-05</v>
+        <v>4.420231466141053e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.235536735472787e-05</v>
+        <v>5.235536735472797e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.437775943913944e-05</v>
+        <v>4.437775943913945e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.421064200377949e-05</v>
+        <v>4.421064200377948e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.421994336427951e-05</v>
+        <v>4.421994336427944e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.997208369476596e-05</v>
+        <v>3.99720836947659e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.420473797646408e-05</v>
+        <v>4.420473797646406e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.428078356333026e-05</v>
+        <v>4.428078356333025e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5746,40 +5746,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.35212199505113e-05</v>
+        <v>1.352121995051132e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.358725930835996e-05</v>
+        <v>1.358725930835998e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.354296653877448e-05</v>
+        <v>1.354296653877449e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.350869081668343e-05</v>
+        <v>1.350869081668345e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.350357741257587e-05</v>
+        <v>1.350357741257588e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.353411392557181e-05</v>
+        <v>1.353411392557182e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.352093872982523e-05</v>
+        <v>1.352093872982524e-05</v>
       </c>
       <c r="I2" t="n">
         <v>1.353017894316742e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.352315542735606e-05</v>
+        <v>1.352315542735605e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.354310253008317e-05</v>
+        <v>1.354310253008319e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.353764838385754e-05</v>
+        <v>1.353764838385756e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.353407008467976e-05</v>
+        <v>1.353407008467977e-05</v>
       </c>
       <c r="N2" t="n">
         <v>1.350850841927277e-05</v>
@@ -5794,34 +5794,34 @@
         <v>1.351643658182052e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.352220123850123e-05</v>
+        <v>1.352220123850122e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.351364748047672e-05</v>
+        <v>1.351364748047674e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.351383719726319e-05</v>
+        <v>1.351383719726322e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.405585626844407e-05</v>
+        <v>1.40558562684441e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.351523895697728e-05</v>
+        <v>1.351523895697731e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.414090821681645e-05</v>
+        <v>1.414090821681649e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.350350364852782e-05</v>
+        <v>1.350350364852784e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.352280787480032e-05</v>
+        <v>1.352280787480033e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.388952571821216e-05</v>
+        <v>1.388952571821217e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.352962214728451e-05</v>
+        <v>1.352962214728453e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.35236809721541e-05</v>
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.370234264974037e-05</v>
+        <v>1.372403392506248e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.367980571721002e-05</v>
+        <v>1.369559985354957e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386871875554433e-05</v>
+        <v>1.389614845431016e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.357199192397275e-05</v>
+        <v>1.35843737541506e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.358454051877205e-05</v>
+        <v>1.360201494193854e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.380884561825755e-05</v>
+        <v>1.383377039269019e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.37078029260491e-05</v>
+        <v>1.372973465256712e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.377364049812851e-05</v>
+        <v>1.379785350831621e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.372667827193978e-05</v>
+        <v>1.374882247001174e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.387485898238896e-05</v>
+        <v>1.390229565550853e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.384317082747553e-05</v>
+        <v>1.386908279081542e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.383706079210508e-05</v>
+        <v>1.386304904908051e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.361528747650626e-05</v>
+        <v>1.363392155432038e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.61410303472376e-05</v>
+        <v>1.61570579051927e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.355969963392583e-05</v>
+        <v>1.357635303272548e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.367846767267778e-05</v>
+        <v>1.369912758384291e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.371595132193709e-05</v>
+        <v>1.373816448829687e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.365860479704613e-05</v>
+        <v>1.367843966446045e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.366210447132188e-05</v>
+        <v>1.368214490170132e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45545798512793e-05</v>
+        <v>1.457413131739631e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36702153165781e-05</v>
+        <v>1.369045337807822e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.478048206593175e-05</v>
+        <v>1.480450778063782e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.358377524411817e-05</v>
+        <v>1.360117435295823e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.371467536087792e-05</v>
+        <v>1.373690029489963e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.430013939705122e-05</v>
+        <v>1.432115436008384e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.376274575430764e-05</v>
+        <v>1.378667833131161e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.375496891105973e-05</v>
+        <v>1.377848935259028e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5922,37 +5922,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.203879728097558e-05</v>
+        <v>1.203879728097559e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.176727083848373e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.228443499933299e-05</v>
+        <v>1.228443499933298e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.189727495070347e-05</v>
+        <v>1.189727495070348e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.183951669902637e-05</v>
+        <v>1.183951669902638e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.218444066080553e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.203562076395835e-05</v>
+        <v>1.203562076395834e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.213999322436666e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.204912005603023e-05</v>
+        <v>1.204912005603024e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.228597108372379e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.22243639930741e-05</v>
+        <v>1.222436399307412e-05</v>
       </c>
       <c r="M4" t="n">
         <v>1.22172620355181e-05</v>
@@ -5961,46 +5961,46 @@
         <v>1.189521468804311e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.178333486153332e-05</v>
+        <v>1.178333486153334e-05</v>
       </c>
       <c r="P4" t="n">
         <v>1.181198456275108e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.198476693115476e-05</v>
+        <v>1.198476693115477e-05</v>
       </c>
       <c r="R4" t="n">
         <v>1.204988138023647e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.195326274842664e-05</v>
+        <v>1.195326274842663e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.195540568680397e-05</v>
+        <v>1.195540568680398e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18756471954947e-05</v>
+        <v>1.187564719549471e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.192279632598906e-05</v>
+        <v>1.192279632598905e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.213848058268066e-05</v>
+        <v>1.213848058268067e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.183868350017066e-05</v>
+        <v>1.183868350017064e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19930411252143e-05</v>
+        <v>1.199304112521429e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.200757991595783e-05</v>
+        <v>1.200757991595784e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.213370395873049e-05</v>
+        <v>1.21337039587305e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21104490839985e-05</v>
+        <v>1.211044908399851e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.578224161689731e-05</v>
+        <v>4.578224161689729e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.640776041028914e-05</v>
+        <v>4.640776041028924e-05</v>
       </c>
       <c r="D5" t="n">
         <v>5.591512338005113e-05</v>
@@ -6022,73 +6022,73 @@
         <v>2.206841904954581e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.64622732679842e-05</v>
+        <v>4.646227326798444e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.586105533556678e-05</v>
+        <v>5.586105533556735e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.959583112807885e-05</v>
+        <v>4.959583112807893e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.138467470393014e-05</v>
+        <v>5.138467470393021e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.161014392506056e-05</v>
+        <v>5.161014392506077e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.862133182264848e-05</v>
+        <v>5.862133182264846e-05</v>
       </c>
       <c r="L5" t="n">
         <v>6.128280481818874e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.184482715387985e-05</v>
+        <v>6.184482715387981e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.51434178881662e-05</v>
+        <v>4.514341788816628e-05</v>
       </c>
       <c r="O5" t="n">
         <v>4.466409031622833e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.211730936601608e-05</v>
+        <v>4.211730936601613e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.014576867337112e-05</v>
+        <v>5.014576867337111e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.940124476139383e-05</v>
+        <v>4.940124476139385e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.961089018006313e-05</v>
+        <v>4.961089018006319e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>5.076072352939727e-05</v>
+        <v>5.07607235293973e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.337958028375688e-05</v>
+        <v>5.337958028375687e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.001102079096687e-05</v>
+        <v>5.001102079096697e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>5.107590698724714e-05</v>
+        <v>5.107590698724718e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.63237759261691e-05</v>
+        <v>4.632377592616952e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.661750115285702e-05</v>
+        <v>4.661750115285704e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.782298261029234e-05</v>
+        <v>4.782298261029232e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.768687622496435e-05</v>
+        <v>4.76868762249644e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.287197255201616e-05</v>
+        <v>5.28719725520162e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6098,19 +6098,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.624687311349246e-05</v>
+        <v>1.624687311349245e-05</v>
       </c>
       <c r="C6" t="n">
         <v>1.301538421931004e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.35325483801593e-05</v>
+        <v>1.353254838015931e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.314538833152977e-05</v>
+        <v>1.314538833152979e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.604759253154321e-05</v>
+        <v>1.604759253154322e-05</v>
       </c>
       <c r="G6" t="n">
         <v>1.639251649332237e-05</v>
@@ -6119,61 +6119,61 @@
         <v>1.624369659647519e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.634806905688352e-05</v>
+        <v>1.634806905688354e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.625719588854709e-05</v>
+        <v>1.62571958885471e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.649404691624064e-05</v>
+        <v>1.649404691624066e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.347247737390042e-05</v>
+        <v>1.347247737390043e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.642533786803495e-05</v>
+        <v>1.642533786803498e-05</v>
       </c>
       <c r="N6" t="n">
         <v>1.314568063648163e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.600161795437108e-05</v>
+        <v>1.600161795437109e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.297304060909203e-05</v>
+        <v>1.297304060909204e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.619284276367161e-05</v>
+        <v>1.619284276367162e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.329799476106278e-05</v>
+        <v>1.329799476106279e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.616133858094349e-05</v>
+        <v>1.61613385809435e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.32035190676303e-05</v>
+        <v>1.320351906763029e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.318745306740801e-05</v>
+        <v>1.318745306740802e-05</v>
       </c>
       <c r="V6" t="n">
         <v>1.317090970681537e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.346769185221521e-05</v>
+        <v>1.34676918522152e-05</v>
       </c>
       <c r="X6" t="n">
         <v>1.604675933268751e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.337364766720494e-05</v>
+        <v>1.337364766720496e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>1.325569329678415e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.634177979124734e-05</v>
+        <v>1.634177979124735e-05</v>
       </c>
       <c r="AB6" t="n">
         <v>1.336101040764785e-05</v>
@@ -6189,82 +6189,82 @@
         <v>2.0004858949821e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.973333250732911e-05</v>
+        <v>1.973333250732912e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.025049666817836e-05</v>
+        <v>2.02504966681784e-05</v>
       </c>
       <c r="E7" t="n">
         <v>1.986333661954887e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.980557836787174e-05</v>
+        <v>1.98055783678718e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.01505023296509e-05</v>
+        <v>2.015050232965091e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.000168243280374e-05</v>
+        <v>2.000168243280375e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.010605489321204e-05</v>
+        <v>2.010605489321207e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.001518172487563e-05</v>
+        <v>2.001518172487568e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.025203275256917e-05</v>
+        <v>2.02520327525692e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.019042566191949e-05</v>
+        <v>2.019042566191951e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.018332370436349e-05</v>
+        <v>2.018332370436352e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.986127635688852e-05</v>
+        <v>1.986127635688855e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.974936477425401e-05</v>
+        <v>1.974936477425403e-05</v>
       </c>
       <c r="P7" t="n">
         <v>1.977801447547177e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.995082860000015e-05</v>
+        <v>1.995082860000017e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.001594304908184e-05</v>
+        <v>2.001594304908187e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.991932441727202e-05</v>
+        <v>1.991932441727205e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.992146735564936e-05</v>
+        <v>1.992146735564939e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.99068652806213e-05</v>
+        <v>1.990686528062132e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.988885799483445e-05</v>
+        <v>1.988885799483449e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.010454225152604e-05</v>
+        <v>2.010454225152606e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.980474516901605e-05</v>
+        <v>1.980474516901614e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.002279528514668e-05</v>
+        <v>2.002279528514671e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.997364158480324e-05</v>
+        <v>1.997364158480325e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.00997656275759e-05</v>
+        <v>2.009976562757591e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.007651075284389e-05</v>
+        <v>2.007651075284392e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6274,82 +6274,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.150109494472759e-05</v>
+        <v>5.150109494472758e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.649671405566552e-05</v>
+        <v>7.649671405566558e-05</v>
       </c>
       <c r="D8" t="n">
         <v>7.701387821651481e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.317270849396941e-05</v>
+        <v>6.317270849396938e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.523814033716629e-05</v>
+        <v>5.523814033716635e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.215319110895322e-05</v>
+        <v>8.215319110895326e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.676506398114017e-05</v>
+        <v>7.676506398114018e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.686943644154845e-05</v>
+        <v>7.686943644154852e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.677856327321196e-05</v>
+        <v>7.677856327321212e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.701541430090555e-05</v>
+        <v>7.70154143009056e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.695380721025595e-05</v>
+        <v>7.695380721025589e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.694670525269968e-05</v>
+        <v>7.69467052526997e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.703839300109647e-05</v>
+        <v>5.703839300109648e-05</v>
       </c>
       <c r="O8" t="n">
         <v>6.230898883725432e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.101826369445538e-05</v>
+        <v>6.10182636944554e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.648149379804776e-05</v>
+        <v>4.648149379804778e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.677932459741827e-05</v>
+        <v>7.677932459741828e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.668270596560842e-05</v>
+        <v>7.668270596560846e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.668484890398586e-05</v>
+        <v>7.668484890398582e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.433738551490287e-05</v>
+        <v>6.433738551490283e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.974762615495241e-05</v>
+        <v>6.974762615495239e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.687288952238966e-05</v>
+        <v>7.687288952238973e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.86511944663314e-05</v>
+        <v>4.865119446633144e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001019107074517904</v>
+        <v>0.0001019107074517905</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.100052737852356e-05</v>
+        <v>5.100052737852358e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.686314717591223e-05</v>
+        <v>7.686314717591233e-05</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001032335386401805</v>
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.440230656864642e-05</v>
+        <v>3.440230656864648e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.03996381258554e-05</v>
+        <v>4.039963812585535e-05</v>
       </c>
       <c r="D9" t="n">
         <v>4.091680228670463e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.908281557722196e-05</v>
+        <v>3.908281557722195e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.602045503205565e-05</v>
+        <v>2.602045503205566e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.081680820203948e-05</v>
+        <v>4.081680820203951e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.066798805132994e-05</v>
+        <v>4.066798805133001e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.077236051173831e-05</v>
+        <v>4.077236051173832e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.06814873434019e-05</v>
+        <v>4.068148734340191e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.091833837109544e-05</v>
+        <v>4.091833837109546e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.085673128044577e-05</v>
+        <v>4.085673128044581e-05</v>
       </c>
       <c r="M9" t="n">
         <v>4.084962932288977e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.052758197541478e-05</v>
+        <v>4.052758197541482e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.24931938196269e-05</v>
+        <v>4.249319381962696e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.297366226026264e-05</v>
+        <v>4.297366226026269e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.06171344723887e-05</v>
+        <v>4.061713447238876e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.068224866760811e-05</v>
+        <v>4.068224866760816e-05</v>
       </c>
       <c r="S9" t="n">
         <v>4.05856300357983e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.058777297417562e-05</v>
+        <v>4.058777297417568e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.057170697395332e-05</v>
+        <v>4.057170697395338e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.778929139244527e-05</v>
+        <v>4.77892913924453e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.077084787005229e-05</v>
+        <v>4.077084787005234e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.04710507875423e-05</v>
+        <v>4.047105078754221e-05</v>
       </c>
       <c r="Y9" t="n">
         <v>4.068910090367294e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.686038337891879e-05</v>
+        <v>3.686038337891882e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.076607124610213e-05</v>
+        <v>4.076607124610216e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.074281637137017e-05</v>
+        <v>4.074281637137019e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.358191623446899e-05</v>
+        <v>1.358191623446896e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.364615534097097e-05</v>
+        <v>1.364615534097096e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.359350600692677e-05</v>
+        <v>1.359350600692683e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.357255822292613e-05</v>
+        <v>1.35725582229261e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.355852964040293e-05</v>
+        <v>1.355852964040297e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.363420810496852e-05</v>
+        <v>1.363420810496848e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.358049621165296e-05</v>
+        <v>1.358049621165292e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.358896187974664e-05</v>
+        <v>1.358896187974666e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.359425353385227e-05</v>
+        <v>1.359425353385228e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.360416419635227e-05</v>
+        <v>1.360416419635224e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35877170686876e-05</v>
+        <v>1.358771706868757e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.360136814695856e-05</v>
+        <v>1.360136814695857e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35657856526933e-05</v>
+        <v>1.356578565269325e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.515994446452488e-05</v>
+        <v>1.515994446452486e-05</v>
       </c>
       <c r="P2" t="n">
         <v>1.355734898644996e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.357400876572287e-05</v>
+        <v>1.357400876572284e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.358142665294142e-05</v>
+        <v>1.358142665294146e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.356480281357134e-05</v>
+        <v>1.356480281357136e-05</v>
       </c>
       <c r="T2" t="n">
         <v>1.357377931202621e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.413575094027547e-05</v>
+        <v>1.413575094027544e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.357672640954988e-05</v>
+        <v>1.357672640954986e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.428587802262302e-05</v>
+        <v>1.428587802262297e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.355897771581821e-05</v>
+        <v>1.355897771581824e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.359765350673753e-05</v>
+        <v>1.359765350673749e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.395169812056492e-05</v>
+        <v>1.395169812056493e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.359561443794518e-05</v>
+        <v>1.359561443794517e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.358388768107922e-05</v>
+        <v>1.358388768107921e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.3816825253684e-05</v>
+        <v>1.3841109507075e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.376841596978118e-05</v>
+        <v>1.378588677467908e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.390742586420818e-05</v>
+        <v>1.393490811219771e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.371527714836899e-05</v>
+        <v>1.373106446921155e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.365550096884655e-05</v>
+        <v>1.367415370338837e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.419507040701752e-05</v>
+        <v>1.423244555135682e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.381502946289811e-05</v>
+        <v>1.383931888916124e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.387237025761199e-05</v>
+        <v>1.38987329620477e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.391064593816874e-05</v>
+        <v>1.393804502796077e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.398617313686463e-05</v>
+        <v>1.401633065629683e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38736737728566e-05</v>
+        <v>1.389952040100272e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.398756930012791e-05</v>
+        <v>1.401788572757708e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.370317745856315e-05</v>
+        <v>1.372356811655411e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.630041946235475e-05</v>
+        <v>1.63189535990621e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.364445574689723e-05</v>
+        <v>1.36625775097437e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.376595545644926e-05</v>
+        <v>1.37884493976382e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.381791245952455e-05</v>
+        <v>1.384239235339616e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.369932952071509e-05</v>
+        <v>1.371937216022223e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.376551891250635e-05</v>
+        <v>1.378800106491683e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.466358131098216e-05</v>
+        <v>1.468429451288716e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.378603665514673e-05</v>
+        <v>1.380906987803859e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.531832610893233e-05</v>
+        <v>1.53582027652195e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.366149339081185e-05</v>
+        <v>1.36801969889782e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.392800467620802e-05</v>
+        <v>1.39564182281452e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.438868049902275e-05</v>
+        <v>1.441096431565007e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.391396883335355e-05</v>
+        <v>1.394185206158132e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.386354041808529e-05</v>
+        <v>1.388959587486396e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6782,19 +6782,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.219917502505978e-05</v>
+        <v>1.219917502505977e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.188524582475869e-05</v>
+        <v>1.188524582475867e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.233008683653027e-05</v>
+        <v>1.233008683653028e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.209347197978525e-05</v>
+        <v>1.209347197978524e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.193501268671946e-05</v>
+        <v>1.193501268671944e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.278983575780075e-05</v>
@@ -6806,58 +6806,58 @@
         <v>1.227875882962837e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.232685612725644e-05</v>
+        <v>1.232685612725645e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.245047598909958e-05</v>
+        <v>1.245047598909957e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.226469811607474e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.245238674874548e-05</v>
+        <v>1.245238674874547e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.20169726834691e-05</v>
+        <v>1.201697268346909e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.193992703026586e-05</v>
+        <v>1.193992703026585e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.192167665719273e-05</v>
+        <v>1.192167665719272e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.210985652795707e-05</v>
+        <v>1.210985652795706e-05</v>
       </c>
       <c r="R4" t="n">
         <v>1.219364497648806e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.200587106345892e-05</v>
+        <v>1.200587106345891e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.210726474289982e-05</v>
+        <v>1.21072647428998e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.196888795932624e-05</v>
+        <v>1.196888795932625e-05</v>
       </c>
       <c r="V4" t="n">
         <v>1.209120442654697e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.289217279136561e-05</v>
+        <v>1.28921727913656e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.194007390466e-05</v>
+        <v>1.194007390465998e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.231101449162504e-05</v>
+        <v>1.231101449162502e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.210807994002773e-05</v>
+        <v>1.210807994002772e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.235390253480855e-05</v>
+        <v>1.235390253480862e-05</v>
       </c>
       <c r="AB4" t="n">
         <v>1.226649905928443e-05</v>
@@ -6873,82 +6873,82 @@
         <v>4.810539218254801e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.67553141209811e-05</v>
+        <v>4.675531412098111e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.450637715240986e-05</v>
+        <v>5.450637715240979e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.822262331212652e-05</v>
+        <v>2.822262331212651e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.63285680941534e-05</v>
+        <v>4.632856809415341e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>6.11617050308425e-05</v>
+        <v>6.116170503084273e-05</v>
       </c>
       <c r="H5" t="n">
         <v>5.214316835601581e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.223876392243324e-05</v>
+        <v>5.223876392243317e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.354796502430911e-05</v>
+        <v>5.354796502430919e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.802410801917189e-05</v>
+        <v>5.802410801917194e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.726964317716245e-05</v>
+        <v>5.72696431771624e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.969241397908524e-05</v>
+        <v>5.969241397908529e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.56482460140957e-05</v>
+        <v>4.564824601409571e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.595073635915338e-05</v>
+        <v>4.595073635915342e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.473555305184219e-05</v>
+        <v>4.473555305184233e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.941019010649173e-05</v>
+        <v>4.941019010649157e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>5.03817650111342e-05</v>
+        <v>5.038176501113427e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.709292340973161e-05</v>
+        <v>4.709292340973156e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.998677864458749e-05</v>
+        <v>4.998677864458756e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>5.163059128723773e-05</v>
+        <v>5.163059128723776e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.025887660711913e-05</v>
+        <v>5.025887660711907e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>6.185681548669891e-05</v>
+        <v>6.185681548669884e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.786625537573735e-05</v>
+        <v>4.786625537573878e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.065948455477219e-05</v>
+        <v>5.0659484554772e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.945263234914688e-05</v>
+        <v>4.945263234914695e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.052009197047775e-05</v>
+        <v>5.05200919704794e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.352754756524756e-05</v>
+        <v>5.352754756524762e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.645679066029204e-05</v>
+        <v>1.645679066029209e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.614286145999096e-05</v>
+        <v>1.614286145999098e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.658770247176255e-05</v>
+        <v>1.658770247176262e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.335607084316898e-05</v>
+        <v>1.335607084316902e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.619262832195173e-05</v>
+        <v>1.619262832195169e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.704745139303302e-05</v>
+        <v>1.704745139303304e-05</v>
       </c>
       <c r="H6" t="n">
         <v>1.64407508493423e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.653637446486064e-05</v>
+        <v>1.653637446486063e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.358945499064018e-05</v>
+        <v>1.35894549906402e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.371307485248334e-05</v>
+        <v>1.371307485248332e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.652231375130702e-05</v>
+        <v>1.652231375130704e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.671000238397775e-05</v>
+        <v>1.671000238397776e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.328162817154839e-05</v>
+        <v>1.328162817154838e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.320435749222119e-05</v>
+        <v>1.320435749222117e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.619089456406503e-05</v>
+        <v>1.619089456406511e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.636747216318932e-05</v>
+        <v>1.63674721631893e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.645126061172033e-05</v>
+        <v>1.645126061172035e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.626348669869118e-05</v>
+        <v>1.626348669869119e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.336986360628358e-05</v>
+        <v>1.336986360628361e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.629242385776929e-05</v>
+        <v>1.629242385776931e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.335380328993073e-05</v>
+        <v>1.335380328993075e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.716122406182341e-05</v>
+        <v>1.716122406182343e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.320267276804358e-05</v>
+        <v>1.320267276804371e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.370851325683093e-05</v>
+        <v>1.370851325683089e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.337067880341149e-05</v>
+        <v>1.337067880341151e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.661151817004081e-05</v>
+        <v>1.661151817004094e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.353126716101529e-05</v>
+        <v>1.353126716101527e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7046,28 +7046,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.018478565814634e-05</v>
+        <v>2.018478565814631e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.987085645784524e-05</v>
+        <v>1.98708564578452e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.031569746961682e-05</v>
+        <v>2.031569746961681e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.007908261287177e-05</v>
+        <v>2.007908261287175e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.992062331980599e-05</v>
+        <v>1.992062331980594e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.077544639088728e-05</v>
+        <v>2.077544639088725e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.016874584719657e-05</v>
+        <v>2.016874584719653e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.026436946271491e-05</v>
+        <v>2.026436946271487e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.031246676034296e-05</v>
@@ -7076,55 +7076,55 @@
         <v>2.043608662218611e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.025030874916128e-05</v>
+        <v>2.025030874916127e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.043799738183199e-05</v>
+        <v>2.043799738183198e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.000258331655562e-05</v>
+        <v>2.000258331655558e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.992550524716402e-05</v>
+        <v>1.992550524716401e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.990725487409091e-05</v>
+        <v>1.990725487409089e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.00954671610436e-05</v>
+        <v>2.009546716104359e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.017925560957459e-05</v>
+        <v>2.017925560957457e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.999148169654544e-05</v>
+        <v>1.999148169654542e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.009287537598637e-05</v>
+        <v>2.009287537598636e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.002209928445266e-05</v>
+        <v>2.002209928445265e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.007681505963355e-05</v>
+        <v>2.007681505963351e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.087778342445214e-05</v>
+        <v>2.087778342445213e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.992568453774656e-05</v>
+        <v>1.992568453774652e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.036254538792233e-05</v>
+        <v>2.036254538792232e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.009369057311426e-05</v>
+        <v>2.009369057311422e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.033951316789509e-05</v>
+        <v>2.033951316789515e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.025210969237096e-05</v>
+        <v>2.025210969237097e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.170369396583843e-05</v>
+        <v>5.170369396583842e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.669103273803321e-05</v>
+        <v>7.669103273803322e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.713587374980482e-05</v>
+        <v>7.713587374980488e-05</v>
       </c>
       <c r="E8" t="n">
         <v>6.342708003754784e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.538117347597077e-05</v>
+        <v>5.538117347597076e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.284200540791858e-05</v>
+        <v>8.284200540791864e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.698892212738453e-05</v>
+        <v>7.698892212738461e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.70845457429029e-05</v>
+        <v>7.708454574290297e-05</v>
       </c>
       <c r="J8" t="n">
         <v>7.7132643040531e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.725626290237409e-05</v>
+        <v>7.72562629023741e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.707048502934928e-05</v>
+        <v>7.707048502934929e-05</v>
       </c>
       <c r="M8" t="n">
         <v>7.725817366202036e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.72100441092667e-05</v>
+        <v>5.721004410926667e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.252274296867638e-05</v>
+        <v>6.252274296867639e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.118333598082759e-05</v>
+        <v>6.118333598082758e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.664209883773311e-05</v>
+        <v>4.664209883773308e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.699943188976267e-05</v>
+        <v>7.699943188976268e-05</v>
       </c>
       <c r="S8" t="n">
         <v>7.681165797673346e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.691305165617439e-05</v>
+        <v>7.691305165617444e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.44927113461355e-05</v>
+        <v>6.449271134613544e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.998323740609147e-05</v>
+        <v>6.998323740609149e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.770293213314882e-05</v>
+        <v>7.770293213314886e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.879122770118344e-05</v>
+        <v>4.879122770118335e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001023414673374164</v>
+        <v>0.0001023414673374165</v>
       </c>
       <c r="Z8" t="n">
         <v>5.114261483816818e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.715968944808309e-05</v>
+        <v>7.715968944808311e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001035015760315023</v>
+        <v>0.0001035015760315022</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.359755213408979e-05</v>
+        <v>3.359755213408978e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.928874408651531e-05</v>
+        <v>3.928874408651535e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.973358509828693e-05</v>
+        <v>3.973358509828694e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.811101299923349e-05</v>
+        <v>3.811101299923347e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.549506735607204e-05</v>
+        <v>2.549506735607199e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.019333431245508e-05</v>
+        <v>4.019333431245507e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.95866334758667e-05</v>
+        <v>3.958663347586664e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.968225709138501e-05</v>
+        <v>3.968225709138502e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.973035438901309e-05</v>
+        <v>3.973035438901304e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.985397425085622e-05</v>
+        <v>3.985397425085626e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.966819637783146e-05</v>
+        <v>3.966819637783137e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.985588501050213e-05</v>
+        <v>3.985588501050211e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.942047094522574e-05</v>
+        <v>3.942047094522575e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.133351496896284e-05</v>
+        <v>4.133351496896282e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.174807489273631e-05</v>
+        <v>4.174807489273627e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.951335508261138e-05</v>
+        <v>3.951335508261139e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>3.95971432382447e-05</v>
+        <v>3.959714323824472e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.940936932521555e-05</v>
+        <v>3.940936932521559e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>3.951076300465645e-05</v>
+        <v>3.951076300465651e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.943830648429364e-05</v>
+        <v>3.943830648429365e-05</v>
       </c>
       <c r="V9" t="n">
         <v>4.642448374454042e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.029567105312231e-05</v>
+        <v>4.029567105312224e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>3.934357216641662e-05</v>
+        <v>3.934357216641666e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.978043301659241e-05</v>
+        <v>3.978043301659237e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.589102425920416e-05</v>
+        <v>3.589102425920415e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.975740079656521e-05</v>
+        <v>3.975740079656524e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.966999732104107e-05</v>
+        <v>3.966999732104109e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7466,79 +7466,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.341914514629238e-05</v>
+        <v>1.341914514629236e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.34891352076083e-05</v>
+        <v>1.348913520760831e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.342570539214742e-05</v>
+        <v>1.342570539214741e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.340950293939889e-05</v>
+        <v>1.340950293939887e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.340853728870288e-05</v>
+        <v>1.340853728870286e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.342738972883602e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341166995429875e-05</v>
+        <v>1.341166995429873e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.341273331176118e-05</v>
+        <v>1.341273331176117e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.341925819007392e-05</v>
+        <v>1.341925819007383e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.341990715633537e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341421273846514e-05</v>
+        <v>1.341421273846491e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.341562562891051e-05</v>
+        <v>1.341562562891053e-05</v>
       </c>
       <c r="N2" t="n">
         <v>1.341326317819973e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.491947964576756e-05</v>
+        <v>1.491947964576755e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.341271220259807e-05</v>
+        <v>1.341271220259803e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.341480144357781e-05</v>
+        <v>1.341480144357778e-05</v>
       </c>
       <c r="R2" t="n">
         <v>1.342098081091204e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.341471028676451e-05</v>
+        <v>1.34147102867645e-05</v>
       </c>
       <c r="T2" t="n">
         <v>1.342073367208771e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.391995006274421e-05</v>
+        <v>1.391995006274412e-05</v>
       </c>
       <c r="V2" t="n">
         <v>1.341524767729105e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.399053299088142e-05</v>
+        <v>1.399053299088134e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341422160842677e-05</v>
+        <v>1.341422160842667e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.341583276567208e-05</v>
+        <v>1.341583276567209e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.375139649640048e-05</v>
+        <v>1.375139649640045e-05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.341574272442905e-05</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.349720584684245e-05</v>
+        <v>1.351336154704066e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.353253140063086e-05</v>
+        <v>1.354540396934786e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.354288094826289e-05</v>
+        <v>1.356083743292301e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.338489198533898e-05</v>
+        <v>1.339243344792233e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.342489182802959e-05</v>
+        <v>1.343851871108778e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.35597606903882e-05</v>
+        <v>1.357798388157668e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.344621963877101e-05</v>
+        <v>1.346065951314633e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.345227246762234e-05</v>
+        <v>1.346694820479171e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.350016001932672e-05</v>
+        <v>1.351624609704229e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.351571247246893e-05</v>
+        <v>1.353218406160159e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.346368113814726e-05</v>
+        <v>1.347865022049201e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.350369952887032e-05</v>
+        <v>1.35198796090767e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.345336809899691e-05</v>
+        <v>1.346813456325248e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.594536971946246e-05</v>
+        <v>1.596006627143236e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34470988677258e-05</v>
+        <v>1.346163233553187e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.346722895987636e-05</v>
+        <v>1.348239687017713e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.351010761422862e-05</v>
+        <v>1.352690091983126e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.347023090102278e-05</v>
+        <v>1.348530102818051e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350842618698644e-05</v>
+        <v>1.352512605295764e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.431844100620736e-05</v>
+        <v>1.433442131096647e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.347568907512826e-05</v>
+        <v>1.349090486010682e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.448719117634384e-05</v>
+        <v>1.450569214104018e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.346178233581862e-05</v>
+        <v>1.347681515309048e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.347450440761933e-05</v>
+        <v>1.348990677085305e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.40183081418311e-05</v>
+        <v>1.403324416820822e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.347141246021198e-05</v>
+        <v>1.348678618352536e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.353282042307578e-05</v>
+        <v>1.355039136105706e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7642,19 +7642,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.172530773558669e-05</v>
+        <v>1.17253077355861e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.157353576025647e-05</v>
+        <v>1.157353576025648e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.179940873038135e-05</v>
+        <v>1.179940873038133e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.161639457309032e-05</v>
+        <v>1.161639457309021e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.160548710425769e-05</v>
+        <v>1.160548710425771e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.181843408811238e-05</v>
@@ -7663,64 +7663,64 @@
         <v>1.164087200326036e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.165288311496707e-05</v>
+        <v>1.165288311496706e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.171508926263739e-05</v>
+        <v>1.171508926263733e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.173391498956414e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.166959392015826e-05</v>
+        <v>1.166959392015696e-05</v>
       </c>
       <c r="M4" t="n">
         <v>1.171893403447837e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.16588682001411e-05</v>
+        <v>1.165886820014109e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16597464261762e-05</v>
+        <v>1.165974642617621e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.165264467725914e-05</v>
+        <v>1.165264467725912e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.167624361522344e-05</v>
+        <v>1.167624361522341e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.174604241191306e-05</v>
+        <v>1.174604241191308e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.167521395708327e-05</v>
+        <v>1.167521395708317e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.174325086520289e-05</v>
+        <v>1.174325086520288e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.164309375945562e-05</v>
+        <v>1.164309375945561e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.163312070350078e-05</v>
+        <v>1.16331207035008e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.182733733559261e-05</v>
+        <v>1.182733733559258e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.166969411045525e-05</v>
+        <v>1.166969411045486e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.161561965639073e-05</v>
+        <v>1.161561965639074e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.166982999910132e-05</v>
+        <v>1.166982999910115e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.1686875815449e-05</v>
+        <v>1.168687581544895e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.178221818599338e-05</v>
+        <v>1.17822181859934e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.479182992065145e-05</v>
+        <v>4.479182992064593e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.402975327693761e-05</v>
+        <v>4.402975327693765e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.555574065905874e-05</v>
+        <v>4.555574065905836e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.854158343259787e-05</v>
+        <v>1.854158343259643e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.441429276033688e-05</v>
+        <v>4.441429276033689e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.861756227821386e-05</v>
+        <v>4.861756227821371e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.451041024403849e-05</v>
+        <v>4.451041024403948e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.388303933572189e-05</v>
+        <v>4.388303933572167e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.599874426066209e-05</v>
+        <v>4.599874426066155e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.222244051282965e-05</v>
+        <v>5.222244051282961e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.467169523047344e-05</v>
+        <v>4.46716952304507e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.216611275383129e-05</v>
+        <v>5.21661127538312e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.250235099084591e-05</v>
+        <v>4.250235099084578e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.546046274628264e-05</v>
+        <v>4.546046274628267e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.10850100588386e-05</v>
+        <v>4.108501005883886e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4433816907683e-05</v>
+        <v>4.443381690768105e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.507294767332755e-05</v>
+        <v>4.507294767332843e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.644571205255058e-05</v>
+        <v>4.64457120525482e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.506600058876184e-05</v>
+        <v>4.506600058876142e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.427725662713061e-05</v>
+        <v>4.427725662713057e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.741484003462218e-05</v>
+        <v>4.741484003462222e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.519038107775642e-05</v>
+        <v>4.519038107775517e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.358235901066299e-05</v>
+        <v>4.358235901066188e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.460672389335438e-05</v>
+        <v>4.460672389335407e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.352426537243835e-05</v>
+        <v>4.352426537243408e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.322529943532125e-05</v>
+        <v>4.322529943531991e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.776476555683693e-05</v>
+        <v>4.776476555683695e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7818,58 +7818,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.304168154221235e-05</v>
+        <v>1.304168154221201e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.288990956688211e-05</v>
+        <v>1.288990956688213e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.311578253700702e-05</v>
+        <v>1.311578253700701e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.60514072626856e-05</v>
+        <v>1.605140726268551e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.292186091088334e-05</v>
+        <v>1.292186091088336e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.625344677770768e-05</v>
+        <v>1.625344677770766e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.295724580988601e-05</v>
+        <v>1.295724580988602e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.296925692159274e-05</v>
+        <v>1.296925692159273e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.303146306926303e-05</v>
+        <v>1.303146306926299e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.616892767915943e-05</v>
+        <v>1.616892767915942e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.610460660975354e-05</v>
+        <v>1.61046066097515e-05</v>
       </c>
       <c r="M6" t="n">
         <v>1.303530784110403e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.297755531930272e-05</v>
+        <v>1.297755531930271e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.610743762035578e-05</v>
+        <v>1.610743762035575e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.610044461291755e-05</v>
+        <v>1.610044461291748e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.29926174218491e-05</v>
+        <v>1.299261742184899e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.618105510150836e-05</v>
+        <v>1.618105510150835e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.299158776370893e-05</v>
+        <v>1.29915877637088e-05</v>
       </c>
       <c r="T6" t="n">
         <v>1.305962467182854e-05</v>
@@ -7878,22 +7878,22 @@
         <v>1.615037966537018e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.294949451012643e-05</v>
+        <v>1.294949451012645e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.322873249831279e-05</v>
+        <v>1.322873249831273e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.610470680005054e-05</v>
+        <v>1.610470680005011e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.307654817481437e-05</v>
+        <v>1.307654817481436e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61048426886966e-05</v>
+        <v>1.610484268869639e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.612188850504423e-05</v>
+        <v>1.612188850504418e-05</v>
       </c>
       <c r="AB6" t="n">
         <v>1.310119579490841e-05</v>
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.02422025444564e-05</v>
+        <v>2.024220254445596e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.009043056912621e-05</v>
+        <v>2.00904305691262e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.031630353925108e-05</v>
+        <v>2.031630353925113e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.013328938196001e-05</v>
+        <v>2.013328938195989e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.012238191312743e-05</v>
+        <v>2.012238191312742e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.03353288969821e-05</v>
+        <v>2.033532889698212e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.015776681213005e-05</v>
+        <v>2.015776681213006e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.016977792383677e-05</v>
+        <v>2.016977792383678e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.023198407150709e-05</v>
+        <v>2.023198407150701e-05</v>
       </c>
       <c r="K7" t="n">
         <v>2.025080979843385e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.018648872902795e-05</v>
+        <v>2.018648872902601e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.023582884334807e-05</v>
+        <v>2.02358288433481e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.01757630090108e-05</v>
+        <v>2.017576300901082e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.017661085456939e-05</v>
+        <v>2.017661085456942e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.016950910565237e-05</v>
+        <v>2.016950910565232e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.019313842409318e-05</v>
+        <v>2.019313842409305e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.02629372207828e-05</v>
+        <v>2.026293722078281e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0192108765953e-05</v>
+        <v>2.019210876595292e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.026014567407261e-05</v>
+        <v>2.02601456740726e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0232410133885e-05</v>
+        <v>2.023241013388499e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.015001551237051e-05</v>
+        <v>2.015001551237049e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>2.03442321444623e-05</v>
+        <v>2.034423214446229e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.018658891932501e-05</v>
+        <v>2.018658891932456e-05</v>
       </c>
       <c r="Y7" t="n">
         <v>2.020478768157974e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.018672480797104e-05</v>
+        <v>2.018672480797093e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.02037706243187e-05</v>
+        <v>2.020377062431869e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.029911299486309e-05</v>
+        <v>2.029911299486312e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7994,82 +7994,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.39987524938877e-05</v>
+        <v>5.399875249388724e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.090138620749481e-05</v>
+        <v>8.090138620749482e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.11272591776197e-05</v>
+        <v>8.112725917761974e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.653857204504778e-05</v>
+        <v>6.653857204504774e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.809369207797187e-05</v>
+        <v>5.80936920779719e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.675619179836124e-05</v>
+        <v>8.675619179836134e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.096872245049872e-05</v>
+        <v>8.09687224504987e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.098073356220542e-05</v>
+        <v>8.098073356220543e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.104293970987566e-05</v>
+        <v>8.10429397098757e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.106176543680246e-05</v>
+        <v>8.106176543680251e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.099744436739651e-05</v>
+        <v>8.099744436739547e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.104678448171574e-05</v>
+        <v>8.104678448171583e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>6.001502813625084e-05</v>
+        <v>6.001502813625081e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.577910901144205e-05</v>
+        <v>6.577910901144213e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.435930703444173e-05</v>
+        <v>6.435930703444172e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.863288016771167e-05</v>
+        <v>4.863288016771168e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.107389285915141e-05</v>
+        <v>8.107389285915148e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.100306440432166e-05</v>
+        <v>8.100306440432162e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>8.107110131244122e-05</v>
+        <v>8.107110131244133e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.783846161141807e-05</v>
+        <v>6.78384616114181e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>7.356674692150846e-05</v>
+        <v>7.35667469215085e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.116050475364309e-05</v>
+        <v>8.116050475364314e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>5.110592070524584e-05</v>
+        <v>5.110592070524556e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.000107915560051936</v>
+        <v>0.0001079155600519362</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.344072528159302e-05</v>
+        <v>5.34407252815929e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.101472626268733e-05</v>
+        <v>8.101472626268729e-05</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001093706576324334</v>
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.703568653410515e-05</v>
+        <v>3.703568653410445e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.396821864645658e-05</v>
+        <v>4.396821864645655e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.419409161658149e-05</v>
+        <v>4.41940916165815e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.237604914214048e-05</v>
+        <v>4.237604914214027e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.766891528995819e-05</v>
+        <v>2.766891528995815e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.421311719523849e-05</v>
+        <v>4.421311719523844e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.403555488946045e-05</v>
+        <v>4.403555488946047e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.404756600116718e-05</v>
+        <v>4.404756600116715e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.41097721488375e-05</v>
+        <v>4.410977214883741e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.412859787576429e-05</v>
+        <v>4.412859787576421e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.406427680635836e-05</v>
+        <v>4.406427680635623e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.411361692067845e-05</v>
+        <v>4.411361692067842e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.405355108634118e-05</v>
+        <v>4.405355108634114e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.640215870506786e-05</v>
+        <v>4.640215870506779e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.690564777076199e-05</v>
+        <v>4.690564777076188e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.407092672234956e-05</v>
+        <v>4.407092672234948e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.41407252981132e-05</v>
+        <v>4.414072529811313e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.40698968432834e-05</v>
+        <v>4.406989684328314e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.413793375140299e-05</v>
+        <v>4.413793375140288e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.411004986197501e-05</v>
+        <v>4.411004986197494e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>5.220293880259593e-05</v>
+        <v>5.220293880259591e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.422202022179272e-05</v>
+        <v>4.422202022179257e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.40643769966554e-05</v>
+        <v>4.406437699665476e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.408257575891013e-05</v>
+        <v>4.408257575891009e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.979330756905494e-05</v>
+        <v>3.979330756905465e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.408155870164909e-05</v>
+        <v>4.408155870164898e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.41769010721935e-05</v>
+        <v>4.417690107219342e-05</v>
       </c>
     </row>
   </sheetData>
@@ -8326,37 +8326,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.348097236986997e-05</v>
+        <v>1.348097236986996e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.354909004044861e-05</v>
+        <v>1.354909004044858e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.349890551495116e-05</v>
+        <v>1.349890551495115e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.346843468040358e-05</v>
+        <v>1.34684346804035e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.346551636847449e-05</v>
+        <v>1.346551636847443e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.347270636889538e-05</v>
+        <v>1.347270636889532e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.346795042837879e-05</v>
+        <v>1.34679504283788e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.349408738021811e-05</v>
+        <v>1.349408738021807e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.347559588027317e-05</v>
+        <v>1.347559588027313e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.348110084396592e-05</v>
+        <v>1.348110084396594e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.347878184386652e-05</v>
+        <v>1.347878184386647e-05</v>
       </c>
       <c r="M2" t="n">
         <v>1.348682608194424e-05</v>
@@ -8365,46 +8365,46 @@
         <v>1.346987708652457e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.502111055462826e-05</v>
+        <v>1.502111055462823e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.346326155030893e-05</v>
+        <v>1.346326155030887e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.347271954527409e-05</v>
+        <v>1.3472719545274e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.348230794945451e-05</v>
+        <v>1.348230794945455e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.347498359583552e-05</v>
+        <v>1.34749835958355e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.348185763750539e-05</v>
+        <v>1.348185763750541e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.400717223442483e-05</v>
+        <v>1.40071722344249e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.347551299690292e-05</v>
+        <v>1.34755129969029e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.408445725642757e-05</v>
+        <v>1.40844572564276e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.34674424323169e-05</v>
+        <v>1.346744243231691e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.346445057771593e-05</v>
+        <v>1.346445057771588e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.38355060254906e-05</v>
+        <v>1.383550602549061e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.348421201164429e-05</v>
+        <v>1.348421201164428e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.347573051014894e-05</v>
+        <v>1.347573051014891e-05</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.364369841749726e-05</v>
+        <v>1.366411606883945e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.36470419642426e-05</v>
+        <v>1.366259629842177e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.377752878185684e-05</v>
+        <v>1.380269776514761e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.351243698276881e-05</v>
+        <v>1.352353615962026e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.354050994131798e-05</v>
+        <v>1.355724404191763e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.359549878381959e-05</v>
+        <v>1.361385576289037e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.355417441936919e-05</v>
+        <v>1.357154823699962e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.374033145020291e-05</v>
+        <v>1.376430720003671e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.361255509360222e-05</v>
+        <v>1.363158221881045e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.366235770041227e-05</v>
+        <v>1.368298737158176e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.363891089182762e-05</v>
+        <v>1.365885703886407e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.372073285641706e-05</v>
+        <v>1.374362903614036e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.356439780548691e-05</v>
+        <v>1.358215336423217e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.609764834075788e-05</v>
+        <v>1.611375360930497e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.351789532940152e-05</v>
+        <v>1.35338686521776e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.359270792652441e-05</v>
+        <v>1.361119981891268e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.365604823480617e-05</v>
+        <v>1.367705458530597e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.360735629077407e-05</v>
+        <v>1.362631102323738e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.365374720833661e-05</v>
+        <v>1.367459543570435e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44830640517622e-05</v>
+        <v>1.450182551126702e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.361407332152769e-05</v>
+        <v>1.363316643695042e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46659212866365e-05</v>
+        <v>1.4687682476608e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.355175603619055e-05</v>
+        <v>1.356892603540006e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.352810928985133e-05</v>
+        <v>1.354447757728773e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.420237675642605e-05</v>
+        <v>1.422136833497819e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.366671131232899e-05</v>
+        <v>1.368805756230434e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.363718623297016e-05</v>
+        <v>1.365745140560868e-05</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.195589560336369e-05</v>
+        <v>1.195589560336367e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.173117857867358e-05</v>
+        <v>1.173117857867357e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.215845872671003e-05</v>
+        <v>1.215845872671002e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.181427663321867e-05</v>
+        <v>1.181427663321865e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.178131295748974e-05</v>
+        <v>1.178131295748971e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.18625273198076e-05</v>
+        <v>1.186252731980744e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.180880678383189e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2104035678449e-05</v>
+        <v>1.210403567844897e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.18837219871729e-05</v>
+        <v>1.188372198717281e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.195734677737869e-05</v>
+        <v>1.195734677737867e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.193115260446325e-05</v>
+        <v>1.193115260446323e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.205481474724622e-05</v>
+        <v>1.205481474724619e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.183056927389532e-05</v>
+        <v>1.18305692738953e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.176149003634982e-05</v>
+        <v>1.17614900363498e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.175584374904244e-05</v>
+        <v>1.175584374904243e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.186267615306646e-05</v>
+        <v>1.186267615306642e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.197098158916821e-05</v>
+        <v>1.19709815891682e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.188824964567243e-05</v>
+        <v>1.188824964567242e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.196589510854926e-05</v>
+        <v>1.196589510854928e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1814133731885e-05</v>
+        <v>1.181413373188499e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.184643254972666e-05</v>
+        <v>1.184643254972665e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.20115968090123e-05</v>
+        <v>1.201159680901228e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.180306873462345e-05</v>
+        <v>1.180306873462344e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.170495168204125e-05</v>
+        <v>1.170495168204123e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.189090369939017e-05</v>
+        <v>1.189090369939015e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.199248884751356e-05</v>
+        <v>1.199248884751352e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.194026631380245e-05</v>
+        <v>1.194026631380243e-05</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.483132235302142e-05</v>
+        <v>4.483132235302128e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.618707400723505e-05</v>
+        <v>4.618707400723503e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.144073570874736e-05</v>
+        <v>5.144073570874728e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.067548253709671e-05</v>
+        <v>2.067548253709667e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.543422040174881e-05</v>
+        <v>4.543422040174874e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.877430340695785e-05</v>
+        <v>4.877430340695442e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.399916115599779e-05</v>
+        <v>4.399916115599768e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.902192985072062e-05</v>
+        <v>4.902192985072045e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.749199023948598e-05</v>
+        <v>4.749199023948426e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.405151594341168e-05</v>
+        <v>5.405151594341161e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.001455695402571e-05</v>
+        <v>5.00145569540256e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>5.561662218787517e-05</v>
+        <v>5.561662218787508e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.255614880189212e-05</v>
+        <v>4.255614880189199e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>4.45517598434729e-05</v>
+        <v>4.455175984347286e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.160396545276925e-05</v>
+        <v>4.160396545276914e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.728191055278946e-05</v>
+        <v>4.728191055278941e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.655835454761327e-05</v>
+        <v>4.655835454761321e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>4.695155691132707e-05</v>
+        <v>4.695155691132695e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.694146472933577e-05</v>
+        <v>4.694146472933653e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.782196149026799e-05</v>
+        <v>4.782196149026795e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>4.853241389451277e-05</v>
+        <v>4.853241389451265e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>4.53012245699403e-05</v>
+        <v>4.530122456994019e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.452328032107371e-05</v>
+        <v>4.452328032107367e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.273690309312095e-05</v>
+        <v>4.273690309312071e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.628494572841465e-05</v>
+        <v>4.628494572841458e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.542226023435644e-05</v>
+        <v>4.542226023435576e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.829719068247169e-05</v>
+        <v>4.829719068247173e-05</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.613403952558383e-05</v>
+        <v>1.613403952558388e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.590932250089381e-05</v>
+        <v>1.590932250089378e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.633660264893026e-05</v>
+        <v>1.633660264893023e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.305465410696978e-05</v>
+        <v>1.305465410696974e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.302169043124082e-05</v>
+        <v>1.302169043124081e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.310290479355873e-05</v>
+        <v>1.310290479355855e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.304918425758297e-05</v>
+        <v>1.304918425758298e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.628217960066925e-05</v>
+        <v>1.628217960066919e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.606186590939308e-05</v>
+        <v>1.606186590939303e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.319772425112976e-05</v>
+        <v>1.319772425112977e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.610929652668342e-05</v>
+        <v>1.610929652668343e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>1.32951922209973e-05</v>
+        <v>1.329519222099731e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.307316744461763e-05</v>
+        <v>1.307316744461761e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.594965434771227e-05</v>
+        <v>1.594965434771225e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.291002208363548e-05</v>
+        <v>1.291002208363549e-05</v>
       </c>
       <c r="Q6" t="n">
         <v>1.310305362681754e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.614912551138845e-05</v>
+        <v>1.614912551138841e-05</v>
       </c>
       <c r="S6" t="n">
         <v>1.312862711942351e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.320627258230037e-05</v>
+        <v>1.320627258230036e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.605660033264796e-05</v>
+        <v>1.605660033264799e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.308681002347777e-05</v>
+        <v>1.308681002347775e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.333221778058069e-05</v>
+        <v>1.333221778058057e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.598121265684366e-05</v>
+        <v>1.598121265684368e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.307817693480897e-05</v>
+        <v>1.307817693480895e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.606904762161035e-05</v>
+        <v>1.60690476216104e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.323286632126465e-05</v>
+        <v>1.323286632126463e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.318271962047029e-05</v>
+        <v>1.318271962047024e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8766,40 +8766,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.991045058245872e-05</v>
+        <v>1.991045058245868e-05</v>
       </c>
       <c r="C7" t="n">
         <v>1.968573355776861e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.011301370580507e-05</v>
+        <v>2.011301370580506e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.976883161231369e-05</v>
+        <v>1.976883161231367e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.973586793658477e-05</v>
+        <v>1.973586793658473e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.981708229890259e-05</v>
+        <v>1.981708229890244e-05</v>
       </c>
       <c r="H7" t="n">
         <v>1.976336176292693e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0058590657544e-05</v>
+        <v>2.005859065754399e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.98382769662679e-05</v>
+        <v>1.983827696626781e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.99119017564737e-05</v>
+        <v>1.991190175647369e-05</v>
       </c>
       <c r="L7" t="n">
         <v>1.988570758355828e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.000936972634126e-05</v>
+        <v>2.000936972634125e-05</v>
       </c>
       <c r="N7" t="n">
         <v>1.978512425299036e-05</v>
@@ -8808,43 +8808,43 @@
         <v>1.971601391629262e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.971036762898525e-05</v>
+        <v>1.971036762898522e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.981723113216147e-05</v>
+        <v>1.981723113216146e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.992553656826324e-05</v>
+        <v>1.992553656826322e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.984280462476746e-05</v>
+        <v>1.984280462476742e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.992045008764427e-05</v>
+        <v>1.992045008764428e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.983382778893449e-05</v>
+        <v>1.983382778893448e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98009875288217e-05</v>
+        <v>1.980098752882169e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.996615178810733e-05</v>
+        <v>1.99661517881073e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.97576237137185e-05</v>
+        <v>1.975762371371845e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.972382933967907e-05</v>
+        <v>1.972382933967904e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.984545867848524e-05</v>
+        <v>1.984545867848521e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99470438266086e-05</v>
+        <v>1.994704382660855e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.989482129289744e-05</v>
+        <v>1.989482129289745e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.139643017231942e-05</v>
+        <v>5.139643017231935e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.642057401242939e-05</v>
+        <v>7.642057401242914e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>7.684785416046579e-05</v>
+        <v>7.684785416046559e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.305939845037821e-05</v>
+        <v>6.305939845037805e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.515532496004835e-05</v>
+        <v>5.515532496004823e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.178743853523233e-05</v>
+        <v>8.178743853523174e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.649820221758768e-05</v>
+        <v>7.649820221758748e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.679343111220478e-05</v>
+        <v>7.679343111220455e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.657311742092858e-05</v>
+        <v>7.657311742092842e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.664674221113441e-05</v>
+        <v>7.664674221113425e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.662054803821905e-05</v>
+        <v>7.66205480382188e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>7.674421018100141e-05</v>
+        <v>7.674421018100121e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.694787349618593e-05</v>
+        <v>5.694787349618579e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.22573748675241e-05</v>
+        <v>6.225737486752398e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.093330850799742e-05</v>
+        <v>6.093330850799731e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.634123328379154e-05</v>
+        <v>4.634123328379146e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>7.666037702292402e-05</v>
+        <v>7.66603770229238e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>7.657764507942821e-05</v>
+        <v>7.657764507942802e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>7.665529054230502e-05</v>
+        <v>7.665529054230482e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.424487664210883e-05</v>
+        <v>6.424487664210869e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>6.963565802582593e-05</v>
+        <v>6.963565802582582e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>7.670595437188384e-05</v>
+        <v>7.670595437188368e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>4.859573413660416e-05</v>
+        <v>4.859573413660413e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001015641610297818</v>
+        <v>0.0001015641610297817</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.086242771463298e-05</v>
+        <v>5.086242771463289e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.668188428126928e-05</v>
+        <v>7.668188428126912e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001030042082003951</v>
+        <v>0.000103004208200395</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.424743437744773e-05</v>
+        <v>3.424743437744767e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.02697317996341e-05</v>
+        <v>4.026973179963408e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.069701194767052e-05</v>
+        <v>4.069701194767051e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.891104456583958e-05</v>
+        <v>3.891104456583954e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.591879262659144e-05</v>
+        <v>2.59187926265914e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.040108075513537e-05</v>
+        <v>4.040108075513479e-05</v>
       </c>
       <c r="H9" t="n">
         <v>4.034736000479239e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.064258889940963e-05</v>
+        <v>4.064258889940946e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.042227520813332e-05</v>
+        <v>4.042227520813325e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.049589999833924e-05</v>
+        <v>4.049589999833913e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.04697058254237e-05</v>
+        <v>4.046970582542381e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.059336796820682e-05</v>
+        <v>4.059336796820665e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.036912249485586e-05</v>
+        <v>4.036912249485578e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.237029595064369e-05</v>
+        <v>4.237029595064375e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.281489405796184e-05</v>
+        <v>4.281489405796193e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.040122958839387e-05</v>
+        <v>4.040122958839384e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.050953481012881e-05</v>
+        <v>4.050953481012867e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>4.042680286663295e-05</v>
+        <v>4.042680286663288e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.050444832950978e-05</v>
+        <v>4.050444832950973e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.041700963138832e-05</v>
+        <v>4.041700963138825e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.759390654191547e-05</v>
+        <v>4.759390654191544e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>4.05501500299728e-05</v>
+        <v>4.055015002997267e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>4.034162195558396e-05</v>
+        <v>4.034162195558392e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.030782758154469e-05</v>
+        <v>4.030782758154452e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.66630628002054e-05</v>
+        <v>3.666306280020535e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.053104206847419e-05</v>
+        <v>4.053104206847398e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.047881953476289e-05</v>
+        <v>4.047881953476286e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.339247146463494e-05</v>
+        <v>1.339247146463506e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.346629612651377e-05</v>
+        <v>1.346629612651376e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.338582815276489e-05</v>
+        <v>1.338582815276487e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.33887555698931e-05</v>
+        <v>1.338875556989312e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.338504651533901e-05</v>
+        <v>1.338504651533909e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.340329471018695e-05</v>
+        <v>1.340329471018712e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.338881494472773e-05</v>
+        <v>1.33888149447278e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.338792459422488e-05</v>
+        <v>1.3387924594225e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.339693742835765e-05</v>
+        <v>1.339693742835779e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.339275637780559e-05</v>
+        <v>1.339275637780554e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.338950447469479e-05</v>
+        <v>1.338950447469489e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.339529725097017e-05</v>
+        <v>1.339529725097016e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.338970309543947e-05</v>
+        <v>1.338970309543943e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.488069660071458e-05</v>
+        <v>1.488069660071463e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.33928554287651e-05</v>
+        <v>1.339285542876524e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.338799460497303e-05</v>
+        <v>1.338799460497302e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.338487208650803e-05</v>
+        <v>1.338487208650841e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.339373781704938e-05</v>
+        <v>1.339373781704917e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.338749309009193e-05</v>
+        <v>1.338749309009184e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.389336015294618e-05</v>
+        <v>1.389336015294629e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.339661020542038e-05</v>
+        <v>1.339661020542058e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.395824088291373e-05</v>
+        <v>1.395824088291363e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.339172613075452e-05</v>
+        <v>1.339172613075467e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.339825956982869e-05</v>
+        <v>1.339825956982891e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.372842783670858e-05</v>
+        <v>1.372842783670838e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.339257163770349e-05</v>
+        <v>1.339257163770373e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.339824420636292e-05</v>
+        <v>1.33982442063629e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.435703408194599e-05</v>
+        <v>1.390091885897633e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.424009309136535e-05</v>
+        <v>1.391612987116116e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.420872780654026e-05</v>
+        <v>1.38439845987678e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.365142603219467e-05</v>
+        <v>1.33905405094404e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.41940459033941e-05</v>
+        <v>1.385219050422973e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.460431136459261e-05</v>
+        <v>1.396756906664278e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.428409746631488e-05</v>
+        <v>1.389013751227977e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.425881161075071e-05</v>
+        <v>1.386427888199631e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.445031489685322e-05</v>
+        <v>1.392225747661488e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.436955781052381e-05</v>
+        <v>1.389844348801766e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.428879813841601e-05</v>
+        <v>1.385892100966567e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.449937639132573e-05</v>
+        <v>1.39629454464118e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.429697764660972e-05</v>
+        <v>1.387195464563292e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.591223417633197e-05</v>
+        <v>1.542901682860565e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.436141127315504e-05</v>
+        <v>1.387682819284814e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.425834505315574e-05</v>
+        <v>1.386187395689053e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.418858507846158e-05</v>
+        <v>1.384279493986505e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.438665021112653e-05</v>
+        <v>1.390294550002798e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.424798563683634e-05</v>
+        <v>1.385865326475343e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.500302598063074e-05</v>
+        <v>1.444162835675608e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.445652680292732e-05</v>
+        <v>1.394764411178394e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.520634413413955e-05</v>
+        <v>1.454250855287734e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.434653798682754e-05</v>
+        <v>1.389639814021552e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.449587639160944e-05</v>
+        <v>1.394756211709748e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.474260459264034e-05</v>
+        <v>1.423506602099968e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.436154675261275e-05</v>
+        <v>1.388754605770894e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.458614665446303e-05</v>
+        <v>1.400485671704887e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.45371020129205e-05</v>
+        <v>4.453710201292043e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.277693576808563e-05</v>
+        <v>4.27769357680857e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>4.271737639525004e-05</v>
+        <v>4.271737639525003e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.82060465008814e-05</v>
+        <v>1.820604650088138e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.366298693236299e-05</v>
+        <v>4.3662986932363e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.545193698689375e-05</v>
+        <v>4.545193698689346e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.512633195796977e-05</v>
+        <v>4.512633195796975e-05</v>
       </c>
       <c r="I4" t="n">
         <v>4.346770255627734e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.443698865028661e-05</v>
+        <v>4.443698865028648e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.422007828678777e-05</v>
+        <v>4.422007828678774e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.243317802511648e-05</v>
+        <v>4.243317802511621e-05</v>
       </c>
       <c r="M4" t="n">
         <v>4.731517445871695e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.336637662839936e-05</v>
+        <v>4.336637662839934e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.670910951550347e-05</v>
+        <v>4.670910951550341e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.251020034927093e-05</v>
+        <v>4.251020034927067e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.325566297427138e-05</v>
+        <v>4.325566297427145e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.300064042251037e-05</v>
+        <v>4.300064042251041e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.419196200484704e-05</v>
+        <v>4.419196200484687e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.320099629513067e-05</v>
+        <v>4.320099629513022e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.55798406945174e-05</v>
+        <v>4.557984069451751e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.648958790440015e-05</v>
+        <v>4.648958790440016e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.640883270315525e-05</v>
+        <v>4.64088327031554e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.446798892669561e-05</v>
+        <v>4.446798892669554e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.587418429683616e-05</v>
+        <v>4.587418429683637e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.365555216518538e-05</v>
+        <v>4.365555216518533e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.344855088076099e-05</v>
+        <v>4.344855088076113e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.915503477661029e-05</v>
+        <v>4.915503477661037e-05</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.678341767653877e-05</v>
+        <v>5.678341767653866e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>8.55843074591812e-05</v>
+        <v>8.558430745918127e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.560945349199325e-05</v>
+        <v>8.560945349199332e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.025355006285824e-05</v>
+        <v>7.025355006285825e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1201999182565e-05</v>
+        <v>6.120199918256487e-05</v>
       </c>
       <c r="G5" t="n">
         <v>9.179957248410405e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>8.564319068120586e-05</v>
+        <v>8.56431906812059e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>8.563313376269459e-05</v>
+        <v>8.563313376269464e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.572347165782939e-05</v>
+        <v>8.572347165782938e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.568771098096903e-05</v>
+        <v>8.568771098096928e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>8.565097923938318e-05</v>
+        <v>8.565097923938321e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>8.574910761210439e-05</v>
+        <v>8.574910761210453e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.336637662839936e-05</v>
+        <v>6.325005452260055e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.94712093349927e-05</v>
+        <v>6.947120933499259e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.793311894741599e-05</v>
+        <v>6.79331189474159e-05</v>
       </c>
       <c r="Q5" t="n">
         <v>5.10531285979562e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>8.559865428380983e-05</v>
+        <v>8.559865428380997e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.569879678871189e-05</v>
+        <v>8.5698796788712e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>8.562825972501121e-05</v>
+        <v>8.562825972501138e-05</v>
       </c>
       <c r="U5" t="n">
         <v>7.165131187151774e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>7.778408688710558e-05</v>
+        <v>7.778408688710575e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>8.583349680577876e-05</v>
+        <v>8.583349680577867e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.374411885977079e-05</v>
+        <v>5.374411885977072e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001144854022830909</v>
+        <v>0.0001144854022830912</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.627289846274298e-05</v>
+        <v>5.62728984627429e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.568562425653111e-05</v>
+        <v>8.568562425653137e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001159813347839443</v>
+        <v>0.0001159813347839445</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.065407256597759e-05</v>
+        <v>4.065407256597763e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.867253052087587e-05</v>
+        <v>4.867253052087576e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.869767655368793e-05</v>
+        <v>4.869767655368779e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.685699349274119e-05</v>
+        <v>4.685699349274125e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.997315884048121e-05</v>
+        <v>2.997315884048114e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.889496956666804e-05</v>
+        <v>4.889496956666788e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.873141374290051e-05</v>
+        <v>4.873141374290052e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.872135682438923e-05</v>
+        <v>4.872135682438929e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.881169471952408e-05</v>
+        <v>4.881169471952397e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.877593404266366e-05</v>
+        <v>4.877593404266372e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.873920230107781e-05</v>
+        <v>4.873920230107772e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.883733067379911e-05</v>
+        <v>4.883733067379907e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.336637662839936e-05</v>
+        <v>4.874144581375883e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>5.149652349563334e-05</v>
+        <v>5.149652349563337e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>5.205270018200611e-05</v>
+        <v>5.205270018200607e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.872214783988081e-05</v>
+        <v>4.872214783988054e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.868687734550451e-05</v>
+        <v>4.868687734550439e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.878701985040656e-05</v>
+        <v>4.878701985040653e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.871648278670589e-05</v>
+        <v>4.871648278670575e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.884585214975633e-05</v>
+        <v>4.884585214975638e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.814024740130151e-05</v>
+        <v>5.81402474013015e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.891603997283466e-05</v>
+        <v>4.891603997283463e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.876429692828468e-05</v>
+        <v>4.876429692828454e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.883809512815792e-05</v>
+        <v>4.883809512815775e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.390422905287122e-05</v>
+        <v>4.390422905287097e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.87738473182258e-05</v>
+        <v>4.877384731822572e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.887996825208839e-05</v>
+        <v>4.887996825208835e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.353632981592002e-05</v>
+        <v>1.353632981591993e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.360422962953077e-05</v>
+        <v>1.360422962953076e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.355647770816469e-05</v>
+        <v>1.35564777081646e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.352196639073168e-05</v>
+        <v>1.352196639073159e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.351998548186434e-05</v>
+        <v>1.351998548186424e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356736374654756e-05</v>
+        <v>1.356736374654747e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.353966913030214e-05</v>
+        <v>1.353966913030206e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.355085420790252e-05</v>
+        <v>1.355085420790245e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.354686692556308e-05</v>
+        <v>1.354686692556294e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.352958918162351e-05</v>
+        <v>1.352958918162343e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.353115742980325e-05</v>
+        <v>1.353115742980318e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.356065926415283e-05</v>
+        <v>1.356065926415284e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.352593033935193e-05</v>
+        <v>1.352593033935189e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.510591907523731e-05</v>
+        <v>1.510591907523722e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.351694776004517e-05</v>
+        <v>1.351694776004482e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.353118166437038e-05</v>
+        <v>1.353118166437028e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.354033709612248e-05</v>
+        <v>1.354033709612241e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.352936142734206e-05</v>
+        <v>1.352936142734194e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.353503897036597e-05</v>
+        <v>1.353503897036588e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.408345145438908e-05</v>
+        <v>1.408345145438903e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.354079540931505e-05</v>
+        <v>1.354079540931494e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42031802559369e-05</v>
+        <v>1.420318025593683e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.352114306803875e-05</v>
+        <v>1.352114306803868e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.355500067798378e-05</v>
+        <v>1.35550006779837e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.390152006787476e-05</v>
+        <v>1.390152006787475e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.354625508605435e-05</v>
+        <v>1.354625508605426e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.355720201408281e-05</v>
+        <v>1.355720201408279e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.510655938715616e-05</v>
+        <v>1.423253352929221e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.47144899938555e-05</v>
+        <v>1.421667292480891e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.559888747632328e-05</v>
+        <v>1.445150598510614e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.414887692933168e-05</v>
+        <v>1.368424358686219e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.474890814962333e-05</v>
+        <v>1.41438314263661e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58279053562108e-05</v>
+        <v>1.45193480378886e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.521229183195577e-05</v>
+        <v>1.430562002587651e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.546698746047327e-05</v>
+        <v>1.438358919788322e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.535466996818896e-05</v>
+        <v>1.434998431010145e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.497915187049826e-05</v>
+        <v>1.430239165936535e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.500144709460192e-05</v>
+        <v>1.425781471759594e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.576776958853011e-05</v>
+        <v>1.452317492249207e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.487371314742131e-05</v>
+        <v>1.413570966786561e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.634445820302417e-05</v>
+        <v>1.572502448077694e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.466049181956403e-05</v>
+        <v>1.409245261713698e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.500317150537438e-05</v>
+        <v>1.422296080795332e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52217139826835e-05</v>
+        <v>1.428610018440014e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.495161222481983e-05</v>
+        <v>1.420083534612225e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.509334850490485e-05</v>
+        <v>1.423380902111127e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.55047605325199e-05</v>
+        <v>1.480337737452602e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.521841821349951e-05</v>
+        <v>1.431245764501129e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.670632154371426e-05</v>
+        <v>1.517945704919309e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.477171653896599e-05</v>
+        <v>1.415156177948213e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.55469962773587e-05</v>
+        <v>1.436503799361856e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.538073554483175e-05</v>
+        <v>1.460604496780161e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.534274180934587e-05</v>
+        <v>1.429286069748119e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.569648450428759e-05</v>
+        <v>1.447424003801532e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1358,82 +1358,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.64462307777875e-05</v>
+        <v>4.644623077778751e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.669656576271354e-05</v>
+        <v>4.669656576271357e-05</v>
       </c>
       <c r="D4" t="n">
         <v>5.437648280689232e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.569165146615795e-05</v>
+        <v>2.569165146615793e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.600774917522174e-05</v>
+        <v>4.600774917522168e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>5.527963894504346e-05</v>
+        <v>5.527963894504341e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.023021992032958e-05</v>
+        <v>5.023021992032961e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.169137369861507e-05</v>
+        <v>5.16913736986148e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>5.079619083308485e-05</v>
+        <v>5.079619083308481e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.348611024414232e-05</v>
+        <v>5.348611024414224e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.992986030396982e-05</v>
+        <v>4.99298603039698e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.701639476582729e-05</v>
+        <v>5.701639476582726e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.342398859320104e-05</v>
+        <v>4.342398859320103e-05</v>
       </c>
       <c r="O4" t="n">
         <v>4.53872465374651e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.35827824043802e-05</v>
+        <v>4.358278240438026e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.754517576286973e-05</v>
+        <v>4.754517576286969e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.867929460455706e-05</v>
+        <v>4.867929460455702e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.66800051762687e-05</v>
+        <v>4.668000517626861e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.695266846768459e-05</v>
+        <v>4.695266846768457e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.008664387519357e-05</v>
+        <v>5.008664387519359e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.028973600149063e-05</v>
+        <v>5.028973600149053e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>5.395653550390582e-05</v>
+        <v>5.395653550390586e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.614133244187205e-05</v>
+        <v>4.614133244187208e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.902212275211137e-05</v>
+        <v>4.902212275211132e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.822198772113384e-05</v>
+        <v>4.822198772113386e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.712355245333856e-05</v>
+        <v>4.71235524533385e-05</v>
       </c>
       <c r="AB4" t="n">
         <v>5.466401440362242e-05</v>
@@ -1446,43 +1446,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.153234321668131e-05</v>
+        <v>5.153234321668129e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>7.656958696831102e-05</v>
+        <v>7.656958696831113e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.704151176210385e-05</v>
+        <v>7.704151176210399e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.318999026091748e-05</v>
+        <v>6.318999026091744e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.528630251345827e-05</v>
+        <v>5.528630251345838e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.240677671275256e-05</v>
+        <v>8.240677671275261e-05</v>
       </c>
       <c r="H5" t="n">
         <v>7.685165114281875e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.697799173970473e-05</v>
+        <v>7.697799173970462e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.692141682504767e-05</v>
+        <v>7.692141682504774e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.673779348548785e-05</v>
+        <v>7.673779348548795e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.675550757010803e-05</v>
+        <v>7.67555075701082e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>7.712085606176892e-05</v>
+        <v>7.712085606176906e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.342398859320104e-05</v>
+        <v>5.709900431597719e-05</v>
       </c>
       <c r="O5" t="n">
         <v>6.243056705486721e-05</v>
@@ -1491,28 +1491,28 @@
         <v>6.106296533089528e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.650578324550452e-05</v>
+        <v>4.65057832455046e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>7.685919612403893e-05</v>
+        <v>7.685919612403886e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.673522089610631e-05</v>
+        <v>7.673522089610645e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>7.67993513563605e-05</v>
+        <v>7.67993513563606e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.439182963107436e-05</v>
+        <v>6.43918296310744e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>6.99072901568671e-05</v>
+        <v>6.990729015686701e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>7.729070014021744e-05</v>
+        <v>7.729070014021746e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.870950053659759e-05</v>
+        <v>4.870950053659758e-05</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0001021635602998464</v>
@@ -1521,10 +1521,10 @@
         <v>5.101297308581894e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.692604254272894e-05</v>
+        <v>7.692604254272903e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000103499723161762</v>
+        <v>0.0001034997231617619</v>
       </c>
     </row>
     <row r="6">
@@ -1534,49 +1534,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.337579328487219e-05</v>
+        <v>3.337579328487216e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.911406339047587e-05</v>
+        <v>3.911406339047582e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.958598818426872e-05</v>
+        <v>3.958598818426865e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.781540396944462e-05</v>
+        <v>3.781540396944458e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.538223058619678e-05</v>
+        <v>2.538223058619677e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.970895122225344e-05</v>
+        <v>3.970895122225338e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.939612756498342e-05</v>
+        <v>3.939612756498341e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.952246816186936e-05</v>
+        <v>3.952246816186932e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.946589324721243e-05</v>
+        <v>3.946589324721242e-05</v>
       </c>
       <c r="K6" t="n">
         <v>3.928226990765263e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.929998399227292e-05</v>
+        <v>3.929998399227287e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.966533248393411e-05</v>
+        <v>3.966533248393405e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.342398859320104e-05</v>
+        <v>3.924094160104511e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.116958307204283e-05</v>
+        <v>4.116958307204278e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.155329858480716e-05</v>
+        <v>4.155329858480715e-05</v>
       </c>
       <c r="Q6" t="n">
         <v>3.930025795948192e-05</v>
@@ -1585,34 +1585,34 @@
         <v>3.94036725462036e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.92796973182711e-05</v>
+        <v>3.927969731827108e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.934382777852534e-05</v>
+        <v>3.934382777852535e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.927484594117738e-05</v>
+        <v>3.927484594117733e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.626423962634282e-05</v>
+        <v>4.626423962634276e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>3.983020800132769e-05</v>
+        <v>3.983020800132764e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>3.918686716930866e-05</v>
+        <v>3.918686716930861e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.956930444890774e-05</v>
+        <v>3.956930444890773e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>3.570167196108077e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.947051896489384e-05</v>
+        <v>3.947051896489376e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.963546603059544e-05</v>
+        <v>3.963546603059539e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1778,28 +1778,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.34093640302311e-05</v>
+        <v>1.340936403023112e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.348262044315815e-05</v>
+        <v>1.348262044315818e-05</v>
       </c>
       <c r="D2" t="n">
         <v>1.341579283206174e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.340318116955506e-05</v>
+        <v>1.340318116955507e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.34009220849298e-05</v>
+        <v>1.340092208492976e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.342019768564219e-05</v>
+        <v>1.342019768564218e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.34039513621197e-05</v>
+        <v>1.340395136211974e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.340325556663912e-05</v>
+        <v>1.34032555666391e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.341335491260775e-05</v>
@@ -1808,55 +1808,55 @@
         <v>1.341070790402086e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.340709835249206e-05</v>
+        <v>1.340709835249224e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.340967498114833e-05</v>
+        <v>1.340967498114835e-05</v>
       </c>
       <c r="N2" t="n">
         <v>1.340954051986062e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.490981444530202e-05</v>
+        <v>1.490981444530203e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.340576168139252e-05</v>
+        <v>1.340576168139247e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.34081611406e-05</v>
+        <v>1.340816114060001e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.341038792529185e-05</v>
+        <v>1.341038792529182e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.341060584398964e-05</v>
+        <v>1.34106058439897e-05</v>
       </c>
       <c r="T2" t="n">
         <v>1.341007932039401e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.391389491907317e-05</v>
+        <v>1.391389491907321e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.340936073452053e-05</v>
+        <v>1.340936073452052e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.398233173969563e-05</v>
+        <v>1.398233173969567e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341128345035364e-05</v>
+        <v>1.34112834503537e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.341371069420507e-05</v>
+        <v>1.341371069420505e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.37487882116953e-05</v>
+        <v>1.374878821169533e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.341103720685335e-05</v>
+        <v>1.341103720685338e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.341517600347018e-05</v>
+        <v>1.341517600347023e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.446856071183652e-05</v>
+        <v>1.394984900789742e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.433146596283574e-05</v>
+        <v>1.398302115022359e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.46262377682025e-05</v>
+        <v>1.39965177095731e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.37045233433251e-05</v>
+        <v>1.341760052148484e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.428483257479465e-05</v>
+        <v>1.390446672959678e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.471688230395728e-05</v>
+        <v>1.402239226199437e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.435640734180284e-05</v>
+        <v>1.392690337860709e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.433476600394518e-05</v>
+        <v>1.389746063874995e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.45535861891315e-05</v>
+        <v>1.397428051016615e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.451621495136849e-05</v>
+        <v>1.402738269915093e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.441653787910165e-05</v>
+        <v>1.390955989860132e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.455538119349469e-05</v>
+        <v>1.399447518382723e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.447741857704388e-05</v>
+        <v>1.394122566174021e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.589671944782905e-05</v>
+        <v>1.545030785518304e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.438084855651715e-05</v>
+        <v>1.389252400949156e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.444712200431915e-05</v>
+        <v>1.393728131637214e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.450327215905851e-05</v>
+        <v>1.396007180806433e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.449814942915934e-05</v>
+        <v>1.395400244394188e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.449418269580362e-05</v>
+        <v>1.395738955442021e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.508588883302301e-05</v>
+        <v>1.44820685895682e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.447710566535241e-05</v>
+        <v>1.399807823196745e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.533291904755732e-05</v>
+        <v>1.459718957891042e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.452137390365892e-05</v>
+        <v>1.396727371927944e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.457568599289959e-05</v>
+        <v>1.399277690004622e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.485485086644312e-05</v>
+        <v>1.42875012483212e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.451099446213784e-05</v>
+        <v>1.39547545307693e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.470004633833164e-05</v>
+        <v>1.405116761099823e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.364196493280563e-05</v>
+        <v>4.364196493282129e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.365788446439401e-05</v>
+        <v>4.365788446439407e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>4.465492732421397e-05</v>
+        <v>4.465492732421401e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.843797351509514e-05</v>
+        <v>1.84379735151042e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.343588959938981e-05</v>
+        <v>4.343588959939002e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.493154443932379e-05</v>
+        <v>4.493154443932439e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.39503139299618e-05</v>
+        <v>4.395031392996199e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.206483604763891e-05</v>
+        <v>4.206483604763906e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.394859953940356e-05</v>
+        <v>4.394859953940347e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.878504404722203e-05</v>
+        <v>4.878504404722359e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.153593772474603e-05</v>
+        <v>4.153593772482783e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.588389300908378e-05</v>
+        <v>4.588389300908392e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.293813936921936e-05</v>
+        <v>4.293813936922021e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.464896777981321e-05</v>
+        <v>4.464896777981325e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.079399711797674e-05</v>
+        <v>4.07939971179764e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.315869839894414e-05</v>
+        <v>4.315869839894745e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.399145836104361e-05</v>
+        <v>4.399145836104384e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.348363549695635e-05</v>
+        <v>4.348363549695729e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.391302379863554e-05</v>
+        <v>4.391302379863735e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.417164105589426e-05</v>
+        <v>4.417164105589443e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.710692631314344e-05</v>
+        <v>4.710692631314335e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.519256400988706e-05</v>
+        <v>4.519256400988671e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.419018661067255e-05</v>
+        <v>4.41901866106773e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.515761206922607e-05</v>
+        <v>4.515761206922598e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.286106109041091e-05</v>
+        <v>4.286106109042256e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.337390612860923e-05</v>
+        <v>4.337390612861113e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.775375533503333e-05</v>
+        <v>4.775375533503347e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.395093710375515e-05</v>
+        <v>5.395093710375514e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>8.089214102868078e-05</v>
+        <v>8.089214102868065e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.107714835514994e-05</v>
+        <v>8.107714835514983e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.652945253022056e-05</v>
+        <v>6.6529452530221e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.807021536411075e-05</v>
+        <v>5.807021536411066e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.673664235935046e-05</v>
+        <v>8.673664235935029e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>8.094339350480926e-05</v>
+        <v>8.094339350480909e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>8.09355341747743e-05</v>
+        <v>8.093553417477402e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.103812253390471e-05</v>
+        <v>8.103812253390461e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.101971175374564e-05</v>
+        <v>8.101971175374559e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>8.097894020875212e-05</v>
+        <v>8.097894020875473e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>8.104151463315421e-05</v>
+        <v>8.104151463315395e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.293813936921936e-05</v>
+        <v>6.00354635386386e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.575814687606421e-05</v>
+        <v>6.575814687606398e-05</v>
       </c>
       <c r="P5" t="n">
         <v>6.434315187382563e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.862070102953323e-05</v>
+        <v>4.862070102953336e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>8.101609744680389e-05</v>
+        <v>8.101609744680378e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.101855893874302e-05</v>
+        <v>8.101855893874304e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>8.101261161251748e-05</v>
+        <v>8.101261161251751e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.785646768966543e-05</v>
+        <v>6.785646768966542e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>7.356206213640329e-05</v>
+        <v>7.356206213640313e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>8.115711909688029e-05</v>
+        <v>8.115711909688023e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.113548469351683e-05</v>
+        <v>5.113548469351692e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001079521565083655</v>
+        <v>0.0001079521565083653</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.347322090677656e-05</v>
+        <v>5.34732209067767e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.102343138072549e-05</v>
+        <v>8.102343138072538e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001093723060277518</v>
+        <v>0.0001093723060277514</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.698593892397392e-05</v>
+        <v>3.698593892397492e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.395696473485048e-05</v>
+        <v>4.395696473485053e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.414197206131968e-05</v>
+        <v>4.414197206131971e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.236469397769967e-05</v>
+        <v>4.23646939777001e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.764479073326193e-05</v>
+        <v>2.764479073326194e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.419172712381528e-05</v>
+        <v>4.419172712381539e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.400821721097892e-05</v>
+        <v>4.400821721097902e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.400035788094397e-05</v>
+        <v>4.400035788094411e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.41029462400744e-05</v>
+        <v>4.410294624007442e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.408453545991531e-05</v>
+        <v>4.408453545991546e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.404376391492183e-05</v>
+        <v>4.404376391492155e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.410633833932474e-05</v>
+        <v>4.410633833932481e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.293813936921936e-05</v>
+        <v>4.407134931880228e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.637843806680059e-05</v>
+        <v>4.637843806680055e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.688662782849804e-05</v>
+        <v>4.688662782849806e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.40557688104793e-05</v>
+        <v>4.405576881047939e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.408092115297356e-05</v>
+        <v>4.408092115297363e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.40833826449127e-05</v>
+        <v>4.408338264491261e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.407743531868728e-05</v>
+        <v>4.407743531868752e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.412593431763452e-05</v>
+        <v>4.412593431763459e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.219531177986906e-05</v>
+        <v>5.21953117798691e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.421662599154819e-05</v>
+        <v>4.421662599154825e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.409103652050841e-05</v>
+        <v>4.409103652050949e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.411845335639764e-05</v>
+        <v>4.411845335639774e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.982350360550773e-05</v>
+        <v>3.982350360550775e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.408825508689519e-05</v>
+        <v>4.408825508689532e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.417738759077471e-05</v>
+        <v>4.417738759077474e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2374,82 +2374,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.344549561464647e-05</v>
+        <v>1.34454956146465e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.352249402739239e-05</v>
+        <v>1.35224940273924e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.345498381017007e-05</v>
+        <v>1.345498381017011e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.344161402297618e-05</v>
+        <v>1.344161402297622e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343440127032414e-05</v>
+        <v>1.343440127032417e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.345308109440237e-05</v>
+        <v>1.34530810944024e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.343900223300974e-05</v>
+        <v>1.343900223300978e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.34506732979247e-05</v>
+        <v>1.345067329792474e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.344782070460531e-05</v>
+        <v>1.344782070460529e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.345440343725682e-05</v>
+        <v>1.345440343725686e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.344233973966822e-05</v>
+        <v>1.344233973966825e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344619767831636e-05</v>
+        <v>1.344619767831639e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.34424105073878e-05</v>
+        <v>1.344241050738784e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.497872954988995e-05</v>
+        <v>1.497872954988999e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343602809896704e-05</v>
+        <v>1.343602809896708e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.34409198672943e-05</v>
+        <v>1.344091986729435e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34422164664332e-05</v>
+        <v>1.344221646643324e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344606350094563e-05</v>
+        <v>1.344606350094567e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344626094961087e-05</v>
+        <v>1.344626094961092e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.396935976496947e-05</v>
+        <v>1.39693597649695e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344341663147083e-05</v>
+        <v>1.344341663147087e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.405186008317625e-05</v>
+        <v>1.405186008317627e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344375441390424e-05</v>
+        <v>1.344375441390428e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.344069231897628e-05</v>
+        <v>1.344069231897632e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.380058476910582e-05</v>
+        <v>1.380058476910584e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.344813730950968e-05</v>
+        <v>1.344813730950972e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>1.344903491833579e-05</v>
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.464248946612044e-05</v>
+        <v>1.401407505100048e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.453267246025014e-05</v>
+        <v>1.410443331865985e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.487683838492992e-05</v>
+        <v>1.411245524895252e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.392928634975236e-05</v>
+        <v>1.350750397189584e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.440223423157729e-05</v>
+        <v>1.397251587780151e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.482009187049282e-05</v>
+        <v>1.409217073570359e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.450869447659967e-05</v>
+        <v>1.399158898615098e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.477736555720023e-05</v>
+        <v>1.407550473628725e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.469520014989218e-05</v>
+        <v>1.405357044332328e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.487555130123784e-05</v>
+        <v>1.420995256550978e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.457327997124546e-05</v>
+        <v>1.398750971201708e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.47434554234057e-05</v>
+        <v>1.407670241148159e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.457868035077423e-05</v>
+        <v>1.399391902576011e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.596581098562541e-05</v>
+        <v>1.55261136385604e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.44230696919025e-05</v>
+        <v>1.393672480810061e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.454768177368336e-05</v>
+        <v>1.400279106154046e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.458080700160846e-05</v>
+        <v>1.400587075170503e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.465949370091348e-05</v>
+        <v>1.4033012781976e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.467290624148559e-05</v>
+        <v>1.40358821218871e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.513832519851387e-05</v>
+        <v>1.45472535100415e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.460678302041598e-05</v>
+        <v>1.407222749544127e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.561252779986401e-05</v>
+        <v>1.473186439881793e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.461410399181683e-05</v>
+        <v>1.402127552877266e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.45397861673022e-05</v>
+        <v>1.399584194818067e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.506037265156016e-05</v>
+        <v>1.442574198076869e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.471000951359749e-05</v>
+        <v>1.40391659426698e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.482597240938397e-05</v>
+        <v>1.41121628180406e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.171748838205324e-05</v>
+        <v>4.171748838205414e-05</v>
       </c>
       <c r="C4" t="n">
         <v>4.516025374015733e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>4.512529866881373e-05</v>
+        <v>4.512529866881381e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.949927426549222e-05</v>
+        <v>1.949927426549223e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.268663590993301e-05</v>
+        <v>4.268663590993305e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.441902980172195e-05</v>
+        <v>4.441902980172192e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.23994534569489e-05</v>
+        <v>4.239945345694893e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.409395382223041e-05</v>
+        <v>4.40939538222304e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.359664008930089e-05</v>
+        <v>4.359664008930098e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.194910901467402e-05</v>
+        <v>5.194910901467403e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.099005202940196e-05</v>
+        <v>4.099005202940189e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.488280366493076e-05</v>
+        <v>4.488280366493072e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.139652223361501e-05</v>
+        <v>4.139652223361498e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.296837949356344e-05</v>
+        <v>4.296837949356349e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.971307791683207e-05</v>
+        <v>3.97130779168321e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.25096264247095e-05</v>
+        <v>4.250962642470948e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.226751992288932e-05</v>
+        <v>4.226751992288933e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.280591650013481e-05</v>
+        <v>4.280591650013479e-05</v>
       </c>
       <c r="T4" t="n">
         <v>4.291972187575562e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.276864783496463e-05</v>
+        <v>4.276864783496462e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.632890836899261e-05</v>
+        <v>4.632890836899241e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.482659246380523e-05</v>
+        <v>4.482659246380434e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.279019166088569e-05</v>
+        <v>4.279019166088576e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.211870481442563e-05</v>
+        <v>4.21187048144256e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.484876127158361e-05</v>
+        <v>4.484876127158352e-05</v>
       </c>
       <c r="AA4" t="n">
         <v>4.250609782940144e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.609808538495139e-05</v>
+        <v>4.609808538495137e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2638,82 +2638,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.121309969772797e-05</v>
+        <v>5.121309969772815e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>7.634831390149111e-05</v>
+        <v>7.634831390149113e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.655999878438329e-05</v>
+        <v>7.655999878438333e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.296957155484693e-05</v>
+        <v>6.296957155484698e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.501983823381924e-05</v>
+        <v>5.501983823381925e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.177212824984257e-05</v>
+        <v>8.177212824984248e-05</v>
       </c>
       <c r="H5" t="n">
         <v>7.637947951846861e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.651130956563829e-05</v>
+        <v>7.651130956563835e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.646759784306794e-05</v>
+        <v>7.646759784306791e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.655344320534346e-05</v>
+        <v>7.655344320534345e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.641717819150505e-05</v>
+        <v>7.641717819150506e-05</v>
       </c>
       <c r="M5" t="n">
         <v>7.64946878986334e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.139652223361501e-05</v>
+        <v>5.685296772861284e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.215403670892209e-05</v>
+        <v>6.21540367089221e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.08395670160598e-05</v>
+        <v>6.083956701605986e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.620123238538318e-05</v>
+        <v>4.620123238538316e-05</v>
       </c>
       <c r="R5" t="n">
         <v>7.641578576360706e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.645923978814828e-05</v>
+        <v>7.645923978814832e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>7.64614700616532e-05</v>
+        <v>7.646147006165315e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.411658984630023e-05</v>
+        <v>6.411658984630026e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>6.948318122787046e-05</v>
+        <v>6.948318122787056e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>7.664038178174219e-05</v>
+        <v>7.664038178174226e-05</v>
       </c>
       <c r="X5" t="n">
         <v>4.854652089513921e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001014944056357762</v>
+        <v>0.0001014944056357763</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.077343179585288e-05</v>
+        <v>5.077343179585291e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.648266440987822e-05</v>
+        <v>7.648266440987827e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>0.0001029008744517881</v>
@@ -2726,67 +2726,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.405382736816174e-05</v>
+        <v>3.405382736816182e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.018951224644395e-05</v>
+        <v>4.018951224644393e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.040119712933618e-05</v>
+        <v>4.040119712933616e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.880996757236762e-05</v>
+        <v>3.880996757236763e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.578335215828491e-05</v>
+        <v>2.578335215828492e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.037970530813405e-05</v>
+        <v>4.037970530813408e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.022067786342143e-05</v>
+        <v>4.02206778634214e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.035250791059114e-05</v>
+        <v>4.035250791059109e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.030879618802075e-05</v>
+        <v>4.030879618802073e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.039464155029629e-05</v>
+        <v>4.039464155029625e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.025837653645789e-05</v>
+        <v>4.025837653645788e-05</v>
       </c>
       <c r="M6" t="n">
         <v>4.0335886243587e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.139652223361501e-05</v>
+        <v>4.025917589040536e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.225160345411406e-05</v>
+        <v>4.22516034541141e-05</v>
       </c>
       <c r="P6" t="n">
         <v>4.270482979736961e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.024233865350765e-05</v>
+        <v>4.024233865350768e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.025698410855992e-05</v>
+        <v>4.025698410855993e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.030043813310112e-05</v>
+        <v>4.030043813310111e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.030266840660598e-05</v>
+        <v>4.030266840660596e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.027663915876573e-05</v>
+        <v>4.02766391587657e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.742347449394616e-05</v>
+        <v>4.742347449394635e-05</v>
       </c>
       <c r="W6" t="n">
         <v>4.047661979288994e-05</v>
@@ -2798,13 +2798,13 @@
         <v>4.023976816189139e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.65609132201084e-05</v>
+        <v>3.656091322010846e-05</v>
       </c>
       <c r="AA6" t="n">
         <v>4.032386275483107e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.037706894047348e-05</v>
+        <v>4.037706894047346e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.346646534323775e-05</v>
+        <v>1.346646534323774e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.354427162869863e-05</v>
+        <v>1.354427162869861e-05</v>
       </c>
       <c r="D2" t="n">
         <v>1.348703839268192e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3463467666707e-05</v>
+        <v>1.346346766670696e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.345610667764809e-05</v>
+        <v>1.345610667764805e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.34770302243533e-05</v>
+        <v>1.347703022435328e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.346418562379769e-05</v>
+        <v>1.346418562379764e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.347616680352301e-05</v>
+        <v>1.347616680352299e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.347070470683227e-05</v>
+        <v>1.347070470683224e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.347229082348234e-05</v>
+        <v>1.347229082348231e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.346159624192127e-05</v>
+        <v>1.346159624192124e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.346913236361161e-05</v>
+        <v>1.346913236361158e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.346170647934244e-05</v>
+        <v>1.346170647934242e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.502315025457429e-05</v>
+        <v>1.502315025457425e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.345855546216597e-05</v>
+        <v>1.345855546216594e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.345996766172561e-05</v>
+        <v>1.345996766172559e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.346338316605255e-05</v>
+        <v>1.346338316605253e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.346511262395807e-05</v>
+        <v>1.346511262395805e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.347095383797871e-05</v>
+        <v>1.347095383797868e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.400463400857542e-05</v>
+        <v>1.400463400857539e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34678582075975e-05</v>
+        <v>1.346785820759748e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.409756556424011e-05</v>
+        <v>1.409756556424007e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.346372978005449e-05</v>
+        <v>1.346372978005448e-05</v>
       </c>
       <c r="Y2" t="n">
         <v>1.34649427108712e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.383063190864565e-05</v>
+        <v>1.383063190864563e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.347610487970078e-05</v>
+        <v>1.347610487970077e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.347347130865085e-05</v>
+        <v>1.347347130865083e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.468648937330069e-05</v>
+        <v>1.406293069920839e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.455994895568946e-05</v>
+        <v>1.413180513110556e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.518206060242189e-05</v>
+        <v>1.426804708567515e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.399478443763431e-05</v>
+        <v>1.359287033719221e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.44613242597769e-05</v>
+        <v>1.400808296229881e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.493390224755106e-05</v>
+        <v>1.417313504921317e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.464847809308737e-05</v>
+        <v>1.404802381300649e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.492679360165737e-05</v>
+        <v>1.415622485827505e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.47856581488049e-05</v>
+        <v>1.411763730759864e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.484447882711351e-05</v>
+        <v>1.420736261636503e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.457986529514285e-05</v>
+        <v>1.403909515655077e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.483685272158568e-05</v>
+        <v>1.416072129374017e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.458059091702565e-05</v>
+        <v>1.400359513046235e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.612526220232636e-05</v>
+        <v>1.560005452844451e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.450371015098192e-05</v>
+        <v>1.40043028537045e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.454590544226021e-05</v>
+        <v>1.402657255008299e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.462666590300349e-05</v>
+        <v>1.403257036717122e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.465717820037583e-05</v>
+        <v>1.405131213336194e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.480086658261263e-05</v>
+        <v>1.408989598688809e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.520996368653706e-05</v>
+        <v>1.462445711631888e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47286096663073e-05</v>
+        <v>1.41309119326689e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.587323477535873e-05</v>
+        <v>1.484141080854996e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.463482662055723e-05</v>
+        <v>1.405936131764457e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.465424228472149e-05</v>
+        <v>1.402591078524693e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.513733440204696e-05</v>
+        <v>1.449908866445316e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.491266125590806e-05</v>
+        <v>1.411415985832022e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.494911592029458e-05</v>
+        <v>1.417373158144016e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3146,40 +3146,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.358625612140882e-05</v>
+        <v>4.358625612140884e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.570608664502567e-05</v>
+        <v>4.570608664502574e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>5.043603836092108e-05</v>
+        <v>5.043603836092123e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.377278034379563e-05</v>
+        <v>2.377278034379567e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.339935286563197e-05</v>
+        <v>4.339935286563196e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.744654887723111e-05</v>
+        <v>4.744654887722748e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.333416862409294e-05</v>
+        <v>4.333416862409284e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.657245214053674e-05</v>
+        <v>4.657245214053691e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.583828503393554e-05</v>
+        <v>4.583828503393534e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.138165582454346e-05</v>
+        <v>5.138165582454349e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.363216506267368e-05</v>
+        <v>4.363216506267369e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.84576424881656e-05</v>
+        <v>4.845764248816563e-05</v>
       </c>
       <c r="N4" t="n">
         <v>4.117839694573047e-05</v>
@@ -3188,43 +3188,43 @@
         <v>4.375202973435693e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.231931467288276e-05</v>
+        <v>4.231931467288277e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.333490085396966e-05</v>
+        <v>4.333490085396968e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.256305675169714e-05</v>
+        <v>4.256305675169709e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.325811955108362e-05</v>
+        <v>4.325811955108363e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.385937427031977e-05</v>
+        <v>4.385937427031986e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.544340397386281e-05</v>
+        <v>4.544340397386265e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.767398941133752e-05</v>
+        <v>4.767398941133816e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.671551753422199e-05</v>
+        <v>4.671551753422198e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.426853726901707e-05</v>
+        <v>4.426853726901699e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.158463071843221e-05</v>
+        <v>4.158463071843228e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.748035513070721e-05</v>
+        <v>4.748035513070723e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.374750122028837e-05</v>
+        <v>4.374750122028842e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.763981162399734e-05</v>
+        <v>4.763981162399741e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3234,28 +3234,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.126956091201825e-05</v>
+        <v>5.126956091201838e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>7.641117276392214e-05</v>
+        <v>7.641117276392221e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.675592336669152e-05</v>
+        <v>7.67559233666916e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.304268155718411e-05</v>
+        <v>6.304268155718413e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.508683001586613e-05</v>
+        <v>5.508683001586623e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.187945385148442e-05</v>
+        <v>8.187945385148436e-05</v>
       </c>
       <c r="H5" t="n">
         <v>7.649779082935084e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.663312376596352e-05</v>
+        <v>7.663312376596351e-05</v>
       </c>
       <c r="J5" t="n">
         <v>7.655994492845388e-05</v>
@@ -3264,52 +3264,52 @@
         <v>7.658934278836508e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.646854256988216e-05</v>
+        <v>7.646854256988217e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>7.658787384205983e-05</v>
+        <v>7.658787384205976e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.117839694573047e-05</v>
+        <v>5.689372804676499e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.226584532338329e-05</v>
+        <v>6.226584532338319e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.091911964482367e-05</v>
+        <v>6.091911964482353e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.623318306706807e-05</v>
+        <v>4.623318306706802e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>7.648872669997087e-05</v>
+        <v>7.648872669997095e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.650826172260371e-05</v>
+        <v>7.650826172260373e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>7.65742409220579e-05</v>
+        <v>7.657424092205789e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.418703044038944e-05</v>
+        <v>6.418703044038954e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>6.958996309552857e-05</v>
+        <v>6.958996309552849e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>7.681044029597486e-05</v>
+        <v>7.681044029597476e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.859025541082714e-05</v>
+        <v>4.859025541082719e-05</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0001016174099850623</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.084129062956028e-05</v>
+        <v>5.084129062956024e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.663242430790505e-05</v>
+        <v>7.663242430790513e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>0.0001030256086449559</v>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.304191872510964e-05</v>
+        <v>3.304191872510958e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.888048775286316e-05</v>
+        <v>3.888048775286309e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.92252383556326e-05</v>
+        <v>3.922523835563251e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.758554423442657e-05</v>
+        <v>3.758554423442662e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.515731481166712e-05</v>
+        <v>2.515731481166703e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.911219173759572e-05</v>
+        <v>3.911219173759579e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.896710581829182e-05</v>
+        <v>3.896710581829181e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.910243875490448e-05</v>
+        <v>3.910243875490449e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.902925991739485e-05</v>
+        <v>3.902925991739483e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.905865777730604e-05</v>
+        <v>3.905865777730598e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.893785755882304e-05</v>
+        <v>3.893785755882309e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.905718883100122e-05</v>
+        <v>3.905718883100125e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.117839694573047e-05</v>
+        <v>3.893910274120712e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.090368208106093e-05</v>
+        <v>4.090368208106076e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.13045488931328e-05</v>
+        <v>4.130454889313274e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.891946224354956e-05</v>
+        <v>3.891946224354961e-05</v>
       </c>
       <c r="R6" t="n">
         <v>3.895804168891187e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.897757671154455e-05</v>
+        <v>3.897757671154462e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.904355591099887e-05</v>
+        <v>3.904355591099882e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.898153529126537e-05</v>
+        <v>3.898153529126527e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.582778832418775e-05</v>
+        <v>4.582778832418762e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>3.927479214965489e-05</v>
+        <v>3.927479214965486e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>3.89619568535142e-05</v>
+        <v>3.896195685351414e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.897565746506458e-05</v>
+        <v>3.897565746506457e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.54458055869684e-05</v>
+        <v>3.544580558696833e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.910173929684597e-05</v>
+        <v>3.910173929684604e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.911502940143479e-05</v>
+        <v>3.911502940143465e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3566,85 +3566,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.345369871715872e-05</v>
+        <v>1.345369871715867e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.351849681435858e-05</v>
+        <v>1.351849681435854e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347250452342799e-05</v>
+        <v>1.347250452342795e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.34350212214354e-05</v>
+        <v>1.343502122143536e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.343592770667738e-05</v>
+        <v>1.343592770667736e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.346024080263276e-05</v>
+        <v>1.346024080263272e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.345343462831853e-05</v>
+        <v>1.345343462831849e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.343808270658375e-05</v>
+        <v>1.343808270658372e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.345018792875421e-05</v>
+        <v>1.345018792875418e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.344724803683535e-05</v>
+        <v>1.344724803683532e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.345041867541866e-05</v>
+        <v>1.345041867541863e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.344290425386709e-05</v>
+        <v>1.344290425386706e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.344324982859847e-05</v>
+        <v>1.344324982859843e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.49597520437794e-05</v>
+        <v>1.495975204377938e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.343841496155347e-05</v>
+        <v>1.343841496155345e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.344656245419344e-05</v>
+        <v>1.344656245419341e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.344867948096997e-05</v>
+        <v>1.344867948096995e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.344603506167151e-05</v>
+        <v>1.344603506167147e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.344441662817759e-05</v>
+        <v>1.344441662817755e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.395498874058912e-05</v>
+        <v>1.395498874058907e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.344508282105598e-05</v>
+        <v>1.344508282105595e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.40329916210145e-05</v>
+        <v>1.403299162101448e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.344493328019819e-05</v>
+        <v>1.344493328019816e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.34457567402858e-05</v>
+        <v>1.344575674028577e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.379697950221668e-05</v>
+        <v>1.379697950221664e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.344441058990461e-05</v>
+        <v>1.344441058990458e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.344725206838598e-05</v>
+        <v>1.344725206838595e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.480001142458392e-05</v>
+        <v>1.408311091292377e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.438327898813451e-05</v>
+        <v>1.402287063247216e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.525201868207528e-05</v>
+        <v>1.424370080519551e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.374298547806949e-05</v>
+        <v>1.344140924276291e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.440385635367408e-05</v>
+        <v>1.3971935514955e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.496140453888449e-05</v>
+        <v>1.421226259377883e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.481438771343451e-05</v>
+        <v>1.410540353019182e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.444949554727959e-05</v>
+        <v>1.396423871570593e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.471805387937949e-05</v>
+        <v>1.40961948097065e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.467306658547099e-05</v>
+        <v>1.412646281927481e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.474149905175522e-05</v>
+        <v>1.415316196339136e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.464762169659619e-05</v>
+        <v>1.41413782020113e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.456612638939116e-05</v>
+        <v>1.40020838243195e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.596267385436882e-05</v>
+        <v>1.551260974192977e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.444347856610546e-05</v>
+        <v>1.393648022847941e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.464659349056543e-05</v>
+        <v>1.404669811294982e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.469745204537508e-05</v>
+        <v>1.404121887266894e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.463551083392752e-05</v>
+        <v>1.409971989468229e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.460306771782078e-05</v>
+        <v>1.406353500406741e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.509700033469054e-05</v>
+        <v>1.453367636926499e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.460990988506583e-05</v>
+        <v>1.406054748033897e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.551636971423489e-05</v>
+        <v>1.468266092294777e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.460752840337399e-05</v>
+        <v>1.401750640094419e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.462365068633256e-05</v>
+        <v>1.402481455023835e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.503371966362182e-05</v>
+        <v>1.44106914517991e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.458958165272518e-05</v>
+        <v>1.399615290982203e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.475467069506123e-05</v>
+        <v>1.410530787033752e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.69553843517709e-05</v>
+        <v>4.695538435177081e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.442541761241062e-05</v>
+        <v>4.442541761241055e-05</v>
       </c>
       <c r="D4" t="n">
         <v>5.169383346767041e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.869893705834227e-05</v>
+        <v>1.869893705834217e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.53934197061298e-05</v>
+        <v>4.539341970612978e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>5.395522611752535e-05</v>
+        <v>5.395522611752526e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.864946540707719e-05</v>
+        <v>4.864946540707712e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.403833644653552e-05</v>
+        <v>4.403833644653547e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.920384765189005e-05</v>
+        <v>4.920384765188994e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.248083353420991e-05</v>
+        <v>5.248083353420985e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.326505212749367e-05</v>
+        <v>5.326505212749358e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.425309542861053e-05</v>
+        <v>5.42530954286104e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.489367678312361e-05</v>
+        <v>4.489367678312359e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.603853183287429e-05</v>
+        <v>4.603853183287425e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.190815375647919e-05</v>
+        <v>4.190815375647918e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.692066011730681e-05</v>
+        <v>4.692066011730672e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.57317409462444e-05</v>
+        <v>4.573174094624427e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>5.099108616487401e-05</v>
+        <v>5.099108616487396e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.893747878710676e-05</v>
+        <v>4.893747878710669e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.606647800487501e-05</v>
+        <v>4.606647800487502e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.843757956271129e-05</v>
+        <v>4.843757956271079e-05</v>
       </c>
       <c r="W4" t="n">
         <v>4.66349923338816e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.53928494783814e-05</v>
+        <v>4.539284947838136e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.562658907223992e-05</v>
+        <v>4.562658907223983e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.732685272815251e-05</v>
+        <v>4.732685272815241e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.403511976993201e-05</v>
+        <v>4.4035119769932e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.978152919314817e-05</v>
+        <v>4.978152919314811e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3830,85 +3830,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.414293887413328e-05</v>
+        <v>5.41429388741332e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>8.095823663478399e-05</v>
+        <v>8.095823663478363e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.142217657596805e-05</v>
+        <v>8.14221765759678e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.65865035547998e-05</v>
+        <v>6.658650355479967e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.815890096134933e-05</v>
+        <v>5.815890096134919e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.689613313443886e-05</v>
+        <v>8.689613313443856e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>8.120677333812152e-05</v>
+        <v>8.120677333812126e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>8.103336631989429e-05</v>
+        <v>8.1033366319894e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.115857707444714e-05</v>
+        <v>8.11585770744471e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.113689294134632e-05</v>
+        <v>8.113689294134623e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>8.117270676271055e-05</v>
+        <v>8.117270676271033e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>8.112265408822182e-05</v>
+        <v>8.112265408822144e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.489367678312361e-05</v>
+        <v>6.011041962296988e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.581643517974178e-05</v>
+        <v>6.581643517974166e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.440830588147465e-05</v>
+        <v>6.440830588147458e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.874308409724393e-05</v>
+        <v>4.874308409724377e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>8.115306176134375e-05</v>
+        <v>8.115306176134364e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.112319182887452e-05</v>
+        <v>8.112319182887436e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>8.11049108780446e-05</v>
+        <v>8.110491087804441e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.789237260114271e-05</v>
+        <v>6.789237260114248e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>7.366731413486563e-05</v>
+        <v>7.366731413486547e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>8.128318354569095e-05</v>
+        <v>8.12831835456908e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.120540943408623e-05</v>
+        <v>5.12054094340861e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001080335177920786</v>
+        <v>0.0001080335177920785</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.35822873258891e-05</v>
+        <v>5.3582287325889e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.11048426729735e-05</v>
+        <v>8.110484267297338e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001094544424010557</v>
+        <v>0.0001094544424010553</v>
       </c>
     </row>
     <row r="6">
@@ -3918,85 +3918,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.721126398642135e-05</v>
+        <v>3.721126398642131e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.40581319382746e-05</v>
+        <v>4.405813193827455e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.452207187945873e-05</v>
+        <v>4.45220718794587e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.246040203766008e-05</v>
+        <v>4.246040203766006e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.774519865194975e-05</v>
+        <v>2.77451986519497e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.438354779169849e-05</v>
+        <v>4.438354779169846e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.43066686416121e-05</v>
+        <v>4.430666864161209e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.413326162338484e-05</v>
+        <v>4.413326162338478e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.425847237793783e-05</v>
+        <v>4.425847237793778e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.423678824483698e-05</v>
+        <v>4.423678824483694e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.427260206620121e-05</v>
+        <v>4.427260206620118e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.422254939171344e-05</v>
+        <v>4.422254939171337e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.489367678312361e-05</v>
+        <v>4.419162664353467e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.648419230933135e-05</v>
+        <v>4.648419230933136e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.700101721686203e-05</v>
+        <v>4.700101721686198e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.42290445537252e-05</v>
+        <v>4.422904455372523e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.425295706483438e-05</v>
+        <v>4.425295706483431e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.422308713236515e-05</v>
+        <v>4.422308713236509e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.420480618153522e-05</v>
+        <v>4.420480618153519e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.42023146614105e-05</v>
+        <v>4.420231466141045e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.235536735472805e-05</v>
+        <v>5.235536735472803e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.437775943913948e-05</v>
+        <v>4.43777594391394e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.421064200377953e-05</v>
+        <v>4.421064200377952e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.421994336427951e-05</v>
+        <v>4.421994336427947e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.997208369476591e-05</v>
+        <v>3.997208369476594e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.420473797646414e-05</v>
+        <v>4.42047379764641e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.428078356333032e-05</v>
+        <v>4.428078356333028e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.352121995051133e-05</v>
+        <v>1.352121995051127e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.358725930836e-05</v>
+        <v>1.358725930835998e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.35429665387745e-05</v>
+        <v>1.354296653877445e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.350869081668346e-05</v>
+        <v>1.35086908166834e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.350357741257589e-05</v>
+        <v>1.350357741257586e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.353411392557185e-05</v>
+        <v>1.353411392557179e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.352093872982524e-05</v>
+        <v>1.352093872982518e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.353017894316746e-05</v>
+        <v>1.353017894316741e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35231554273561e-05</v>
+        <v>1.352315542735608e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.35431025300832e-05</v>
+        <v>1.354310253008314e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.353764838385756e-05</v>
+        <v>1.353764838385752e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.353407008467978e-05</v>
+        <v>1.353407008467977e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.350850841927279e-05</v>
+        <v>1.350850841927273e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.506979605397168e-05</v>
+        <v>1.506979605397161e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.350113996104936e-05</v>
+        <v>1.35011399610493e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.351643658182055e-05</v>
+        <v>1.351643658182048e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.352220123850125e-05</v>
+        <v>1.352220123850119e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.351364748047675e-05</v>
+        <v>1.35136474804767e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.351383719726321e-05</v>
+        <v>1.351383719726319e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.405585626844413e-05</v>
+        <v>1.405585626844405e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.351523895697731e-05</v>
+        <v>1.351523895697726e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41409082168165e-05</v>
+        <v>1.414090821681641e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.350350364852785e-05</v>
+        <v>1.35035036485278e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.352280787480035e-05</v>
+        <v>1.352280787480031e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.388952571821222e-05</v>
+        <v>1.388952571821215e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.352962214728454e-05</v>
+        <v>1.352962214728449e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.352368097215413e-05</v>
+        <v>1.352368097215411e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.510821745611204e-05</v>
+        <v>1.420920726102873e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.466250496439198e-05</v>
+        <v>1.418725303889965e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.564173659746338e-05</v>
+        <v>1.446869704677113e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.419042838201955e-05</v>
+        <v>1.363028684059638e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.47231807082228e-05</v>
+        <v>1.413041169400418e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.542061401519401e-05</v>
+        <v>1.442272736525215e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.513089732056023e-05</v>
+        <v>1.426441866804399e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.534177506596768e-05</v>
+        <v>1.433738022207547e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.516119376586254e-05</v>
+        <v>1.430490107586925e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.564815439064189e-05</v>
+        <v>1.450918137243438e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.551841696077756e-05</v>
+        <v>1.452056026698997e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.551858360088822e-05</v>
+        <v>1.452307650908852e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.482729652026548e-05</v>
+        <v>1.41357871653776e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.61639681507404e-05</v>
+        <v>1.564968885637348e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.464477345014738e-05</v>
+        <v>1.405380165851042e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.50197027444324e-05</v>
+        <v>1.424954413853637e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.515675053851529e-05</v>
+        <v>1.426787708680764e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.494653419652908e-05</v>
+        <v>1.422738096519237e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.496409286460101e-05</v>
+        <v>1.424551572109288e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.547103804016387e-05</v>
+        <v>1.482011693370663e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.498375068298795e-05</v>
+        <v>1.424203161382945e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.593826872164821e-05</v>
+        <v>1.494277921843539e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.47172710385619e-05</v>
+        <v>1.412791064393073e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.515536229940767e-05</v>
+        <v>1.42297394738793e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.542161971719301e-05</v>
+        <v>1.459638351756458e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.53121594486068e-05</v>
+        <v>1.427990759243087e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.52787593211149e-05</v>
+        <v>1.43421212854452e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4338,82 +4338,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.57822416168973e-05</v>
+        <v>4.578224161689734e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.640776041028932e-05</v>
+        <v>4.640776041028919e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>5.591512338005127e-05</v>
+        <v>5.591512338005117e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.206841904954584e-05</v>
+        <v>2.206841904954579e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.646227326798428e-05</v>
+        <v>4.646227326798418e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>5.58610553355673e-05</v>
+        <v>5.586105533556733e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.959583112807895e-05</v>
+        <v>4.959583112807892e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.138467470393029e-05</v>
+        <v>5.138467470393006e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>5.161014392506067e-05</v>
+        <v>5.161014392506065e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.862133182264856e-05</v>
+        <v>5.862133182264853e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>6.128280481818878e-05</v>
+        <v>6.128280481818875e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.184482715387988e-05</v>
+        <v>6.184482715387984e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.514341788816634e-05</v>
+        <v>4.51434178881663e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.466409031622838e-05</v>
+        <v>4.466409031622832e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.211730936601618e-05</v>
+        <v>4.21173093660161e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.014576867337115e-05</v>
+        <v>5.01457686733712e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.94012447613939e-05</v>
+        <v>4.940124476139391e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.961089018006327e-05</v>
+        <v>4.96108901800632e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>5.076072352939736e-05</v>
+        <v>5.076072352939729e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.337958028375696e-05</v>
+        <v>5.33795802837569e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.001102079096685e-05</v>
+        <v>5.001102079096659e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>5.107590698724724e-05</v>
+        <v>5.107590698724707e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.632377592616917e-05</v>
+        <v>4.632377592616911e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.661750115285713e-05</v>
+        <v>4.661750115285676e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.782298261029235e-05</v>
+        <v>4.782298261029228e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.768687622496439e-05</v>
+        <v>4.768687622496438e-05</v>
       </c>
       <c r="AB4" t="n">
         <v>5.287197255201629e-05</v>
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.15010949447278e-05</v>
+        <v>5.150109494472764e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>7.649671405566588e-05</v>
+        <v>7.64967140556656e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.70138782165151e-05</v>
+        <v>7.701387821651487e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.317270849396965e-05</v>
+        <v>6.317270849396942e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.523814033716646e-05</v>
+        <v>5.523814033716632e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.215319110895365e-05</v>
+        <v>8.215319110895318e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>7.676506398114055e-05</v>
+        <v>7.676506398114017e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.686943644154878e-05</v>
+        <v>7.686943644154854e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.677856327321239e-05</v>
+        <v>7.677856327321204e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.701541430090593e-05</v>
+        <v>7.701541430090557e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.69538072102563e-05</v>
+        <v>7.695380721025599e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>7.694670525269999e-05</v>
+        <v>7.694670525269971e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.514341788816634e-05</v>
+        <v>5.703839300109651e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.230898883725456e-05</v>
+        <v>6.230898883725432e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.101826369445558e-05</v>
+        <v>6.101826369445542e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.648149379804793e-05</v>
+        <v>4.648149379804776e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>7.677932459741865e-05</v>
+        <v>7.677932459741827e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.668270596560872e-05</v>
+        <v>7.668270596560848e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>7.668484890398618e-05</v>
+        <v>7.668484890398586e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.43373855149031e-05</v>
+        <v>6.433738551490288e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>6.974762615495266e-05</v>
+        <v>6.974762615495243e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>7.687288952238996e-05</v>
+        <v>7.687288952238968e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.865119446633164e-05</v>
+        <v>4.865119446633144e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001019107074517909</v>
+        <v>0.0001019107074517905</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.100052737852378e-05</v>
+        <v>5.100052737852353e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.686314717591262e-05</v>
+        <v>7.686314717591234e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001032335386401809</v>
+        <v>0.0001032335386401805</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.440230656864652e-05</v>
+        <v>3.440230656864649e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.039963812585545e-05</v>
+        <v>4.039963812585538e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.091680228670478e-05</v>
+        <v>4.091680228670462e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.908281557722201e-05</v>
+        <v>3.908281557722191e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.602045503205569e-05</v>
+        <v>2.602045503205565e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.081680820203979e-05</v>
+        <v>4.081680820203954e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.066798805133012e-05</v>
+        <v>4.066798805133001e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.077236051173838e-05</v>
+        <v>4.077236051173834e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.068148734340193e-05</v>
+        <v>4.068148734340188e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.091833837109558e-05</v>
+        <v>4.091833837109548e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.08567312804459e-05</v>
+        <v>4.085673128044573e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.084962932288979e-05</v>
+        <v>4.084962932288974e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.514341788816634e-05</v>
+        <v>4.052758197541477e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2493193819627e-05</v>
+        <v>4.249319381962689e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.297366226026273e-05</v>
+        <v>4.297366226026262e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.061713447238881e-05</v>
+        <v>4.06171344723888e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.068224866760823e-05</v>
+        <v>4.068224866760807e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.058563003579838e-05</v>
+        <v>4.058563003579828e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.05877729741757e-05</v>
+        <v>4.058777297417566e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.057170697395341e-05</v>
+        <v>4.057170697395334e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.778929139244536e-05</v>
+        <v>4.778929139244523e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.077084787005236e-05</v>
+        <v>4.07708478700523e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.047105078754237e-05</v>
+        <v>4.047105078754234e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.068910090367307e-05</v>
+        <v>4.068910090367296e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.686038337891889e-05</v>
+        <v>3.686038337891882e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.076607124610219e-05</v>
+        <v>4.076607124610217e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.074281637137029e-05</v>
+        <v>4.074281637137017e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.358191623446902e-05</v>
+        <v>1.358191623446896e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.364615534097097e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.359350600692688e-05</v>
+        <v>1.359350600692685e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.357255822292615e-05</v>
+        <v>1.357255822292612e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.355852964040299e-05</v>
+        <v>1.355852964040296e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.36342081049685e-05</v>
+        <v>1.363420810496849e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.358049621165298e-05</v>
+        <v>1.358049621165295e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.358896187974664e-05</v>
+        <v>1.358896187974668e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.359425353385229e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.360416419635229e-05</v>
+        <v>1.360416419635225e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.358771706868763e-05</v>
+        <v>1.358771706868761e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.360136814695856e-05</v>
+        <v>1.360136814695857e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.356578565269324e-05</v>
+        <v>1.356578565269328e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.515994446452492e-05</v>
+        <v>1.515994446452488e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.355734898644985e-05</v>
+        <v>1.355734898644997e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.357400876572289e-05</v>
+        <v>1.357400876572285e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35814266529415e-05</v>
+        <v>1.358142665294147e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.356480281357142e-05</v>
+        <v>1.356480281357137e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.357377931202629e-05</v>
+        <v>1.357377931202623e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.413575094027538e-05</v>
+        <v>1.413575094027546e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.357672640954978e-05</v>
+        <v>1.357672640954987e-05</v>
       </c>
       <c r="W2" t="n">
         <v>1.428587802262297e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.355897771581828e-05</v>
+        <v>1.355897771581825e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.359765350673754e-05</v>
+        <v>1.35976535067375e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.395169812056497e-05</v>
+        <v>1.395169812056495e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.359561443794521e-05</v>
+        <v>1.359561443794518e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.358388768107923e-05</v>
+        <v>1.358388768107922e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.538658337488268e-05</v>
+        <v>1.434093193565109e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.485547274915514e-05</v>
+        <v>1.427292104856659e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.568260602395824e-05</v>
+        <v>1.449417815929192e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.454356085269697e-05</v>
+        <v>1.382858061126368e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.486810393964244e-05</v>
+        <v>1.419698783616729e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.659825279191132e-05</v>
+        <v>1.479729592835966e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.538733461268602e-05</v>
+        <v>1.439376951770516e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.557638631360227e-05</v>
+        <v>1.443786875171759e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.567886985294264e-05</v>
+        <v>1.448359109576823e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.593171631937761e-05</v>
+        <v>1.459981621533493e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55435770162014e-05</v>
+        <v>1.450532174742026e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.594392653484403e-05</v>
+        <v>1.462244936336069e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.502594117856578e-05</v>
+        <v>1.422350243940635e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.646234258246825e-05</v>
+        <v>1.579424478544418e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.482180724803042e-05</v>
+        <v>1.416720119117252e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.522289820682456e-05</v>
+        <v>1.432049414836294e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.540208252181783e-05</v>
+        <v>1.437247193768557e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.499930983741078e-05</v>
+        <v>1.423964515923695e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.522199185568717e-05</v>
+        <v>1.432789531099189e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.563661932525965e-05</v>
+        <v>1.488782080698502e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52763498724458e-05</v>
+        <v>1.43472208459938e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.74640649544436e-05</v>
+        <v>1.549627330782903e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.48769575808571e-05</v>
+        <v>1.422179212646246e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.57618178520839e-05</v>
+        <v>1.445832802109344e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.558535106355468e-05</v>
+        <v>1.469790222438176e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.571389716708472e-05</v>
+        <v>1.444594428216636e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.554775344375891e-05</v>
+        <v>1.444731429621695e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4934,58 +4934,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.810539218254805e-05</v>
+        <v>4.810539218254806e-05</v>
       </c>
       <c r="C4" t="n">
         <v>4.675531412098111e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>5.450637715240984e-05</v>
+        <v>5.450637715240985e-05</v>
       </c>
       <c r="E4" t="n">
         <v>2.822262331212652e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.632856809415341e-05</v>
+        <v>4.632856809415343e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>6.116170503084067e-05</v>
+        <v>6.116170503084248e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.214316835601577e-05</v>
+        <v>5.214316835601584e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.223876392243326e-05</v>
+        <v>5.22387639224333e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>5.354796502430936e-05</v>
+        <v>5.35479650243092e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.80241080191719e-05</v>
+        <v>5.802410801917197e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.726964317716248e-05</v>
+        <v>5.726964317716249e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.969241397908523e-05</v>
+        <v>5.969241397908528e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>4.564824601409573e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.595073635915337e-05</v>
+        <v>4.595073635915339e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.473555305184223e-05</v>
+        <v>4.473555305184224e-05</v>
       </c>
       <c r="Q4" t="n">
         <v>4.941019010649169e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>5.038176501113492e-05</v>
+        <v>5.038176501113427e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.70929234097316e-05</v>
+        <v>4.70929234097317e-05</v>
       </c>
       <c r="T4" t="n">
         <v>4.998677864458755e-05</v>
@@ -4994,25 +4994,25 @@
         <v>5.163059128723783e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.025887660711909e-05</v>
+        <v>5.025887660711915e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>6.185681548669884e-05</v>
+        <v>6.185681548669892e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.786625537573862e-05</v>
+        <v>4.786625537573864e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.0659484554772e-05</v>
+        <v>5.065948455477211e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.945263234914692e-05</v>
+        <v>4.945263234914693e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.052009197047771e-05</v>
+        <v>5.052009197047779e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.352754756524763e-05</v>
+        <v>5.352754756524766e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5022,64 +5022,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.170369396583844e-05</v>
+        <v>5.170369396583851e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>7.669103273803326e-05</v>
+        <v>7.669103273803331e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.71358737498049e-05</v>
+        <v>7.713587374980493e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.342708003754792e-05</v>
+        <v>6.342708003754787e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.538117347597075e-05</v>
+        <v>5.53811734759708e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.284200540791858e-05</v>
+        <v>8.284200540791861e-05</v>
       </c>
       <c r="H5" t="n">
         <v>7.698892212738467e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.7084545742903e-05</v>
+        <v>7.708454574290303e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.713264304053096e-05</v>
+        <v>7.713264304053103e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.725626290237419e-05</v>
+        <v>7.725626290237418e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.707048502934935e-05</v>
+        <v>7.707048502934939e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>7.725817366202043e-05</v>
+        <v>7.72581736620205e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>5.721004410926679e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.25227429686764e-05</v>
+        <v>6.252274296867642e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.118333598082758e-05</v>
+        <v>6.118333598082763e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.664209883773311e-05</v>
+        <v>4.664209883773314e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>7.699943188976271e-05</v>
+        <v>7.699943188976268e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.681165797673348e-05</v>
+        <v>7.681165797673356e-05</v>
       </c>
       <c r="T5" t="n">
         <v>7.691305165617441e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.449271134613547e-05</v>
+        <v>6.449271134613551e-05</v>
       </c>
       <c r="V5" t="n">
         <v>6.998323740609157e-05</v>
@@ -5088,13 +5088,13 @@
         <v>7.77029321331489e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.879122770118334e-05</v>
+        <v>4.879122770118338e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001023414673374165</v>
+        <v>0.0001023414673374166</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.114261483816817e-05</v>
+        <v>5.11426148381682e-05</v>
       </c>
       <c r="AA5" t="n">
         <v>7.715968944808316e-05</v>
@@ -5110,76 +5110,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.359755213408976e-05</v>
+        <v>3.359755213408978e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.928874408651536e-05</v>
+        <v>3.928874408651534e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.973358509828695e-05</v>
+        <v>3.973358509828693e-05</v>
       </c>
       <c r="E6" t="n">
         <v>3.811101299923349e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.549506735607203e-05</v>
+        <v>2.549506735607206e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.019333431245492e-05</v>
+        <v>4.019333431245507e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.958663347586675e-05</v>
+        <v>3.958663347586668e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.968225709138499e-05</v>
+        <v>3.968225709138502e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.973035438901307e-05</v>
+        <v>3.973035438901308e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.985397425085622e-05</v>
+        <v>3.985397425085625e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.96681963778314e-05</v>
+        <v>3.966819637783141e-05</v>
       </c>
       <c r="M6" t="n">
         <v>3.985588501050215e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.564824601409569e-05</v>
+        <v>3.942047094522573e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.133351496896277e-05</v>
+        <v>4.133351496896283e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.174807489273631e-05</v>
+        <v>4.174807489273629e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.951335508261137e-05</v>
+        <v>3.951335508261138e-05</v>
       </c>
       <c r="R6" t="n">
         <v>3.959714323824471e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.940936932521555e-05</v>
+        <v>3.940936932521556e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.951076300465646e-05</v>
+        <v>3.951076300465645e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.943830648429364e-05</v>
+        <v>3.943830648429366e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.64244837445404e-05</v>
+        <v>4.642448374454045e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.029567105312226e-05</v>
+        <v>4.029567105312227e-05</v>
       </c>
       <c r="X6" t="n">
         <v>3.934357216641666e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.978043301659241e-05</v>
+        <v>3.978043301659243e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>3.589102425920418e-05</v>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.341914514629242e-05</v>
+        <v>1.341914514629233e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.34891352076083e-05</v>
+        <v>1.348913520760831e-05</v>
       </c>
       <c r="D2" t="n">
         <v>1.342570539214736e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.340950293939892e-05</v>
+        <v>1.340950293939884e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.340853728870291e-05</v>
+        <v>1.340853728870283e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.342738972883599e-05</v>
+        <v>1.342738972883597e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341166995429868e-05</v>
+        <v>1.341166995429891e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.34127333117612e-05</v>
+        <v>1.341273331176133e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.341925819007396e-05</v>
+        <v>1.341925819007384e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.341990715633546e-05</v>
+        <v>1.341990715633541e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341421273846515e-05</v>
+        <v>1.341421273846531e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.341562562891062e-05</v>
+        <v>1.341562562891052e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.341326317819963e-05</v>
+        <v>1.341326317819969e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.49194796457676e-05</v>
+        <v>1.49194796457677e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.341271220259807e-05</v>
+        <v>1.341271220259793e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.341480144357773e-05</v>
+        <v>1.341480144357792e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.342098081091214e-05</v>
+        <v>1.342098081091217e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.341471028676463e-05</v>
+        <v>1.34147102867645e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.342073367208775e-05</v>
+        <v>1.342073367208792e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.391995006274427e-05</v>
+        <v>1.391995006274435e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.341524767729108e-05</v>
+        <v>1.3415247677291e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.399053299088152e-05</v>
+        <v>1.399053299088153e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341422160842672e-05</v>
+        <v>1.341422160842683e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.341583276567212e-05</v>
+        <v>1.341583276567203e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.375139649640044e-05</v>
+        <v>1.375139649640038e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.341574272442904e-05</v>
+        <v>1.341574272442911e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.342042841642728e-05</v>
+        <v>1.342042841642729e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.455964894507481e-05</v>
+        <v>1.398687823224221e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.434243124642842e-05</v>
+        <v>1.399195059283219e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.472094435012165e-05</v>
+        <v>1.403082043066429e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.371507952965011e-05</v>
+        <v>1.342249438903972e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.432711888604689e-05</v>
+        <v>1.392819292618075e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.475385174512266e-05</v>
+        <v>1.40811052317938e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.440038208765845e-05</v>
+        <v>1.394541692694065e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.442126441461998e-05</v>
+        <v>1.394214666333831e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.455756852887341e-05</v>
+        <v>1.400401018525322e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.459903583399179e-05</v>
+        <v>1.409286433435027e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44508751481666e-05</v>
+        <v>1.396033407462607e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.456869664711528e-05</v>
+        <v>1.408248543433273e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.442787836167958e-05</v>
+        <v>1.392582337292466e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59348605254536e-05</v>
+        <v>1.547279358311891e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.440619101311654e-05</v>
+        <v>1.390344147219971e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.446739759296103e-05</v>
+        <v>1.396013246256883e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46142383527579e-05</v>
+        <v>1.400030860108597e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44637132898719e-05</v>
+        <v>1.398715155300555e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.460641402506252e-05</v>
+        <v>1.399891236510173e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.504357535471039e-05</v>
+        <v>1.447711952670564e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.447840713325507e-05</v>
+        <v>1.400384473059439e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53335455361384e-05</v>
+        <v>1.460056441089737e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.44534122384316e-05</v>
+        <v>1.394553261971685e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.448945342494649e-05</v>
+        <v>1.396768841571145e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.47837905086398e-05</v>
+        <v>1.428180232123032e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.448450063358772e-05</v>
+        <v>1.394827293476216e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.468629857169777e-05</v>
+        <v>1.40496558596163e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.479182992065139e-05</v>
+        <v>4.479182992065146e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.402975327693767e-05</v>
+        <v>4.402975327693771e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>4.555574065905879e-05</v>
+        <v>4.55557406590588e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.854158343259779e-05</v>
+        <v>1.854158343259789e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.441429276033686e-05</v>
+        <v>4.44142927603369e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.861756227821382e-05</v>
+        <v>4.861756227821443e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.451041024403857e-05</v>
+        <v>4.451041024403862e-05</v>
       </c>
       <c r="I4" t="n">
         <v>4.388303933572192e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.599874426066206e-05</v>
+        <v>4.599874426066225e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.222244051282971e-05</v>
+        <v>5.222244051282973e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.467169523047304e-05</v>
+        <v>4.467169523047348e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.216611275383135e-05</v>
+        <v>5.216611275383147e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.250235099084593e-05</v>
+        <v>4.250235099084605e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.546046274628261e-05</v>
+        <v>4.546046274628266e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.108501005883899e-05</v>
+        <v>4.108501005883907e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.443381690768309e-05</v>
+        <v>4.443381690768313e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.507294767332765e-05</v>
+        <v>4.507294767332761e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.644571205255058e-05</v>
+        <v>4.644571205255067e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.506600058876183e-05</v>
+        <v>4.50660005887619e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.427725662713061e-05</v>
+        <v>4.427725662713071e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.741484003462228e-05</v>
+        <v>4.74148400346223e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.51903810777564e-05</v>
+        <v>4.519038107775634e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.358235901066311e-05</v>
+        <v>4.358235901066309e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.460672389335443e-05</v>
+        <v>4.46067238933544e-05</v>
       </c>
       <c r="Z4" t="n">
         <v>4.352426537243841e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.322529943532131e-05</v>
+        <v>4.322529943532141e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.776476555683702e-05</v>
+        <v>4.776476555683694e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5618,82 +5618,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.399875249388767e-05</v>
+        <v>5.399875249388775e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>8.090138620749478e-05</v>
+        <v>8.090138620749493e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.112725917761967e-05</v>
+        <v>8.112725917761983e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.653857204504778e-05</v>
+        <v>6.653857204504782e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.809369207797184e-05</v>
+        <v>5.809369207797186e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.675619179836126e-05</v>
+        <v>8.675619179836129e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>8.096872245049857e-05</v>
+        <v>8.096872245049875e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>8.098073356220539e-05</v>
+        <v>8.098073356220549e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.104293970987563e-05</v>
+        <v>8.104293970987568e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.106176543680242e-05</v>
+        <v>8.106176543680261e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>8.09974443673965e-05</v>
+        <v>8.099744436739658e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>8.104678448171574e-05</v>
+        <v>8.104678448171569e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.250235099084593e-05</v>
+        <v>6.001502813625086e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.577910901144205e-05</v>
+        <v>6.577910901144215e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.435930703444175e-05</v>
+        <v>6.435930703444179e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.863288016771163e-05</v>
+        <v>4.863288016771168e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>8.10738928591514e-05</v>
+        <v>8.107389285915128e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.100306440432151e-05</v>
+        <v>8.100306440432147e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>8.107110131244125e-05</v>
+        <v>8.10711013124413e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>6.783846161141802e-05</v>
+        <v>6.783846161141815e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>7.356674692150843e-05</v>
+        <v>7.356674692150846e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>8.116050475364305e-05</v>
+        <v>8.116050475364309e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.110592070524582e-05</v>
+        <v>5.110592070524583e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000107915560051936</v>
+        <v>0.0001079155600519361</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.344072528159296e-05</v>
+        <v>5.344072528159311e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.101472626268724e-05</v>
+        <v>8.101472626268727e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>0.0001093706576324333</v>
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.703568653410513e-05</v>
+        <v>3.703568653410516e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.396821864645658e-05</v>
+        <v>4.396821864645661e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.419409161658148e-05</v>
+        <v>4.419409161658151e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.237604914214048e-05</v>
+        <v>4.237604914214049e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.766891528995816e-05</v>
+        <v>2.766891528995822e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.421311719523849e-05</v>
+        <v>4.421311719523854e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.403555488946044e-05</v>
+        <v>4.403555488946056e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.404756600116715e-05</v>
+        <v>4.404756600116721e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.41097721488375e-05</v>
+        <v>4.410977214883759e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.412859787576427e-05</v>
+        <v>4.412859787576434e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.406427680635838e-05</v>
+        <v>4.406427680635844e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.411361692067848e-05</v>
+        <v>4.411361692067854e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.250235099084593e-05</v>
+        <v>4.405355108634127e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.640215870506789e-05</v>
+        <v>4.64021587050679e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.690564777076194e-05</v>
+        <v>4.690564777076196e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.407092672234956e-05</v>
+        <v>4.407092672234962e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.414072529811318e-05</v>
+        <v>4.414072529811321e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.406989684328342e-05</v>
+        <v>4.406989684328348e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.4137933751403e-05</v>
+        <v>4.413793375140304e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.411004986197501e-05</v>
+        <v>4.411004986197505e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.220293880259596e-05</v>
+        <v>5.220293880259594e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.422202022179269e-05</v>
+        <v>4.422202022179271e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.406437699665537e-05</v>
+        <v>4.406437699665543e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.408257575891012e-05</v>
+        <v>4.408257575891019e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.979330756905497e-05</v>
+        <v>3.979330756905499e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.408155870164909e-05</v>
+        <v>4.408155870164916e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.417690107219348e-05</v>
+        <v>4.417690107219356e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.348097236986991e-05</v>
+        <v>1.348097236986993e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.354909004044858e-05</v>
@@ -5959,22 +5959,22 @@
         <v>1.349890551495111e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.346843468040353e-05</v>
+        <v>1.346843468040354e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.346551636847444e-05</v>
+        <v>1.346551636847443e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.347270636889533e-05</v>
+        <v>1.347270636889534e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.346795042837875e-05</v>
+        <v>1.346795042837876e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.349408738021807e-05</v>
+        <v>1.349408738021809e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.347559588027313e-05</v>
+        <v>1.347559588027314e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.34811008439659e-05</v>
@@ -5983,52 +5983,52 @@
         <v>1.34787818438665e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.348682608194421e-05</v>
+        <v>1.348682608194423e-05</v>
       </c>
       <c r="N2" t="n">
         <v>1.346987708652456e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.50211105546282e-05</v>
+        <v>1.502111055462821e-05</v>
       </c>
       <c r="P2" t="n">
         <v>1.34632615503089e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.347271954527405e-05</v>
+        <v>1.347271954527406e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.348230794945448e-05</v>
+        <v>1.348230794945449e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.347498359583548e-05</v>
+        <v>1.347498359583547e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.348185763750536e-05</v>
+        <v>1.348185763750537e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.400717223442482e-05</v>
+        <v>1.40071722344248e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.347551299690287e-05</v>
+        <v>1.347551299690288e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.408445725642754e-05</v>
+        <v>1.408445725642756e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.346744243231688e-05</v>
+        <v>1.346744243231689e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.346445057771589e-05</v>
+        <v>1.34644505777159e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.383550602549057e-05</v>
+        <v>1.383550602549058e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.348421201164424e-05</v>
+        <v>1.348421201164425e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.347573051014889e-05</v>
+        <v>1.34757305101489e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.496978170498591e-05</v>
+        <v>1.414384231823897e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.461718671312963e-05</v>
+        <v>1.415150080017981e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.540771314957397e-05</v>
+        <v>1.4332145959971e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.405458288786013e-05</v>
+        <v>1.356247875283151e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.463322433487899e-05</v>
+        <v>1.407493434903375e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.479044427917826e-05</v>
+        <v>1.41601475605972e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.468780274104321e-05</v>
+        <v>1.406615133090384e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.529462896769865e-05</v>
+        <v>1.427221856689815e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.484983737142325e-05</v>
+        <v>1.4155950790253e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.500304502976402e-05</v>
+        <v>1.428051143867349e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.493544885830382e-05</v>
+        <v>1.420920393516428e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.520635382048315e-05</v>
+        <v>1.434440537895204e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.472171096382539e-05</v>
+        <v>1.405448188606593e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.613582262315972e-05</v>
+        <v>1.561012865501255e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.456096822633456e-05</v>
+        <v>1.400684715083649e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.479705147552515e-05</v>
+        <v>1.413845080396068e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.502117465469475e-05</v>
+        <v>1.41764143597588e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.484052710307854e-05</v>
+        <v>1.414486062977511e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.500852771008401e-05</v>
+        <v>1.417970816481923e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.535725029514979e-05</v>
+        <v>1.468638785726456e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.485599386750027e-05</v>
+        <v>1.417152067220002e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.568874184938524e-05</v>
+        <v>1.477439581113574e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.467193709545507e-05</v>
+        <v>1.40711804222177e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.459692566505547e-05</v>
+        <v>1.402968551288677e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.520334092046958e-05</v>
+        <v>1.449648677415636e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.505263624816969e-05</v>
+        <v>1.416909214920366e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.49547398567453e-05</v>
+        <v>1.418432328769121e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6126,85 +6126,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.483132235302125e-05</v>
+        <v>4.483132235302132e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.618707400723496e-05</v>
+        <v>4.6187074007235e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>5.144073570874721e-05</v>
+        <v>5.144073570874719e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.067548253709663e-05</v>
+        <v>2.067548253709666e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>4.543422040174876e-05</v>
+        <v>4.54342204017487e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.877430340695449e-05</v>
+        <v>4.877430340695455e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.399916115599767e-05</v>
+        <v>4.39991611559977e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.902192985072049e-05</v>
+        <v>4.902192985072048e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.749199023948435e-05</v>
+        <v>4.749199023948431e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.405151594341161e-05</v>
+        <v>5.405151594341159e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.001455695402562e-05</v>
+        <v>5.001455695402558e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>5.561662218787503e-05</v>
+        <v>5.561662218787504e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.255614880189197e-05</v>
+        <v>4.255614880189202e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.455175984347278e-05</v>
+        <v>4.455175984347349e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.160396545276916e-05</v>
+        <v>4.160396545276918e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.728191055278934e-05</v>
+        <v>4.728191055278933e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.655835454761315e-05</v>
+        <v>4.655835454761324e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.695155691132696e-05</v>
+        <v>4.695155691132693e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.694146472933653e-05</v>
+        <v>4.694146472933646e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.782196149026789e-05</v>
+        <v>4.782196149026784e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.853241389451266e-05</v>
+        <v>4.853241389451262e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.530122456994016e-05</v>
+        <v>4.530122456994018e-05</v>
       </c>
       <c r="X4" t="n">
         <v>4.452328032107381e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.273690309312101e-05</v>
+        <v>4.273690309312098e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.628494572841454e-05</v>
+        <v>4.628494572841458e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.542226023435577e-05</v>
+        <v>4.542226023435575e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.82971906824716e-05</v>
+        <v>4.829719068247168e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.13964301723193e-05</v>
+        <v>5.139643017231936e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>7.642057401242913e-05</v>
+        <v>7.642057401242924e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.684785416046549e-05</v>
+        <v>7.684785416046562e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.305939845037799e-05</v>
+        <v>6.305939845037806e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.515532496004812e-05</v>
+        <v>5.515532496004823e-05</v>
       </c>
       <c r="G5" t="n">
         <v>8.178743853523168e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>7.649820221758739e-05</v>
+        <v>7.649820221758752e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.679343111220443e-05</v>
+        <v>7.679343111220459e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.657311742092823e-05</v>
+        <v>7.657311742092842e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.664674221113424e-05</v>
+        <v>7.664674221113429e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.662054803821876e-05</v>
+        <v>7.662054803821886e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>7.674421018100111e-05</v>
+        <v>7.674421018100121e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.255614880189197e-05</v>
+        <v>5.694787349618579e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>6.225737486752387e-05</v>
+        <v>6.225737486752398e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.093330850799728e-05</v>
+        <v>6.093330850799729e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.634123328379142e-05</v>
+        <v>4.634123328379146e-05</v>
       </c>
       <c r="R5" t="n">
         <v>7.666037702292383e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>7.657764507942794e-05</v>
+        <v>7.657764507942806e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>7.665529054230471e-05</v>
+        <v>7.665529054230489e-05</v>
       </c>
       <c r="U5" t="n">
         <v>6.424487664210871e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>6.963565802582573e-05</v>
+        <v>6.963565802582584e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>7.670595437188365e-05</v>
+        <v>7.670595437188366e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>4.859573413660402e-05</v>
+        <v>4.859573413660408e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001015641610297815</v>
+        <v>0.0001015641610297817</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.086242771463282e-05</v>
+        <v>5.086242771463284e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.668188428126904e-05</v>
+        <v>7.668188428126912e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001030042082003948</v>
+        <v>0.000103004208200395</v>
       </c>
     </row>
     <row r="6">
@@ -6302,85 +6302,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.424743437744759e-05</v>
+        <v>3.42474343774476e-05</v>
       </c>
       <c r="C6" t="n">
         <v>4.026973179963394e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.069701194767038e-05</v>
+        <v>4.069701194767036e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.891104456583942e-05</v>
+        <v>3.891104456583946e-05</v>
       </c>
       <c r="F6" t="n">
         <v>2.591879262659136e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.040108075513473e-05</v>
+        <v>4.040108075513472e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.034736000479225e-05</v>
+        <v>4.034736000479223e-05</v>
       </c>
       <c r="I6" t="n">
         <v>4.064258889940933e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.04222752081332e-05</v>
+        <v>4.042227520813319e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.049589999833904e-05</v>
+        <v>4.049589999833905e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.046970582542362e-05</v>
+        <v>4.046970582542361e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.059336796820658e-05</v>
+        <v>4.059336796820659e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.255614880189197e-05</v>
+        <v>4.03691224948557e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.237029595064366e-05</v>
+        <v>4.237029595064364e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.281489405796177e-05</v>
+        <v>4.28148940579618e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.040122958839373e-05</v>
+        <v>4.040122958839374e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.050953481012859e-05</v>
+        <v>4.05095348101286e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.042680286663279e-05</v>
+        <v>4.042680286663278e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>4.050444832950963e-05</v>
+        <v>4.050444832950966e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.041700963138819e-05</v>
+        <v>4.041700963138815e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.759390654191536e-05</v>
+        <v>4.759390654191535e-05</v>
       </c>
       <c r="W6" t="n">
         <v>4.055015002997265e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.034162195558383e-05</v>
+        <v>4.034162195558386e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.030782758154436e-05</v>
+        <v>4.030782758154437e-05</v>
       </c>
       <c r="Z6" t="n">
         <v>3.666306280020527e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.053104206847389e-05</v>
+        <v>4.053104206847391e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.047881953476277e-05</v>
+        <v>4.047881953476281e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.390091885897633e-05</v>
+        <v>1.353017975743376e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.391612987116116e-05</v>
+        <v>1.356390555943537e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.38439845987678e-05</v>
+        <v>1.349270505859719e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.33905405094404e-05</v>
+        <v>1.3313019738185e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.385219050422973e-05</v>
+        <v>1.34902655126195e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.396756906664278e-05</v>
+        <v>1.358798981622711e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.389013751227977e-05</v>
+        <v>1.351236569881061e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.386427888199631e-05</v>
+        <v>1.350489461270567e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.392225747661488e-05</v>
+        <v>1.355306975676148e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.389844348801766e-05</v>
+        <v>1.353127624218105e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.385892100966567e-05</v>
+        <v>1.351127447117484e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.39629454464118e-05</v>
+        <v>1.356194148129209e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.387195464563292e-05</v>
+        <v>1.351392459168762e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.542901682860565e-05</v>
+        <v>1.503442340129481e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.387682819284814e-05</v>
+        <v>1.352874474763432e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.386187395689053e-05</v>
+        <v>1.350486351596222e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.384279493986505e-05</v>
+        <v>1.348823553133051e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.390294550002798e-05</v>
+        <v>1.353621549924004e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.385865326475343e-05</v>
+        <v>1.350218937150084e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.444162835675608e-05</v>
+        <v>1.406007468308335e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.394764411178394e-05</v>
+        <v>1.355511424813518e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.454250855287734e-05</v>
+        <v>1.415249146881344e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.389639814021552e-05</v>
+        <v>1.352633599843255e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.394756211709748e-05</v>
+        <v>1.356263892911782e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.423506602099968e-05</v>
+        <v>1.387445309702661e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.388754605770894e-05</v>
+        <v>1.352896085765401e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.400485671704887e-05</v>
+        <v>1.358380721989443e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.423253352929221e-05</v>
+        <v>1.378861058532482e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.421667292480891e-05</v>
+        <v>1.376642201598764e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.445150598510614e-05</v>
+        <v>1.390905018540658e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.368424358686219e-05</v>
+        <v>1.350373855392389e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.41438314263661e-05</v>
+        <v>1.370315593025855e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.45193480378886e-05</v>
+        <v>1.396691197765855e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.430562002587651e-05</v>
+        <v>1.381377466340452e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.438358919788322e-05</v>
+        <v>1.387466885815565e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.434998431010145e-05</v>
+        <v>1.385179147283419e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.430239165936535e-05</v>
+        <v>1.376744036196787e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.425781471759594e-05</v>
+        <v>1.376858169395092e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.452317492249207e-05</v>
+        <v>1.394796425106017e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.413570966786561e-05</v>
+        <v>1.372894471206395e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.572502448077694e-05</v>
+        <v>1.529245482239935e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.409245261713698e-05</v>
+        <v>1.36823584551522e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.422296080795332e-05</v>
+        <v>1.376423625469411e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.428610018440014e-05</v>
+        <v>1.381419082888816e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.420083534612225e-05</v>
+        <v>1.375291507594772e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.423380902111127e-05</v>
+        <v>1.378322119161177e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.480337737452602e-05</v>
+        <v>1.431181720307733e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.431245764501129e-05</v>
+        <v>1.381939430659246e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.517945704919309e-05</v>
+        <v>1.464549729869856e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.415156177948213e-05</v>
+        <v>1.370934474337206e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.436503799361856e-05</v>
+        <v>1.389086193749801e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.460604496780161e-05</v>
+        <v>1.413877005372619e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.429286069748119e-05</v>
+        <v>1.384170755213584e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.447424003801532e-05</v>
+        <v>1.392873904635153e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.394984900789742e-05</v>
+        <v>1.356521252609911e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.398302115022359e-05</v>
+        <v>1.359685524929155e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.39965177095731e-05</v>
+        <v>1.360067261739024e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.341760052148484e-05</v>
+        <v>1.333255471693105e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.390446672959678e-05</v>
+        <v>1.352114998922864e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.402239226199437e-05</v>
+        <v>1.362384304765755e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.392690337860709e-05</v>
+        <v>1.353786272883688e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.389746063874995e-05</v>
+        <v>1.35308005724853e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.397428051016615e-05</v>
+        <v>1.358638943361703e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.402738269915093e-05</v>
+        <v>1.358162337558868e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.390955989860132e-05</v>
+        <v>1.35497215083536e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.399447518382723e-05</v>
+        <v>1.358355649078335e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.394122566174021e-05</v>
+        <v>1.356500230686764e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.545030785518304e-05</v>
+        <v>1.505321108128033e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.389252400949156e-05</v>
+        <v>1.354134933562527e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.393728131637214e-05</v>
+        <v>1.355824325483029e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.396007180806433e-05</v>
+        <v>1.357140733708108e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.395400244394188e-05</v>
+        <v>1.357142039136451e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.395738955442021e-05</v>
+        <v>1.35696184471429e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44820685895682e-05</v>
+        <v>1.409179294311261e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.399807823196745e-05</v>
+        <v>1.357156657662974e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.459718957891042e-05</v>
+        <v>1.419582588753858e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.396727371927944e-05</v>
+        <v>1.357636104599055e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.399277690004622e-05</v>
+        <v>1.35906596391964e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.42875012483212e-05</v>
+        <v>1.39124687033103e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.39547545307693e-05</v>
+        <v>1.357353849334061e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.405116761099823e-05</v>
+        <v>1.361880766931747e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.401407505100048e-05</v>
+        <v>1.362740138966356e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.410443331865985e-05</v>
+        <v>1.367238276867028e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.411245524895252e-05</v>
+        <v>1.368355972594918e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.350750397189584e-05</v>
+        <v>1.340448562986963e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.397251587780151e-05</v>
+        <v>1.357184180399314e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.409217073570359e-05</v>
+        <v>1.367203490187762e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.399158898615098e-05</v>
+        <v>1.359525336234613e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.407550473628725e-05</v>
+        <v>1.365917937870424e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.405357044332328e-05</v>
+        <v>1.364304757864179e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.420995256550978e-05</v>
+        <v>1.369368276089143e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.398750971201708e-05</v>
+        <v>1.360968544369502e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.407670241148159e-05</v>
+        <v>1.365007343396144e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.399391902576011e-05</v>
+        <v>1.361090540162553e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.55261136385604e-05</v>
+        <v>1.51220261231475e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.393672480810061e-05</v>
+        <v>1.357432365652734e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.400279106154046e-05</v>
+        <v>1.360532318391424e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.400587075170503e-05</v>
+        <v>1.36116872570845e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4033012781976e-05</v>
+        <v>1.363249796477938e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.40358821218871e-05</v>
+        <v>1.363394003205227e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45472535100415e-05</v>
+        <v>1.41469109976047e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.407222749544127e-05</v>
+        <v>1.362564845383644e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.473186439881793e-05</v>
+        <v>1.43077547454856e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.402127552877266e-05</v>
+        <v>1.362062821984768e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.399584194818067e-05</v>
+        <v>1.360334187467539e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.442574198076869e-05</v>
+        <v>1.399938614779844e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.40391659426698e-05</v>
+        <v>1.364278606506153e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.41121628180406e-05</v>
+        <v>1.367051472444099e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.406293069920839e-05</v>
+        <v>1.365278696155579e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.413180513110556e-05</v>
+        <v>1.36931070243011e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426804708567515e-05</v>
+        <v>1.377325333169605e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.359287033719221e-05</v>
+        <v>1.343574813987292e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.400808296229881e-05</v>
+        <v>1.359883335417331e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.417313504921317e-05</v>
+        <v>1.371513685057564e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.404802381300649e-05</v>
+        <v>1.364077538645813e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.415622485827505e-05</v>
+        <v>1.370928337856081e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.411763730759864e-05</v>
+        <v>1.3679151213116e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.420736261636503e-05</v>
+        <v>1.369834158583921e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.403909515655077e-05</v>
+        <v>1.362766060429281e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.416072129374017e-05</v>
+        <v>1.368908555404334e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.400359513046235e-05</v>
+        <v>1.36235651948446e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.560005452844451e-05</v>
+        <v>1.518700596163051e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.40043028537045e-05</v>
+        <v>1.360922296178465e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.402657255008299e-05</v>
+        <v>1.361870529537474e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.403257036717122e-05</v>
+        <v>1.363507008220628e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.405131213336194e-05</v>
+        <v>1.364517047327103e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.408989598688809e-05</v>
+        <v>1.367690706348487e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.462445711631888e-05</v>
+        <v>1.419041185917311e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41309119326689e-05</v>
+        <v>1.366806429767295e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.484141080854996e-05</v>
+        <v>1.439484398197745e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.405936131764457e-05</v>
+        <v>1.36400945487241e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.402591078524693e-05</v>
+        <v>1.364115190220881e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.449908866445316e-05</v>
+        <v>1.403965384252653e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.411415985832022e-05</v>
+        <v>1.370334630283758e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.417373158144016e-05</v>
+        <v>1.371329746159358e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.408311091292377e-05</v>
+        <v>1.366102013017121e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.402287063247216e-05</v>
+        <v>1.362793817427925e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.424370080519551e-05</v>
+        <v>1.376766127590915e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.344140924276291e-05</v>
+        <v>1.335361113381909e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3971935514955e-05</v>
+        <v>1.356607017198236e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.421226259377883e-05</v>
+        <v>1.370761685842438e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.410540353019182e-05</v>
+        <v>1.366308431293196e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.396423871570593e-05</v>
+        <v>1.357481565585972e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.40961948097065e-05</v>
+        <v>1.364669305869321e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.412646281927481e-05</v>
+        <v>1.363764202784854e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.415316196339136e-05</v>
+        <v>1.365542043805268e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.41413782020113e-05</v>
+        <v>1.363126292075692e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.40020838243195e-05</v>
+        <v>1.360316108595779e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.551260974192977e-05</v>
+        <v>1.509932754883971e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.393648022847941e-05</v>
+        <v>1.357249296614292e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.404669811294982e-05</v>
+        <v>1.362406041857186e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.404121887266894e-05</v>
+        <v>1.363303772857341e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.409971989468229e-05</v>
+        <v>1.362849307966282e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.406353500406741e-05</v>
+        <v>1.361656859753384e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.453367636926499e-05</v>
+        <v>1.412090163121432e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.406054748033897e-05</v>
+        <v>1.361905306967974e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.468266092294777e-05</v>
+        <v>1.426520092765718e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.401750640094419e-05</v>
+        <v>1.361286034816434e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.402481455023835e-05</v>
+        <v>1.361749326897963e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.44106914517991e-05</v>
+        <v>1.398348308148858e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.399615290982203e-05</v>
+        <v>1.360762016584218e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.410530787033752e-05</v>
+        <v>1.364918629091932e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.420920726102873e-05</v>
+        <v>1.377366914192061e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.418725303889965e-05</v>
+        <v>1.374023988552202e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.446869704677113e-05</v>
+        <v>1.390668095341317e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.363028684059638e-05</v>
+        <v>1.349628641681436e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.413041169400418e-05</v>
+        <v>1.368362538182385e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.442272736525215e-05</v>
+        <v>1.386012378112237e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.426441866804399e-05</v>
+        <v>1.378005634339944e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.433738022207547e-05</v>
+        <v>1.3831470083561e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.430490107586925e-05</v>
+        <v>1.379494427436075e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.450918137243438e-05</v>
+        <v>1.391256701495697e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.452056026698997e-05</v>
+        <v>1.388911217308805e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.452307650908852e-05</v>
+        <v>1.388434815717127e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.41357871653776e-05</v>
+        <v>1.370658418833103e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.564968885637348e-05</v>
+        <v>1.522518628383539e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.405380165851042e-05</v>
+        <v>1.366224408562419e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.424954413853637e-05</v>
+        <v>1.375749646941117e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.426787708680764e-05</v>
+        <v>1.378618634012894e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.422738096519237e-05</v>
+        <v>1.374177247798714e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.424551572109288e-05</v>
+        <v>1.37452259377058e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.482011693370663e-05</v>
+        <v>1.428612112558767e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.424203161382945e-05</v>
+        <v>1.37509149141994e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.494277921843539e-05</v>
+        <v>1.444079949766803e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.412791064393073e-05</v>
+        <v>1.368288533631851e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.42297394738793e-05</v>
+        <v>1.378374612758601e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.459638351756458e-05</v>
+        <v>1.413434083411935e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.427990759243087e-05</v>
+        <v>1.382121936986295e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.43421212854452e-05</v>
+        <v>1.381680765076057e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.434093193565109e-05</v>
+        <v>1.387758067268919e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.427292104856659e-05</v>
+        <v>1.382282423835214e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.449417815929192e-05</v>
+        <v>1.395061989952904e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.382858061126368e-05</v>
+        <v>1.36182182712855e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.419698783616729e-05</v>
+        <v>1.375298659561865e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.479729592835966e-05</v>
+        <v>1.417448360424311e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.439376951770516e-05</v>
+        <v>1.387856169781318e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.443786875171759e-05</v>
+        <v>1.392266129063068e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.448359109576823e-05</v>
+        <v>1.39522515503758e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.459981621533493e-05</v>
+        <v>1.401279904064096e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.450532174742026e-05</v>
+        <v>1.392557923647421e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.462244936336069e-05</v>
+        <v>1.401411560254076e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.422350243940635e-05</v>
+        <v>1.378925233804723e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.579424478544418e-05</v>
+        <v>1.535513964622036e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.416720119117252e-05</v>
+        <v>1.374340726022368e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.432049414836294e-05</v>
+        <v>1.383930929901403e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.437247193768557e-05</v>
+        <v>1.38799304927043e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.423964515923695e-05</v>
+        <v>1.378677268140769e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.432789531099189e-05</v>
+        <v>1.383930156653874e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.488782080698502e-05</v>
+        <v>1.437727248691691e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43472208459938e-05</v>
+        <v>1.385494097068242e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.549627330782903e-05</v>
+        <v>1.486587820520504e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.422179212646246e-05</v>
+        <v>1.375818547929757e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.445832802109344e-05</v>
+        <v>1.396457862722683e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.469790222438176e-05</v>
+        <v>1.421615172619374e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.444594428216636e-05</v>
+        <v>1.395368337418004e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.444731429621695e-05</v>
+        <v>1.391546384193986e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.398687823224221e-05</v>
+        <v>1.358909048013258e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.399195059283219e-05</v>
+        <v>1.360143746771111e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.403082043066429e-05</v>
+        <v>1.362481037773056e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.342249438903972e-05</v>
+        <v>1.333630256397689e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.392819292618075e-05</v>
+        <v>1.35334770686744e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.40811052317938e-05</v>
+        <v>1.363882606779043e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.394541692694065e-05</v>
+        <v>1.354997715739066e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.394214666333831e-05</v>
+        <v>1.355432811305766e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.400401018525322e-05</v>
+        <v>1.359171461816456e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.409286433435027e-05</v>
+        <v>1.360660879133206e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.396033407462607e-05</v>
+        <v>1.356331419774048e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.408248543433273e-05</v>
+        <v>1.359672273135223e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.392582337292466e-05</v>
+        <v>1.355453350492518e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.547279358311891e-05</v>
+        <v>1.506625448312283e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.390344147219971e-05</v>
+        <v>1.354897165051521e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.396013246256883e-05</v>
+        <v>1.356602727765684e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.400030860108597e-05</v>
+        <v>1.359941717002271e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.398715155300555e-05</v>
+        <v>1.356905297945254e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.399891236510173e-05</v>
+        <v>1.359807046665639e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.447711952670564e-05</v>
+        <v>1.408534682517517e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.400384473059439e-05</v>
+        <v>1.357369273901378e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.460056441089737e-05</v>
+        <v>1.41992422212622e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.394553261971685e-05</v>
+        <v>1.35614984595103e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.396768841571145e-05</v>
+        <v>1.357166109275516e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.428180232123032e-05</v>
+        <v>1.389846223745717e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.394827293476216e-05</v>
+        <v>1.356869960511941e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.40496558596163e-05</v>
+        <v>1.361711006514751e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.414384231823897e-05</v>
+        <v>1.371949763513364e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.415150080017981e-05</v>
+        <v>1.370693870603786e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4332145959971e-05</v>
+        <v>1.382584462291416e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.356247875283151e-05</v>
+        <v>1.344532482905216e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.407493434903375e-05</v>
+        <v>1.364064410548446e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.41601475605972e-05</v>
+        <v>1.368416975452481e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.406615133090384e-05</v>
+        <v>1.365057011779349e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.427221856689815e-05</v>
+        <v>1.379616249806524e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4155950790253e-05</v>
+        <v>1.369664750233975e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.428051143867349e-05</v>
+        <v>1.373824027770725e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.420920393516428e-05</v>
+        <v>1.371823861907061e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.434440537895204e-05</v>
+        <v>1.378336013745724e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.405448188606593e-05</v>
+        <v>1.36576381243812e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.561012865501255e-05</v>
+        <v>1.518687330251706e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.400684715083649e-05</v>
+        <v>1.362122786056165e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.413845080396068e-05</v>
+        <v>1.368156564375133e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41764143597588e-05</v>
+        <v>1.373017040042127e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.414486062977511e-05</v>
+        <v>1.369252850200773e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.417970816481923e-05</v>
+        <v>1.372849838009689e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.468638785726456e-05</v>
+        <v>1.422279620803972e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.417152067220002e-05</v>
+        <v>1.369843124042896e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.477439581113574e-05</v>
+        <v>1.43447526540977e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.40711804222177e-05</v>
+        <v>1.364882125694992e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.402968551288677e-05</v>
+        <v>1.362974544924769e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.449648677415636e-05</v>
+        <v>1.4052715910881e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.416909214920366e-05</v>
+        <v>1.373765626996423e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.418432328769121e-05</v>
+        <v>1.37154431643547e-05</v>
       </c>
     </row>
     <row r="4">
